--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="گزارش مانیتورینگ رویال‌دیجی" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="گزارش مانیتورینگ رویال‌دیجی" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,29 +784,29 @@
         <v>18</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4900000</v>
+        <v>4990000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4500000</v>
+        <v>5000000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5790000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5145000</v>
+        <v>5395000</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>رویال -4.8% ارزان‌تر</t>
+          <t>رویال -7.5% ارزان‌تر</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="L5" s="6" t="n">
-        <v>88200000</v>
+        <v>89820000</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -845,29 +845,29 @@
         <v>17</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6470000</v>
+        <v>6420000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6400000</v>
+        <v>6550000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>7460210</v>
+        <v>8946080</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>6930105</v>
+        <v>7748040</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>رویال -6.6% ارزان‌تر</t>
+          <t>رویال -17.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>109990000</v>
+        <v>109140000</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -909,22 +909,22 @@
         <v>3970000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3900000</v>
+        <v>3800000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4250000</v>
+        <v>4500000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4075000</v>
+        <v>4150000</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>رویال -2.6% ارزان‌تر</t>
+          <t>رویال -4.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
@@ -967,7 +967,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3970000</v>
+        <v>1630000</v>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="6" t="n">
-        <v>51610000</v>
+        <v>21190000</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -1017,18 +1017,28 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>فقط در رویال‌دیجی</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>97000</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>146000</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>رویال -31.5% ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>-31.5%</t>
+        </is>
+      </c>
       <c r="L9" s="6" t="n">
         <v>1100000</v>
       </c>
@@ -1068,22 +1078,22 @@
         <v>9200000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8900000</v>
+        <v>7100000</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>8800000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>8850000</v>
+        <v>7950000</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.0% گران‌تر</t>
+          <t>رویال +15.7% گران‌تر</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
@@ -1126,29 +1136,29 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>8500000</v>
+        <v>5930000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5900000</v>
+        <v>6600000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>8220000</v>
+        <v>8610000</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7060000</v>
+        <v>7605000</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>رویال +20.4% گران‌تر</t>
+          <t>رویال -22.0% ارزان‌تر</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>93500000</v>
+        <v>65230000</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1187,27 +1197,29 @@
         <v>10</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4310000</v>
+        <v>7310000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7265700</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+        <v>4300000</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4925670</v>
+      </c>
       <c r="I12" s="6" t="n">
-        <v>7265700</v>
+        <v>4612835</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>رویال -40.7% ارزان‌تر</t>
+          <t>رویال +58.5% گران‌تر</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>+58.5%</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>43100000</v>
+        <v>73100000</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1249,22 +1261,22 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>9100000</v>
+        <v>11800000</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>9300000</v>
+        <v>10650000</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>رویال +9.7% گران‌تر</t>
+          <t>رویال -4.2% ارزان‌تر</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
@@ -1299,29 +1311,29 @@
         <v>8</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>15200000</v>
+        <v>12880000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11480000</v>
+        <v>11180000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>19000000</v>
+        <v>20550000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>15240000</v>
+        <v>15865000</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>رویال -0.3% ارزان‌تر</t>
+          <t>رویال -18.8% ارزان‌تر</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>121600000</v>
+        <v>103040000</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1363,22 +1375,22 @@
         <v>6297000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6200000</v>
+        <v>5800000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7860000</v>
+        <v>7780000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7030000</v>
+        <v>6790000</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.4% ارزان‌تر</t>
+          <t>رویال -7.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="L15" s="6" t="n">
@@ -1421,29 +1433,29 @@
         <v>7</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3800000</v>
+        <v>4240000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4195000</v>
+        <v>4205000</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>4900000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4547500</v>
+        <v>4552500</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>رویال -16.4% ارزان‌تر</t>
+          <t>رویال -6.9% ارزان‌تر</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="L16" s="6" t="n">
-        <v>26600000</v>
+        <v>29680000</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1481,18 +1493,26 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>8000000</v>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="6" t="n">
+        <v>8500000</v>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>فقط در رویال‌دیجی</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="I17" s="6" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>رویال -5.9% ارزان‌تر</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>-5.9%</t>
+        </is>
+      </c>
       <c r="L17" s="6" t="n">
         <v>48000000</v>
       </c>
@@ -1592,29 +1612,29 @@
         <v>6</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7700000</v>
+        <v>9200000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>8900000</v>
+        <v>7100000</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>8800000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>8850000</v>
+        <v>7950000</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>رویال -13.0% ارزان‌تر</t>
+          <t>رویال +15.7% گران‌تر</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="L19" s="6" t="n">
-        <v>46200000</v>
+        <v>55200000</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1653,29 +1673,29 @@
         <v>6</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3000000</v>
+        <v>3580000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2980000</v>
+        <v>4200000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>5130000</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>4055000</v>
+        <v>4665000</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>رویال -26.0% ارزان‌تر</t>
+          <t>رویال -23.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="L20" s="6" t="n">
-        <v>18000000</v>
+        <v>21480000</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1717,22 +1737,22 @@
         <v>5930000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5900000</v>
+        <v>6600000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>8220000</v>
+        <v>8610000</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>7060000</v>
+        <v>7605000</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>رویال -16.0% ارزان‌تر</t>
+          <t>رویال -22.0% ارزان‌تر</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="L21" s="6" t="n">
@@ -1778,22 +1798,22 @@
         <v>15380000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>15300000</v>
+        <v>14900000</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>16890000</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>16095000</v>
+        <v>15895000</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>رویال -4.4% ارزان‌تر</t>
+          <t>رویال -3.2% ارزان‌تر</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="L22" s="6" t="n">
@@ -1836,29 +1856,29 @@
         <v>5</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>7200000</v>
+        <v>12220000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7800000</v>
+        <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>6902400</v>
+        <v>7190000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>7351200</v>
+        <v>7345000</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>رویال -2.1% ارزان‌تر</t>
+          <t>رویال +66.4% گران‌تر</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+66.4%</t>
         </is>
       </c>
       <c r="L23" s="6" t="n">
-        <v>36000000</v>
+        <v>61100000</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1903,19 +1923,19 @@
         <v>5616000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>7069000</v>
+        <v>7599000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6342500</v>
+        <v>6607500</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.6% ارزان‌تر</t>
+          <t>رویال -14.2% ارزان‌تر</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="L24" s="6" t="n">
@@ -1961,22 +1981,22 @@
         <v>6990000</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>6500000</v>
+        <v>5590000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>12590000</v>
+        <v>13070000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>9545000</v>
+        <v>9330000</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>رویال -26.8% ارزان‌تر</t>
+          <t>رویال -25.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="L25" s="6" t="n">
@@ -2076,29 +2096,29 @@
         <v>5</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>15480000</v>
+        <v>9850000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>8300000</v>
+        <v>12550000</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>19500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>13900000</v>
+        <v>16025000</v>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>رویال +11.4% گران‌تر</t>
+          <t>رویال -38.5% ارزان‌تر</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>+11.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="L27" s="6" t="n">
-        <v>77400000</v>
+        <v>49250000</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
@@ -2192,29 +2212,29 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>4990000</v>
+        <v>4870000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>4800000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5790000</v>
+        <v>6150000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5370000</v>
+        <v>5475000</v>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>رویال -7.1% ارزان‌تر</t>
+          <t>رویال -11.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="L29" s="6" t="n">
-        <v>19960000</v>
+        <v>19480000</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2297,22 +2317,22 @@
         <v>28000000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22950000</v>
+        <v>11800000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>29900000</v>
+        <v>29990000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>26425000</v>
+        <v>20895000</v>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>رویال +6.0% گران‌تر</t>
+          <t>رویال +34.0% گران‌تر</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>+6.0%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="L31" s="6" t="n">
@@ -2355,29 +2375,29 @@
         <v>4</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>11500000</v>
+        <v>10970000</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10799000</v>
+        <v>10950000</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>19500000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>15149500</v>
+        <v>15225000</v>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>رویال -24.1% ارزان‌تر</t>
+          <t>رویال -27.9% ارزان‌تر</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="L32" s="6" t="n">
-        <v>46000000</v>
+        <v>43880000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2419,20 +2439,20 @@
         <v>9650000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>9600000</v>
+        <v>5400000</v>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="6" t="n">
-        <v>9600000</v>
+        <v>5400000</v>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>رویال +0.5% گران‌تر</t>
+          <t>رویال +78.7% گران‌تر</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+78.7%</t>
         </is>
       </c>
       <c r="L33" s="6" t="n">
@@ -2478,22 +2498,22 @@
         <v>7040000</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7000000</v>
+        <v>6900000</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>7100000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>7050000</v>
+        <v>7000000</v>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>رویال -0.1% ارزان‌تر</t>
+          <t>رویال +0.6% گران‌تر</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="L34" s="6" t="n">
@@ -2587,19 +2607,19 @@
         <v>6500000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7150000</v>
+        <v>6900000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>6825000</v>
+        <v>6700000</v>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>رویال +2.1% گران‌تر</t>
+          <t>رویال +4.0% گران‌تر</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="L36" s="6" t="n">
@@ -2648,19 +2668,19 @@
         <v>6500000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7150000</v>
+        <v>6900000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>6825000</v>
+        <v>6700000</v>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>رویال +2.1% گران‌تر</t>
+          <t>رویال +4.0% گران‌تر</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="L37" s="6" t="n">
@@ -2703,27 +2723,29 @@
         <v>3</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>12540000</v>
+        <v>12400000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11880000</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+        <v>11890000</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>16790000</v>
+      </c>
       <c r="I38" s="6" t="n">
-        <v>11880000</v>
+        <v>14340000</v>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>رویال +5.6% گران‌تر</t>
+          <t>رویال -13.5% ارزان‌تر</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="L38" s="6" t="n">
-        <v>37620000</v>
+        <v>37200000</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
@@ -2765,22 +2787,22 @@
         <v>3970000</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3900000</v>
+        <v>3800000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4250000</v>
+        <v>4500000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4075000</v>
+        <v>4150000</v>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>رویال -2.6% ارزان‌تر</t>
+          <t>رویال -4.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="L39" s="6" t="n">
@@ -2823,7 +2845,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>18480000</v>
+        <v>9850000</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>8300000</v>
@@ -2834,16 +2856,16 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>رویال +122.7% گران‌تر</t>
+          <t>رویال +18.7% گران‌تر</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>+122.7%</t>
+          <t>+18.7%</t>
         </is>
       </c>
       <c r="L40" s="6" t="n">
-        <v>55440000</v>
+        <v>29550000</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2877,20 +2899,20 @@
         <v>13570000</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>12000000</v>
+        <v>10000000</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="6" t="n">
-        <v>12000000</v>
+        <v>10000000</v>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>رویال +13.1% گران‌تر</t>
+          <t>رویال +35.7% گران‌تر</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+35.7%</t>
         </is>
       </c>
       <c r="L41" s="6" t="n">
@@ -2993,18 +3015,20 @@
       <c r="G43" s="6" t="n">
         <v>6980000</v>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="6" t="n">
+        <v>8000000</v>
+      </c>
       <c r="I43" s="6" t="n">
-        <v>6980000</v>
+        <v>7490000</v>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>رویال +2.3% گران‌تر</t>
+          <t>رویال -4.7% ارزان‌تر</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="L43" s="6" t="n">
@@ -3160,22 +3184,22 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>2839550</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4515000</v>
+        <v>3734775</v>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>رویال +6.3% گران‌تر</t>
+          <t>رویال +28.5% گران‌تر</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>+6.3%</t>
+          <t>+28.5%</t>
         </is>
       </c>
       <c r="L46" s="6" t="n">
@@ -3220,19 +3244,19 @@
         <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>7069000</v>
+        <v>7599000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6342500</v>
+        <v>6607500</v>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.6% ارزان‌تر</t>
+          <t>رویال -14.2% ارزان‌تر</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="L47" s="6" t="n">
@@ -3281,19 +3305,19 @@
         <v>8700000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>11000000</v>
+        <v>12900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>9850000</v>
+        <v>10800000</v>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>رویال -11.7% ارزان‌تر</t>
+          <t>رویال -19.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="L48" s="6" t="n">
@@ -3402,18 +3426,20 @@
       <c r="G50" s="6" t="n">
         <v>6690000</v>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="6" t="n">
+        <v>6900000</v>
+      </c>
       <c r="I50" s="6" t="n">
-        <v>6690000</v>
+        <v>6795000</v>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>رویال +1.2% گران‌تر</t>
+          <t>رویال -0.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="L50" s="6" t="n">
@@ -3461,18 +3487,20 @@
       <c r="G51" s="6" t="n">
         <v>11890000</v>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="6" t="n">
+        <v>16750000</v>
+      </c>
       <c r="I51" s="6" t="n">
-        <v>11890000</v>
+        <v>14320000</v>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.3% گران‌تر</t>
+          <t>رویال -13.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>+4.3%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="L51" s="6" t="n">
@@ -3520,18 +3548,20 @@
       <c r="G52" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="6" t="n">
+        <v>13000000</v>
+      </c>
       <c r="I52" s="6" t="n">
-        <v>11000000</v>
+        <v>12000000</v>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.1% گران‌تر</t>
+          <t>رویال -4.6% ارزان‌تر</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="L52" s="6" t="n">
@@ -3684,7 +3714,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -3697,16 +3727,16 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>رویال +26.7% گران‌تر</t>
+          <t>رویال +15.3% گران‌تر</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+15.3%</t>
         </is>
       </c>
       <c r="L55" s="6" t="n">
-        <v>21900000</v>
+        <v>19940000</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -3840,24 +3870,26 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="5" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>4500000</v>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="6" t="n">
+        <v>8091000</v>
+      </c>
       <c r="I58" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>هم‌قیمت بازار</t>
+        <v>6295500</v>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>رویال -28.5% ارزان‌تر</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="L58" s="6" t="n">
@@ -3902,19 +3934,19 @@
         <v>4600000</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>8075000</v>
+        <v>8500000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>6337500</v>
+        <v>6550000</v>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>رویال -3.0% ارزان‌تر</t>
+          <t>رویال -6.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="L59" s="6" t="n">
@@ -3962,18 +3994,20 @@
       <c r="G60" s="6" t="n">
         <v>6460000</v>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="6" t="n">
+        <v>7099000</v>
+      </c>
       <c r="I60" s="6" t="n">
-        <v>6460000</v>
+        <v>6779500</v>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>رویال +29.1% گران‌تر</t>
+          <t>رویال +23.0% گران‌تر</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>+29.1%</t>
+          <t>+23.0%</t>
         </is>
       </c>
       <c r="L60" s="6" t="n">
@@ -4081,19 +4115,19 @@
         <v>3900000</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>4582400</v>
+        <v>4666940</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>4241200</v>
+        <v>4283470</v>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>رویال -7.0% ارزان‌تر</t>
+          <t>رویال -7.9% ارزان‌تر</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="L62" s="6" t="n">
@@ -4142,19 +4176,19 @@
         <v>21500000</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>8075000</v>
+        <v>19100000</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>14787500</v>
+        <v>20300000</v>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>رویال +49.5% گران‌تر</t>
+          <t>رویال +8.9% گران‌تر</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>+49.5%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="L63" s="6" t="n">
@@ -4203,19 +4237,19 @@
         <v>4600000</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>5500000</v>
+        <v>6150000</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>5050000</v>
+        <v>5375000</v>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>رویال -3.6% ارزان‌تر</t>
+          <t>رویال -9.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="L64" s="6" t="n">
@@ -4435,19 +4469,19 @@
         <v>3620000</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>3866860</v>
+        <v>4009230</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>3743430</v>
+        <v>3814615</v>
       </c>
       <c r="J68" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.7% گران‌تر</t>
+          <t>رویال +2.8% گران‌تر</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="L68" s="6" t="n">
@@ -4554,18 +4588,20 @@
       <c r="G70" s="6" t="n">
         <v>7200000</v>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="6" t="n">
+        <v>15000000</v>
+      </c>
       <c r="I70" s="6" t="n">
-        <v>7200000</v>
+        <v>11100000</v>
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>رویال +0.6% گران‌تر</t>
+          <t>رویال -34.8% ارزان‌تر</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="L70" s="6" t="n">
@@ -4614,19 +4650,19 @@
         <v>6400000</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>6377900</v>
+        <v>9700000</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>6388950</v>
+        <v>8050000</v>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>رویال +13.3% گران‌تر</t>
+          <t>رویال -10.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="L71" s="6" t="n">
@@ -4734,19 +4770,19 @@
         <v>3290000</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>5200000</v>
+        <v>5079040</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>4245000</v>
+        <v>4184520</v>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.7% ارزان‌تر</t>
+          <t>رویال -9.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="L73" s="6" t="n">
@@ -5092,19 +5128,19 @@
         <v>3750000</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>4630000</v>
+        <v>4500000</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>4190000</v>
+        <v>4125000</v>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>رویال -8.8% ارزان‌تر</t>
+          <t>رویال -7.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="L79" s="6" t="n">
@@ -5153,19 +5189,19 @@
         <v>14700000</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>24980000</v>
+        <v>24400000</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>19840000</v>
+        <v>19550000</v>
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>رویال -24.4% ارزان‌تر</t>
+          <t>رویال -23.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="L80" s="6" t="n">
@@ -5214,19 +5250,19 @@
         <v>6190000</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>7660000</v>
+        <v>7780000</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>6925000</v>
+        <v>6985000</v>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.5% ارزان‌تر</t>
+          <t>رویال -11.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="L81" s="6" t="n">
@@ -5336,19 +5372,19 @@
         <v>10000000</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>14300000</v>
+        <v>14500000</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>12150000</v>
+        <v>12250000</v>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>رویال -6.6% ارزان‌تر</t>
+          <t>رویال -7.3% ارزان‌تر</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="L83" s="6" t="n">
@@ -5676,29 +5712,29 @@
         <v>1</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>7000000</v>
+        <v>6970000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>6675000</v>
+        <v>6650000</v>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.9% گران‌تر</t>
+          <t>رویال +4.8% گران‌تر</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7000000</v>
+        <v>6970000</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
@@ -5737,29 +5773,29 @@
         <v>1</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>7000000</v>
+        <v>6970000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>6675000</v>
+        <v>6650000</v>
       </c>
       <c r="J90" s="7" t="inlineStr">
         <is>
-          <t>رویال +4.9% گران‌تر</t>
+          <t>رویال +4.8% گران‌تر</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7000000</v>
+        <v>6970000</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
@@ -5804,19 +5840,19 @@
         <v>3900000</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>4582400</v>
+        <v>4666940</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>4241200</v>
+        <v>4283470</v>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>رویال -7.0% ارزان‌تر</t>
+          <t>رویال -7.9% ارزان‌تر</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="L91" s="6" t="n">
@@ -5865,10 +5901,10 @@
         <v>2900000</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>3324800</v>
+        <v>3324700</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>3112400</v>
+        <v>3112350</v>
       </c>
       <c r="J92" s="7" t="inlineStr">
         <is>
@@ -5926,19 +5962,19 @@
         <v>6898000</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>7850000</v>
+        <v>8600000</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>7374000</v>
+        <v>7749000</v>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>رویال -6.4% ارزان‌تر</t>
+          <t>رویال -10.9% ارزان‌تر</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="L93" s="6" t="n">
@@ -6219,7 +6255,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -6232,16 +6268,16 @@
       </c>
       <c r="J98" s="7" t="inlineStr">
         <is>
-          <t>رویال +26.7% گران‌تر</t>
+          <t>رویال +15.3% گران‌تر</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>+15.3%</t>
         </is>
       </c>
       <c r="L98" s="6" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
@@ -6286,19 +6322,19 @@
         <v>3290000</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>5200000</v>
+        <v>5079040</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>4245000</v>
+        <v>4184520</v>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>رویال -10.7% ارزان‌تر</t>
+          <t>رویال -9.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="L99" s="6" t="n">
@@ -6453,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>36520000</v>
+        <v>24000000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -6466,16 +6502,16 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>رویال +81.4% گران‌تر</t>
+          <t>رویال +19.2% گران‌تر</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>+81.4%</t>
+          <t>+19.2%</t>
         </is>
       </c>
       <c r="L102" s="6" t="n">
-        <v>36520000</v>
+        <v>24000000</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
@@ -6561,19 +6597,19 @@
         <v>3750000</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>4630000</v>
+        <v>4500000</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>4190000</v>
+        <v>4125000</v>
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>رویال -8.8% ارزان‌تر</t>
+          <t>رویال -7.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="L104" s="6" t="n">
@@ -6793,19 +6829,19 @@
         <v>7560000</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>16990000</v>
+        <v>14590000</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>12275000</v>
+        <v>11075000</v>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>رویال -21.9% ارزان‌تر</t>
+          <t>رویال -13.4% ارزان‌تر</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="L108" s="6" t="n">
@@ -7127,19 +7163,19 @@
         <v>9000000</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>11000000</v>
+        <v>10900000</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>10000000</v>
+        <v>9950000</v>
       </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
-          <t>رویال -5.6% ارزان‌تر</t>
+          <t>رویال -5.1% ارزان‌تر</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="L114" s="6" t="n">
@@ -7247,10 +7283,10 @@
         <v>2900000</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>3324800</v>
+        <v>3324700</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>3112400</v>
+        <v>3112350</v>
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
@@ -7779,18 +7815,20 @@
       <c r="G125" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="H125" s="6" t="n">
+        <v>16000000</v>
+      </c>
       <c r="I125" s="6" t="n">
-        <v>13000000</v>
+        <v>14500000</v>
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>رویال +18.9% گران‌تر</t>
+          <t>رویال +6.6% گران‌تر</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>+18.9%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="L125" s="6" t="n">
@@ -8236,19 +8274,19 @@
         <v>7800000</v>
       </c>
       <c r="H133" s="6" t="n">
-        <v>6902400</v>
+        <v>7190000</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>7351200</v>
+        <v>7495000</v>
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>رویال +66.2% گران‌تر</t>
+          <t>رویال +63.0% گران‌تر</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>+66.2%</t>
+          <t>+63.0%</t>
         </is>
       </c>
       <c r="L133" s="6" t="n">

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مانیتورینگ ۳ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="مانیتورینگ ۳ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -631,7 +631,7 @@
         <v>9400000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10280000</v>
+        <v>10400000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>4900000</v>
+      <c r="F5" s="8" t="n">
+        <v>5400000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4500000</v>
+        <v>5000000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4800000</v>
+        <v>5100000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5000000</v>
+        <v>5100000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5790000</v>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+300,000 ت از رتبه ۳ ترب (+5.9%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>88200000</v>
+        <v>97200000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -875,32 +875,32 @@
         <v>17</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6470000</v>
+        <v>6500000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6400000</v>
+        <v>6550000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>6450000</v>
+        <v>6889000</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>7460210</v>
+        <v>9524230</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>109990000</v>
+        <v>110500000</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -938,33 +938,33 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>3970000</v>
+      <c r="F7" s="8" t="n">
+        <v>3997000</v>
       </c>
       <c r="G7" s="6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>3900000</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>3950000</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>3995000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4250000</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>4500000</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+2,000 ت از رتبه ۳ ترب (+0.1%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>59550000</v>
+        <v>59955000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3970000</v>
+        <v>1630000</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>51610000</v>
+        <v>21190000</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -1074,37 +1074,29 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="G9" s="6" t="n">
+        <v>97000</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>115500</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
@@ -1142,33 +1134,33 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>9200000</v>
+      <c r="F10" s="8" t="n">
+        <v>8950000</v>
       </c>
       <c r="G10" s="6" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>8900000</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>9000000</v>
-      </c>
       <c r="I10" s="6" t="n">
-        <v>9500000</v>
+        <v>8900000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>8800000</v>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>101200000</v>
+        <v>98450000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1207,23 +1199,19 @@
         <v>11</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8500000</v>
+        <v>6830000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6600000</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>6799000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8220000</v>
+        <v>8610000</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
@@ -1232,11 +1220,11 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه ۳ ترب (+44.1%)</t>
+          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>93500000</v>
+        <v>75130000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1274,39 +1262,33 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>4310000</v>
+      <c r="F12" s="5" t="n">
+        <v>4495000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7265700</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+        <v>4300000</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4490000</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>-2,955,700 ت از کف ترب (-40.7%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>43100000</v>
+        <v>44950000</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1344,29 +1326,29 @@
       <c r="E13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="11" t="n">
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>9100000</v>
+        <v>11800000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9500000</v>
+        <v>12000000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>10200000</v>
+        <v>12400000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>-1,600,000 ت از کف ترب (-13.6%)</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
@@ -1401,19 +1383,19 @@
         <v>8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>15200000</v>
+        <v>17960000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11480000</v>
+        <v>11180000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11590000</v>
+        <v>11200000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>14179000</v>
+        <v>11479000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>19000000</v>
+        <v>21000000</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
@@ -1422,11 +1404,11 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+1,021,000 ت از رتبه ۳ ترب (+7.2%)</t>
+          <t>+6,481,000 ت از رتبه ۳ ترب (+56.5%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>121600000</v>
+        <v>143680000</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1465,19 +1447,19 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6297000</v>
+        <v>6240000</v>
       </c>
       <c r="G15" s="6" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>6200000</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <v>6295000</v>
-      </c>
       <c r="I15" s="6" t="n">
-        <v>6300000</v>
+        <v>6290000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7860000</v>
+        <v>7780000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1490,7 +1472,7 @@
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>44079000</v>
+        <v>43680000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1528,33 +1510,33 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <v>3800000</v>
+      <c r="F16" s="5" t="n">
+        <v>4440000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4195000</v>
+        <v>4205000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4200000</v>
+        <v>4400000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4290000</v>
+        <v>4480000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>-395,000 ت از کف ترب (-9.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>26600000</v>
+        <v>31080000</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1592,13 +1574,11 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="11" t="n">
         <v>8000000</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G17" s="6" t="n">
+        <v>8500000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1615,14 +1595,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>-500,000 ت از کف ترب (-5.9%)</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
@@ -1664,8 +1644,8 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>11000000</v>
+      <c r="F18" s="8" t="n">
+        <v>9750000</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>9250000</v>
@@ -1674,25 +1654,25 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>12500000</v>
+        <v>9500000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+250,000 ت از رتبه ۳ ترب (+2.6%)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>66000000</v>
+        <v>58500000</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1730,33 +1710,33 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>7700000</v>
+      <c r="F19" s="8" t="n">
+        <v>8950000</v>
       </c>
       <c r="G19" s="6" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="H19" s="6" t="n">
         <v>8900000</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <v>9000000</v>
-      </c>
       <c r="I19" s="6" t="n">
-        <v>9500000</v>
+        <v>8900000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>8800000</v>
       </c>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>-1,200,000 ت از کف ترب (-13.5%)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>46200000</v>
+        <v>53700000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1794,11 +1774,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>3000000</v>
+      <c r="F20" s="11" t="n">
+        <v>3580000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2980000</v>
+        <v>4200000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -1811,18 +1791,18 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-299,000 ت از کف ترب (-7.7%)</t>
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>18000000</v>
+        <v>21480000</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1861,23 +1841,19 @@
         <v>5</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>5930000</v>
+        <v>6830000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6600000</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>6799000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8220000</v>
+        <v>8610000</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1886,11 +1862,11 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>29650000</v>
+        <v>34150000</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1929,10 +1905,10 @@
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>15380000</v>
+        <v>14970000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>15300000</v>
+        <v>14900000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1954,11 +1930,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>76900000</v>
+        <v>74850000</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1996,11 +1972,11 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>7200000</v>
+      <c r="F23" s="5" t="n">
+        <v>12140000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7800000</v>
+        <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>8090000</v>
@@ -2009,20 +1985,20 @@
         <v>16200000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>6902400</v>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+        <v>7190000</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>-600,000 ت از کف ترب (-7.7%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>36000000</v>
+        <v>60700000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2060,8 +2036,8 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>5670000</v>
+      <c r="F24" s="8" t="n">
+        <v>5770000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>5616000</v>
@@ -2070,23 +2046,23 @@
         <v>5650000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5698000</v>
+        <v>5650000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>7599000</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+120,000 ت از رتبه ۳ ترب (+2.1%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>28350000</v>
+        <v>28850000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2124,33 +2100,33 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>6990000</v>
+      <c r="F25" s="8" t="n">
+        <v>8960000</v>
       </c>
       <c r="G25" s="6" t="n">
+        <v>5590000</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>6500000</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>6980000</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>7000000</v>
-      </c>
       <c r="J25" s="6" t="n">
-        <v>12590000</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>13500000</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,980,000 ت از رتبه ۳ ترب (+28.4%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>34950000</v>
+        <v>44800000</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -2188,8 +2164,8 @@
       <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>7690000</v>
+      <c r="F26" s="8" t="n">
+        <v>10210000</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>6900000</v>
@@ -2203,18 +2179,18 @@
       <c r="J26" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+2,230,000 ت از رتبه ۳ ترب (+27.9%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>38450000</v>
+        <v>51050000</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -2248,33 +2224,33 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>15480000</v>
+      <c r="F27" s="5" t="n">
+        <v>15000000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>8300000</v>
+        <v>12550000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>9200000</v>
+        <v>14500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>10500000</v>
+        <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>+4,980,000 ت از رتبه ۳ ترب (+47.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>77400000</v>
+        <v>75000000</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -2379,19 +2355,19 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>4990000</v>
+        <v>4895000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>4800000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4980000</v>
+        <v>4890000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5000000</v>
+        <v>4900000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5790000</v>
+        <v>6150000</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2404,7 +2380,7 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>19960000</v>
+        <v>19580000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2509,19 +2485,19 @@
         <v>4</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>28000000</v>
+        <v>11940000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22950000</v>
+        <v>11800000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>23000000</v>
+        <v>11890000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>33000000</v>
+        <v>12000000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>29900000</v>
+        <v>29990000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2534,7 +2510,7 @@
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>112000000</v>
+        <v>47760000</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2572,33 +2548,33 @@
       <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="5" t="n">
-        <v>11500000</v>
+      <c r="F32" s="8" t="n">
+        <v>11600000</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10799000</v>
+        <v>10950000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>10800000</v>
+        <v>11000000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12200000</v>
+        <v>11000000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>46000000</v>
+        <v>46400000</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2636,39 +2612,35 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>9650000</v>
+      <c r="F33" s="5" t="n">
+        <v>5999500</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>9600000</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5400000</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>5999000</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>6000000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>28950000</v>
+        <v>17998500</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2706,37 +2678,33 @@
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>7040000</v>
+      <c r="F34" s="5" t="n">
+        <v>8650000</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6900000</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>8700000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
-        <v>21120000</v>
+        <v>25950000</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2826,8 +2794,8 @@
       <c r="E36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>6970000</v>
+      <c r="F36" s="8" t="n">
+        <v>7000000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6500000</v>
@@ -2836,23 +2804,23 @@
         <v>6950000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7000000</v>
+        <v>6950000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>6900000</v>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>20910000</v>
+        <v>21000000</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2890,8 +2858,8 @@
       <c r="E37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>6970000</v>
+      <c r="F37" s="8" t="n">
+        <v>7000000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6500000</v>
@@ -2900,23 +2868,23 @@
         <v>6950000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7000000</v>
+        <v>6950000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>6900000</v>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M37" s="6" t="n">
-        <v>20910000</v>
+        <v>21000000</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2955,21 +2923,19 @@
         <v>3</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>12540000</v>
+        <v>13220000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11880000</v>
+        <v>11890000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>11890000</v>
+        <v>13200000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13200000</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>13250000</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>16790000</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
@@ -2982,7 +2948,7 @@
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>37620000</v>
+        <v>39660000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -3020,33 +2986,33 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>3970000</v>
+      <c r="F39" s="8" t="n">
+        <v>3997000</v>
       </c>
       <c r="G39" s="6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="H39" s="6" t="n">
         <v>3900000</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>3950000</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>3995000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4250000</v>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>4500000</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+2,000 ت از رتبه ۳ ترب (+0.1%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>11910000</v>
+        <v>11991000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3051,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>18480000</v>
+        <v>15000000</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>8300000</v>
@@ -3108,11 +3074,11 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>+7,980,000 ت از رتبه ۳ ترب (+76.0%)</t>
+          <t>+4,500,000 ت از رتبه ۳ ترب (+42.9%)</t>
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>55440000</v>
+        <v>45000000</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -3142,37 +3108,35 @@
       <c r="E41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>13570000</v>
+      <c r="F41" s="5" t="n">
+        <v>12750000</v>
       </c>
       <c r="G41" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H41" s="6" t="n">
         <v>12000000</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="6" t="n">
         <v>13500000</v>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>40710000</v>
+        <v>38250000</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -3276,8 +3240,8 @@
       <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>7140000</v>
+      <c r="F43" s="8" t="n">
+        <v>7294000</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>6980000</v>
@@ -3288,23 +3252,21 @@
       <c r="I43" s="6" t="n">
         <v>7289000</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="J43" s="6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+5,000 ت از رتبه ۳ ترب (+0.1%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
-        <v>21420000</v>
+        <v>21882000</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -3540,8 +3502,8 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>5670000</v>
+      <c r="F47" s="8" t="n">
+        <v>5770000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3553,20 +3515,20 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>7599000</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+72,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>11340000</v>
+        <v>11540000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3617,7 +3579,7 @@
         <v>9100000</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>11000000</v>
+        <v>12900000</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
@@ -3668,8 +3630,8 @@
       <c r="E49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>3149500</v>
+      <c r="F49" s="8" t="n">
+        <v>3170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -3683,18 +3645,18 @@
       <c r="J49" s="6" t="n">
         <v>4085000</v>
       </c>
-      <c r="K49" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>6299000</v>
+        <v>6340000</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3732,8 +3694,8 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>6770000</v>
+      <c r="F50" s="8" t="n">
+        <v>7340000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -3749,18 +3711,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+490,000 ت از رتبه ۳ ترب (+7.2%)</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">
-        <v>13540000</v>
+        <v>14680000</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3798,8 +3760,8 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>12400000</v>
+      <c r="F51" s="8" t="n">
+        <v>13220000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3810,23 +3772,21 @@
       <c r="I51" s="6" t="n">
         <v>12900000</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="J51" s="6" t="n">
+        <v>16750000</v>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+320,000 ت از رتبه ۳ ترب (+2.5%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>24800000</v>
+        <v>26440000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3865,7 +3825,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>11450000</v>
+        <v>11200000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -3876,23 +3836,21 @@
       <c r="I52" s="6" t="n">
         <v>11500000</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J52" s="6" t="n">
+        <v>13000000</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M52" s="6" t="n">
-        <v>22900000</v>
+        <v>22400000</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -4069,7 +4027,7 @@
         <v>2</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -4094,7 +4052,7 @@
         </is>
       </c>
       <c r="M55" s="6" t="n">
-        <v>21900000</v>
+        <v>19940000</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -4133,7 +4091,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>5920000</v>
+        <v>5950000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4160,7 +4118,7 @@
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>11840000</v>
+        <v>11900000</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -4276,10 +4234,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J58" s="6" t="n">
+        <v>8091000</v>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
@@ -4326,8 +4282,8 @@
       <c r="E59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="5" t="n">
-        <v>6150000</v>
+      <c r="F59" s="8" t="n">
+        <v>8300000</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>4600000</v>
@@ -4339,20 +4295,20 @@
         <v>6800000</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>8075000</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>8500000</v>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,500,000 ت از رتبه ۳ ترب (+22.1%)</t>
         </is>
       </c>
       <c r="M59" s="6" t="n">
-        <v>12300000</v>
+        <v>16600000</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -4390,8 +4346,8 @@
       <c r="E60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F60" s="8" t="n">
-        <v>8340000</v>
+      <c r="F60" s="11" t="n">
+        <v>5750000</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>6460000</v>
@@ -4404,23 +4360,21 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="J60" s="6" t="n">
+        <v>7099000</v>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>-710,000 ت از کف ترب (-11.0%)</t>
         </is>
       </c>
       <c r="M60" s="6" t="n">
-        <v>16680000</v>
+        <v>11500000</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -4458,8 +4412,8 @@
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>8850000</v>
+      <c r="F61" s="8" t="n">
+        <v>22740000</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>8500000</v>
@@ -4475,18 +4429,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+13,740,000 ت از رتبه ۳ ترب (+152.7%)</t>
         </is>
       </c>
       <c r="M61" s="6" t="n">
-        <v>17700000</v>
+        <v>45480000</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -4524,8 +4478,8 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>3945000</v>
+      <c r="F62" s="8" t="n">
+        <v>4330000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4537,20 +4491,20 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>4390000</v>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+380,000 ت از رتبه ۳ ترب (+9.6%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>7890000</v>
+        <v>8660000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4589,7 +4543,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>22110000</v>
+        <v>22080000</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>21500000</v>
@@ -4603,7 +4557,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>8075000</v>
+        <v>19100000</v>
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
@@ -4612,11 +4566,11 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>+110,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+80,000 ت از رتبه ۳ ترب (+0.4%)</t>
         </is>
       </c>
       <c r="M63" s="6" t="n">
-        <v>44220000</v>
+        <v>44160000</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -4655,7 +4609,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>4870000</v>
+        <v>4895000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4667,7 +4621,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5500000</v>
+        <v>6150000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -4680,7 +4634,7 @@
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>9740000</v>
+        <v>9790000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4795,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>4000000</v>
+        <v>6880000</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>3980000</v>
@@ -4868,11 +4822,11 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+2,900,000 ت از رتبه ۳ ترب (+72.9%)</t>
         </is>
       </c>
       <c r="M67" s="6" t="n">
-        <v>8000000</v>
+        <v>13760000</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -4910,8 +4864,8 @@
       <c r="E68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>3920000</v>
+      <c r="F68" s="8" t="n">
+        <v>4320000</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>3620000</v>
@@ -4923,20 +4877,20 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3866860</v>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>4009230</v>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+220,000 ت از رتبه ۳ ترب (+5.4%)</t>
         </is>
       </c>
       <c r="M68" s="6" t="n">
-        <v>7840000</v>
+        <v>8640000</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -5041,7 +4995,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>7240000</v>
+        <v>8320000</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>7200000</v>
@@ -5056,10 +5010,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J70" s="6" t="n">
+        <v>15000000</v>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
@@ -5068,11 +5020,11 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+1,120,000 ت از رتبه ۳ ترب (+15.6%)</t>
         </is>
       </c>
       <c r="M70" s="6" t="n">
-        <v>14480000</v>
+        <v>16640000</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -5125,7 +5077,7 @@
         </is>
       </c>
       <c r="J71" s="6" t="n">
-        <v>6377900</v>
+        <v>9700000</v>
       </c>
       <c r="K71" s="9" t="inlineStr">
         <is>
@@ -5176,8 +5128,8 @@
       <c r="E72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F72" s="8" t="n">
-        <v>17590000</v>
+      <c r="F72" s="5" t="n">
+        <v>17090000</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>11000000</v>
@@ -5195,18 +5147,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K72" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M72" s="6" t="n">
-        <v>35180000</v>
+        <v>34180000</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -5245,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>3790000</v>
+        <v>3699500</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -5257,20 +5209,20 @@
         <v>3890000</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>5200000</v>
+        <v>5050000</v>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M73" s="6" t="n">
-        <v>7580000</v>
+        <v>7399000</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -5621,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>3820000</v>
+        <v>3850000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -5646,7 +5598,7 @@
         </is>
       </c>
       <c r="M79" s="6" t="n">
-        <v>3820000</v>
+        <v>3850000</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -5697,7 +5649,7 @@
         <v>14990000</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>24980000</v>
+        <v>24400000</v>
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
@@ -5748,8 +5700,8 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>6199000</v>
+      <c r="F81" s="8" t="n">
+        <v>6240000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -5761,20 +5713,20 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7660000</v>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>7780000</v>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M81" s="6" t="n">
-        <v>6199000</v>
+        <v>6240000</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -5878,8 +5830,8 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>11350000</v>
+      <c r="F83" s="8" t="n">
+        <v>12750000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5891,20 +5843,20 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>14300000</v>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>14500000</v>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+950,000 ت از رتبه ۳ ترب (+8.1%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>11350000</v>
+        <v>12750000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -6211,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>6880000</v>
+        <v>6890000</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>5800000</v>
@@ -6238,7 +6190,7 @@
         </is>
       </c>
       <c r="M88" s="6" t="n">
-        <v>6880000</v>
+        <v>6890000</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -6289,7 +6241,7 @@
         <v>6950000</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="K89" s="9" t="inlineStr">
         <is>
@@ -6353,7 +6305,7 @@
         <v>6950000</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
@@ -6404,8 +6356,8 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>3945000</v>
+      <c r="F91" s="8" t="n">
+        <v>4330000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6417,20 +6369,20 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="K91" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>4390000</v>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+380,000 ت از رتبه ۳ ترب (+9.6%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>3945000</v>
+        <v>4330000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6468,8 +6420,8 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>2960000</v>
+      <c r="F92" s="8" t="n">
+        <v>3170000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6481,20 +6433,20 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3324800</v>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>3324700</v>
+      </c>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+182,000 ت از رتبه ۳ ترب (+6.1%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>2960000</v>
+        <v>3170000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -6532,8 +6484,8 @@
       <c r="E93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>6905000</v>
+      <c r="F93" s="8" t="n">
+        <v>7050000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -6545,20 +6497,20 @@
         <v>6920000</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>7850000</v>
-      </c>
-      <c r="K93" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>8600000</v>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+130,000 ت از رتبه ۳ ترب (+1.9%)</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
-        <v>6905000</v>
+        <v>7050000</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -6677,7 +6629,7 @@
         <v>21350000</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>27800000</v>
+        <v>27900000</v>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
@@ -6799,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>7240000</v>
+        <v>8320000</v>
       </c>
       <c r="G97" s="6" t="n">
         <v>7200000</v>
@@ -6826,11 +6778,11 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+1,120,000 ت از رتبه ۳ ترب (+15.6%)</t>
         </is>
       </c>
       <c r="M97" s="6" t="n">
-        <v>7240000</v>
+        <v>8320000</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -6869,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -6894,7 +6846,7 @@
         </is>
       </c>
       <c r="M98" s="6" t="n">
-        <v>10950000</v>
+        <v>9970000</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -6933,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>3790000</v>
+        <v>3699500</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -6945,20 +6897,20 @@
         <v>3890000</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>5200000</v>
+        <v>5050000</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M99" s="6" t="n">
-        <v>3790000</v>
+        <v>3699500</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>3390000</v>
+        <v>3580000</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>3580000</v>
@@ -7024,7 +6976,7 @@
         </is>
       </c>
       <c r="M100" s="6" t="n">
-        <v>3390000</v>
+        <v>3580000</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -7120,8 +7072,8 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="8" t="n">
-        <v>36520000</v>
+      <c r="F102" s="11" t="n">
+        <v>24000000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -7137,18 +7089,18 @@
       <c r="J102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="K102" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>+184,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>-1,757,000 ت از کف ترب (-6.8%)</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>36520000</v>
+        <v>24000000</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
@@ -7253,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>3820000</v>
+        <v>3850000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -7278,7 +7230,7 @@
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>3820000</v>
+        <v>3850000</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -7317,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4440000</v>
+        <v>4380000</v>
       </c>
       <c r="G105" s="6" t="n">
         <v>4000000</v>
@@ -7342,7 +7294,7 @@
         </is>
       </c>
       <c r="M105" s="6" t="n">
-        <v>4440000</v>
+        <v>4380000</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
@@ -7533,7 +7485,7 @@
         <v>9699000</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>16990000</v>
+        <v>14590000</v>
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
@@ -7651,7 +7603,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>3600000</v>
+        <v>5520000</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>3580000</v>
@@ -7678,11 +7630,11 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+1,940,000 ت از رتبه ۳ ترب (+54.2%)</t>
         </is>
       </c>
       <c r="M110" s="6" t="n">
-        <v>3600000</v>
+        <v>5520000</v>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
@@ -7869,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>6220000</v>
+        <v>6270000</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>5900000</v>
@@ -7894,7 +7846,7 @@
         </is>
       </c>
       <c r="M113" s="6" t="n">
-        <v>6220000</v>
+        <v>6270000</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
@@ -7932,8 +7884,8 @@
       <c r="E114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="5" t="n">
-        <v>9440000</v>
+      <c r="F114" s="8" t="n">
+        <v>10140000</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>9000000</v>
@@ -7945,20 +7897,20 @@
         <v>9790000</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="K114" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>10790000</v>
+      </c>
+      <c r="K114" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+350,000 ت از رتبه ۳ ترب (+3.6%)</t>
         </is>
       </c>
       <c r="M114" s="6" t="n">
-        <v>9440000</v>
+        <v>10140000</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -7997,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>9650000</v>
+        <v>9400000</v>
       </c>
       <c r="G115" s="6" t="n">
         <v>8900000</v>
@@ -8015,16 +7967,16 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M115" s="6" t="n">
-        <v>9650000</v>
+        <v>9400000</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -8062,8 +8014,8 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>2960000</v>
+      <c r="F116" s="8" t="n">
+        <v>3170000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8075,20 +8027,20 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3324800</v>
-      </c>
-      <c r="K116" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>3324700</v>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+182,000 ت از رتبه ۳ ترب (+6.1%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>2960000</v>
+        <v>3170000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>6200000</v>
+        <v>5370000</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>5248000</v>
@@ -8213,16 +8165,16 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M118" s="6" t="n">
-        <v>6200000</v>
+        <v>5370000</v>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
@@ -8452,8 +8404,8 @@
       <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="5" t="n">
-        <v>10970000</v>
+      <c r="F122" s="8" t="n">
+        <v>11600000</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>10800000</v>
@@ -8467,18 +8419,18 @@
       <c r="J122" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K122" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K122" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
         </is>
       </c>
       <c r="M122" s="6" t="n">
-        <v>10970000</v>
+        <v>11600000</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
@@ -8576,8 +8528,8 @@
       <c r="E124" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F124" s="8" t="n">
-        <v>9650000</v>
+      <c r="F124" s="11" t="n">
+        <v>5999500</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -8597,18 +8549,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K124" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>-3,600,500 ت از کف ترب (-37.5%)</t>
         </is>
       </c>
       <c r="M124" s="6" t="n">
-        <v>9650000</v>
+        <v>5999500</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
@@ -8660,10 +8612,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J125" s="6" t="n">
+        <v>16000000</v>
       </c>
       <c r="K125" s="9" t="inlineStr">
         <is>
@@ -8714,8 +8664,8 @@
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="5" t="n">
-        <v>10970000</v>
+      <c r="F126" s="8" t="n">
+        <v>11600000</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>10800000</v>
@@ -8729,18 +8679,18 @@
       <c r="J126" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K126" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K126" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
         </is>
       </c>
       <c r="M126" s="6" t="n">
-        <v>10970000</v>
+        <v>11600000</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
@@ -8990,8 +8940,8 @@
       <c r="E130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="5" t="n">
-        <v>6770000</v>
+      <c r="F130" s="8" t="n">
+        <v>7340000</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>6690000</v>
@@ -9007,18 +8957,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K130" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+490,000 ت از رتبه ۳ ترب (+7.2%)</t>
         </is>
       </c>
       <c r="M130" s="6" t="n">
-        <v>6770000</v>
+        <v>7340000</v>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
@@ -9123,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>11320000</v>
+        <v>12570000</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>9945000</v>
@@ -9150,7 +9100,7 @@
         </is>
       </c>
       <c r="M132" s="6" t="n">
-        <v>11320000</v>
+        <v>12570000</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
@@ -9189,7 +9139,7 @@
         <v>1</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>12220000</v>
+        <v>12140000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9201,7 +9151,7 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>6902400</v>
+        <v>7190000</v>
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
@@ -9214,7 +9164,7 @@
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>12220000</v>
+        <v>12140000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9253,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>19750000</v>
+        <v>19900000</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>19000000</v>
@@ -9280,7 +9230,7 @@
         </is>
       </c>
       <c r="M134" s="6" t="n">
-        <v>19750000</v>
+        <v>19900000</v>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -695,7 +695,7 @@
         <v>15499000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>14990000</v>
+        <v>15490000</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
@@ -750,10 +750,10 @@
         <v>13500000</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>12870000</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>12899000</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>12990000</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>12990000</v>
@@ -810,8 +810,8 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>5400000</v>
+      <c r="F5" s="5" t="n">
+        <v>5150000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5000000</v>
@@ -820,23 +820,23 @@
         <v>5100000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5100000</v>
+        <v>5200000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5790000</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه ۳ ترب (+5.9%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97200000</v>
+        <v>92700000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -1134,33 +1134,33 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>8950000</v>
+      <c r="F10" s="5" t="n">
+        <v>9000000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>7100000</v>
+        <v>8900000</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>8900000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>8900000</v>
+        <v>9000000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>9300000</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>98450000</v>
+        <v>99000000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1263,16 +1263,16 @@
         <v>10</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4495000</v>
+        <v>4600000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4300000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4490000</v>
+        <v>4500000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4500000</v>
+        <v>4700000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5100000</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>44950000</v>
+        <v>46000000</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>17960000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11180000</v>
+        <v>11200000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11200000</v>
+        <v>11450000</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>11479000</v>
@@ -1453,22 +1453,22 @@
         <v>5800000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6200000</v>
+        <v>6300000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6290000</v>
+        <v>6300000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7780000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
@@ -1511,16 +1511,16 @@
         <v>7</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>4440000</v>
+        <v>4490000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4205000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4400000</v>
+        <v>4480000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4480000</v>
+        <v>4500000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>4900000</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>31080000</v>
+        <v>31430000</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1710,33 +1710,33 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="8" t="n">
-        <v>8950000</v>
+      <c r="F19" s="5" t="n">
+        <v>9000000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>7100000</v>
+        <v>8900000</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>8900000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>8900000</v>
+        <v>9000000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>9300000</v>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>53700000</v>
+        <v>54000000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         <v>5</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>14970000</v>
+        <v>14470000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>14900000</v>
+        <v>14400000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16890000</v>
+        <v>16590000</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>74850000</v>
+        <v>72350000</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>6980000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>13500000</v>
+        <v>13890000</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
         <v>10210000</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>6900000</v>
+        <v>7400000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7400000</v>
+        <v>7500000</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>7980000</v>
@@ -2228,7 +2228,7 @@
         <v>15000000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>12550000</v>
+        <v>12680000</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>14500000</v>
@@ -2354,14 +2354,14 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>4895000</v>
+      <c r="F29" s="8" t="n">
+        <v>4940000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4800000</v>
+        <v>4890000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4890000</v>
+        <v>4900000</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>4900000</v>
@@ -2369,18 +2369,18 @@
       <c r="J29" s="6" t="n">
         <v>6150000</v>
       </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.8%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>19580000</v>
+        <v>19760000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>11600000</v>
+        <v>11150000</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>10950000</v>
@@ -2570,11 +2570,11 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>46400000</v>
+        <v>44600000</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2923,16 +2923,16 @@
         <v>3</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>13220000</v>
+        <v>14070000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>11890000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>13200000</v>
+        <v>13250000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13250000</v>
+        <v>14900000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>39660000</v>
+        <v>42210000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -3109,17 +3109,19 @@
         <v>3</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>12750000</v>
+        <v>13500000</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="I41" s="6" t="n">
         <v>13500000</v>
       </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -3127,16 +3129,16 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>38250000</v>
+        <v>40500000</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -3643,7 +3645,7 @@
         <v>3150000</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>4085000</v>
+        <v>3800000</v>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
@@ -3761,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>13220000</v>
+        <v>14070000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3782,11 +3784,11 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>+320,000 ت از رتبه ۳ ترب (+2.5%)</t>
+          <t>+1,170,000 ت از رتبه ۳ ترب (+9.1%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>26440000</v>
+        <v>28140000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3888,8 +3890,8 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>7240000</v>
+      <c r="F53" s="8" t="n">
+        <v>9240000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -3903,18 +3905,18 @@
       <c r="J53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,751,000 ت از رتبه ۳ ترب (+23.4%)</t>
         </is>
       </c>
       <c r="M53" s="6" t="n">
-        <v>14480000</v>
+        <v>18480000</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -4413,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="F61" s="8" t="n">
-        <v>22740000</v>
+        <v>21690000</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>8500000</v>
@@ -4436,11 +4438,11 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>+13,740,000 ت از رتبه ۳ ترب (+152.7%)</t>
+          <t>+12,690,000 ت از رتبه ۳ ترب (+141.0%)</t>
         </is>
       </c>
       <c r="M61" s="6" t="n">
-        <v>45480000</v>
+        <v>43380000</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -4479,7 +4481,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>4330000</v>
+        <v>4344000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4500,11 +4502,11 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+380,000 ت از رتبه ۳ ترب (+9.6%)</t>
+          <t>+394,000 ت از رتبه ۳ ترب (+10.0%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>8660000</v>
+        <v>8688000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4611,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>4895000</v>
+        <v>4940000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4634,7 +4636,7 @@
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>9790000</v>
+        <v>9880000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4865,7 +4867,7 @@
         <v>2</v>
       </c>
       <c r="F68" s="8" t="n">
-        <v>4320000</v>
+        <v>4270000</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>3620000</v>
@@ -4877,7 +4879,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>4009230</v>
+        <v>3988930</v>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
@@ -4886,11 +4888,11 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>+220,000 ت از رتبه ۳ ترب (+5.4%)</t>
+          <t>+170,000 ت از رتبه ۳ ترب (+4.1%)</t>
         </is>
       </c>
       <c r="M68" s="6" t="n">
-        <v>8640000</v>
+        <v>8540000</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -5572,8 +5574,8 @@
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>3850000</v>
+      <c r="F79" s="8" t="n">
+        <v>3920000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -5587,18 +5589,18 @@
       <c r="J79" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K79" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+65,000 ت از رتبه ۳ ترب (+1.7%)</t>
         </is>
       </c>
       <c r="M79" s="6" t="n">
-        <v>3850000</v>
+        <v>3920000</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -5701,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>6240000</v>
+        <v>6340000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -5722,11 +5724,11 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+140,000 ت از رتبه ۳ ترب (+2.3%)</t>
         </is>
       </c>
       <c r="M81" s="6" t="n">
-        <v>6240000</v>
+        <v>6340000</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -5831,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>12750000</v>
+        <v>12740000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5843,7 +5845,7 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>14500000</v>
+        <v>14490000</v>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
@@ -5852,11 +5854,11 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>+950,000 ت از رتبه ۳ ترب (+8.1%)</t>
+          <t>+940,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>12750000</v>
+        <v>12740000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -5954,8 +5956,8 @@
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>9100000</v>
+      <c r="F85" s="8" t="n">
+        <v>9350000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -5969,18 +5971,18 @@
       <c r="J85" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+1.6%)</t>
         </is>
       </c>
       <c r="M85" s="6" t="n">
-        <v>9100000</v>
+        <v>9350000</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -6163,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>6890000</v>
+        <v>7400000</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>5800000</v>
@@ -6190,7 +6192,7 @@
         </is>
       </c>
       <c r="M88" s="6" t="n">
-        <v>6890000</v>
+        <v>7400000</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -6357,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>4330000</v>
+        <v>4344000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6378,11 +6380,11 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>+380,000 ت از رتبه ۳ ترب (+9.6%)</t>
+          <t>+394,000 ت از رتبه ۳ ترب (+10.0%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>4330000</v>
+        <v>4344000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3170000</v>
+        <v>3220000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6442,11 +6444,11 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>+182,000 ت از رتبه ۳ ترب (+6.1%)</t>
+          <t>+232,000 ت از رتبه ۳ ترب (+7.8%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>3170000</v>
+        <v>3220000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -7204,8 +7206,8 @@
       <c r="E104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="5" t="n">
-        <v>3850000</v>
+      <c r="F104" s="8" t="n">
+        <v>3920000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -7219,18 +7221,18 @@
       <c r="J104" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+65,000 ت از رتبه ۳ ترب (+1.7%)</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>3850000</v>
+        <v>3920000</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -7885,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="8" t="n">
-        <v>10140000</v>
+        <v>10500000</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>9000000</v>
@@ -7906,11 +7908,11 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>+350,000 ت از رتبه ۳ ترب (+3.6%)</t>
+          <t>+710,000 ت از رتبه ۳ ترب (+7.3%)</t>
         </is>
       </c>
       <c r="M114" s="6" t="n">
-        <v>10140000</v>
+        <v>10500000</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -7949,7 +7951,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>9400000</v>
+        <v>9500000</v>
       </c>
       <c r="G115" s="6" t="n">
         <v>8900000</v>
@@ -7976,7 +7978,7 @@
         </is>
       </c>
       <c r="M115" s="6" t="n">
-        <v>9400000</v>
+        <v>9500000</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -8015,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>3170000</v>
+        <v>3220000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8036,11 +8038,11 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>+182,000 ت از رتبه ۳ ترب (+6.1%)</t>
+          <t>+232,000 ت از رتبه ۳ ترب (+7.8%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3170000</v>
+        <v>3220000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8212,8 +8214,8 @@
       <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="5" t="n">
-        <v>7240000</v>
+      <c r="F119" s="8" t="n">
+        <v>9240000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -8227,18 +8229,18 @@
       <c r="J119" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K119" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,751,000 ت از رتبه ۳ ترب (+23.4%)</t>
         </is>
       </c>
       <c r="M119" s="6" t="n">
-        <v>7240000</v>
+        <v>9240000</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -8405,7 +8407,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="8" t="n">
-        <v>11600000</v>
+        <v>11150000</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>10800000</v>
@@ -8426,11 +8428,11 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
         </is>
       </c>
       <c r="M122" s="6" t="n">
-        <v>11600000</v>
+        <v>11150000</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
@@ -8665,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="F126" s="8" t="n">
-        <v>11600000</v>
+        <v>11150000</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>10800000</v>
@@ -8686,11 +8688,11 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>+600,000 ت از رتبه ۳ ترب (+5.5%)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
         </is>
       </c>
       <c r="M126" s="6" t="n">
-        <v>11600000</v>
+        <v>11150000</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -628,7 +628,7 @@
         <v>9250000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9400000</v>
+        <v>9250000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>10400000</v>
@@ -689,7 +689,7 @@
         <v>14590000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>14990000</v>
+        <v>15490000</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>15499000</v>
@@ -699,12 +699,12 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
@@ -820,7 +820,7 @@
         <v>5100000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5200000</v>
+        <v>5150000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5790000</v>
@@ -938,7 +938,7 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="5" t="n">
         <v>3997000</v>
       </c>
       <c r="G7" s="6" t="n">
@@ -948,19 +948,19 @@
         <v>3900000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3995000</v>
+        <v>3997000</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>4500000</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+2,000 ت از رتبه ۳ ترب (+0.1%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
@@ -1002,13 +1002,11 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>1630000</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G8" s="6" t="n">
+        <v>1630000</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1025,14 +1023,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
@@ -1147,7 +1145,7 @@
         <v>9000000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9300000</v>
+        <v>8928000</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
         <v>6799000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8610000</v>
+        <v>8570000</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
@@ -1395,7 +1393,7 @@
         <v>11479000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>21000000</v>
+        <v>20200000</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
@@ -1453,10 +1451,10 @@
         <v>5800000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6300000</v>
+        <v>6240000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6300000</v>
+        <v>6290000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7780000</v>
@@ -1510,29 +1508,29 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="8" t="n">
         <v>4490000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4205000</v>
       </c>
       <c r="H16" s="6" t="n">
+        <v>4440000</v>
+      </c>
+      <c r="I16" s="6" t="n">
         <v>4480000</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>4500000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+10,000 ت از رتبه ۳ ترب (+0.2%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1644,7 +1642,7 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="5" t="n">
         <v>9750000</v>
       </c>
       <c r="G18" s="6" t="n">
@@ -1654,21 +1652,21 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9500000</v>
+        <v>9750000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>+250,000 ت از رتبه ۳ ترب (+2.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
@@ -1723,7 +1721,7 @@
         <v>9000000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9300000</v>
+        <v>8928000</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1774,11 +1772,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="5" t="n">
         <v>3580000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4200000</v>
+        <v>3580000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -1791,14 +1789,14 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>-299,000 ت از کف ترب (-7.7%)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M20" s="6" t="n">
@@ -1853,7 +1851,7 @@
         <v>6799000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8610000</v>
+        <v>8570000</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1972,29 +1970,29 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="8" t="n">
         <v>12140000</v>
       </c>
       <c r="G23" s="6" t="n">
+        <v>6890000</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>7500000</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="6" t="n">
         <v>8090000</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>16200000</v>
-      </c>
       <c r="J23" s="6" t="n">
-        <v>7190000</v>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>7150000</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+4,050,000 ت از رتبه ۳ ترب (+50.1%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
@@ -2043,13 +2041,13 @@
         <v>5616000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5650000</v>
+        <v>5649000</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>5650000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7599000</v>
+        <v>6544400</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -2224,29 +2222,29 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="11" t="n">
         <v>15000000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>12680000</v>
+        <v>15300000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14500000</v>
+        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>15500000</v>
+        <v>20500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>-300,000 ت از کف ترب (-2.0%)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
@@ -2284,16 +2282,14 @@
       <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="5" t="n">
         <v>6530000</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>6500000</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="H28" s="6" t="n">
+        <v>6530000</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2305,14 +2301,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M28" s="6" t="n">
@@ -2484,29 +2480,29 @@
       <c r="E31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="11" t="n">
         <v>11940000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>11800000</v>
+        <v>12000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>11890000</v>
+        <v>12000000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>12000000</v>
+        <v>12800000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>29990000</v>
       </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>-60,000 ت از کف ترب (-0.5%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2622,7 +2618,7 @@
         <v>5999000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6000000</v>
+        <v>5999500</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2922,29 +2918,29 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="8" t="n">
         <v>14070000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>11890000</v>
       </c>
       <c r="H38" s="6" t="n">
+        <v>13220000</v>
+      </c>
+      <c r="I38" s="6" t="n">
         <v>13250000</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>14900000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+820,000 ت از رتبه ۳ ترب (+6.2%)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
@@ -2986,7 +2982,7 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="5" t="n">
         <v>3997000</v>
       </c>
       <c r="G39" s="6" t="n">
@@ -2996,19 +2992,19 @@
         <v>3900000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3995000</v>
+        <v>3997000</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>4500000</v>
       </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+2,000 ت از رتبه ۳ ترب (+0.1%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
@@ -3112,7 +3108,7 @@
         <v>13500000</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>10000000</v>
+        <v>12000000</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>13500000</v>
@@ -3176,16 +3172,14 @@
       <c r="E42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="5" t="n">
         <v>3170000</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>3150000</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="H42" s="6" t="n">
+        <v>3170000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3197,14 +3191,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M42" s="6" t="n">
@@ -3242,7 +3236,7 @@
       <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="F43" s="5" t="n">
         <v>7294000</v>
       </c>
       <c r="G43" s="6" t="n">
@@ -3252,19 +3246,19 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
+        <v>7294000</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>8000000</v>
       </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+5,000 ت از رتبه ۳ ترب (+0.1%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3517,7 +3511,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7599000</v>
+        <v>6544400</v>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
@@ -4237,7 +4231,7 @@
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>8091000</v>
+        <v>7911200</v>
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
@@ -4493,7 +4487,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4390000</v>
+        <v>4695100</v>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
@@ -4559,7 +4553,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>19100000</v>
+        <v>19000000</v>
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
@@ -4879,7 +4873,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3988930</v>
+        <v>3910330</v>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
@@ -5587,7 +5581,7 @@
         <v>3855000</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>4630000</v>
+        <v>4120000</v>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
@@ -6371,7 +6365,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4390000</v>
+        <v>4695100</v>
       </c>
       <c r="K91" s="9" t="inlineStr">
         <is>
@@ -6435,7 +6429,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3324700</v>
+        <v>3332090</v>
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
@@ -7219,7 +7213,7 @@
         <v>3855000</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>4630000</v>
+        <v>4120000</v>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
@@ -7283,7 +7277,7 @@
         <v>4699000</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>5300000</v>
+        <v>7100000</v>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
@@ -8029,7 +8023,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3324700</v>
+        <v>3332090</v>
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
@@ -9153,7 +9147,7 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>7190000</v>
+        <v>7150000</v>
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -57,12 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEE2E2"/>
         <bgColor rgb="00FEE2E2"/>
       </patternFill>
@@ -71,6 +65,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E8FF"/>
         <bgColor rgb="00F3E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -619,7 +619,7 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9250000</v>
+        <v>9990000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9200000</v>
@@ -628,23 +628,23 @@
         <v>9250000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9250000</v>
+        <v>9400000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10400000</v>
+        <v>10580000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+590,000 ت از رتبه ۳ ترب (+6.3%)</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1748250000</v>
+        <v>1888110000</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>15240000</v>
+        <v>16734000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>14590000</v>
@@ -692,23 +692,23 @@
         <v>15490000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15499000</v>
+        <v>15840000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>15490000</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+894,000 ت از رتبه ۳ ترب (+5.6%)</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>960120000</v>
+        <v>1054242000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -746,14 +746,14 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>13500000</v>
+      <c r="F4" s="5" t="n">
+        <v>14580000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>12870000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12899000</v>
+        <v>12990000</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>12990000</v>
@@ -761,18 +761,18 @@
       <c r="J4" s="6" t="n">
         <v>12990000</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>+510,000 ت از رتبه ۳ ترب (+3.9%)</t>
+          <t>+1,590,000 ت از رتبه ۳ ترب (+12.2%)</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>405000000</v>
+        <v>437400000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5150000</v>
+        <v>5530000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5000000</v>
@@ -820,23 +820,23 @@
         <v>5100000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5150000</v>
+        <v>5200000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5790000</v>
+        <v>5799000</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+330,000 ت از رتبه ۳ ترب (+6.3%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>92700000</v>
+        <v>99540000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6500000</v>
+        <v>7020000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>6550000</v>
@@ -891,16 +891,16 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>+131,000 ت از رتبه ۳ ترب (+1.9%)</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>110500000</v>
+        <v>119340000</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -939,32 +939,32 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>3997000</v>
+        <v>4255000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3800000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3997000</v>
+        <v>4000000</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>4500000</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+255,000 ت از رتبه ۳ ترب (+6.4%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>59955000</v>
+        <v>63825000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       <c r="B8" s="2" t="n">
         <v>2144</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1002,11 +1002,11 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>1630000</v>
+      <c r="F8" s="9" t="n">
+        <v>1760000</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1630000</v>
+        <v>1760000</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>21190000</v>
+        <v>22880000</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="9" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
@@ -1087,7 +1087,7 @@
       <c r="J9" s="6" t="n">
         <v>195000</v>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -1133,7 +1133,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>9000000</v>
+        <v>9936000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>8900000</v>
@@ -1149,16 +1149,16 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+936,000 ت از رتبه ۳ ترب (+10.4%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>99000000</v>
+        <v>109296000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1196,8 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>6830000</v>
+      <c r="F11" s="5" t="n">
+        <v>7376000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6600000</v>
@@ -1211,18 +1211,18 @@
       <c r="J11" s="6" t="n">
         <v>8570000</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+577,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>75130000</v>
+        <v>81136000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       <c r="B12" s="2" t="n">
         <v>2121</v>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1261,7 +1261,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4600000</v>
+        <v>4936000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4300000</v>
@@ -1270,23 +1270,23 @@
         <v>4500000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4700000</v>
+        <v>4653000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5100000</v>
+        <v>5500000</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+283,000 ت از رتبه ۳ ترب (+6.1%)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>46000000</v>
+        <v>49360000</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>12000000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>12400000</v>
+        <v>12800000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
@@ -1367,7 +1367,7 @@
       <c r="B14" s="2" t="n">
         <v>1953</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1380,33 +1380,33 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>17960000</v>
+      <c r="F14" s="5" t="n">
+        <v>19510000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11200000</v>
+        <v>11480000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11450000</v>
+        <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11479000</v>
+        <v>11690000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>20200000</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
+        <v>19800000</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+6,481,000 ت از رتبه ۳ ترب (+56.5%)</t>
+          <t>+7,820,000 ت از رتبه ۳ ترب (+66.9%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>143680000</v>
+        <v>156080000</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1445,32 +1445,32 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6240000</v>
+        <v>6799000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>5800000</v>
+        <v>6230000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6240000</v>
+        <v>6300000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6290000</v>
+        <v>6300000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7780000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+499,000 ت از رتبه ۳ ترب (+7.9%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>43680000</v>
+        <v>47593000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
       <c r="B16" s="2" t="n">
         <v>1964</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1508,33 +1508,33 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>4490000</v>
+      <c r="F16" s="5" t="n">
+        <v>4844000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4205000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4440000</v>
+        <v>4480000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4480000</v>
+        <v>4500000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+10,000 ت از رتبه ۳ ترب (+0.2%)</t>
+          <t>+344,000 ت از رتبه ۳ ترب (+7.6%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>31430000</v>
+        <v>33908000</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       <c r="B18" s="2" t="n">
         <v>1962</v>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1642,8 +1642,8 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>9750000</v>
+      <c r="F18" s="9" t="n">
+        <v>10390000</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>9250000</v>
@@ -1652,14 +1652,14 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9750000</v>
+        <v>10390000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>58500000</v>
+        <v>62340000</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
       <c r="B19" s="2" t="n">
         <v>1814</v>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1709,7 +1709,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>9000000</v>
+        <v>9936000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>8900000</v>
@@ -1725,16 +1725,16 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+936,000 ت از رتبه ۳ ترب (+10.4%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>54000000</v>
+        <v>59616000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       <c r="B20" s="2" t="n">
         <v>2559</v>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1772,11 +1772,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>3580000</v>
+      <c r="F20" s="9" t="n">
+        <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3580000</v>
+        <v>3866000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -1789,7 +1789,7 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>21480000</v>
+        <v>23196000</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1838,8 +1838,8 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>6830000</v>
+      <c r="F21" s="5" t="n">
+        <v>7376000</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>6600000</v>
@@ -1853,18 +1853,18 @@
       <c r="J21" s="6" t="n">
         <v>8570000</v>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+577,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>34150000</v>
+        <v>36880000</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1902,8 +1902,8 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>14470000</v>
+      <c r="F22" s="5" t="n">
+        <v>15628000</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>14400000</v>
@@ -1919,20 +1919,20 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16590000</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>16890000</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+1,228,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>72350000</v>
+        <v>78140000</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1970,11 +1970,11 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>12140000</v>
+      <c r="F23" s="5" t="n">
+        <v>8413000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>6890000</v>
+        <v>7150000</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>7500000</v>
@@ -1983,20 +1983,20 @@
         <v>8090000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
+        <v>7000000</v>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>+4,050,000 ت از رتبه ۳ ترب (+50.1%)</t>
+          <t>+323,000 ت از رتبه ۳ ترب (+4.0%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>60700000</v>
+        <v>42065000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       <c r="B24" s="2" t="n">
         <v>1714</v>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2034,33 +2034,33 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>5770000</v>
+      <c r="F24" s="5" t="n">
+        <v>6080000</v>
       </c>
       <c r="G24" s="6" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>5616000</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>5649000</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>5650000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6544400</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+        <v>7542200</v>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه ۳ ترب (+2.1%)</t>
+          <t>+430,000 ت از رتبه ۳ ترب (+7.6%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>28850000</v>
+        <v>30400000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       <c r="B25" s="2" t="n">
         <v>2071</v>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2098,33 +2098,33 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>8960000</v>
+      <c r="F25" s="5" t="n">
+        <v>11900000</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>5590000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6500000</v>
+        <v>6980000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6980000</v>
+        <v>7000000</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>13890000</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+1,980,000 ت از رتبه ۳ ترب (+28.4%)</t>
+          <t>+4,900,000 ت از رتبه ۳ ترب (+70.0%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>44800000</v>
+        <v>59500000</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       <c r="B26" s="2" t="n">
         <v>1994</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2162,33 +2162,33 @@
       <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>10210000</v>
+      <c r="F26" s="5" t="n">
+        <v>13560000</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>7400000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7500000</v>
+        <v>7980000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7980000</v>
+        <v>8270000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>+2,230,000 ت از رتبه ۳ ترب (+27.9%)</t>
+          <t>+5,290,000 ت از رتبه ۳ ترب (+64.0%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>51050000</v>
+        <v>67800000</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       <c r="B27" s="2" t="n">
         <v>2420</v>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2222,33 +2222,33 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>15000000</v>
+      <c r="F27" s="5" t="n">
+        <v>16632000</v>
       </c>
       <c r="G27" s="6" t="n">
+        <v>12680000</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>15300000</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>15500000</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>20500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>-300,000 ت از کف ترب (-2.0%)</t>
+          <t>+1,132,000 ت از رتبه ۳ ترب (+7.3%)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>75000000</v>
+        <v>83160000</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       <c r="B28" s="2" t="n">
         <v>2167</v>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2282,14 +2282,14 @@
       <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>6530000</v>
+      <c r="F28" s="9" t="n">
+        <v>7085000</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>6530000</v>
+        <v>7085000</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>32650000</v>
+        <v>35425000</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -2350,8 +2350,8 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>4940000</v>
+      <c r="F29" s="5" t="n">
+        <v>5335000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>4890000</v>
@@ -2363,20 +2363,20 @@
         <v>4900000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>6150000</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
+        <v>6250000</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.8%)</t>
+          <t>+435,000 ت از رتبه ۳ ترب (+8.9%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>19760000</v>
+        <v>21340000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       <c r="B31" s="2" t="n">
         <v>1759</v>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2480,33 +2480,33 @@
       <c r="E31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>11940000</v>
+      <c r="F31" s="5" t="n">
+        <v>14332000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12000000</v>
+        <v>12800000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>12000000</v>
+        <v>13700000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>12800000</v>
+        <v>13750000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>29990000</v>
       </c>
-      <c r="K31" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>-60,000 ت از کف ترب (-0.5%)</t>
+          <t>+582,000 ت از رتبه ۳ ترب (+4.2%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>47760000</v>
+        <v>57328000</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       <c r="B32" s="2" t="n">
         <v>1862</v>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2544,8 +2544,8 @@
       <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>11150000</v>
+      <c r="F32" s="5" t="n">
+        <v>12528000</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>10950000</v>
@@ -2554,23 +2554,23 @@
         <v>11000000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11000000</v>
+        <v>11097000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
+          <t>+1,431,000 ت از رتبه ۳ ترب (+12.9%)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>44600000</v>
+        <v>50112000</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>5999500</v>
+        <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>5400000</v>
@@ -2618,7 +2618,7 @@
         <v>5999000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>5999500</v>
+        <v>6000000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2627,16 +2627,16 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+479,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>17998500</v>
+        <v>19437000</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
       <c r="B34" s="2" t="n">
         <v>1930</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2675,13 +2675,13 @@
         <v>3</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>8650000</v>
+        <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>6900000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>8600000</v>
+        <v>6900000</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>8700000</v>
@@ -2691,16 +2691,16 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+642,000 ت از رتبه ۳ ترب (+7.4%)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
-        <v>25950000</v>
+        <v>28026000</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       <c r="B35" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2734,7 +2734,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="9" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -2753,7 +2753,7 @@
       <c r="J35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -2777,7 +2777,7 @@
       <c r="B36" s="2" t="n">
         <v>1958</v>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2790,11 +2790,11 @@
       <c r="E36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>7000000</v>
+      <c r="F36" s="5" t="n">
+        <v>7528000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>6950000</v>
@@ -2803,20 +2803,20 @@
         <v>6950000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
+        <v>7400000</v>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>21000000</v>
+        <v>22584000</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
       <c r="B37" s="2" t="n">
         <v>1958</v>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2854,11 +2854,11 @@
       <c r="E37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="8" t="n">
-        <v>7000000</v>
+      <c r="F37" s="5" t="n">
+        <v>7528000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>6950000</v>
@@ -2867,20 +2867,20 @@
         <v>6950000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="K37" s="9" t="inlineStr">
+        <v>7400000</v>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
         </is>
       </c>
       <c r="M37" s="6" t="n">
-        <v>21000000</v>
+        <v>22584000</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       <c r="B38" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2918,33 +2918,33 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>14070000</v>
+      <c r="F38" s="9" t="n">
+        <v>14753000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>11890000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>13220000</v>
+        <v>13250000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13250000</v>
+        <v>14753000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>+820,000 ت از رتبه ۳ ترب (+6.2%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>42210000</v>
+        <v>44259000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
       <c r="B39" s="2" t="n">
         <v>1753</v>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2983,32 +2983,32 @@
         <v>3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3997000</v>
+        <v>4255000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>3800000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3997000</v>
+        <v>4000000</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>4500000</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+255,000 ت از رتبه ۳ ترب (+6.4%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>11991000</v>
+        <v>12765000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       <c r="B40" s="2" t="n">
         <v>2420</v>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3046,8 +3046,8 @@
       <c r="E40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>15000000</v>
+      <c r="F40" s="5" t="n">
+        <v>16632000</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>8300000</v>
@@ -3063,18 +3063,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>+4,500,000 ت از رتبه ۳ ترب (+42.9%)</t>
+          <t>+6,132,000 ت از رتبه ۳ ترب (+58.4%)</t>
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>45000000</v>
+        <v>49896000</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       <c r="B41" s="2" t="n">
         <v>1980</v>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3105,7 +3105,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>13500000</v>
+        <v>14580000</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>12000000</v>
@@ -3125,16 +3125,16 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+1,080,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>40500000</v>
+        <v>43740000</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
       <c r="B42" s="2" t="n">
         <v>2139</v>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3172,14 +3172,14 @@
       <c r="E42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>3170000</v>
+      <c r="F42" s="9" t="n">
+        <v>3445000</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>3150000</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3170000</v>
+        <v>3445000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="M42" s="6" t="n">
-        <v>9510000</v>
+        <v>10335000</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       <c r="B43" s="2" t="n">
         <v>2133</v>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3237,7 +3237,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>7294000</v>
+        <v>7970000</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>6980000</v>
@@ -3246,23 +3246,23 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7294000</v>
+        <v>7485000</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>8000000</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+485,000 ت از رتبه ۳ ترب (+6.5%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
-        <v>21882000</v>
+        <v>23910000</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
       <c r="B44" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3373,7 +3373,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>7560000</v>
+        <v>8132000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -3382,7 +3382,7 @@
         <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7600000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3391,16 +3391,16 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+532,000 ت از رتبه ۳ ترب (+7.0%)</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
-        <v>15120000</v>
+        <v>16264000</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="9" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
@@ -3453,7 +3453,7 @@
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -3498,8 +3498,8 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>5770000</v>
+      <c r="F47" s="5" t="n">
+        <v>6080000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3511,20 +3511,20 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>6544400</v>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
+        <v>7542200</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+72,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>+382,000 ت از رتبه ۳ ترب (+6.7%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>11540000</v>
+        <v>12160000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>8700000</v>
+        <v>9396000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -3579,16 +3579,16 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>+296,000 ت از رتبه ۳ ترب (+3.3%)</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>17400000</v>
+        <v>18792000</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3626,8 +3626,8 @@
       <c r="E49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>3170000</v>
+      <c r="F49" s="5" t="n">
+        <v>3455000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -3641,18 +3641,18 @@
       <c r="J49" s="6" t="n">
         <v>3800000</v>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+305,000 ت از رتبه ۳ ترب (+9.7%)</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>6340000</v>
+        <v>6910000</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3690,8 +3690,8 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>7340000</v>
+      <c r="F50" s="5" t="n">
+        <v>7927000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -3707,18 +3707,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>+490,000 ت از رتبه ۳ ترب (+7.2%)</t>
+          <t>+1,077,000 ت از رتبه ۳ ترب (+15.7%)</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">
-        <v>14680000</v>
+        <v>15854000</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3756,8 +3756,8 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="8" t="n">
-        <v>14070000</v>
+      <c r="F51" s="5" t="n">
+        <v>14753000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3771,18 +3771,18 @@
       <c r="J51" s="6" t="n">
         <v>16750000</v>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>+1,170,000 ت از رتبه ۳ ترب (+9.1%)</t>
+          <t>+1,853,000 ت از رتبه ۳ ترب (+14.4%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>28140000</v>
+        <v>29506000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>11200000</v>
+        <v>12366000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -3837,16 +3837,16 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+866,000 ت از رتبه ۳ ترب (+7.5%)</t>
         </is>
       </c>
       <c r="M52" s="6" t="n">
-        <v>22400000</v>
+        <v>24732000</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3884,8 +3884,8 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="8" t="n">
-        <v>9240000</v>
+      <c r="F53" s="5" t="n">
+        <v>9439000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -3899,18 +3899,18 @@
       <c r="J53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>+1,751,000 ت از رتبه ۳ ترب (+23.4%)</t>
+          <t>+1,950,000 ت از رتبه ۳ ترب (+26.0%)</t>
         </is>
       </c>
       <c r="M53" s="6" t="n">
-        <v>18480000</v>
+        <v>18878000</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -4022,8 +4022,8 @@
       <c r="E55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>9970000</v>
+      <c r="F55" s="9" t="n">
+        <v>10768000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -4037,7 +4037,7 @@
       <c r="J55" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="M55" s="6" t="n">
-        <v>19940000</v>
+        <v>21536000</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>5950000</v>
+        <v>6426000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4105,16 +4105,16 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+476,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>11900000</v>
+        <v>12852000</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       <c r="B57" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4201,7 +4201,7 @@
       <c r="B58" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4214,7 +4214,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="9" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -4233,7 +4233,7 @@
       <c r="J58" s="6" t="n">
         <v>7911200</v>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -4265,7 +4265,7 @@
       <c r="B59" s="2" t="n">
         <v>1775</v>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4278,8 +4278,8 @@
       <c r="E59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="8" t="n">
-        <v>8300000</v>
+      <c r="F59" s="5" t="n">
+        <v>9958000</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>4600000</v>
@@ -4291,20 +4291,20 @@
         <v>6800000</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
+        <v>9700000</v>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>+1,500,000 ت از رتبه ۳ ترب (+22.1%)</t>
+          <t>+3,158,000 ت از رتبه ۳ ترب (+46.4%)</t>
         </is>
       </c>
       <c r="M59" s="6" t="n">
-        <v>16600000</v>
+        <v>19916000</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
       <c r="B60" s="2" t="n">
         <v>1902</v>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4343,7 +4343,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>5750000</v>
+        <v>6199000</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>6460000</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7099000</v>
+        <v>7299000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4366,11 +4366,11 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>-710,000 ت از کف ترب (-11.0%)</t>
+          <t>-261,000 ت از کف ترب (-4.0%)</t>
         </is>
       </c>
       <c r="M60" s="6" t="n">
-        <v>11500000</v>
+        <v>12398000</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
       <c r="B61" s="2" t="n">
         <v>3231</v>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4408,8 +4408,8 @@
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="8" t="n">
-        <v>21690000</v>
+      <c r="F61" s="5" t="n">
+        <v>13424000</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>8500000</v>
@@ -4425,18 +4425,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>+12,690,000 ت از رتبه ۳ ترب (+141.0%)</t>
+          <t>+4,424,000 ت از رتبه ۳ ترب (+49.2%)</t>
         </is>
       </c>
       <c r="M61" s="6" t="n">
-        <v>43380000</v>
+        <v>26848000</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
       <c r="B62" s="2" t="n">
         <v>2092</v>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4474,8 +4474,8 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="8" t="n">
-        <v>4344000</v>
+      <c r="F62" s="5" t="n">
+        <v>4828000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4487,20 +4487,20 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4695100</v>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
+        <v>4694800</v>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+394,000 ت از رتبه ۳ ترب (+10.0%)</t>
+          <t>+878,000 ت از رتبه ۳ ترب (+22.2%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>8688000</v>
+        <v>9656000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       <c r="B63" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4538,8 +4538,8 @@
       <c r="E63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="8" t="n">
-        <v>22080000</v>
+      <c r="F63" s="5" t="n">
+        <v>23846000</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>21500000</v>
@@ -4555,18 +4555,18 @@
       <c r="J63" s="6" t="n">
         <v>19000000</v>
       </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+0.4%)</t>
+          <t>+1,846,000 ت از رتبه ۳ ترب (+8.4%)</t>
         </is>
       </c>
       <c r="M63" s="6" t="n">
-        <v>44160000</v>
+        <v>47692000</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       <c r="B64" s="2" t="n">
         <v>1819</v>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4605,7 +4605,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>4940000</v>
+        <v>5335000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4617,20 +4617,20 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>6150000</v>
+        <v>6250000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>9880000</v>
+        <v>10670000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       <c r="B65" s="2" t="n">
         <v>2066</v>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4669,7 +4669,7 @@
         <v>2</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>2650000</v>
+        <v>2862000</v>
       </c>
       <c r="G65" s="6" t="n">
         <v>2300000</v>
@@ -4687,16 +4687,16 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+62,000 ت از رتبه ۳ ترب (+2.2%)</t>
         </is>
       </c>
       <c r="M65" s="6" t="n">
-        <v>5300000</v>
+        <v>5724000</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
       <c r="B66" s="2" t="n">
         <v>1942</v>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4735,7 +4735,7 @@
         <v>2</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>15600000</v>
+        <v>16848000</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>14500000</v>
@@ -4751,16 +4751,16 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+848,000 ت از رتبه ۳ ترب (+5.3%)</t>
         </is>
       </c>
       <c r="M66" s="6" t="n">
-        <v>31200000</v>
+        <v>33696000</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
       <c r="B67" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="C67" s="10" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4790,8 +4790,8 @@
       <c r="E67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="8" t="n">
-        <v>6880000</v>
+      <c r="F67" s="5" t="n">
+        <v>7430000</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>3980000</v>
@@ -4811,18 +4811,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>+2,900,000 ت از رتبه ۳ ترب (+72.9%)</t>
+          <t>+3,450,000 ت از رتبه ۳ ترب (+86.7%)</t>
         </is>
       </c>
       <c r="M67" s="6" t="n">
-        <v>13760000</v>
+        <v>14860000</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
       <c r="B68" s="2" t="n">
         <v>3240</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4860,8 +4860,8 @@
       <c r="E68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="8" t="n">
-        <v>4270000</v>
+      <c r="F68" s="5" t="n">
+        <v>4612000</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>3620000</v>
@@ -4875,18 +4875,18 @@
       <c r="J68" s="6" t="n">
         <v>3910330</v>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>+170,000 ت از رتبه ۳ ترب (+4.1%)</t>
+          <t>+512,000 ت از رتبه ۳ ترب (+12.5%)</t>
         </is>
       </c>
       <c r="M68" s="6" t="n">
-        <v>8540000</v>
+        <v>9224000</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
       <c r="B69" s="2" t="n">
         <v>2009</v>
       </c>
-      <c r="C69" s="10" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4924,8 +4924,8 @@
       <c r="E69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>13290000</v>
+      <c r="F69" s="9" t="n">
+        <v>14353000</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>10000000</v>
@@ -4941,7 +4941,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K69" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="M69" s="6" t="n">
-        <v>26580000</v>
+        <v>28706000</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
       <c r="B70" s="2" t="n">
         <v>1885</v>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4990,8 +4990,8 @@
       <c r="E70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="8" t="n">
-        <v>8320000</v>
+      <c r="F70" s="5" t="n">
+        <v>8986000</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>7200000</v>
@@ -5009,18 +5009,18 @@
       <c r="J70" s="6" t="n">
         <v>15000000</v>
       </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>+1,120,000 ت از رتبه ۳ ترب (+15.6%)</t>
+          <t>+1,786,000 ت از رتبه ۳ ترب (+24.8%)</t>
         </is>
       </c>
       <c r="M70" s="6" t="n">
-        <v>16640000</v>
+        <v>17972000</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
       <c r="B71" s="2" t="n">
         <v>1991</v>
       </c>
-      <c r="C71" s="10" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5058,8 +5058,8 @@
       <c r="E71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="8" t="n">
-        <v>7240000</v>
+      <c r="F71" s="5" t="n">
+        <v>7819000</v>
       </c>
       <c r="G71" s="6" t="n">
         <v>6400000</v>
@@ -5075,18 +5075,18 @@
       <c r="J71" s="6" t="n">
         <v>9700000</v>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+619,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M71" s="6" t="n">
-        <v>14480000</v>
+        <v>15638000</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       <c r="B72" s="2" t="n">
         <v>1914</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5125,7 +5125,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>17090000</v>
+        <v>18457000</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>11000000</v>
@@ -5145,16 +5145,16 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+957,000 ت از رتبه ۳ ترب (+5.5%)</t>
         </is>
       </c>
       <c r="M72" s="6" t="n">
-        <v>34180000</v>
+        <v>36914000</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
       <c r="B73" s="2" t="n">
         <v>2127</v>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C73" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5193,7 +5193,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>3699500</v>
+        <v>4018000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -5205,20 +5205,20 @@
         <v>3890000</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>5050000</v>
+        <v>4876910</v>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+128,000 ت از رتبه ۳ ترب (+3.3%)</t>
         </is>
       </c>
       <c r="M73" s="6" t="n">
-        <v>7399000</v>
+        <v>8036000</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>9200000</v>
+        <v>9936000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -5273,16 +5273,16 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M74" s="6" t="n">
-        <v>9200000</v>
+        <v>9936000</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -5320,8 +5320,8 @@
       <c r="E75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="8" t="n">
-        <v>17500000</v>
+      <c r="F75" s="5" t="n">
+        <v>18900000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -5335,18 +5335,18 @@
       <c r="J75" s="6" t="n">
         <v>23900000</v>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>+15,055,000 ت از رتبه ۳ ترب (+615.7%)</t>
+          <t>+16,455,000 ت از رتبه ۳ ترب (+673.0%)</t>
         </is>
       </c>
       <c r="M75" s="6" t="n">
-        <v>17500000</v>
+        <v>18900000</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -5380,8 +5380,8 @@
       <c r="E76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="8" t="n">
-        <v>24000000</v>
+      <c r="F76" s="5" t="n">
+        <v>25920000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -5395,18 +5395,18 @@
       <c r="J76" s="6" t="n">
         <v>36400000</v>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>+8,400,000 ت از رتبه ۳ ترب (+53.8%)</t>
+          <t>+10,320,000 ت از رتبه ۳ ترب (+66.2%)</t>
         </is>
       </c>
       <c r="M76" s="6" t="n">
-        <v>24000000</v>
+        <v>25920000</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -5440,8 +5440,8 @@
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>9300000</v>
+      <c r="F77" s="5" t="n">
+        <v>10044000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -5455,18 +5455,18 @@
       <c r="J77" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>+100,000 ت از رتبه ۳ ترب (+1.1%)</t>
+          <t>+844,000 ت از رتبه ۳ ترب (+9.2%)</t>
         </is>
       </c>
       <c r="M77" s="6" t="n">
-        <v>9300000</v>
+        <v>10044000</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>9200000</v>
+        <v>9936000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -5521,16 +5521,16 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M78" s="6" t="n">
-        <v>9200000</v>
+        <v>9936000</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -5568,8 +5568,8 @@
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="8" t="n">
-        <v>3920000</v>
+      <c r="F79" s="5" t="n">
+        <v>4234000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -5583,18 +5583,18 @@
       <c r="J79" s="6" t="n">
         <v>4120000</v>
       </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>+65,000 ت از رتبه ۳ ترب (+1.7%)</t>
+          <t>+379,000 ت از رتبه ۳ ترب (+9.8%)</t>
         </is>
       </c>
       <c r="M79" s="6" t="n">
-        <v>3920000</v>
+        <v>4234000</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -5632,8 +5632,8 @@
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="8" t="n">
-        <v>14999000</v>
+      <c r="F80" s="5" t="n">
+        <v>16199000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -5647,18 +5647,18 @@
       <c r="J80" s="6" t="n">
         <v>24400000</v>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>+9,000 ت از رتبه ۳ ترب (+0.1%)</t>
+          <t>+1,209,000 ت از رتبه ۳ ترب (+8.1%)</t>
         </is>
       </c>
       <c r="M80" s="6" t="n">
-        <v>14999000</v>
+        <v>16199000</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -5696,8 +5696,8 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="8" t="n">
-        <v>6340000</v>
+      <c r="F81" s="5" t="n">
+        <v>6799000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -5711,18 +5711,18 @@
       <c r="J81" s="6" t="n">
         <v>7780000</v>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>+140,000 ت از رتبه ۳ ترب (+2.3%)</t>
+          <t>+599,000 ت از رتبه ۳ ترب (+9.7%)</t>
         </is>
       </c>
       <c r="M81" s="6" t="n">
-        <v>6340000</v>
+        <v>6799000</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -5760,8 +5760,8 @@
       <c r="E82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="8" t="n">
-        <v>5980000</v>
+      <c r="F82" s="5" t="n">
+        <v>6458000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -5777,18 +5777,18 @@
       <c r="J82" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+508,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M82" s="6" t="n">
-        <v>5980000</v>
+        <v>6458000</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -5826,8 +5826,8 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="8" t="n">
-        <v>12740000</v>
+      <c r="F83" s="5" t="n">
+        <v>14035000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5841,18 +5841,18 @@
       <c r="J83" s="6" t="n">
         <v>14490000</v>
       </c>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>+940,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+2,235,000 ت از رتبه ۳ ترب (+18.9%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>12740000</v>
+        <v>14035000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -5890,8 +5890,8 @@
       <c r="E84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F84" s="8" t="n">
-        <v>2700000</v>
+      <c r="F84" s="5" t="n">
+        <v>2916000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -5905,18 +5905,18 @@
       <c r="J84" s="6" t="n">
         <v>3795000</v>
       </c>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>+255,000 ت از رتبه ۳ ترب (+10.4%)</t>
+          <t>+471,000 ت از رتبه ۳ ترب (+19.3%)</t>
         </is>
       </c>
       <c r="M84" s="6" t="n">
-        <v>2700000</v>
+        <v>2916000</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -5950,8 +5950,8 @@
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="8" t="n">
-        <v>9350000</v>
+      <c r="F85" s="5" t="n">
+        <v>10098000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -5965,18 +5965,18 @@
       <c r="J85" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه ۳ ترب (+1.6%)</t>
+          <t>+898,000 ت از رتبه ۳ ترب (+9.8%)</t>
         </is>
       </c>
       <c r="M85" s="6" t="n">
-        <v>9350000</v>
+        <v>10098000</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -6088,8 +6088,8 @@
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="8" t="n">
-        <v>4220000</v>
+      <c r="F87" s="5" t="n">
+        <v>4558000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -6109,18 +6109,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+358,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M87" s="6" t="n">
-        <v>4220000</v>
+        <v>4558000</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>7400000</v>
+        <v>7992000</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>5800000</v>
@@ -6177,16 +6177,16 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+203,000 ت از رتبه ۳ ترب (+2.6%)</t>
         </is>
       </c>
       <c r="M88" s="6" t="n">
-        <v>7400000</v>
+        <v>7992000</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -6224,8 +6224,8 @@
       <c r="E89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="8" t="n">
-        <v>7000000</v>
+      <c r="F89" s="5" t="n">
+        <v>7528000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -6237,20 +6237,20 @@
         <v>6950000</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="K89" s="9" t="inlineStr">
+        <v>7400000</v>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
         </is>
       </c>
       <c r="M89" s="6" t="n">
-        <v>7000000</v>
+        <v>7528000</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -6288,8 +6288,8 @@
       <c r="E90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="8" t="n">
-        <v>7000000</v>
+      <c r="F90" s="5" t="n">
+        <v>7528000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -6301,20 +6301,20 @@
         <v>6950000</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="K90" s="9" t="inlineStr">
+        <v>7400000</v>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
         </is>
       </c>
       <c r="M90" s="6" t="n">
-        <v>7000000</v>
+        <v>7528000</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
@@ -6352,8 +6352,8 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="8" t="n">
-        <v>4344000</v>
+      <c r="F91" s="5" t="n">
+        <v>4828000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6365,20 +6365,20 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4695100</v>
-      </c>
-      <c r="K91" s="9" t="inlineStr">
+        <v>4694800</v>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>+394,000 ت از رتبه ۳ ترب (+10.0%)</t>
+          <t>+878,000 ت از رتبه ۳ ترب (+22.2%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>4344000</v>
+        <v>4828000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6416,8 +6416,8 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="8" t="n">
-        <v>3220000</v>
+      <c r="F92" s="5" t="n">
+        <v>3499000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6429,20 +6429,20 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3332090</v>
-      </c>
-      <c r="K92" s="9" t="inlineStr">
+        <v>3621200</v>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>+232,000 ت از رتبه ۳ ترب (+7.8%)</t>
+          <t>+511,000 ت از رتبه ۳ ترب (+17.1%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>3220000</v>
+        <v>3499000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -6480,8 +6480,8 @@
       <c r="E93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="8" t="n">
-        <v>7050000</v>
+      <c r="F93" s="5" t="n">
+        <v>7571000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -6495,18 +6495,18 @@
       <c r="J93" s="6" t="n">
         <v>8600000</v>
       </c>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="K93" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>+130,000 ت از رتبه ۳ ترب (+1.9%)</t>
+          <t>+651,000 ت از رتبه ۳ ترب (+9.4%)</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
-        <v>7050000</v>
+        <v>7571000</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -6544,8 +6544,8 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="8" t="n">
-        <v>5920000</v>
+      <c r="F94" s="5" t="n">
+        <v>6394000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -6563,18 +6563,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K94" s="9" t="inlineStr">
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+505,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M94" s="6" t="n">
-        <v>5920000</v>
+        <v>6394000</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>21350000</v>
+        <v>23058000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -6629,16 +6629,16 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,708,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M95" s="6" t="n">
-        <v>21350000</v>
+        <v>23058000</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -6676,8 +6676,8 @@
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="8" t="n">
-        <v>4520000</v>
+      <c r="F96" s="5" t="n">
+        <v>4882000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -6697,18 +6697,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K96" s="9" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.4%)</t>
+          <t>+382,000 ت از رتبه ۳ ترب (+8.5%)</t>
         </is>
       </c>
       <c r="M96" s="6" t="n">
-        <v>4520000</v>
+        <v>4882000</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -6746,8 +6746,8 @@
       <c r="E97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="8" t="n">
-        <v>8320000</v>
+      <c r="F97" s="5" t="n">
+        <v>8986000</v>
       </c>
       <c r="G97" s="6" t="n">
         <v>7200000</v>
@@ -6767,18 +6767,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>+1,120,000 ت از رتبه ۳ ترب (+15.6%)</t>
+          <t>+1,786,000 ت از رتبه ۳ ترب (+24.8%)</t>
         </is>
       </c>
       <c r="M97" s="6" t="n">
-        <v>8320000</v>
+        <v>8986000</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -6816,8 +6816,8 @@
       <c r="E98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>9970000</v>
+      <c r="F98" s="9" t="n">
+        <v>10768000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -6831,7 +6831,7 @@
       <c r="J98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="K98" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="M98" s="6" t="n">
-        <v>9970000</v>
+        <v>10768000</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>3699500</v>
+        <v>4018000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -6893,20 +6893,20 @@
         <v>3890000</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>5050000</v>
+        <v>4876910</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+128,000 ت از رتبه ۳ ترب (+3.3%)</t>
         </is>
       </c>
       <c r="M99" s="6" t="n">
-        <v>3699500</v>
+        <v>4018000</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
       <c r="B100" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6945,7 +6945,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>3580000</v>
+        <v>3866000</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>3580000</v>
@@ -6963,16 +6963,16 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+286,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M100" s="6" t="n">
-        <v>3580000</v>
+        <v>3866000</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
       <c r="B101" s="2" t="n">
         <v>3250</v>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7010,8 +7010,8 @@
       <c r="E101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="8" t="n">
-        <v>3120000</v>
+      <c r="F101" s="5" t="n">
+        <v>3370000</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>2900000</v>
@@ -7027,18 +7027,18 @@
       <c r="J101" s="6" t="n">
         <v>3200000</v>
       </c>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>+270,000 ت از رتبه ۳ ترب (+8.7%)</t>
         </is>
       </c>
       <c r="M101" s="6" t="n">
-        <v>3120000</v>
+        <v>3370000</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
       <c r="B102" s="2" t="n">
         <v>3229</v>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7068,8 +7068,8 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="11" t="n">
-        <v>24000000</v>
+      <c r="F102" s="9" t="n">
+        <v>25920000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -7085,18 +7085,18 @@
       <c r="J102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="K102" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>-1,757,000 ت از کف ترب (-6.8%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>24000000</v>
+        <v>25920000</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
       <c r="B103" s="2" t="n">
         <v>1840</v>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7187,7 +7187,7 @@
       <c r="B104" s="2" t="n">
         <v>2554</v>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C104" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7200,8 +7200,8 @@
       <c r="E104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="8" t="n">
-        <v>3920000</v>
+      <c r="F104" s="5" t="n">
+        <v>4234000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -7215,18 +7215,18 @@
       <c r="J104" s="6" t="n">
         <v>4120000</v>
       </c>
-      <c r="K104" s="9" t="inlineStr">
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>+65,000 ت از رتبه ۳ ترب (+1.7%)</t>
+          <t>+379,000 ت از رتبه ۳ ترب (+9.8%)</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>3920000</v>
+        <v>4234000</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
       <c r="B105" s="2" t="n">
         <v>3227</v>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C105" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7265,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4380000</v>
+        <v>4730000</v>
       </c>
       <c r="G105" s="6" t="n">
         <v>4000000</v>
@@ -7281,16 +7281,16 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+31,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M105" s="6" t="n">
-        <v>4380000</v>
+        <v>4730000</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
       <c r="B106" s="2" t="n">
         <v>3232</v>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7328,8 +7328,8 @@
       <c r="E106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="8" t="n">
-        <v>13070000</v>
+      <c r="F106" s="5" t="n">
+        <v>14116000</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>7400000</v>
@@ -7345,18 +7345,18 @@
       <c r="J106" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="K106" s="9" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+1,116,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M106" s="6" t="n">
-        <v>13070000</v>
+        <v>14116000</v>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
       <c r="B107" s="2" t="n">
         <v>3242</v>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7455,7 +7455,7 @@
       <c r="B108" s="2" t="n">
         <v>1868</v>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7469,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>9590000</v>
+        <v>10357000</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>7560000</v>
@@ -7485,16 +7485,16 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+658,000 ت از رتبه ۳ ترب (+6.8%)</t>
         </is>
       </c>
       <c r="M108" s="6" t="n">
-        <v>9590000</v>
+        <v>10357000</v>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
       <c r="B109" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7532,7 +7532,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F109" s="9" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -7553,7 +7553,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K109" s="7" t="inlineStr">
+      <c r="K109" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -7585,7 +7585,7 @@
       <c r="B110" s="2" t="n">
         <v>3228</v>
       </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7598,8 +7598,8 @@
       <c r="E110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F110" s="8" t="n">
-        <v>5520000</v>
+      <c r="F110" s="5" t="n">
+        <v>5962000</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>3580000</v>
@@ -7619,18 +7619,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>+1,940,000 ت از رتبه ۳ ترب (+54.2%)</t>
+          <t>+2,382,000 ت از رتبه ۳ ترب (+66.5%)</t>
         </is>
       </c>
       <c r="M110" s="6" t="n">
-        <v>5520000</v>
+        <v>5962000</v>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
       <c r="B111" s="2" t="n">
         <v>3233</v>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7729,7 +7729,7 @@
       <c r="B112" s="2" t="n">
         <v>3251</v>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7803,7 +7803,7 @@
       <c r="B113" s="2" t="n">
         <v>1948</v>
       </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7817,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>6270000</v>
+        <v>6772000</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>5900000</v>
@@ -7833,16 +7833,16 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+322,000 ت از رتبه ۳ ترب (+5.0%)</t>
         </is>
       </c>
       <c r="M113" s="6" t="n">
-        <v>6270000</v>
+        <v>6772000</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       <c r="B114" s="2" t="n">
         <v>1783</v>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7880,8 +7880,8 @@
       <c r="E114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="8" t="n">
-        <v>10500000</v>
+      <c r="F114" s="5" t="n">
+        <v>10951000</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>9000000</v>
@@ -7893,20 +7893,20 @@
         <v>9790000</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>10790000</v>
-      </c>
-      <c r="K114" s="9" t="inlineStr">
+        <v>10900000</v>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>+710,000 ت از رتبه ۳ ترب (+7.3%)</t>
+          <t>+1,161,000 ت از رتبه ۳ ترب (+11.9%)</t>
         </is>
       </c>
       <c r="M114" s="6" t="n">
-        <v>10500000</v>
+        <v>10951000</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
       <c r="B115" s="2" t="n">
         <v>2082</v>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7945,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>9500000</v>
+        <v>10152000</v>
       </c>
       <c r="G115" s="6" t="n">
         <v>8900000</v>
@@ -7963,16 +7963,16 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+352,000 ت از رتبه ۳ ترب (+3.6%)</t>
         </is>
       </c>
       <c r="M115" s="6" t="n">
-        <v>9500000</v>
+        <v>10152000</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
       <c r="B116" s="2" t="n">
         <v>1809</v>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8010,8 +8010,8 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="8" t="n">
-        <v>3220000</v>
+      <c r="F116" s="5" t="n">
+        <v>3499000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8023,20 +8023,20 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3332090</v>
-      </c>
-      <c r="K116" s="9" t="inlineStr">
+        <v>3621200</v>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>+232,000 ت از رتبه ۳ ترب (+7.8%)</t>
+          <t>+511,000 ت از رتبه ۳ ترب (+17.1%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3220000</v>
+        <v>3499000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
       <c r="B117" s="2" t="n">
         <v>3239</v>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8074,8 +8074,8 @@
       <c r="E117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F117" s="8" t="n">
-        <v>4920000</v>
+      <c r="F117" s="5" t="n">
+        <v>5314000</v>
       </c>
       <c r="G117" s="6" t="n">
         <v>4400000</v>
@@ -8093,18 +8093,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K117" s="9" t="inlineStr">
+      <c r="K117" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>+20,000 ت از رتبه ۳ ترب (+0.4%)</t>
+          <t>+414,000 ت از رتبه ۳ ترب (+8.4%)</t>
         </is>
       </c>
       <c r="M117" s="6" t="n">
-        <v>4920000</v>
+        <v>5314000</v>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
       <c r="B118" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8142,8 +8142,8 @@
       <c r="E118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>5370000</v>
+      <c r="F118" s="9" t="n">
+        <v>6696000</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>5248000</v>
@@ -8159,18 +8159,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K118" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M118" s="6" t="n">
-        <v>5370000</v>
+        <v>6696000</v>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
       <c r="B119" s="2" t="n">
         <v>2115</v>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8208,8 +8208,8 @@
       <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="8" t="n">
-        <v>9240000</v>
+      <c r="F119" s="5" t="n">
+        <v>9439000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -8223,18 +8223,18 @@
       <c r="J119" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K119" s="9" t="inlineStr">
+      <c r="K119" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>+1,751,000 ت از رتبه ۳ ترب (+23.4%)</t>
+          <t>+1,950,000 ت از رتبه ۳ ترب (+26.0%)</t>
         </is>
       </c>
       <c r="M119" s="6" t="n">
-        <v>9240000</v>
+        <v>9439000</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
       <c r="B120" s="2" t="n">
         <v>2563</v>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8273,7 +8273,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>6370000</v>
+        <v>6880000</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>5950000</v>
@@ -8291,16 +8291,16 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+380,000 ت از رتبه ۳ ترب (+5.8%)</t>
         </is>
       </c>
       <c r="M120" s="6" t="n">
-        <v>6370000</v>
+        <v>6880000</v>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
       <c r="B121" s="2" t="n">
         <v>2567</v>
       </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8338,8 +8338,8 @@
       <c r="E121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F121" s="8" t="n">
-        <v>7540000</v>
+      <c r="F121" s="5" t="n">
+        <v>8143000</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>6800000</v>
@@ -8355,18 +8355,18 @@
       <c r="J121" s="6" t="n">
         <v>9900000</v>
       </c>
-      <c r="K121" s="9" t="inlineStr">
+      <c r="K121" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+643,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M121" s="6" t="n">
-        <v>7540000</v>
+        <v>8143000</v>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
       <c r="B122" s="2" t="n">
         <v>1862</v>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8400,8 +8400,8 @@
       <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="8" t="n">
-        <v>11150000</v>
+      <c r="F122" s="5" t="n">
+        <v>12528000</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>10800000</v>
@@ -8415,18 +8415,18 @@
       <c r="J122" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K122" s="9" t="inlineStr">
+      <c r="K122" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
+          <t>+1,528,000 ت از رتبه ۳ ترب (+13.9%)</t>
         </is>
       </c>
       <c r="M122" s="6" t="n">
-        <v>11150000</v>
+        <v>12528000</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
       <c r="B123" s="2" t="n">
         <v>1846</v>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8465,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>9550000</v>
+        <v>10314000</v>
       </c>
       <c r="G123" s="6" t="n">
         <v>8800000</v>
@@ -8481,16 +8481,16 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+414,000 ت از رتبه ۳ ترب (+4.2%)</t>
         </is>
       </c>
       <c r="M123" s="6" t="n">
-        <v>9550000</v>
+        <v>10314000</v>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
       <c r="B124" s="2" t="n">
         <v>1851</v>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8525,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>5999500</v>
+        <v>6479000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -8552,11 +8552,11 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>-3,600,500 ت از کف ترب (-37.5%)</t>
+          <t>-3,121,000 ت از کف ترب (-32.5%)</t>
         </is>
       </c>
       <c r="M124" s="6" t="n">
-        <v>5999500</v>
+        <v>6479000</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
       <c r="B125" s="2" t="n">
         <v>3244</v>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8594,8 +8594,8 @@
       <c r="E125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F125" s="8" t="n">
-        <v>15460000</v>
+      <c r="F125" s="5" t="n">
+        <v>16697000</v>
       </c>
       <c r="G125" s="6" t="n">
         <v>13000000</v>
@@ -8611,18 +8611,18 @@
       <c r="J125" s="6" t="n">
         <v>16000000</v>
       </c>
-      <c r="K125" s="9" t="inlineStr">
+      <c r="K125" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+1,317,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M125" s="6" t="n">
-        <v>15460000</v>
+        <v>16697000</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
       <c r="B126" s="2" t="n">
         <v>2566</v>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8660,8 +8660,8 @@
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="8" t="n">
-        <v>11150000</v>
+      <c r="F126" s="5" t="n">
+        <v>12528000</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>10800000</v>
@@ -8675,18 +8675,18 @@
       <c r="J126" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K126" s="9" t="inlineStr">
+      <c r="K126" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه ۳ ترب (+1.4%)</t>
+          <t>+1,528,000 ت از رتبه ۳ ترب (+13.9%)</t>
         </is>
       </c>
       <c r="M126" s="6" t="n">
-        <v>11150000</v>
+        <v>12528000</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
       <c r="B127" s="2" t="n">
         <v>2150</v>
       </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="C127" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8785,7 +8785,7 @@
       <c r="B128" s="2" t="n">
         <v>1879</v>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8798,8 +8798,8 @@
       <c r="E128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>9970000</v>
+      <c r="F128" s="9" t="n">
+        <v>10768000</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>7990000</v>
@@ -8813,7 +8813,7 @@
       <c r="J128" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K128" s="7" t="inlineStr">
+      <c r="K128" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="M128" s="6" t="n">
-        <v>9970000</v>
+        <v>10768000</v>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
       <c r="B129" s="2" t="n">
         <v>1908</v>
       </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="C129" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8923,7 +8923,7 @@
       <c r="B130" s="2" t="n">
         <v>2558</v>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C130" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8936,8 +8936,8 @@
       <c r="E130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="8" t="n">
-        <v>7340000</v>
+      <c r="F130" s="5" t="n">
+        <v>7927000</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>6690000</v>
@@ -8953,18 +8953,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
+      <c r="K130" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>+490,000 ت از رتبه ۳ ترب (+7.2%)</t>
+          <t>+1,077,000 ت از رتبه ۳ ترب (+15.7%)</t>
         </is>
       </c>
       <c r="M130" s="6" t="n">
-        <v>7340000</v>
+        <v>7927000</v>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
       <c r="B131" s="2" t="n">
         <v>2052</v>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9003,7 +9003,7 @@
         <v>1</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>10250000</v>
+        <v>11070000</v>
       </c>
       <c r="G131" s="6" t="n">
         <v>9000000</v>
@@ -9021,16 +9021,16 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+70,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M131" s="6" t="n">
-        <v>10250000</v>
+        <v>11070000</v>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
       <c r="B132" s="2" t="n">
         <v>1986</v>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9069,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>12570000</v>
+        <v>13576000</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>9945000</v>
@@ -9087,16 +9087,16 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+926,000 ت از رتبه ۳ ترب (+7.3%)</t>
         </is>
       </c>
       <c r="M132" s="6" t="n">
-        <v>12570000</v>
+        <v>13576000</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
       <c r="B133" s="2" t="n">
         <v>1770</v>
       </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9134,8 +9134,8 @@
       <c r="E133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>12140000</v>
+      <c r="F133" s="9" t="n">
+        <v>8413000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9147,9 +9147,9 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="K133" s="7" t="inlineStr">
+        <v>7000000</v>
+      </c>
+      <c r="K133" s="10" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>12140000</v>
+        <v>8413000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
       <c r="B134" s="2" t="n">
         <v>3236</v>
       </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="C134" s="8" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9199,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>19900000</v>
+        <v>21492000</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>19000000</v>
@@ -9217,16 +9217,16 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,592,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M134" s="6" t="n">
-        <v>19900000</v>
+        <v>21492000</v>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -814,7 +814,7 @@
         <v>5530000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5100000</v>
@@ -823,7 +823,7 @@
         <v>5200000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5799000</v>
+        <v>5740000</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>6500000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>9524230</v>
+        <v>9625650</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>115500</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>195000</v>
+        <v>181350</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         <v>8900000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8900000</v>
+        <v>9000000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9000000</v>
+        <v>9200000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>8928000</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+936,000 ت از رتبه ۳ ترب (+10.4%)</t>
+          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
@@ -1209,7 +1209,7 @@
         <v>6799000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8570000</v>
+        <v>8900000</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         <v>4936000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4300000</v>
+        <v>4500000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4500000</v>
+        <v>4600000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4653000</v>
+        <v>4700000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5500000</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>+283,000 ت از رتبه ۳ ترب (+6.1%)</t>
+          <t>+236,000 ت از رتبه ۳ ترب (+5.0%)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -1384,16 +1384,16 @@
         <v>19510000</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>11450000</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>11480000</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>11600000</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>11690000</v>
-      </c>
       <c r="J14" s="6" t="n">
-        <v>19800000</v>
+        <v>19450000</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+7,820,000 ت از رتبه ۳ ترب (+66.9%)</t>
+          <t>+7,910,000 ت از رتبه ۳ ترب (+68.2%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
@@ -1448,16 +1448,16 @@
         <v>6799000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6230000</v>
+        <v>6300000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6300000</v>
+        <v>6350000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6300000</v>
+        <v>6400000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7780000</v>
+        <v>7765000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+499,000 ت از رتبه ۳ ترب (+7.9%)</t>
+          <t>+399,000 ت از رتبه ۳ ترب (+6.2%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
@@ -1512,16 +1512,16 @@
         <v>4844000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4205000</v>
+        <v>4480000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4480000</v>
+        <v>4500000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4500000</v>
+        <v>4600000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>4900000</v>
+        <v>5100000</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+344,000 ت از رتبه ۳ ترب (+7.6%)</t>
+          <t>+244,000 ت از رتبه ۳ ترب (+5.3%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1715,10 +1715,10 @@
         <v>8900000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>8900000</v>
+        <v>9000000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9000000</v>
+        <v>9200000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>8928000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+936,000 ت از رتبه ۳ ترب (+10.4%)</t>
+          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
@@ -1851,7 +1851,7 @@
         <v>6799000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8570000</v>
+        <v>8900000</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1902,11 +1902,11 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="11" t="n">
         <v>15628000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>14400000</v>
+        <v>15900000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1919,16 +1919,16 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16890000</v>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>18115600</v>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>+1,228,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>-272,000 ت از کف ترب (-1.7%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
@@ -1977,13 +1977,13 @@
         <v>7150000</v>
       </c>
       <c r="H23" s="6" t="n">
+        <v>7454000</v>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>7500000</v>
       </c>
-      <c r="I23" s="6" t="n">
-        <v>8090000</v>
-      </c>
       <c r="J23" s="6" t="n">
-        <v>7000000</v>
+        <v>6900000</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>+323,000 ت از رتبه ۳ ترب (+4.0%)</t>
+          <t>+913,000 ت از رتبه ۳ ترب (+12.2%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
@@ -2038,16 +2038,16 @@
         <v>6080000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5300000</v>
+        <v>5650000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5616000</v>
+        <v>5900000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5650000</v>
+        <v>5999000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7542200</v>
+        <v>6470000</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+430,000 ت از رتبه ۳ ترب (+7.6%)</t>
+          <t>+81,000 ت از رتبه ۳ ترب (+1.4%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
@@ -2105,10 +2105,10 @@
         <v>5590000</v>
       </c>
       <c r="H25" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>6980000</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>7000000</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>13890000</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,900,000 ت از رتبه ۳ ترب (+70.0%)</t>
+          <t>+4,920,000 ت از رتبه ۳ ترب (+70.5%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2166,7 +2166,7 @@
         <v>13560000</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>7400000</v>
+        <v>7500000</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>7980000</v>
@@ -2360,10 +2360,10 @@
         <v>4900000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4900000</v>
+        <v>4950000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>6250000</v>
+        <v>5770000</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+435,000 ت از رتبه ۳ ترب (+8.9%)</t>
+          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
@@ -2484,16 +2484,16 @@
         <v>14332000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12800000</v>
+        <v>12000000</v>
       </c>
       <c r="H31" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>13750000</v>
-      </c>
       <c r="J31" s="6" t="n">
-        <v>29990000</v>
+        <v>26590000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+582,000 ت از رتبه ۳ ترب (+4.2%)</t>
+          <t>+632,000 ت از رتبه ۳ ترب (+4.6%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2612,10 +2612,10 @@
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>5400000</v>
+        <v>5999000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>5999000</v>
+        <v>6000000</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>6000000</v>
@@ -2678,10 +2678,10 @@
         <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>6900000</v>
+        <v>7900000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>6900000</v>
+        <v>8000000</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>8700000</v>
@@ -2794,16 +2794,16 @@
         <v>7528000</v>
       </c>
       <c r="G36" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>6700000</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>6950000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7400000</v>
+        <v>7290000</v>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
@@ -2858,16 +2858,16 @@
         <v>7528000</v>
       </c>
       <c r="G37" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>6700000</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>6950000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7400000</v>
+        <v>7290000</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7600000</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>+532,000 ت از رتبه ۳ ترب (+7.0%)</t>
+          <t>+525,000 ت از رتبه ۳ ترب (+6.9%)</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
@@ -3511,7 +3511,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7542200</v>
+        <v>6470000</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>7489000</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>13700000</v>
+        <v>7500000</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4694800</v>
+        <v>4507200</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>6250000</v>
+        <v>5770000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3910330</v>
+        <v>3780980</v>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>3890000</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>4876910</v>
+        <v>4870000</v>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>3855000</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>4120000</v>
+        <v>4630000</v>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7780000</v>
+        <v>7765000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>6950000</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>7400000</v>
+        <v>7290000</v>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>6950000</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>7400000</v>
+        <v>7290000</v>
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4694800</v>
+        <v>4507200</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3621200</v>
+        <v>3579500</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>3890000</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>4876910</v>
+        <v>4870000</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>3855000</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>4120000</v>
+        <v>4630000</v>
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>4699000</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>7100000</v>
+        <v>5300000</v>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3621200</v>
+        <v>3579500</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>7489000</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>13700000</v>
+        <v>7500000</v>
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>7000000</v>
+        <v>6900000</v>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -631,7 +631,7 @@
         <v>9400000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10580000</v>
+        <v>10980000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
@@ -814,16 +814,16 @@
         <v>5530000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5100000</v>
+        <v>5250000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5200000</v>
+        <v>5300000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5740000</v>
+        <v>5999000</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+330,000 ت از رتبه ۳ ترب (+6.3%)</t>
+          <t>+230,000 ت از رتبه ۳ ترب (+4.3%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
@@ -1079,22 +1079,22 @@
         <v>97000</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>99300</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>100000</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>115500</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>181350</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
@@ -1145,7 +1145,7 @@
         <v>9200000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>8928000</v>
+        <v>9300000</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -1203,13 +1203,13 @@
         <v>6600000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6600000</v>
+        <v>6799000</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6799000</v>
+        <v>6930000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8900000</v>
+        <v>8880000</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>+577,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>+446,000 ت از رتبه ۳ ترب (+6.4%)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
@@ -1264,7 +1264,7 @@
         <v>4936000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4500000</v>
+        <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>4600000</v>
@@ -1273,7 +1273,7 @@
         <v>4700000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5500000</v>
+        <v>5400000</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>11600000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>19450000</v>
+        <v>19800000</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1451,13 +1451,13 @@
         <v>6300000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6350000</v>
+        <v>6400000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6400000</v>
+        <v>6420000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7765000</v>
+        <v>7985000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+399,000 ت از رتبه ۳ ترب (+6.2%)</t>
+          <t>+379,000 ت از رتبه ۳ ترب (+5.9%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
@@ -1512,10 +1512,10 @@
         <v>4844000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4480000</v>
+        <v>4599000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4500000</v>
+        <v>4600000</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>4600000</v>
@@ -1642,7 +1642,7 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="5" t="n">
         <v>10390000</v>
       </c>
       <c r="G18" s="6" t="n">
@@ -1652,21 +1652,21 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10390000</v>
+        <v>9500000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+890,000 ت از رتبه ۳ ترب (+9.4%)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
@@ -1721,7 +1721,7 @@
         <v>9200000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8928000</v>
+        <v>9300000</v>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>6600000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6600000</v>
+        <v>6799000</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6799000</v>
+        <v>6930000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8900000</v>
+        <v>8880000</v>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>+577,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>+446,000 ت از رتبه ۳ ترب (+6.4%)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>18115600</v>
+        <v>16689660</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>7500000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>6900000</v>
+        <v>7300000</v>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         <v>5900000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5999000</v>
+        <v>6000000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6470000</v>
+        <v>7014000</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+81,000 ت از رتبه ۳ ترب (+1.4%)</t>
+          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
@@ -2108,10 +2108,10 @@
         <v>6500000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6980000</v>
+        <v>7150000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>13890000</v>
+        <v>13850000</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,920,000 ت از رتبه ۳ ترب (+70.5%)</t>
+          <t>+4,750,000 ت از رتبه ۳ ترب (+66.4%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2166,13 +2166,13 @@
         <v>13560000</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>7500000</v>
+        <v>7900000</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>7980000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8270000</v>
+        <v>8260000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>+5,290,000 ت از رتبه ۳ ترب (+64.0%)</t>
+          <t>+5,300,000 ت از رتبه ۳ ترب (+64.2%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
@@ -2226,13 +2226,13 @@
         <v>16632000</v>
       </c>
       <c r="G27" s="6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>12680000</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="6" t="n">
         <v>15300000</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>+1,132,000 ت از رتبه ۳ ترب (+7.3%)</t>
+          <t>+1,332,000 ت از رتبه ۳ ترب (+8.7%)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
@@ -2363,7 +2363,7 @@
         <v>4950000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5770000</v>
+        <v>6250000</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2487,13 +2487,13 @@
         <v>12000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>12000000</v>
+        <v>13400000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13700000</v>
+        <v>13750000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>26590000</v>
+        <v>27590000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+632,000 ت از رتبه ۳ ترب (+4.6%)</t>
+          <t>+582,000 ت از رتبه ۳ ترب (+4.2%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2554,7 +2554,7 @@
         <v>11000000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11097000</v>
+        <v>11300000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>19500000</v>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>+1,431,000 ت از رتبه ۳ ترب (+12.9%)</t>
+          <t>+1,228,000 ت از رتبه ۳ ترب (+10.9%)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
@@ -2612,13 +2612,13 @@
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>5999000</v>
+        <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6000000</v>
+        <v>6399000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>+479,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
@@ -2678,13 +2678,13 @@
         <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7900000</v>
+        <v>8700000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>8000000</v>
+        <v>8900000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>8700000</v>
+        <v>8900000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>7100000</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>+642,000 ت از رتبه ۳ ترب (+7.4%)</t>
+          <t>+442,000 ت از رتبه ۳ ترب (+5.0%)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
@@ -2803,7 +2803,7 @@
         <v>6950000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7290000</v>
+        <v>7400000</v>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>6950000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7290000</v>
+        <v>7400000</v>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
@@ -3176,10 +3176,10 @@
         <v>3445000</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>3445000</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>3445000</v>
+        <v>4150000</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M42" s="6" t="n">
@@ -3246,7 +3246,7 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7485000</v>
+        <v>7500000</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>8000000</v>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+485,000 ت از رتبه ۳ ترب (+6.5%)</t>
+          <t>+470,000 ت از رتبه ۳ ترب (+6.3%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3379,7 +3379,7 @@
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7600000</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3438,29 +3438,29 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>2839550</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>3500000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
+        <v>3600000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,200,000 ت از رتبه ۳ ترب (+33.3%)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3511,7 +3511,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>6470000</v>
+        <v>7014000</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>3150000</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>3800000</v>
+        <v>4285000</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>7489000</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>7500000</v>
+        <v>13700000</v>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7299000</v>
+        <v>7753070</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4507200</v>
+        <v>4910900</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>19000000</v>
+        <v>22000000</v>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5770000</v>
+        <v>6250000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3780980</v>
+        <v>3800000</v>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7765000</v>
+        <v>7985000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>14490000</v>
+        <v>17500000</v>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>6950000</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>7290000</v>
+        <v>7400000</v>
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>6950000</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>7290000</v>
+        <v>7400000</v>
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4507200</v>
+        <v>4910900</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3579500</v>
+        <v>3621000</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>6920000</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>8600000</v>
+        <v>8500000</v>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>9790000</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>10900000</v>
+        <v>11290000</v>
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3579500</v>
+        <v>3621000</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>7489000</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>7500000</v>
+        <v>13700000</v>
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>6900000</v>
+        <v>7300000</v>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -814,13 +814,13 @@
         <v>5530000</v>
       </c>
       <c r="G5" s="6" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>5250000</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>5300000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5999000</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+230,000 ت از رتبه ۳ ترب (+4.3%)</t>
+          <t>+280,000 ت از رتبه ۳ ترب (+5.3%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
@@ -948,7 +948,7 @@
         <v>4000000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4000000</v>
+        <v>4150000</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>4500000</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+255,000 ت از رتبه ۳ ترب (+6.4%)</t>
+          <t>+105,000 ت از رتبه ۳ ترب (+2.5%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
@@ -1084,8 +1084,10 @@
       <c r="I9" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>181350</v>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -1196,29 +1198,29 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="9" t="n">
         <v>7376000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6600000</v>
+        <v>6799000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6799000</v>
+        <v>6930000</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6930000</v>
+        <v>7600000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8880000</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>8960000</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>+446,000 ت از رتبه ۳ ترب (+6.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
@@ -1384,13 +1386,13 @@
         <v>19510000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11450000</v>
+        <v>11480000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11480000</v>
+        <v>11690000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11600000</v>
+        <v>12300000</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>19800000</v>
@@ -1402,7 +1404,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+7,910,000 ت از رتبه ۳ ترب (+68.2%)</t>
+          <t>+7,210,000 ت از رتبه ۳ ترب (+58.6%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
@@ -1451,13 +1453,13 @@
         <v>6300000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6400000</v>
+        <v>6490000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6420000</v>
+        <v>6500000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7985000</v>
+        <v>8180000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1466,7 +1468,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+379,000 ت از رتبه ۳ ترب (+5.9%)</t>
+          <t>+299,000 ت از رتبه ۳ ترب (+4.6%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
@@ -1512,13 +1514,13 @@
         <v>4844000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4599000</v>
+        <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4600000</v>
+        <v>4650000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>5100000</v>
@@ -1530,7 +1532,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+244,000 ت از رتبه ۳ ترب (+5.3%)</t>
+          <t>+194,000 ت از رتبه ۳ ترب (+4.2%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1576,7 +1578,7 @@
         <v>8000000</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1600,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>-500,000 ت از کف ترب (-5.9%)</t>
+          <t>-1,000,000 ت از کف ترب (-11.1%)</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
@@ -1642,31 +1644,31 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="9" t="n">
         <v>10390000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9250000</v>
+        <v>10390000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>9500000</v>
+        <v>11500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9500000</v>
+        <v>13300000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>+890,000 ت از رتبه ۳ ترب (+9.4%)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
@@ -1838,29 +1840,29 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="9" t="n">
         <v>7376000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>6600000</v>
+        <v>6799000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6799000</v>
+        <v>6930000</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>6930000</v>
+        <v>7600000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8880000</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>8960000</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>+446,000 ت از رتبه ۳ ترب (+6.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
@@ -1970,29 +1972,29 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="9" t="n">
         <v>8413000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7150000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>7454000</v>
+        <v>8890000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>7500000</v>
+        <v>13300000</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>7300000</v>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>+913,000 ت از رتبه ۳ ترب (+12.2%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
@@ -2047,7 +2049,7 @@
         <v>6000000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7014000</v>
+        <v>7133800</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2108,10 +2110,10 @@
         <v>6500000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7150000</v>
+        <v>7480000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>13850000</v>
+        <v>13800000</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -2120,7 +2122,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,750,000 ت از رتبه ۳ ترب (+66.4%)</t>
+          <t>+4,420,000 ت از رتبه ۳ ترب (+59.1%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2357,13 +2359,13 @@
         <v>4890000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4900000</v>
+        <v>4950000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4950000</v>
+        <v>4980000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>6250000</v>
+        <v>5812500</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2372,7 +2374,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
+          <t>+355,000 ت از رتبه ۳ ترب (+7.1%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
@@ -2487,13 +2489,13 @@
         <v>12000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13400000</v>
+        <v>13500000</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>13750000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>27590000</v>
+        <v>26500000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2608,31 +2610,31 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="9" t="n">
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6000000</v>
+        <v>6399000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6399000</v>
+        <v>6479000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
@@ -2925,7 +2927,7 @@
         <v>11890000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>13250000</v>
+        <v>14250000</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>14753000</v>
@@ -2992,7 +2994,7 @@
         <v>4000000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4000000</v>
+        <v>4150000</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>4500000</v>
@@ -3004,7 +3006,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+255,000 ت از رتبه ۳ ترب (+6.4%)</t>
+          <t>+105,000 ت از رتبه ۳ ترب (+2.5%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
@@ -3243,13 +3245,15 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8000000</v>
+        <v>7700000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
@@ -3258,7 +3262,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+470,000 ت از رتبه ۳ ترب (+6.3%)</t>
+          <t>+270,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3379,7 +3383,7 @@
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7600000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3438,29 +3442,29 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="9" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>2839550</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>3500000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>3600000</v>
+        <v>4800000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>+1,200,000 ت از رتبه ۳ ترب (+33.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3511,7 +3515,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7014000</v>
+        <v>7133800</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3575,7 +3579,7 @@
         <v>9100000</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>12900000</v>
+        <v>13500000</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
@@ -4357,7 +4361,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7753070</v>
+        <v>7491000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4487,7 +4491,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4910900</v>
+        <v>4908300</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4617,7 +4621,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>6250000</v>
+        <v>5812500</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -5709,7 +5713,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7985000</v>
+        <v>8180000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -5839,7 +5843,7 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>17500000</v>
+        <v>14300000</v>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6369,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4910900</v>
+        <v>4908300</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6493,7 +6497,7 @@
         <v>6920000</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>8500000</v>
+        <v>8600000</v>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -814,13 +814,13 @@
         <v>5530000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4750000</v>
+        <v>5200000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5200000</v>
+        <v>5250000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5250000</v>
+        <v>5300000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5999000</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+280,000 ت از رتبه ۳ ترب (+5.3%)</t>
+          <t>+230,000 ت از رتبه ۳ ترب (+4.3%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
@@ -1211,7 +1211,7 @@
         <v>7600000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>8960000</v>
+        <v>10244390</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>4600000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4700000</v>
+        <v>4900000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5400000</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>+236,000 ت از رتبه ۳ ترب (+5.0%)</t>
+          <t>+36,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -1386,13 +1386,13 @@
         <v>19510000</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>11480000</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <v>11690000</v>
-      </c>
       <c r="I14" s="6" t="n">
-        <v>12300000</v>
+        <v>11500000</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>19800000</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+7,210,000 ت از رتبه ۳ ترب (+58.6%)</t>
+          <t>+8,010,000 ت از رتبه ۳ ترب (+69.7%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
@@ -1459,7 +1459,7 @@
         <v>6500000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8180000</v>
+        <v>8310000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
         <v>10390000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>11500000</v>
+        <v>13300000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>13300000</v>
+        <v>13500000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>7600000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8960000</v>
+        <v>10244390</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>14332000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12000000</v>
+        <v>13000000</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>13500000</v>
@@ -3245,10 +3245,10 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7500000</v>
+        <v>7700000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7700000</v>
+        <v>7900000</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+270,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+70,000 ت از رتبه ۳ ترب (+0.9%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3383,7 +3383,7 @@
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7600000</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3442,29 +3442,29 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>1210000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>2839550</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
+        <v>3600000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,200,000 ت از رتبه ۳ ترب (+33.3%)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3706,10 +3706,8 @@
       <c r="I50" s="6" t="n">
         <v>6850000</v>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J50" s="6" t="n">
+        <v>7590000</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
@@ -4491,7 +4489,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4908300</v>
+        <v>4908200</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4877,7 +4875,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>3800000</v>
+        <v>4374620</v>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
@@ -4940,10 +4938,8 @@
       <c r="I69" s="6" t="n">
         <v>15600000</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J69" s="6" t="n">
+        <v>9500000</v>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
@@ -5713,7 +5709,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>8180000</v>
+        <v>8310000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -6369,7 +6365,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4908300</v>
+        <v>4908200</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -631,7 +631,7 @@
         <v>9400000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10980000</v>
+        <v>11000000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>5300000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5999000</v>
+        <v>5950000</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>7020000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6550000</v>
+        <v>6850000</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>6889000</v>
@@ -887,7 +887,7 @@
         <v>6500000</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>9625650</v>
+        <v>9560380</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>9000000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9200000</v>
+        <v>9600000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9300000</v>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+336,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
@@ -1211,7 +1211,7 @@
         <v>7600000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>10244390</v>
+        <v>10558090</v>
       </c>
       <c r="K11" s="10" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>4900000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5400000</v>
+        <v>5473960</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -1330,13 +1330,13 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>11800000</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>12000000</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>12800000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>-1,600,000 ت از کف ترب (-13.6%)</t>
+          <t>-1,000,000 ت از کف ترب (-8.9%)</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
@@ -1517,13 +1517,13 @@
         <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4600000</v>
+        <v>4650000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4650000</v>
+        <v>4680000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5100000</v>
+        <v>5781220</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+194,000 ت از رتبه ۳ ترب (+4.2%)</t>
+          <t>+164,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1720,7 +1720,7 @@
         <v>9000000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9200000</v>
+        <v>9600000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9300000</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+336,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
@@ -1853,7 +1853,7 @@
         <v>7600000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>10244390</v>
+        <v>10558090</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>7150000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8890000</v>
+        <v>9080000</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>13300000</v>
@@ -2049,7 +2049,7 @@
         <v>6000000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7133800</v>
+        <v>7155400</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>6500000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7480000</v>
+        <v>7150000</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>13800000</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,420,000 ت از رتبه ۳ ترب (+59.1%)</t>
+          <t>+4,750,000 ت از رتبه ۳ ترب (+66.4%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2492,7 +2492,7 @@
         <v>13500000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13750000</v>
+        <v>13900000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>26500000</v>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+582,000 ت از رتبه ۳ ترب (+4.2%)</t>
+          <t>+432,000 ت از رتبه ۳ ترب (+3.1%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2550,13 +2550,13 @@
         <v>12528000</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10950000</v>
+        <v>11000000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>11000000</v>
+        <v>11300000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11300000</v>
+        <v>11500000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>19500000</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>+1,228,000 ت از رتبه ۳ ترب (+10.9%)</t>
+          <t>+1,028,000 ت از رتبه ۳ ترب (+8.9%)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
@@ -2610,31 +2610,31 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="5" t="n">
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I33" s="6" t="n">
         <v>6399000</v>
       </c>
-      <c r="I33" s="6" t="n">
-        <v>6479000</v>
-      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
@@ -3452,7 +3452,7 @@
         <v>2839550</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>3600000</v>
+        <v>4000000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>+1,200,000 ت از رتبه ۳ ترب (+33.3%)</t>
+          <t>+800,000 ت از رتبه ۳ ترب (+20.0%)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3515,7 +3515,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7133800</v>
+        <v>7155400</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7491000</v>
+        <v>7492000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>4374620</v>
+        <v>4328410</v>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3621000</v>
+        <v>3621200</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3621000</v>
+        <v>3621200</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -817,13 +817,13 @@
         <v>5200000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5250000</v>
+        <v>5300000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5300000</v>
+        <v>5400000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5950000</v>
+        <v>5999000</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+230,000 ت از رتبه ۳ ترب (+4.3%)</t>
+          <t>+130,000 ت از رتبه ۳ ترب (+2.4%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
@@ -948,7 +948,7 @@
         <v>4000000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4150000</v>
+        <v>4200000</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>4500000</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+105,000 ت از رتبه ۳ ترب (+2.5%)</t>
+          <t>+55,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
@@ -1002,11 +1002,13 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="6" t="n">
         <v>1760000</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1760000</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1023,14 +1025,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
@@ -1084,10 +1086,8 @@
       <c r="I9" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J9" s="6" t="n">
+        <v>195000</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>9000000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9600000</v>
+        <v>9500000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9300000</v>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+336,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+436,000 ت از رتبه ۳ ترب (+4.6%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
@@ -1262,29 +1262,29 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="9" t="n">
         <v>4936000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4600000</v>
+        <v>4700000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4900000</v>
+        <v>5050000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5473960</v>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>5675110</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>+36,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -1450,16 +1450,16 @@
         <v>6799000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6300000</v>
+        <v>6500000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6490000</v>
+        <v>6500000</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8310000</v>
+        <v>7800000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1517,13 +1517,13 @@
         <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4650000</v>
+        <v>4680000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4680000</v>
+        <v>4700000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5781220</v>
+        <v>6400000</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+164,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+144,000 ت از رتبه ۳ ترب (+3.1%)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1648,14 +1648,14 @@
         <v>10390000</v>
       </c>
       <c r="G18" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>10280000</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>10390000</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>13500000</v>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="K18" s="10" t="inlineStr">
         <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
@@ -1720,7 +1720,7 @@
         <v>9000000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9600000</v>
+        <v>9500000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9300000</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+336,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+436,000 ت از رتبه ۳ ترب (+4.6%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
@@ -1908,7 +1908,7 @@
         <v>15628000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>15900000</v>
+        <v>18000000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16689660</v>
+        <v>16500000</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>-272,000 ت از کف ترب (-1.7%)</t>
+          <t>-2,372,000 ت از کف ترب (-13.2%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
@@ -1976,7 +1976,7 @@
         <v>8413000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7150000</v>
+        <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>9080000</v>
@@ -1985,7 +1985,7 @@
         <v>13300000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>7300000</v>
+        <v>7652540</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -2043,13 +2043,13 @@
         <v>5650000</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>5899000</v>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>5900000</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <v>6000000</v>
-      </c>
       <c r="J24" s="6" t="n">
-        <v>7155400</v>
+        <v>7161100</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>+180,000 ت از رتبه ۳ ترب (+3.1%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
@@ -2104,10 +2104,10 @@
         <v>11900000</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>5590000</v>
+        <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6500000</v>
+        <v>6900000</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>7150000</v>
@@ -2231,7 +2231,7 @@
         <v>12500000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>12680000</v>
+        <v>14680000</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>15300000</v>
@@ -2359,13 +2359,13 @@
         <v>4890000</v>
       </c>
       <c r="H29" s="6" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>4950000</v>
       </c>
-      <c r="I29" s="6" t="n">
-        <v>4980000</v>
-      </c>
       <c r="J29" s="6" t="n">
-        <v>5812500</v>
+        <v>5599000</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+355,000 ت از رتبه ۳ ترب (+7.1%)</t>
+          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
@@ -2489,10 +2489,10 @@
         <v>13000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13500000</v>
+        <v>13900000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13900000</v>
+        <v>14000000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>26500000</v>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+432,000 ت از رتبه ۳ ترب (+3.1%)</t>
+          <t>+332,000 ت از رتبه ۳ ترب (+2.4%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2610,31 +2610,31 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="9" t="n">
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6000000</v>
+        <v>6399000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6399000</v>
+        <v>6479000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
@@ -2676,29 +2676,29 @@
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="9" t="n">
         <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>8700000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>8900000</v>
+        <v>9260000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>8900000</v>
+        <v>9350000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>+442,000 ت از رتبه ۳ ترب (+5.0%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
@@ -2924,25 +2924,25 @@
         <v>14753000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11890000</v>
+        <v>14250000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>14250000</v>
+        <v>14753000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>14753000</v>
+        <v>14900000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
@@ -2994,7 +2994,7 @@
         <v>4000000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4150000</v>
+        <v>4200000</v>
       </c>
       <c r="J39" s="6" t="n">
         <v>4500000</v>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+105,000 ت از رتبه ۳ ترب (+2.5%)</t>
+          <t>+55,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
@@ -3245,11 +3245,11 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="I43" s="6" t="n">
         <v>7700000</v>
       </c>
-      <c r="I43" s="6" t="n">
-        <v>7900000</v>
-      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه ۳ ترب (+0.9%)</t>
+          <t>+270,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3383,7 +3383,7 @@
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7600000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3442,29 +3442,29 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="9" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1210000</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>2839550</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4000000</v>
+        <v>4800000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>+800,000 ت از رتبه ۳ ترب (+20.0%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3515,7 +3515,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7155400</v>
+        <v>7161100</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>3150000</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>4285000</v>
+        <v>4385000</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7492000</v>
+        <v>7502000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4908200</v>
+        <v>4449000</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5812500</v>
+        <v>5599000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>4100000</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>4328410</v>
+        <v>4326110</v>
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>8310000</v>
+        <v>7800000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4908200</v>
+        <v>4449000</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3621200</v>
+        <v>3798600</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>6920000</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>8600000</v>
+        <v>8550000</v>
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3621200</v>
+        <v>3798600</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>16200000</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>7300000</v>
+        <v>7652540</v>
       </c>
       <c r="K133" s="10" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -63,14 +63,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3E8FF"/>
-        <bgColor rgb="00F3E8FF"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -619,10 +619,10 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9990000</v>
+        <v>9550000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9200000</v>
+        <v>9250000</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>9250000</v>
@@ -640,11 +640,11 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>+590,000 ت از رتبه ۳ ترب (+6.3%)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+1.6%)</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1888110000</v>
+        <v>1804950000</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -682,33 +682,33 @@
       <c r="E3" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>16734000</v>
+      <c r="F3" s="8" t="n">
+        <v>15660000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>14590000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>15490000</v>
+        <v>15660000</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>15840000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>15490000</v>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>15990000</v>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>+894,000 ت از رتبه ۳ ترب (+5.6%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>1054242000</v>
+        <v>986580000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -746,14 +746,14 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>14580000</v>
+      <c r="F4" s="8" t="n">
+        <v>12930000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>12870000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12990000</v>
+        <v>12930000</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>12990000</v>
@@ -761,18 +761,18 @@
       <c r="J4" s="6" t="n">
         <v>12990000</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>+1,590,000 ت از رتبه ۳ ترب (+12.2%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>437400000</v>
+        <v>387900000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>5530000</v>
+      <c r="F5" s="8" t="n">
+        <v>5420000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5200000</v>
+        <v>5400000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5300000</v>
+        <v>5420000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5400000</v>
+        <v>5450000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5999000</v>
       </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+130,000 ت از رتبه ۳ ترب (+2.4%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>99540000</v>
+        <v>97560000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -874,14 +874,14 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>7020000</v>
+      <c r="F6" s="8" t="n">
+        <v>6500000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6850000</v>
+        <v>6950000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>6889000</v>
+        <v>6450000</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6500000</v>
@@ -889,18 +889,18 @@
       <c r="J6" s="6" t="n">
         <v>9560380</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>+131,000 ت از رتبه ۳ ترب (+1.9%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>119340000</v>
+        <v>110500000</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4255000</v>
+        <v>4300000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3800000</v>
@@ -960,11 +960,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+55,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>+100,000 ت از رتبه ۳ ترب (+2.4%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>63825000</v>
+        <v>64500000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       <c r="B8" s="2" t="n">
         <v>2144</v>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1002,13 +1002,11 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>1760000</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G8" s="6" t="n">
+        <v>1760000</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1025,14 +1023,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
@@ -1074,29 +1072,29 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>97000</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>99300</v>
+        <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>100000</v>
+        <v>101200</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>195000</v>
       </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
@@ -1134,33 +1132,33 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>9936000</v>
+      <c r="F10" s="8" t="n">
+        <v>9350000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8900000</v>
+        <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9000000</v>
+        <v>9300000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9500000</v>
+        <v>9350000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+436,000 ت از رتبه ۳ ترب (+4.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>109296000</v>
+        <v>102850000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1198,8 +1196,8 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>7376000</v>
+      <c r="F11" s="8" t="n">
+        <v>7260000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1213,7 +1211,7 @@
       <c r="J11" s="6" t="n">
         <v>10558090</v>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1224,7 +1222,7 @@
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>81136000</v>
+        <v>79860000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1249,7 +1247,7 @@
       <c r="B12" s="2" t="n">
         <v>2121</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1262,8 +1260,8 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="9" t="n">
-        <v>4936000</v>
+      <c r="F12" s="8" t="n">
+        <v>4870000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
@@ -1272,12 +1270,12 @@
         <v>4700000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5050000</v>
+        <v>5150000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5675110</v>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
+        <v>6000000</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1288,7 +1286,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>49360000</v>
+        <v>48700000</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1330,13 +1328,13 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>11200000</v>
+        <v>11800000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>11800000</v>
+        <v>12000000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>12000000</v>
+        <v>13100000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
@@ -1348,7 +1346,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>-1,000,000 ت از کف ترب (-8.9%)</t>
+          <t>-1,600,000 ت از کف ترب (-13.6%)</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
@@ -1369,7 +1367,7 @@
       <c r="B14" s="2" t="n">
         <v>1953</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1386,16 +1384,16 @@
         <v>19510000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11000000</v>
+        <v>11480000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11480000</v>
+        <v>11500000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11500000</v>
+        <v>11690000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>19800000</v>
+        <v>20400000</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1404,7 +1402,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+8,010,000 ت از رتبه ۳ ترب (+69.7%)</t>
+          <t>+7,820,000 ت از رتبه ۳ ترب (+66.9%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
@@ -1447,7 +1445,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6799000</v>
+        <v>6740000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6500000</v>
@@ -1456,10 +1454,10 @@
         <v>6500000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6500000</v>
+        <v>6695000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7800000</v>
+        <v>7700000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1468,11 +1466,11 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+299,000 ت از رتبه ۳ ترب (+4.6%)</t>
+          <t>+45,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>47593000</v>
+        <v>47180000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1497,7 +1495,7 @@
       <c r="B16" s="2" t="n">
         <v>1964</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1510,8 +1508,8 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>4844000</v>
+      <c r="F16" s="8" t="n">
+        <v>4690000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4600000</v>
@@ -1520,23 +1518,23 @@
         <v>4680000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4700000</v>
+        <v>4690000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>6400000</v>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>6823370</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>+144,000 ت از رتبه ۳ ترب (+3.1%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>33908000</v>
+        <v>32830000</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1574,8 +1572,8 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>8000000</v>
+      <c r="F17" s="5" t="n">
+        <v>9900000</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>9000000</v>
@@ -1595,18 +1593,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>-1,000,000 ت از کف ترب (-11.1%)</t>
+          <t>+900,000 ت از رتبه ۳ ترب (+10.0%)</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>48000000</v>
+        <v>59400000</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1631,7 +1629,7 @@
       <c r="B18" s="2" t="n">
         <v>1962</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1644,24 +1642,24 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>10390000</v>
+      <c r="F18" s="8" t="n">
+        <v>9750000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>10000000</v>
+        <v>9420000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>10280000</v>
+        <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10390000</v>
+        <v>9750000</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1672,7 +1670,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>62340000</v>
+        <v>58500000</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1697,7 +1695,7 @@
       <c r="B19" s="2" t="n">
         <v>1814</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1710,33 +1708,33 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>9936000</v>
+      <c r="F19" s="8" t="n">
+        <v>9350000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>8900000</v>
+        <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9000000</v>
+        <v>9300000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9500000</v>
+        <v>9350000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+436,000 ت از رتبه ۳ ترب (+4.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>59616000</v>
+        <v>56100000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1761,7 +1759,7 @@
       <c r="B20" s="2" t="n">
         <v>2559</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1774,7 +1772,7 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
@@ -1791,7 +1789,7 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="10" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -1840,8 +1838,8 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>7376000</v>
+      <c r="F21" s="8" t="n">
+        <v>7260000</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>6799000</v>
@@ -1855,7 +1853,7 @@
       <c r="J21" s="6" t="n">
         <v>10558090</v>
       </c>
-      <c r="K21" s="10" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1866,7 +1864,7 @@
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>36880000</v>
+        <v>36300000</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1905,7 +1903,7 @@
         <v>5</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>15628000</v>
+        <v>17910000</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>18000000</v>
@@ -1921,7 +1919,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>16500000</v>
+        <v>17500000</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1930,11 +1928,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>-2,372,000 ت از کف ترب (-13.2%)</t>
+          <t>-90,000 ت از کف ترب (-0.5%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>78140000</v>
+        <v>89550000</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1972,8 +1970,8 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>8413000</v>
+      <c r="F23" s="8" t="n">
+        <v>11190000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7500000</v>
@@ -1987,18 +1985,18 @@
       <c r="J23" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>42065000</v>
+        <v>55950000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2023,7 +2021,7 @@
       <c r="B24" s="2" t="n">
         <v>1714</v>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2049,7 +2047,7 @@
         <v>5900000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7161100</v>
+        <v>6440000</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2087,7 +2085,7 @@
       <c r="B25" s="2" t="n">
         <v>2071</v>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2107,13 +2105,13 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6900000</v>
+        <v>7480000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7150000</v>
+        <v>7500000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>13800000</v>
+        <v>14290000</v>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
@@ -2122,7 +2120,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,750,000 ت از رتبه ۳ ترب (+66.4%)</t>
+          <t>+4,400,000 ت از رتبه ۳ ترب (+58.7%)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2151,7 +2149,7 @@
       <c r="B26" s="2" t="n">
         <v>1994</v>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2168,13 +2166,13 @@
         <v>13560000</v>
       </c>
       <c r="G26" s="6" t="n">
+        <v>7890000</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>7900000</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="6" t="n">
         <v>7980000</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>8260000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
@@ -2186,7 +2184,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>+5,300,000 ت از رتبه ۳ ترب (+64.2%)</t>
+          <t>+5,580,000 ت از رتبه ۳ ترب (+69.9%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
@@ -2211,7 +2209,7 @@
       <c r="B27" s="2" t="n">
         <v>2420</v>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2228,13 +2226,13 @@
         <v>16632000</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>12500000</v>
+        <v>14500000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14680000</v>
+        <v>14751744</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>15300000</v>
+        <v>15680000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
@@ -2246,7 +2244,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>+1,332,000 ت از رتبه ۳ ترب (+8.7%)</t>
+          <t>+952,000 ت از رتبه ۳ ترب (+6.1%)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
@@ -2271,7 +2269,7 @@
       <c r="B28" s="2" t="n">
         <v>2167</v>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2284,14 +2282,16 @@
       <c r="E28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="11" t="n">
         <v>7085000</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>7085000</v>
+        <v>7600000</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -2303,14 +2303,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-515,000 ت از کف ترب (-6.8%)</t>
         </is>
       </c>
       <c r="M28" s="6" t="n">
@@ -2356,13 +2356,13 @@
         <v>5335000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4890000</v>
+        <v>4980000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4900000</v>
+        <v>4990000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4950000</v>
+        <v>4995000</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>5599000</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
+          <t>+340,000 ت از رتبه ۳ ترب (+6.8%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
@@ -2469,7 +2469,7 @@
       <c r="B31" s="2" t="n">
         <v>1759</v>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2495,7 +2495,7 @@
         <v>14000000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>26500000</v>
+        <v>26990000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       <c r="B32" s="2" t="n">
         <v>1862</v>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2610,7 +2610,7 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
@@ -2620,14 +2620,14 @@
         <v>6399000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6479000</v>
+        <v>6500000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -2663,7 +2663,7 @@
       <c r="B34" s="2" t="n">
         <v>1930</v>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2676,29 +2676,29 @@
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>8700000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9260000</v>
+        <v>9350000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9350000</v>
+        <v>9450000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
@@ -2723,7 +2723,7 @@
       <c r="B35" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2736,7 +2736,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -2755,7 +2755,7 @@
       <c r="J35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="K35" s="10" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -2779,7 +2779,7 @@
       <c r="B36" s="2" t="n">
         <v>1958</v>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2796,10 +2796,10 @@
         <v>7528000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>6700000</v>
+        <v>6950000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>6950000</v>
@@ -2843,7 +2843,7 @@
       <c r="B37" s="2" t="n">
         <v>1958</v>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2860,10 +2860,10 @@
         <v>7528000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>6700000</v>
+        <v>6950000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>6950000</v>
@@ -2907,7 +2907,7 @@
       <c r="B38" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2920,22 +2920,22 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>14753000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>14250000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>14753000</v>
+        <v>14900000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>14900000</v>
+        <v>15700000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
-      <c r="K38" s="10" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -2971,7 +2971,7 @@
       <c r="B39" s="2" t="n">
         <v>1753</v>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2985,7 +2985,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4255000</v>
+        <v>4300000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>3800000</v>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+55,000 ت از رتبه ۳ ترب (+1.3%)</t>
+          <t>+100,000 ت از رتبه ۳ ترب (+2.4%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>12765000</v>
+        <v>12900000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
       <c r="B40" s="2" t="n">
         <v>2420</v>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3093,7 +3093,7 @@
       <c r="B41" s="2" t="n">
         <v>1980</v>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3161,7 +3161,7 @@
       <c r="B42" s="2" t="n">
         <v>2139</v>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3174,15 +3174,17 @@
       <c r="E42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="11" t="n">
         <v>3445000</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3445000</v>
-      </c>
-      <c r="H42" s="6" t="n">
         <v>4150000</v>
       </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -3193,14 +3195,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>-705,000 ت از کف ترب (-17.0%)</t>
         </is>
       </c>
       <c r="M42" s="6" t="n">
@@ -3225,7 +3227,7 @@
       <c r="B43" s="2" t="n">
         <v>2133</v>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3248,7 +3250,7 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7700000</v>
+        <v>7880000</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3262,7 +3264,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+270,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+90,000 ت از رتبه ۳ ترب (+1.1%)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
@@ -3291,7 +3293,7 @@
       <c r="B44" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3383,7 +3385,7 @@
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7600000</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3442,29 +3444,29 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>1210000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>2839550</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
+        <v>3680000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+1,120,000 ت از رتبه ۳ ترب (+30.4%)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3506,16 +3508,16 @@
         <v>6080000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5616000</v>
+        <v>5650000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5650000</v>
+        <v>5899000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>5698000</v>
+        <v>5900000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7161100</v>
+        <v>6440000</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3524,7 +3526,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+382,000 ت از رتبه ۳ ترب (+6.7%)</t>
+          <t>+180,000 ت از رتبه ۳ ترب (+3.1%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
@@ -3706,8 +3708,10 @@
       <c r="I50" s="6" t="n">
         <v>6850000</v>
       </c>
-      <c r="J50" s="6" t="n">
-        <v>7590000</v>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
@@ -4024,7 +4028,7 @@
       <c r="E55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="9" t="n">
+      <c r="F55" s="8" t="n">
         <v>10768000</v>
       </c>
       <c r="G55" s="6" t="n">
@@ -4039,7 +4043,7 @@
       <c r="J55" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K55" s="10" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4141,7 +4145,7 @@
       <c r="B57" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4203,7 +4207,7 @@
       <c r="B58" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4216,7 +4220,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="8" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -4233,9 +4237,9 @@
         </is>
       </c>
       <c r="J58" s="6" t="n">
-        <v>7911200</v>
-      </c>
-      <c r="K58" s="10" t="inlineStr">
+        <v>9900000</v>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -4267,7 +4271,7 @@
       <c r="B59" s="2" t="n">
         <v>1775</v>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4331,7 +4335,7 @@
       <c r="B60" s="2" t="n">
         <v>1902</v>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4359,7 +4363,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7502000</v>
+        <v>7600000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4397,7 +4401,7 @@
       <c r="B61" s="2" t="n">
         <v>3231</v>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4463,7 +4467,7 @@
       <c r="B62" s="2" t="n">
         <v>2092</v>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4489,7 +4493,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4449000</v>
+        <v>4908200</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4527,7 +4531,7 @@
       <c r="B63" s="2" t="n">
         <v>1926</v>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4593,7 +4597,7 @@
       <c r="B64" s="2" t="n">
         <v>1819</v>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4657,7 +4661,7 @@
       <c r="B65" s="2" t="n">
         <v>2066</v>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4723,7 +4727,7 @@
       <c r="B66" s="2" t="n">
         <v>1942</v>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4779,7 +4783,7 @@
       <c r="B67" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4849,7 +4853,7 @@
       <c r="B68" s="2" t="n">
         <v>3240</v>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4913,7 +4917,7 @@
       <c r="B69" s="2" t="n">
         <v>2009</v>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4926,7 +4930,7 @@
       <c r="E69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="9" t="n">
+      <c r="F69" s="8" t="n">
         <v>14353000</v>
       </c>
       <c r="G69" s="6" t="n">
@@ -4941,7 +4945,7 @@
       <c r="J69" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="K69" s="10" t="inlineStr">
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4977,7 +4981,7 @@
       <c r="B70" s="2" t="n">
         <v>1885</v>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5045,7 +5049,7 @@
       <c r="B71" s="2" t="n">
         <v>1991</v>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5111,7 +5115,7 @@
       <c r="B72" s="2" t="n">
         <v>1914</v>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5179,7 +5183,7 @@
       <c r="B73" s="2" t="n">
         <v>2127</v>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5269,7 +5273,7 @@
         <v>9200000</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
@@ -5453,7 +5457,7 @@
         <v>9200000</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
@@ -5517,7 +5521,7 @@
         <v>9200000</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
@@ -5709,7 +5713,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7800000</v>
+        <v>7700000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -5775,7 +5779,7 @@
         </is>
       </c>
       <c r="J82" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
@@ -5963,7 +5967,7 @@
         <v>9200000</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
@@ -6365,7 +6369,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4449000</v>
+        <v>4908200</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6429,7 +6433,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3798600</v>
+        <v>3792000</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -6625,7 +6629,7 @@
         <v>21350000</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>27900000</v>
+        <v>27850000</v>
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
@@ -6816,7 +6820,7 @@
       <c r="E98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="9" t="n">
+      <c r="F98" s="8" t="n">
         <v>10768000</v>
       </c>
       <c r="G98" s="6" t="n">
@@ -6831,7 +6835,7 @@
       <c r="J98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K98" s="10" t="inlineStr">
+      <c r="K98" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -6931,7 +6935,7 @@
       <c r="B100" s="2" t="n">
         <v>1997</v>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6997,7 +7001,7 @@
       <c r="B101" s="2" t="n">
         <v>3250</v>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7055,7 +7059,7 @@
       <c r="B102" s="2" t="n">
         <v>3229</v>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7068,7 +7072,7 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="9" t="n">
+      <c r="F102" s="8" t="n">
         <v>25920000</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -7085,7 +7089,7 @@
       <c r="J102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="K102" s="10" t="inlineStr">
+      <c r="K102" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -7113,7 +7117,7 @@
       <c r="B103" s="2" t="n">
         <v>1840</v>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7126,10 +7130,8 @@
       <c r="E103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F103" s="6" t="n">
+        <v>9900000</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -7153,16 +7155,16 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="M103" s="6" t="n">
-        <v>0</v>
+        <v>9900000</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
@@ -7187,7 +7189,7 @@
       <c r="B104" s="2" t="n">
         <v>2554</v>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7251,7 +7253,7 @@
       <c r="B105" s="2" t="n">
         <v>3227</v>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7277,7 +7279,7 @@
         <v>4699000</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>5300000</v>
+        <v>7100000</v>
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
@@ -7315,7 +7317,7 @@
       <c r="B106" s="2" t="n">
         <v>3232</v>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7381,7 +7383,7 @@
       <c r="B107" s="2" t="n">
         <v>3242</v>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7455,7 +7457,7 @@
       <c r="B108" s="2" t="n">
         <v>1868</v>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7481,7 +7483,7 @@
         <v>9699000</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>14590000</v>
+        <v>14550000</v>
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
@@ -7519,7 +7521,7 @@
       <c r="B109" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7532,7 +7534,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F109" s="8" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -7553,7 +7555,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K109" s="10" t="inlineStr">
+      <c r="K109" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -7585,7 +7587,7 @@
       <c r="B110" s="2" t="n">
         <v>3228</v>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7655,7 +7657,7 @@
       <c r="B111" s="2" t="n">
         <v>3233</v>
       </c>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7729,7 +7731,7 @@
       <c r="B112" s="2" t="n">
         <v>3251</v>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7803,7 +7805,7 @@
       <c r="B113" s="2" t="n">
         <v>1948</v>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7867,7 +7869,7 @@
       <c r="B114" s="2" t="n">
         <v>1783</v>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7931,7 +7933,7 @@
       <c r="B115" s="2" t="n">
         <v>2082</v>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -7997,7 +7999,7 @@
       <c r="B116" s="2" t="n">
         <v>1809</v>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8023,7 +8025,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3798600</v>
+        <v>3792000</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
@@ -8061,7 +8063,7 @@
       <c r="B117" s="2" t="n">
         <v>3239</v>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8129,7 +8131,7 @@
       <c r="B118" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8142,7 +8144,7 @@
       <c r="E118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="9" t="n">
+      <c r="F118" s="8" t="n">
         <v>6696000</v>
       </c>
       <c r="G118" s="6" t="n">
@@ -8159,7 +8161,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K118" s="10" t="inlineStr">
+      <c r="K118" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8195,7 +8197,7 @@
       <c r="B119" s="2" t="n">
         <v>2115</v>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8259,7 +8261,7 @@
       <c r="B120" s="2" t="n">
         <v>2563</v>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8325,7 +8327,7 @@
       <c r="B121" s="2" t="n">
         <v>2567</v>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8387,7 +8389,7 @@
       <c r="B122" s="2" t="n">
         <v>1862</v>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8451,7 +8453,7 @@
       <c r="B123" s="2" t="n">
         <v>1846</v>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8511,7 +8513,7 @@
       <c r="B124" s="2" t="n">
         <v>1851</v>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8581,7 +8583,7 @@
       <c r="B125" s="2" t="n">
         <v>3244</v>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8647,7 +8649,7 @@
       <c r="B126" s="2" t="n">
         <v>2566</v>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8711,7 +8713,7 @@
       <c r="B127" s="2" t="n">
         <v>2150</v>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8785,7 +8787,7 @@
       <c r="B128" s="2" t="n">
         <v>1879</v>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8798,7 +8800,7 @@
       <c r="E128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="9" t="n">
+      <c r="F128" s="8" t="n">
         <v>10768000</v>
       </c>
       <c r="G128" s="6" t="n">
@@ -8813,7 +8815,7 @@
       <c r="J128" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K128" s="10" t="inlineStr">
+      <c r="K128" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8849,7 +8851,7 @@
       <c r="B129" s="2" t="n">
         <v>1908</v>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8923,7 +8925,7 @@
       <c r="B130" s="2" t="n">
         <v>2558</v>
       </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8989,7 +8991,7 @@
       <c r="B131" s="2" t="n">
         <v>2052</v>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9055,7 +9057,7 @@
       <c r="B132" s="2" t="n">
         <v>1986</v>
       </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9121,7 +9123,7 @@
       <c r="B133" s="2" t="n">
         <v>1770</v>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9134,8 +9136,8 @@
       <c r="E133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="9" t="n">
-        <v>8413000</v>
+      <c r="F133" s="8" t="n">
+        <v>11190000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9149,7 +9151,7 @@
       <c r="J133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K133" s="10" t="inlineStr">
+      <c r="K133" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9160,7 +9162,7 @@
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>8413000</v>
+        <v>11190000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9185,7 +9187,7 @@
       <c r="B134" s="2" t="n">
         <v>3236</v>
       </c>
-      <c r="C134" s="8" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -57,14 +57,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -619,32 +619,32 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9550000</v>
+        <v>9470000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9250000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9250000</v>
+        <v>9400000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9400000</v>
+        <v>9470000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>11000000</v>
+        <v>11450000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه ۳ ترب (+1.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1804950000</v>
+        <v>1789830000</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -682,33 +682,33 @@
       <c r="E3" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F3" s="8" t="n">
-        <v>15660000</v>
+      <c r="F3" s="5" t="n">
+        <v>15750000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14590000</v>
+        <v>15750000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>15660000</v>
+        <v>15840000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15840000</v>
+        <v>15890000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>15990000</v>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>20590000</v>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>986580000</v>
+        <v>992250000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -746,22 +746,22 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>12930000</v>
+      <c r="F4" s="5" t="n">
+        <v>12900000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>12870000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12930000</v>
+        <v>12900000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12990000</v>
+        <v>13520000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12990000</v>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+        <v>17190000</v>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>387900000</v>
+        <v>387000000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -811,32 +811,32 @@
         <v>18</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>5420000</v>
+        <v>5750000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5400000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5420000</v>
+        <v>5500000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5450000</v>
+        <v>5500000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>5999000</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+250,000 ت از رتبه ۳ ترب (+4.5%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>97560000</v>
+        <v>103500000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -874,11 +874,11 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="5" t="n">
         <v>6500000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6950000</v>
+        <v>7350000</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>6450000</v>
@@ -889,7 +889,7 @@
       <c r="J6" s="6" t="n">
         <v>9560380</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -938,8 +938,8 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>4300000</v>
+      <c r="F7" s="8" t="n">
+        <v>4349000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3800000</v>
@@ -951,20 +951,20 @@
         <v>4200000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
+        <v>4250000</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+100,000 ت از رتبه ۳ ترب (+2.4%)</t>
+          <t>+149,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>64500000</v>
+        <v>65235000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="5" t="n">
         <v>1760000</v>
       </c>
       <c r="G8" s="6" t="n">
@@ -1023,7 +1023,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -1072,7 +1072,7 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="5" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
@@ -1087,7 +1087,7 @@
       <c r="J9" s="6" t="n">
         <v>195000</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -1132,33 +1132,33 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <v>9350000</v>
+      <c r="F10" s="5" t="n">
+        <v>9220000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
+        <v>9220000</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="I10" s="6" t="n">
-        <v>9350000</v>
-      </c>
       <c r="J10" s="6" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>10800000</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>102850000</v>
+        <v>101420000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1196,14 +1196,14 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>7260000</v>
+      <c r="F11" s="5" t="n">
+        <v>7600000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6930000</v>
+        <v>7600000</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>7600000</v>
@@ -1211,18 +1211,18 @@
       <c r="J11" s="6" t="n">
         <v>10558090</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>79860000</v>
+        <v>83600000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1260,8 +1260,8 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>4870000</v>
+      <c r="F12" s="5" t="n">
+        <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
@@ -1270,12 +1270,12 @@
         <v>4700000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5150000</v>
+        <v>5190000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
+        <v>5700000</v>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>48700000</v>
+        <v>49500000</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1380,33 +1380,33 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>19510000</v>
+      <c r="F14" s="8" t="n">
+        <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11480000</v>
+        <v>11500000</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>11500000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11690000</v>
+        <v>11670000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>20400000</v>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
+        <v>20500000</v>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>+7,820,000 ت از رتبه ۳ ترب (+66.9%)</t>
+          <t>+8,180,000 ت از رتبه ۳ ترب (+70.1%)</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>156080000</v>
+        <v>158800000</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1445,32 +1445,32 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>6740000</v>
+        <v>6950000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6500000</v>
+        <v>6950000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6695000</v>
+        <v>7100000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7700000</v>
+        <v>8650000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+45,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>47180000</v>
+        <v>48650000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1508,33 +1508,33 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>4690000</v>
+      <c r="F16" s="5" t="n">
+        <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4680000</v>
+        <v>4620000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4690000</v>
+        <v>4700000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>6823370</v>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>6800000</v>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>32830000</v>
+        <v>32340000</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1572,11 +1572,11 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="11" t="n">
         <v>9900000</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>9000000</v>
+        <v>12000000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>+900,000 ت از رتبه ۳ ترب (+10.0%)</t>
+          <t>-2,100,000 ت از کف ترب (-17.5%)</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
@@ -1642,8 +1642,8 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>9750000</v>
+      <c r="F18" s="5" t="n">
+        <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>9420000</v>
@@ -1652,14 +1652,12 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9750000</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
+        <v>9620000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1670,7 +1668,7 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>58500000</v>
+        <v>57720000</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1708,33 +1706,33 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="8" t="n">
-        <v>9350000</v>
+      <c r="F19" s="5" t="n">
+        <v>9220000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
+        <v>9220000</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="I19" s="6" t="n">
-        <v>9350000</v>
-      </c>
       <c r="J19" s="6" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>10800000</v>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>56100000</v>
+        <v>55320000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1772,7 +1770,7 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="5" t="n">
         <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
@@ -1789,7 +1787,7 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -1838,14 +1836,14 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>7260000</v>
+      <c r="F21" s="5" t="n">
+        <v>7600000</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>6799000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6930000</v>
+        <v>7600000</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>7600000</v>
@@ -1853,18 +1851,18 @@
       <c r="J21" s="6" t="n">
         <v>10558090</v>
       </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>36300000</v>
+        <v>38000000</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1919,7 +1917,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>17500000</v>
+        <v>17865000</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
@@ -1970,14 +1968,14 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>11190000</v>
+      <c r="F23" s="5" t="n">
+        <v>11350000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9080000</v>
+        <v>9400000</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>13300000</v>
@@ -1985,7 +1983,7 @@
       <c r="J23" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -1996,7 +1994,7 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>55950000</v>
+        <v>56750000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2035,32 +2033,32 @@
         <v>5</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>6080000</v>
+        <v>5910000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>5650000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5899000</v>
+        <v>5910000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5900000</v>
+        <v>6000000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6440000</v>
+        <v>7257200</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+180,000 ت از رتبه ۳ ترب (+3.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>30400000</v>
+        <v>29550000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2098,7 +2096,7 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="8" t="n">
         <v>11900000</v>
       </c>
       <c r="G25" s="6" t="n">
@@ -2111,9 +2109,9 @@
         <v>7500000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>14290000</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
+        <v>12590000</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2162,7 +2160,7 @@
       <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="8" t="n">
         <v>13560000</v>
       </c>
       <c r="G26" s="6" t="n">
@@ -2177,7 +2175,7 @@
       <c r="J26" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2222,29 +2220,29 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="8" t="n">
         <v>16632000</v>
       </c>
       <c r="G27" s="6" t="n">
+        <v>12320000</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="H27" s="6" t="n">
-        <v>14751744</v>
-      </c>
       <c r="I27" s="6" t="n">
-        <v>15680000</v>
+        <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>+952,000 ت از رتبه ۳ ترب (+6.1%)</t>
+          <t>+1,132,000 ت از رتبه ۳ ترب (+7.3%)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
@@ -2352,29 +2350,29 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="8" t="n">
         <v>5335000</v>
       </c>
       <c r="G29" s="6" t="n">
+        <v>4890000</v>
+      </c>
+      <c r="H29" s="6" t="n">
         <v>4980000</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>4990000</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>4995000</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>5599000</v>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+340,000 ت از رتبه ۳ ترب (+6.8%)</t>
+          <t>+345,000 ت از رتبه ۳ ترب (+6.9%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
@@ -2492,19 +2490,19 @@
         <v>13900000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>14000000</v>
+        <v>14900000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>26990000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+332,000 ت از رتبه ۳ ترب (+2.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2546,7 +2544,7 @@
       <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="8" t="n">
         <v>12528000</v>
       </c>
       <c r="G32" s="6" t="n">
@@ -2561,7 +2559,7 @@
       <c r="J32" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2610,31 +2608,31 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="5" t="n">
         <v>6479000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6399000</v>
+        <v>6500000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6500000</v>
+        <v>6999000</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
@@ -2676,14 +2674,14 @@
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="5" t="n">
         <v>9342000</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>8700000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9350000</v>
+        <v>9440000</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>9450000</v>
@@ -2691,7 +2689,7 @@
       <c r="J34" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -2736,7 +2734,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="F35" s="5" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -2755,7 +2753,7 @@
       <c r="J35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -2792,14 +2790,14 @@
       <c r="E36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="8" t="n">
         <v>7528000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6700000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>6950000</v>
@@ -2807,7 +2805,7 @@
       <c r="J36" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2856,14 +2854,14 @@
       <c r="E37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="8" t="n">
         <v>7528000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6700000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>6950000</v>
+        <v>6900000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>6950000</v>
@@ -2871,7 +2869,7 @@
       <c r="J37" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K37" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2920,7 +2918,7 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="5" t="n">
         <v>14753000</v>
       </c>
       <c r="G38" s="6" t="n">
@@ -2930,12 +2928,12 @@
         <v>14900000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>15700000</v>
+        <v>15750000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -2984,8 +2982,8 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>4300000</v>
+      <c r="F39" s="8" t="n">
+        <v>4349000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>3800000</v>
@@ -2997,20 +2995,20 @@
         <v>4200000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
+        <v>4250000</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+100,000 ت از رتبه ۳ ترب (+2.4%)</t>
+          <t>+149,000 ت از رتبه ۳ ترب (+3.5%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>12900000</v>
+        <v>13047000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3048,7 +3046,7 @@
       <c r="E40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="8" t="n">
         <v>16632000</v>
       </c>
       <c r="G40" s="6" t="n">
@@ -3065,7 +3063,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3106,7 +3104,7 @@
       <c r="E41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="8" t="n">
         <v>14580000</v>
       </c>
       <c r="G41" s="6" t="n">
@@ -3125,7 +3123,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3240,7 +3238,7 @@
       <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="8" t="n">
         <v>7970000</v>
       </c>
       <c r="G43" s="6" t="n">
@@ -3257,7 +3255,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3378,14 +3376,14 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>8132000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7600000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7607000</v>
@@ -3395,7 +3393,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3448,25 +3446,25 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1210000</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>2839550</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>3680000</v>
+        <v>4800000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>+1,120,000 ت از رتبه ۳ ترب (+30.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M46" s="6" t="n">
@@ -3504,33 +3502,33 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>6080000</v>
+      <c r="F47" s="8" t="n">
+        <v>5910000</v>
       </c>
       <c r="G47" s="6" t="n">
+        <v>5616000</v>
+      </c>
+      <c r="H47" s="6" t="n">
         <v>5650000</v>
       </c>
-      <c r="H47" s="6" t="n">
-        <v>5899000</v>
-      </c>
       <c r="I47" s="6" t="n">
-        <v>5900000</v>
+        <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>6440000</v>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
+        <v>7257200</v>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+180,000 ت از رتبه ۳ ترب (+3.1%)</t>
+          <t>+212,000 ت از رتبه ۳ ترب (+3.7%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>12160000</v>
+        <v>11820000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3568,8 +3566,8 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>9396000</v>
+      <c r="F48" s="8" t="n">
+        <v>9350000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -3583,18 +3581,18 @@
       <c r="J48" s="6" t="n">
         <v>13500000</v>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K48" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>+296,000 ت از رتبه ۳ ترب (+3.3%)</t>
+          <t>+250,000 ت از رتبه ۳ ترب (+2.7%)</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>18792000</v>
+        <v>18700000</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3632,7 +3630,7 @@
       <c r="E49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="8" t="n">
         <v>3455000</v>
       </c>
       <c r="G49" s="6" t="n">
@@ -3645,9 +3643,9 @@
         <v>3150000</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>4385000</v>
-      </c>
-      <c r="K49" s="7" t="inlineStr">
+        <v>4350000</v>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3696,7 +3694,7 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="8" t="n">
         <v>7927000</v>
       </c>
       <c r="G50" s="6" t="n">
@@ -3713,7 +3711,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3762,7 +3760,7 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="8" t="n">
         <v>14753000</v>
       </c>
       <c r="G51" s="6" t="n">
@@ -3777,7 +3775,7 @@
       <c r="J51" s="6" t="n">
         <v>16750000</v>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K51" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3826,7 +3824,7 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="8" t="n">
         <v>12366000</v>
       </c>
       <c r="G52" s="6" t="n">
@@ -3841,7 +3839,7 @@
       <c r="J52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3890,7 +3888,7 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="8" t="n">
         <v>9439000</v>
       </c>
       <c r="G53" s="6" t="n">
@@ -3905,7 +3903,7 @@
       <c r="J53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4028,7 +4026,7 @@
       <c r="E55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="5" t="n">
         <v>10768000</v>
       </c>
       <c r="G55" s="6" t="n">
@@ -4043,7 +4041,7 @@
       <c r="J55" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4092,7 +4090,7 @@
       <c r="E56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="8" t="n">
         <v>6426000</v>
       </c>
       <c r="G56" s="6" t="n">
@@ -4109,7 +4107,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4220,7 +4218,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="F58" s="5" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -4239,7 +4237,7 @@
       <c r="J58" s="6" t="n">
         <v>9900000</v>
       </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -4284,7 +4282,7 @@
       <c r="E59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="8" t="n">
         <v>9958000</v>
       </c>
       <c r="G59" s="6" t="n">
@@ -4299,7 +4297,7 @@
       <c r="J59" s="6" t="n">
         <v>9700000</v>
       </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4363,7 +4361,7 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>7600000</v>
+        <v>8652000</v>
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
@@ -4414,7 +4412,7 @@
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="8" t="n">
         <v>13424000</v>
       </c>
       <c r="G61" s="6" t="n">
@@ -4431,7 +4429,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4480,7 +4478,7 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F62" s="8" t="n">
         <v>4828000</v>
       </c>
       <c r="G62" s="6" t="n">
@@ -4493,9 +4491,9 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4908200</v>
-      </c>
-      <c r="K62" s="7" t="inlineStr">
+        <v>4905200</v>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4544,7 +4542,7 @@
       <c r="E63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="F63" s="8" t="n">
         <v>23846000</v>
       </c>
       <c r="G63" s="6" t="n">
@@ -4561,7 +4559,7 @@
       <c r="J63" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4610,7 +4608,7 @@
       <c r="E64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="8" t="n">
         <v>5335000</v>
       </c>
       <c r="G64" s="6" t="n">
@@ -4625,7 +4623,7 @@
       <c r="J64" s="6" t="n">
         <v>5599000</v>
       </c>
-      <c r="K64" s="7" t="inlineStr">
+      <c r="K64" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4674,7 +4672,7 @@
       <c r="E65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="8" t="n">
         <v>2862000</v>
       </c>
       <c r="G65" s="6" t="n">
@@ -4691,7 +4689,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K65" s="7" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4740,7 +4738,7 @@
       <c r="E66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="8" t="n">
         <v>16848000</v>
       </c>
       <c r="G66" s="6" t="n">
@@ -4755,7 +4753,7 @@
       <c r="J66" s="6" t="n">
         <v>16019000</v>
       </c>
-      <c r="K66" s="7" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4796,7 +4794,7 @@
       <c r="E67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="8" t="n">
         <v>7430000</v>
       </c>
       <c r="G67" s="6" t="n">
@@ -4817,7 +4815,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4866,7 +4864,7 @@
       <c r="E68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="8" t="n">
         <v>4612000</v>
       </c>
       <c r="G68" s="6" t="n">
@@ -4881,7 +4879,7 @@
       <c r="J68" s="6" t="n">
         <v>4326110</v>
       </c>
-      <c r="K68" s="7" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4930,7 +4928,7 @@
       <c r="E69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="8" t="n">
+      <c r="F69" s="5" t="n">
         <v>14353000</v>
       </c>
       <c r="G69" s="6" t="n">
@@ -4945,7 +4943,7 @@
       <c r="J69" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4994,7 +4992,7 @@
       <c r="E70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="8" t="n">
         <v>8986000</v>
       </c>
       <c r="G70" s="6" t="n">
@@ -5013,7 +5011,7 @@
       <c r="J70" s="6" t="n">
         <v>15000000</v>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5062,7 +5060,7 @@
       <c r="E71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="8" t="n">
         <v>7819000</v>
       </c>
       <c r="G71" s="6" t="n">
@@ -5079,7 +5077,7 @@
       <c r="J71" s="6" t="n">
         <v>9700000</v>
       </c>
-      <c r="K71" s="7" t="inlineStr">
+      <c r="K71" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5128,7 +5126,7 @@
       <c r="E72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="8" t="n">
         <v>18457000</v>
       </c>
       <c r="G72" s="6" t="n">
@@ -5147,7 +5145,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="K72" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5196,7 +5194,7 @@
       <c r="E73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="8" t="n">
         <v>4018000</v>
       </c>
       <c r="G73" s="6" t="n">
@@ -5211,7 +5209,7 @@
       <c r="J73" s="6" t="n">
         <v>4870000</v>
       </c>
-      <c r="K73" s="7" t="inlineStr">
+      <c r="K73" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5260,7 +5258,7 @@
       <c r="E74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="8" t="n">
         <v>9936000</v>
       </c>
       <c r="G74" s="6" t="n">
@@ -5275,7 +5273,7 @@
       <c r="J74" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K74" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5324,7 +5322,7 @@
       <c r="E75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="8" t="n">
         <v>18900000</v>
       </c>
       <c r="G75" s="6" t="n">
@@ -5339,7 +5337,7 @@
       <c r="J75" s="6" t="n">
         <v>23900000</v>
       </c>
-      <c r="K75" s="7" t="inlineStr">
+      <c r="K75" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5384,7 +5382,7 @@
       <c r="E76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="8" t="n">
         <v>25920000</v>
       </c>
       <c r="G76" s="6" t="n">
@@ -5399,7 +5397,7 @@
       <c r="J76" s="6" t="n">
         <v>36400000</v>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="K76" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5444,7 +5442,7 @@
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="8" t="n">
         <v>10044000</v>
       </c>
       <c r="G77" s="6" t="n">
@@ -5459,7 +5457,7 @@
       <c r="J77" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="K77" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5508,7 +5506,7 @@
       <c r="E78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="8" t="n">
         <v>9936000</v>
       </c>
       <c r="G78" s="6" t="n">
@@ -5523,7 +5521,7 @@
       <c r="J78" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5572,7 +5570,7 @@
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="8" t="n">
         <v>4234000</v>
       </c>
       <c r="G79" s="6" t="n">
@@ -5585,9 +5583,9 @@
         <v>3855000</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>4630000</v>
-      </c>
-      <c r="K79" s="7" t="inlineStr">
+        <v>4824000</v>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5636,7 +5634,7 @@
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="8" t="n">
         <v>16199000</v>
       </c>
       <c r="G80" s="6" t="n">
@@ -5649,9 +5647,9 @@
         <v>14990000</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>24400000</v>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
+        <v>29987800</v>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5700,7 +5698,7 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="8" t="n">
         <v>6799000</v>
       </c>
       <c r="G81" s="6" t="n">
@@ -5713,9 +5711,9 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>7700000</v>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
+        <v>8660000</v>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5764,7 +5762,7 @@
       <c r="E82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F82" s="8" t="n">
         <v>6458000</v>
       </c>
       <c r="G82" s="6" t="n">
@@ -5781,7 +5779,7 @@
       <c r="J82" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="K82" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5830,7 +5828,7 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="8" t="n">
         <v>14035000</v>
       </c>
       <c r="G83" s="6" t="n">
@@ -5843,9 +5841,9 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>14300000</v>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
+        <v>26000000</v>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5894,7 +5892,7 @@
       <c r="E84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="8" t="n">
         <v>2916000</v>
       </c>
       <c r="G84" s="6" t="n">
@@ -5909,7 +5907,7 @@
       <c r="J84" s="6" t="n">
         <v>3795000</v>
       </c>
-      <c r="K84" s="7" t="inlineStr">
+      <c r="K84" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5954,7 +5952,7 @@
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="8" t="n">
         <v>10098000</v>
       </c>
       <c r="G85" s="6" t="n">
@@ -5969,7 +5967,7 @@
       <c r="J85" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="K85" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6092,7 +6090,7 @@
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F87" s="8" t="n">
         <v>4558000</v>
       </c>
       <c r="G87" s="6" t="n">
@@ -6113,7 +6111,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K87" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6162,7 +6160,7 @@
       <c r="E88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F88" s="8" t="n">
         <v>7992000</v>
       </c>
       <c r="G88" s="6" t="n">
@@ -6179,7 +6177,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="K88" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6228,7 +6226,7 @@
       <c r="E89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" s="8" t="n">
         <v>7528000</v>
       </c>
       <c r="G89" s="6" t="n">
@@ -6243,7 +6241,7 @@
       <c r="J89" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K89" s="7" t="inlineStr">
+      <c r="K89" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6292,7 +6290,7 @@
       <c r="E90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="5" t="n">
+      <c r="F90" s="8" t="n">
         <v>7528000</v>
       </c>
       <c r="G90" s="6" t="n">
@@ -6307,7 +6305,7 @@
       <c r="J90" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K90" s="7" t="inlineStr">
+      <c r="K90" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6356,7 +6354,7 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="8" t="n">
         <v>4828000</v>
       </c>
       <c r="G91" s="6" t="n">
@@ -6369,9 +6367,9 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4908200</v>
-      </c>
-      <c r="K91" s="7" t="inlineStr">
+        <v>4905200</v>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6420,7 +6418,7 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="8" t="n">
         <v>3499000</v>
       </c>
       <c r="G92" s="6" t="n">
@@ -6433,9 +6431,9 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3792000</v>
-      </c>
-      <c r="K92" s="7" t="inlineStr">
+        <v>3933400</v>
+      </c>
+      <c r="K92" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6484,7 +6482,7 @@
       <c r="E93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="8" t="n">
         <v>7571000</v>
       </c>
       <c r="G93" s="6" t="n">
@@ -6499,7 +6497,7 @@
       <c r="J93" s="6" t="n">
         <v>8550000</v>
       </c>
-      <c r="K93" s="7" t="inlineStr">
+      <c r="K93" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6548,7 +6546,7 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="5" t="n">
+      <c r="F94" s="8" t="n">
         <v>6394000</v>
       </c>
       <c r="G94" s="6" t="n">
@@ -6567,7 +6565,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K94" s="7" t="inlineStr">
+      <c r="K94" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6616,7 +6614,7 @@
       <c r="E95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F95" s="8" t="n">
         <v>23058000</v>
       </c>
       <c r="G95" s="6" t="n">
@@ -6631,7 +6629,7 @@
       <c r="J95" s="6" t="n">
         <v>27850000</v>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="K95" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6680,7 +6678,7 @@
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F96" s="8" t="n">
         <v>4882000</v>
       </c>
       <c r="G96" s="6" t="n">
@@ -6701,7 +6699,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K96" s="7" t="inlineStr">
+      <c r="K96" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6750,7 +6748,7 @@
       <c r="E97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="5" t="n">
+      <c r="F97" s="8" t="n">
         <v>8986000</v>
       </c>
       <c r="G97" s="6" t="n">
@@ -6771,7 +6769,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="K97" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6820,7 +6818,7 @@
       <c r="E98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="5" t="n">
         <v>10768000</v>
       </c>
       <c r="G98" s="6" t="n">
@@ -6835,7 +6833,7 @@
       <c r="J98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -6884,7 +6882,7 @@
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F99" s="8" t="n">
         <v>4018000</v>
       </c>
       <c r="G99" s="6" t="n">
@@ -6899,7 +6897,7 @@
       <c r="J99" s="6" t="n">
         <v>4870000</v>
       </c>
-      <c r="K99" s="7" t="inlineStr">
+      <c r="K99" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6948,7 +6946,7 @@
       <c r="E100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F100" s="8" t="n">
         <v>3866000</v>
       </c>
       <c r="G100" s="6" t="n">
@@ -6965,7 +6963,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="K100" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7014,7 +7012,7 @@
       <c r="E101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F101" s="8" t="n">
         <v>3370000</v>
       </c>
       <c r="G101" s="6" t="n">
@@ -7031,7 +7029,7 @@
       <c r="J101" s="6" t="n">
         <v>3200000</v>
       </c>
-      <c r="K101" s="7" t="inlineStr">
+      <c r="K101" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7072,7 +7070,7 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="8" t="n">
+      <c r="F102" s="5" t="n">
         <v>25920000</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -7089,7 +7087,7 @@
       <c r="J102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="K102" s="9" t="inlineStr">
+      <c r="K102" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -7202,7 +7200,7 @@
       <c r="E104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="5" t="n">
+      <c r="F104" s="8" t="n">
         <v>4234000</v>
       </c>
       <c r="G104" s="6" t="n">
@@ -7215,9 +7213,9 @@
         <v>3855000</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>4630000</v>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
+        <v>4824000</v>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7266,7 +7264,7 @@
       <c r="E105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="5" t="n">
+      <c r="F105" s="8" t="n">
         <v>4730000</v>
       </c>
       <c r="G105" s="6" t="n">
@@ -7281,7 +7279,7 @@
       <c r="J105" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K105" s="7" t="inlineStr">
+      <c r="K105" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7330,7 +7328,7 @@
       <c r="E106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F106" s="8" t="n">
         <v>14116000</v>
       </c>
       <c r="G106" s="6" t="n">
@@ -7347,7 +7345,7 @@
       <c r="J106" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="K106" s="7" t="inlineStr">
+      <c r="K106" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7470,7 +7468,7 @@
       <c r="E108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="5" t="n">
+      <c r="F108" s="8" t="n">
         <v>10357000</v>
       </c>
       <c r="G108" s="6" t="n">
@@ -7485,7 +7483,7 @@
       <c r="J108" s="6" t="n">
         <v>14550000</v>
       </c>
-      <c r="K108" s="7" t="inlineStr">
+      <c r="K108" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7534,7 +7532,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="5" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -7555,7 +7553,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K109" s="9" t="inlineStr">
+      <c r="K109" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -7600,7 +7598,7 @@
       <c r="E110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F110" s="8" t="n">
         <v>5962000</v>
       </c>
       <c r="G110" s="6" t="n">
@@ -7621,7 +7619,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K110" s="7" t="inlineStr">
+      <c r="K110" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7818,7 +7816,7 @@
       <c r="E113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="5" t="n">
+      <c r="F113" s="8" t="n">
         <v>6772000</v>
       </c>
       <c r="G113" s="6" t="n">
@@ -7833,7 +7831,7 @@
       <c r="J113" s="6" t="n">
         <v>7900000</v>
       </c>
-      <c r="K113" s="7" t="inlineStr">
+      <c r="K113" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7882,7 +7880,7 @@
       <c r="E114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F114" s="8" t="n">
         <v>10951000</v>
       </c>
       <c r="G114" s="6" t="n">
@@ -7897,7 +7895,7 @@
       <c r="J114" s="6" t="n">
         <v>11290000</v>
       </c>
-      <c r="K114" s="7" t="inlineStr">
+      <c r="K114" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7946,7 +7944,7 @@
       <c r="E115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F115" s="5" t="n">
+      <c r="F115" s="8" t="n">
         <v>10152000</v>
       </c>
       <c r="G115" s="6" t="n">
@@ -7963,7 +7961,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr">
+      <c r="K115" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8012,7 +8010,7 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="5" t="n">
+      <c r="F116" s="8" t="n">
         <v>3499000</v>
       </c>
       <c r="G116" s="6" t="n">
@@ -8025,9 +8023,9 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>3792000</v>
-      </c>
-      <c r="K116" s="7" t="inlineStr">
+        <v>4119900</v>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8076,7 +8074,7 @@
       <c r="E117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F117" s="5" t="n">
+      <c r="F117" s="8" t="n">
         <v>5314000</v>
       </c>
       <c r="G117" s="6" t="n">
@@ -8095,7 +8093,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K117" s="7" t="inlineStr">
+      <c r="K117" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8144,7 +8142,7 @@
       <c r="E118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="8" t="n">
+      <c r="F118" s="5" t="n">
         <v>6696000</v>
       </c>
       <c r="G118" s="6" t="n">
@@ -8161,7 +8159,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K118" s="9" t="inlineStr">
+      <c r="K118" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8210,7 +8208,7 @@
       <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="5" t="n">
+      <c r="F119" s="8" t="n">
         <v>9439000</v>
       </c>
       <c r="G119" s="6" t="n">
@@ -8225,7 +8223,7 @@
       <c r="J119" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K119" s="7" t="inlineStr">
+      <c r="K119" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8274,7 +8272,7 @@
       <c r="E120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="5" t="n">
+      <c r="F120" s="8" t="n">
         <v>6880000</v>
       </c>
       <c r="G120" s="6" t="n">
@@ -8291,7 +8289,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K120" s="7" t="inlineStr">
+      <c r="K120" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8340,7 +8338,7 @@
       <c r="E121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F121" s="8" t="n">
         <v>8143000</v>
       </c>
       <c r="G121" s="6" t="n">
@@ -8357,7 +8355,7 @@
       <c r="J121" s="6" t="n">
         <v>9900000</v>
       </c>
-      <c r="K121" s="7" t="inlineStr">
+      <c r="K121" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8402,7 +8400,7 @@
       <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="5" t="n">
+      <c r="F122" s="8" t="n">
         <v>12528000</v>
       </c>
       <c r="G122" s="6" t="n">
@@ -8417,7 +8415,7 @@
       <c r="J122" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K122" s="7" t="inlineStr">
+      <c r="K122" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8466,7 +8464,7 @@
       <c r="E123" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="5" t="n">
+      <c r="F123" s="8" t="n">
         <v>10314000</v>
       </c>
       <c r="G123" s="6" t="n">
@@ -8481,7 +8479,7 @@
       <c r="J123" s="6" t="n">
         <v>18900000</v>
       </c>
-      <c r="K123" s="7" t="inlineStr">
+      <c r="K123" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8596,7 +8594,7 @@
       <c r="E125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F125" s="5" t="n">
+      <c r="F125" s="8" t="n">
         <v>16697000</v>
       </c>
       <c r="G125" s="6" t="n">
@@ -8611,9 +8609,9 @@
         </is>
       </c>
       <c r="J125" s="6" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="K125" s="7" t="inlineStr">
+        <v>17800000</v>
+      </c>
+      <c r="K125" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8662,7 +8660,7 @@
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F126" s="8" t="n">
         <v>12528000</v>
       </c>
       <c r="G126" s="6" t="n">
@@ -8677,7 +8675,7 @@
       <c r="J126" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K126" s="7" t="inlineStr">
+      <c r="K126" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8800,7 +8798,7 @@
       <c r="E128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="8" t="n">
+      <c r="F128" s="5" t="n">
         <v>10768000</v>
       </c>
       <c r="G128" s="6" t="n">
@@ -8815,7 +8813,7 @@
       <c r="J128" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K128" s="9" t="inlineStr">
+      <c r="K128" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8938,7 +8936,7 @@
       <c r="E130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="5" t="n">
+      <c r="F130" s="8" t="n">
         <v>7927000</v>
       </c>
       <c r="G130" s="6" t="n">
@@ -8955,7 +8953,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K130" s="7" t="inlineStr">
+      <c r="K130" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -9004,7 +9002,7 @@
       <c r="E131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="8" t="n">
         <v>11070000</v>
       </c>
       <c r="G131" s="6" t="n">
@@ -9021,7 +9019,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K131" s="7" t="inlineStr">
+      <c r="K131" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -9070,7 +9068,7 @@
       <c r="E132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F132" s="5" t="n">
+      <c r="F132" s="8" t="n">
         <v>13576000</v>
       </c>
       <c r="G132" s="6" t="n">
@@ -9087,7 +9085,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K132" s="7" t="inlineStr">
+      <c r="K132" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -9136,8 +9134,8 @@
       <c r="E133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>11190000</v>
+      <c r="F133" s="5" t="n">
+        <v>11350000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9151,7 +9149,7 @@
       <c r="J133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K133" s="9" t="inlineStr">
+      <c r="K133" s="7" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9162,7 +9160,7 @@
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>11190000</v>
+        <v>11350000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9200,7 +9198,7 @@
       <c r="E134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F134" s="5" t="n">
+      <c r="F134" s="8" t="n">
         <v>21492000</v>
       </c>
       <c r="G134" s="6" t="n">
@@ -9217,7 +9215,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K134" s="7" t="inlineStr">
+      <c r="K134" s="9" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -619,16 +619,16 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>9470000</v>
+        <v>10160000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9250000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9400000</v>
+        <v>9900000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9470000</v>
+        <v>10160000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>11450000</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1789830000</v>
+        <v>1920240000</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -683,32 +683,32 @@
         <v>63</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>15750000</v>
+        <v>20290000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>15750000</v>
+        <v>19990000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>15840000</v>
+        <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15890000</v>
+        <v>20290000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20590000</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>992250000</v>
+        <v>1278270000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -747,32 +747,32 @@
         <v>30</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>12900000</v>
+        <v>14220000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>12870000</v>
+        <v>14200000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12900000</v>
+        <v>14200000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>13520000</v>
+        <v>14220000</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>387000000</v>
+        <v>426600000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>5750000</v>
+        <v>7640000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5400000</v>
@@ -823,7 +823,7 @@
         <v>5500000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5999000</v>
+        <v>6049000</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
@@ -832,11 +832,11 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+250,000 ت از رتبه ۳ ترب (+4.5%)</t>
+          <t>+2,140,000 ت از رتبه ۳ ترب (+38.9%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>103500000</v>
+        <v>137520000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6500000</v>
+        <v>6530000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>7350000</v>
@@ -891,16 +891,16 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>110500000</v>
+        <v>111010000</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4349000</v>
+        <v>4485000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3800000</v>
@@ -951,7 +951,7 @@
         <v>4200000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4250000</v>
+        <v>7599000</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
@@ -960,11 +960,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+149,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+285,000 ت از رتبه ۳ ترب (+6.8%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>65235000</v>
+        <v>67275000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1002,11 +1002,13 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>1760000</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1760000</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1023,14 +1025,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
@@ -1082,7 +1084,7 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>101200</v>
+        <v>106300</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>195000</v>
@@ -1132,33 +1134,33 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>9220000</v>
+      <c r="F10" s="8" t="n">
+        <v>9640000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9220000</v>
+        <v>9300000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9300000</v>
+        <v>9500000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>10800000</v>
       </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+140,000 ت از رتبه ۳ ترب (+1.5%)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>101420000</v>
+        <v>106040000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1196,8 +1198,8 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="5" t="n">
-        <v>7600000</v>
+      <c r="F11" s="8" t="n">
+        <v>7640000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1209,20 +1211,20 @@
         <v>7600000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>10558090</v>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>9450000</v>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>83600000</v>
+        <v>84040000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1267,22 +1269,22 @@
         <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4700000</v>
+        <v>4990000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5190000</v>
+        <v>5000000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5700000</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
@@ -1444,33 +1446,33 @@
       <c r="E15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>6950000</v>
+      <c r="F15" s="8" t="n">
+        <v>7400000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6950000</v>
+        <v>7100000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7100000</v>
+        <v>7200000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>8760000</v>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+200,000 ت از رتبه ۳ ترب (+2.8%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>48650000</v>
+        <v>51800000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1515,13 +1517,13 @@
         <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4620000</v>
+        <v>5190000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4700000</v>
+        <v>5200000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>6800000</v>
+        <v>6750000</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
@@ -1572,8 +1574,8 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>9900000</v>
+      <c r="F17" s="8" t="n">
+        <v>12060000</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>12000000</v>
@@ -1593,18 +1595,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>-2,100,000 ت از کف ترب (-17.5%)</t>
+          <t>+60,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>59400000</v>
+        <v>72360000</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1642,7 +1644,7 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="8" t="n">
         <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
@@ -1652,19 +1654,21 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9620000</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+        <v>9500000</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+120,000 ت از رتبه ۳ ترب (+1.3%)</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
@@ -1706,33 +1710,33 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="5" t="n">
-        <v>9220000</v>
+      <c r="F19" s="8" t="n">
+        <v>9640000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9220000</v>
+        <v>9300000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9300000</v>
+        <v>9500000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>10800000</v>
       </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+140,000 ت از رتبه ۳ ترب (+1.5%)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>55320000</v>
+        <v>57840000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1770,11 +1774,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="11" t="n">
         <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>3866000</v>
+        <v>4000000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -1787,14 +1791,14 @@
       <c r="J20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>-13,000 ت از کف ترب (-0.3%)</t>
         </is>
       </c>
       <c r="M20" s="6" t="n">
@@ -1836,8 +1840,8 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>7600000</v>
+      <c r="F21" s="8" t="n">
+        <v>7640000</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>6799000</v>
@@ -1849,20 +1853,20 @@
         <v>7600000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>10558090</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>9450000</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>38000000</v>
+        <v>38200000</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1900,8 +1904,8 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>17910000</v>
+      <c r="F22" s="8" t="n">
+        <v>18590000</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>18000000</v>
@@ -1919,18 +1923,18 @@
       <c r="J22" s="6" t="n">
         <v>17865000</v>
       </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>-90,000 ت از کف ترب (-0.5%)</t>
+          <t>+590,000 ت از رتبه ۳ ترب (+3.3%)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>89550000</v>
+        <v>92950000</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1968,14 +1972,14 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>11350000</v>
+      <c r="F23" s="8" t="n">
+        <v>16750000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9400000</v>
+        <v>9660000</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>13300000</v>
@@ -1983,18 +1987,18 @@
       <c r="J23" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+3,450,000 ت از رتبه ۳ ترب (+25.9%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>56750000</v>
+        <v>83750000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2032,33 +2036,33 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>5910000</v>
+      <c r="F24" s="8" t="n">
+        <v>6490000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5650000</v>
+        <v>6099000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5910000</v>
+        <v>6200000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6000000</v>
+        <v>6400000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7257200</v>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>7421400</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+90,000 ت از رتبه ۳ ترب (+1.4%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>29550000</v>
+        <v>32450000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2096,8 +2100,8 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>11900000</v>
+      <c r="F25" s="5" t="n">
+        <v>6990000</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>6500000</v>
@@ -2109,20 +2113,20 @@
         <v>7500000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>12590000</v>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>15300000</v>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>+4,400,000 ت از رتبه ۳ ترب (+58.7%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>59500000</v>
+        <v>34950000</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -2160,33 +2164,33 @@
       <c r="E26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>13560000</v>
+      <c r="F26" s="11" t="n">
+        <v>7690000</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>7890000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7900000</v>
+        <v>7980000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7980000</v>
+        <v>9000000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>+5,580,000 ت از رتبه ۳ ترب (+69.9%)</t>
+          <t>-200,000 ت از کف ترب (-2.5%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>67800000</v>
+        <v>38450000</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -2220,8 +2224,8 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>16632000</v>
+      <c r="F27" s="5" t="n">
+        <v>15480000</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>12320000</v>
@@ -2235,18 +2239,18 @@
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>+1,132,000 ت از رتبه ۳ ترب (+7.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>83160000</v>
+        <v>77400000</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -2281,7 +2285,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7085000</v>
+        <v>6530000</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>7600000</v>
@@ -2308,11 +2312,11 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>-515,000 ت از کف ترب (-6.8%)</t>
+          <t>-1,070,000 ت از کف ترب (-14.1%)</t>
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>35425000</v>
+        <v>32650000</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -2350,33 +2354,33 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5335000</v>
+      <c r="F29" s="5" t="n">
+        <v>5070000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4890000</v>
+        <v>4950000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4980000</v>
+        <v>5070000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>4990000</v>
+        <v>5150000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5599000</v>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+        <v>5812500</v>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>+345,000 ت از رتبه ۳ ترب (+6.9%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>21340000</v>
+        <v>20280000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2480,8 +2484,8 @@
       <c r="E31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>14332000</v>
+      <c r="F31" s="8" t="n">
+        <v>28000000</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>13000000</v>
@@ -2490,23 +2494,23 @@
         <v>13900000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>14900000</v>
+        <v>14500000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>26990000</v>
       </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+13,500,000 ت از رتبه ۳ ترب (+93.1%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
-        <v>57328000</v>
+        <v>112000000</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2544,8 +2548,8 @@
       <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>12528000</v>
+      <c r="F32" s="5" t="n">
+        <v>11500000</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>11000000</v>
@@ -2559,18 +2563,18 @@
       <c r="J32" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>+1,028,000 ت از رتبه ۳ ترب (+8.9%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>50112000</v>
+        <v>46000000</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2608,8 +2612,8 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="5" t="n">
-        <v>6479000</v>
+      <c r="F33" s="8" t="n">
+        <v>7140000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
@@ -2625,18 +2629,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+141,000 ت از رتبه ۳ ترب (+2.0%)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>19437000</v>
+        <v>21420000</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2674,8 +2678,8 @@
       <c r="E34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>9342000</v>
+      <c r="F34" s="11" t="n">
+        <v>7040000</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>8700000</v>
@@ -2684,23 +2688,23 @@
         <v>9440000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9450000</v>
+        <v>9440000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-1,660,000 ت از کف ترب (-19.1%)</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
-        <v>28026000</v>
+        <v>21120000</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2791,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6700000</v>
@@ -2812,11 +2816,11 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
+          <t>+1,870,000 ت از رتبه ۳ ترب (+26.9%)</t>
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>22584000</v>
+        <v>26460000</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2855,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="8" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6700000</v>
@@ -2876,11 +2880,11 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
+          <t>+1,870,000 ت از رتبه ۳ ترب (+26.9%)</t>
         </is>
       </c>
       <c r="M37" s="6" t="n">
-        <v>22584000</v>
+        <v>26460000</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2919,32 +2923,32 @@
         <v>3</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>14753000</v>
+        <v>16750000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>14250000</v>
+        <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>14900000</v>
+        <v>15800000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>15750000</v>
+        <v>16750000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>44259000</v>
+        <v>50250000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2983,7 +2987,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4349000</v>
+        <v>4485000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>3800000</v>
@@ -2995,7 +2999,7 @@
         <v>4200000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4250000</v>
+        <v>7599000</v>
       </c>
       <c r="K39" s="9" t="inlineStr">
         <is>
@@ -3004,11 +3008,11 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+149,000 ت از رتبه ۳ ترب (+3.5%)</t>
+          <t>+285,000 ت از رتبه ۳ ترب (+6.8%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>13047000</v>
+        <v>13455000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3047,7 +3051,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>16632000</v>
+        <v>18480000</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>8300000</v>
@@ -3070,11 +3074,11 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>+6,132,000 ت از رتبه ۳ ترب (+58.4%)</t>
+          <t>+7,980,000 ت از رتبه ۳ ترب (+76.0%)</t>
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>49896000</v>
+        <v>55440000</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -3105,7 +3109,7 @@
         <v>3</v>
       </c>
       <c r="F41" s="8" t="n">
-        <v>14580000</v>
+        <v>13570000</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>12000000</v>
@@ -3130,11 +3134,11 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>+1,080,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>43740000</v>
+        <v>40710000</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -3173,7 +3177,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3445000</v>
+        <v>3170000</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>4150000</v>
@@ -3200,11 +3204,11 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>-705,000 ت از کف ترب (-17.0%)</t>
+          <t>-980,000 ت از کف ترب (-23.6%)</t>
         </is>
       </c>
       <c r="M42" s="6" t="n">
-        <v>10335000</v>
+        <v>9510000</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -3238,8 +3242,8 @@
       <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="8" t="n">
-        <v>7970000</v>
+      <c r="F43" s="5" t="n">
+        <v>7140000</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>6980000</v>
@@ -3255,18 +3259,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه ۳ ترب (+1.1%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M43" s="6" t="n">
-        <v>23910000</v>
+        <v>21420000</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -3377,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>8132000</v>
+        <v>7750000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -3400,11 +3404,11 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>+525,000 ت از رتبه ۳ ترب (+6.9%)</t>
+          <t>+143,000 ت از رتبه ۳ ترب (+1.9%)</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
-        <v>16264000</v>
+        <v>15500000</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -3503,7 +3507,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="8" t="n">
-        <v>5910000</v>
+        <v>6490000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3515,7 +3519,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7257200</v>
+        <v>7421400</v>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
@@ -3524,11 +3528,11 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+212,000 ت از رتبه ۳ ترب (+3.7%)</t>
+          <t>+792,000 ت از رتبه ۳ ترب (+13.9%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>11820000</v>
+        <v>12980000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3567,7 +3571,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="8" t="n">
-        <v>9350000</v>
+        <v>9325000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -3579,7 +3583,7 @@
         <v>9100000</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>13500000</v>
+        <v>13400000</v>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
@@ -3588,11 +3592,11 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>+250,000 ت از رتبه ۳ ترب (+2.7%)</t>
+          <t>+225,000 ت از رتبه ۳ ترب (+2.5%)</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>18700000</v>
+        <v>18650000</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3631,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="8" t="n">
-        <v>3455000</v>
+        <v>3840000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -3643,7 +3647,7 @@
         <v>3150000</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>4350000</v>
+        <v>4600000</v>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
@@ -3652,11 +3656,11 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>+305,000 ت از رتبه ۳ ترب (+9.7%)</t>
+          <t>+690,000 ت از رتبه ۳ ترب (+21.9%)</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>6910000</v>
+        <v>7680000</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3695,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="8" t="n">
-        <v>7927000</v>
+        <v>9510000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -3718,11 +3722,11 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>+1,077,000 ت از رتبه ۳ ترب (+15.7%)</t>
+          <t>+2,660,000 ت از رتبه ۳ ترب (+38.8%)</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">
-        <v>15854000</v>
+        <v>19020000</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3761,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="8" t="n">
-        <v>14753000</v>
+        <v>16750000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3782,11 +3786,11 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>+1,853,000 ت از رتبه ۳ ترب (+14.4%)</t>
+          <t>+3,850,000 ت از رتبه ۳ ترب (+29.8%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>29506000</v>
+        <v>33500000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3825,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>12366000</v>
+        <v>12520000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -3846,11 +3850,11 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>+866,000 ت از رتبه ۳ ترب (+7.5%)</t>
+          <t>+1,020,000 ت از رتبه ۳ ترب (+8.9%)</t>
         </is>
       </c>
       <c r="M52" s="6" t="n">
-        <v>24732000</v>
+        <v>25040000</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3889,7 +3893,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="8" t="n">
-        <v>9439000</v>
+        <v>12250000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -3910,11 +3914,11 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>+1,950,000 ت از رتبه ۳ ترب (+26.0%)</t>
+          <t>+4,761,000 ت از رتبه ۳ ترب (+63.6%)</t>
         </is>
       </c>
       <c r="M53" s="6" t="n">
-        <v>18878000</v>
+        <v>24500000</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -4026,8 +4030,8 @@
       <c r="E55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>10768000</v>
+      <c r="F55" s="8" t="n">
+        <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -4041,18 +4045,18 @@
       <c r="J55" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M55" s="6" t="n">
-        <v>21536000</v>
+        <v>22000000</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -4091,7 +4095,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>6426000</v>
+        <v>9990000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4114,11 +4118,11 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>+476,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+4,040,000 ت از رتبه ۳ ترب (+67.9%)</t>
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>12852000</v>
+        <v>19980000</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -4282,8 +4286,8 @@
       <c r="E59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="8" t="n">
-        <v>9958000</v>
+      <c r="F59" s="5" t="n">
+        <v>6150000</v>
       </c>
       <c r="G59" s="6" t="n">
         <v>4600000</v>
@@ -4297,18 +4301,18 @@
       <c r="J59" s="6" t="n">
         <v>9700000</v>
       </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>+3,158,000 ت از رتبه ۳ ترب (+46.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M59" s="6" t="n">
-        <v>19916000</v>
+        <v>12300000</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -4346,8 +4350,8 @@
       <c r="E60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F60" s="11" t="n">
-        <v>6199000</v>
+      <c r="F60" s="8" t="n">
+        <v>8340000</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>6460000</v>
@@ -4361,20 +4365,20 @@
         </is>
       </c>
       <c r="J60" s="6" t="n">
-        <v>8652000</v>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+        <v>8486000</v>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>-261,000 ت از کف ترب (-4.0%)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M60" s="6" t="n">
-        <v>12398000</v>
+        <v>16680000</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -4412,8 +4416,8 @@
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="8" t="n">
-        <v>13424000</v>
+      <c r="F61" s="5" t="n">
+        <v>8850000</v>
       </c>
       <c r="G61" s="6" t="n">
         <v>8500000</v>
@@ -4429,18 +4433,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>+4,424,000 ت از رتبه ۳ ترب (+49.2%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M61" s="6" t="n">
-        <v>26848000</v>
+        <v>17700000</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -4479,7 +4483,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="8" t="n">
-        <v>4828000</v>
+        <v>7470000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4500,11 +4504,11 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+878,000 ت از رتبه ۳ ترب (+22.2%)</t>
+          <t>+3,520,000 ت از رتبه ۳ ترب (+89.1%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>9656000</v>
+        <v>14940000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4543,7 +4547,7 @@
         <v>2</v>
       </c>
       <c r="F63" s="8" t="n">
-        <v>23846000</v>
+        <v>22110000</v>
       </c>
       <c r="G63" s="6" t="n">
         <v>21500000</v>
@@ -4566,11 +4570,11 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>+1,846,000 ت از رتبه ۳ ترب (+8.4%)</t>
+          <t>+110,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M63" s="6" t="n">
-        <v>47692000</v>
+        <v>44220000</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -4609,7 +4613,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="8" t="n">
-        <v>5335000</v>
+        <v>5070000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4621,7 +4625,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5599000</v>
+        <v>5812500</v>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
@@ -4630,11 +4634,11 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>+385,000 ت از رتبه ۳ ترب (+7.8%)</t>
+          <t>+120,000 ت از رتبه ۳ ترب (+2.4%)</t>
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>10670000</v>
+        <v>10140000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4672,8 +4676,8 @@
       <c r="E65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="8" t="n">
-        <v>2862000</v>
+      <c r="F65" s="5" t="n">
+        <v>2650000</v>
       </c>
       <c r="G65" s="6" t="n">
         <v>2300000</v>
@@ -4689,18 +4693,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K65" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>+62,000 ت از رتبه ۳ ترب (+2.2%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M65" s="6" t="n">
-        <v>5724000</v>
+        <v>5300000</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -4738,8 +4742,8 @@
       <c r="E66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="8" t="n">
-        <v>16848000</v>
+      <c r="F66" s="5" t="n">
+        <v>15600000</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>14500000</v>
@@ -4753,18 +4757,18 @@
       <c r="J66" s="6" t="n">
         <v>16019000</v>
       </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>+848,000 ت از رتبه ۳ ترب (+5.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M66" s="6" t="n">
-        <v>33696000</v>
+        <v>31200000</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -4795,7 +4799,7 @@
         <v>2</v>
       </c>
       <c r="F67" s="8" t="n">
-        <v>7430000</v>
+        <v>4000000</v>
       </c>
       <c r="G67" s="6" t="n">
         <v>3980000</v>
@@ -4822,11 +4826,11 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>+3,450,000 ت از رتبه ۳ ترب (+86.7%)</t>
+          <t>+20,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M67" s="6" t="n">
-        <v>14860000</v>
+        <v>8000000</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -4864,8 +4868,8 @@
       <c r="E68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="8" t="n">
-        <v>4612000</v>
+      <c r="F68" s="5" t="n">
+        <v>3920000</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>3620000</v>
@@ -4879,18 +4883,18 @@
       <c r="J68" s="6" t="n">
         <v>4326110</v>
       </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>+512,000 ت از رتبه ۳ ترب (+12.5%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M68" s="6" t="n">
-        <v>9224000</v>
+        <v>7840000</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -4929,7 +4933,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>14353000</v>
+        <v>13290000</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>10000000</v>
@@ -4940,8 +4944,10 @@
       <c r="I69" s="6" t="n">
         <v>15600000</v>
       </c>
-      <c r="J69" s="6" t="n">
-        <v>9500000</v>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
@@ -4954,7 +4960,7 @@
         </is>
       </c>
       <c r="M69" s="6" t="n">
-        <v>28706000</v>
+        <v>26580000</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4993,7 +4999,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="8" t="n">
-        <v>8986000</v>
+        <v>9550000</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>7200000</v>
@@ -5018,11 +5024,11 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>+1,786,000 ت از رتبه ۳ ترب (+24.8%)</t>
+          <t>+2,350,000 ت از رتبه ۳ ترب (+32.6%)</t>
         </is>
       </c>
       <c r="M70" s="6" t="n">
-        <v>17972000</v>
+        <v>19100000</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -5061,7 +5067,7 @@
         <v>2</v>
       </c>
       <c r="F71" s="8" t="n">
-        <v>7819000</v>
+        <v>7240000</v>
       </c>
       <c r="G71" s="6" t="n">
         <v>6400000</v>
@@ -5084,11 +5090,11 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>+619,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M71" s="6" t="n">
-        <v>15638000</v>
+        <v>14480000</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -5127,7 +5133,7 @@
         <v>2</v>
       </c>
       <c r="F72" s="8" t="n">
-        <v>18457000</v>
+        <v>17590000</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>11000000</v>
@@ -5152,11 +5158,11 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>+957,000 ت از رتبه ۳ ترب (+5.5%)</t>
+          <t>+90,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M72" s="6" t="n">
-        <v>36914000</v>
+        <v>35180000</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -5195,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="8" t="n">
-        <v>4018000</v>
+        <v>4310000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -5207,7 +5213,7 @@
         <v>3890000</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>4870000</v>
+        <v>4703670</v>
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
@@ -5216,11 +5222,11 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>+128,000 ت از رتبه ۳ ترب (+3.3%)</t>
+          <t>+420,000 ت از رتبه ۳ ترب (+10.8%)</t>
         </is>
       </c>
       <c r="M73" s="6" t="n">
-        <v>8036000</v>
+        <v>8620000</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -5259,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="8" t="n">
-        <v>9936000</v>
+        <v>12630000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -5280,11 +5286,11 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+3,430,000 ت از رتبه ۳ ترب (+37.3%)</t>
         </is>
       </c>
       <c r="M74" s="6" t="n">
-        <v>9936000</v>
+        <v>12630000</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -5323,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="8" t="n">
-        <v>18900000</v>
+        <v>21750000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -5344,11 +5350,11 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>+16,455,000 ت از رتبه ۳ ترب (+673.0%)</t>
+          <t>+19,305,000 ت از رتبه ۳ ترب (+789.6%)</t>
         </is>
       </c>
       <c r="M75" s="6" t="n">
-        <v>18900000</v>
+        <v>21750000</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -5383,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="8" t="n">
-        <v>25920000</v>
+        <v>27470000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -5404,11 +5410,11 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>+10,320,000 ت از رتبه ۳ ترب (+66.2%)</t>
+          <t>+11,870,000 ت از رتبه ۳ ترب (+76.1%)</t>
         </is>
       </c>
       <c r="M76" s="6" t="n">
-        <v>25920000</v>
+        <v>27470000</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -5443,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="8" t="n">
-        <v>10044000</v>
+        <v>11060000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -5464,11 +5470,11 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>+844,000 ت از رتبه ۳ ترب (+9.2%)</t>
+          <t>+1,860,000 ت از رتبه ۳ ترب (+20.2%)</t>
         </is>
       </c>
       <c r="M77" s="6" t="n">
-        <v>10044000</v>
+        <v>11060000</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -5507,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="8" t="n">
-        <v>9936000</v>
+        <v>12630000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -5528,11 +5534,11 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>+736,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+3,430,000 ت از رتبه ۳ ترب (+37.3%)</t>
         </is>
       </c>
       <c r="M78" s="6" t="n">
-        <v>9936000</v>
+        <v>12630000</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -5571,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>4234000</v>
+        <v>4950000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -5592,11 +5598,11 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>+379,000 ت از رتبه ۳ ترب (+9.8%)</t>
+          <t>+1,095,000 ت از رتبه ۳ ترب (+28.4%)</t>
         </is>
       </c>
       <c r="M79" s="6" t="n">
-        <v>4234000</v>
+        <v>4950000</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -5635,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="8" t="n">
-        <v>16199000</v>
+        <v>15390000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -5656,11 +5662,11 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>+1,209,000 ت از رتبه ۳ ترب (+8.1%)</t>
+          <t>+400,000 ت از رتبه ۳ ترب (+2.7%)</t>
         </is>
       </c>
       <c r="M80" s="6" t="n">
-        <v>16199000</v>
+        <v>15390000</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -5699,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="8" t="n">
-        <v>6799000</v>
+        <v>6495000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -5711,7 +5717,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>8660000</v>
+        <v>8760000</v>
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
@@ -5720,11 +5726,11 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>+599,000 ت از رتبه ۳ ترب (+9.7%)</t>
+          <t>+295,000 ت از رتبه ۳ ترب (+4.8%)</t>
         </is>
       </c>
       <c r="M81" s="6" t="n">
-        <v>6799000</v>
+        <v>6495000</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -5763,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="8" t="n">
-        <v>6458000</v>
+        <v>5980000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -5786,11 +5792,11 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>+508,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>+30,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M82" s="6" t="n">
-        <v>6458000</v>
+        <v>5980000</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -5829,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="8" t="n">
-        <v>14035000</v>
+        <v>15520000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5850,11 +5856,11 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>+2,235,000 ت از رتبه ۳ ترب (+18.9%)</t>
+          <t>+3,720,000 ت از رتبه ۳ ترب (+31.5%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>14035000</v>
+        <v>15520000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -5893,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="8" t="n">
-        <v>2916000</v>
+        <v>2670000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -5914,11 +5920,11 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>+471,000 ت از رتبه ۳ ترب (+19.3%)</t>
+          <t>+225,000 ت از رتبه ۳ ترب (+9.2%)</t>
         </is>
       </c>
       <c r="M84" s="6" t="n">
-        <v>2916000</v>
+        <v>2670000</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="8" t="n">
-        <v>10098000</v>
+        <v>12630000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -5974,11 +5980,11 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>+898,000 ت از رتبه ۳ ترب (+9.8%)</t>
+          <t>+3,430,000 ت از رتبه ۳ ترب (+37.3%)</t>
         </is>
       </c>
       <c r="M85" s="6" t="n">
-        <v>10098000</v>
+        <v>12630000</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
@@ -6091,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="8" t="n">
-        <v>4558000</v>
+        <v>8250000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -6118,11 +6124,11 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>+358,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>+4,050,000 ت از رتبه ۳ ترب (+96.4%)</t>
         </is>
       </c>
       <c r="M87" s="6" t="n">
-        <v>4558000</v>
+        <v>8250000</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -6161,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="8" t="n">
-        <v>7992000</v>
+        <v>7840000</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>5800000</v>
@@ -6184,11 +6190,11 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>+203,000 ت از رتبه ۳ ترب (+2.6%)</t>
+          <t>+51,000 ت از رتبه ۳ ترب (+0.7%)</t>
         </is>
       </c>
       <c r="M88" s="6" t="n">
-        <v>7992000</v>
+        <v>7840000</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
@@ -6227,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="F89" s="8" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -6248,11 +6254,11 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
+          <t>+1,870,000 ت از رتبه ۳ ترب (+26.9%)</t>
         </is>
       </c>
       <c r="M89" s="6" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
@@ -6291,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="8" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -6312,11 +6318,11 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>+578,000 ت از رتبه ۳ ترب (+8.3%)</t>
+          <t>+1,870,000 ت از رتبه ۳ ترب (+26.9%)</t>
         </is>
       </c>
       <c r="M90" s="6" t="n">
-        <v>7528000</v>
+        <v>8820000</v>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
@@ -6355,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="8" t="n">
-        <v>4828000</v>
+        <v>7470000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6376,11 +6382,11 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>+878,000 ت از رتبه ۳ ترب (+22.2%)</t>
+          <t>+3,520,000 ت از رتبه ۳ ترب (+89.1%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>4828000</v>
+        <v>7470000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6419,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="8" t="n">
-        <v>3499000</v>
+        <v>3503000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6431,7 +6437,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>3933400</v>
+        <v>4119900</v>
       </c>
       <c r="K92" s="9" t="inlineStr">
         <is>
@@ -6440,11 +6446,11 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>+511,000 ت از رتبه ۳ ترب (+17.1%)</t>
+          <t>+515,000 ت از رتبه ۳ ترب (+17.2%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>3499000</v>
+        <v>3503000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -6483,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="8" t="n">
-        <v>7571000</v>
+        <v>7780000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -6504,11 +6510,11 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>+651,000 ت از رتبه ۳ ترب (+9.4%)</t>
+          <t>+860,000 ت از رتبه ۳ ترب (+12.4%)</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
-        <v>7571000</v>
+        <v>7780000</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -6547,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>6394000</v>
+        <v>5920000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -6572,11 +6578,11 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>+505,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M94" s="6" t="n">
-        <v>6394000</v>
+        <v>5920000</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -6615,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="8" t="n">
-        <v>23058000</v>
+        <v>24150000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -6636,11 +6642,11 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>+1,708,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>+2,800,000 ت از رتبه ۳ ترب (+13.1%)</t>
         </is>
       </c>
       <c r="M95" s="6" t="n">
-        <v>23058000</v>
+        <v>24150000</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -6679,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="8" t="n">
-        <v>4882000</v>
+        <v>4910000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -6706,11 +6712,11 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>+382,000 ت از رتبه ۳ ترب (+8.5%)</t>
+          <t>+410,000 ت از رتبه ۳ ترب (+9.1%)</t>
         </is>
       </c>
       <c r="M96" s="6" t="n">
-        <v>4882000</v>
+        <v>4910000</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -6749,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="8" t="n">
-        <v>8986000</v>
+        <v>9550000</v>
       </c>
       <c r="G97" s="6" t="n">
         <v>7200000</v>
@@ -6776,11 +6782,11 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>+1,786,000 ت از رتبه ۳ ترب (+24.8%)</t>
+          <t>+2,350,000 ت از رتبه ۳ ترب (+32.6%)</t>
         </is>
       </c>
       <c r="M97" s="6" t="n">
-        <v>8986000</v>
+        <v>9550000</v>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
@@ -6818,8 +6824,8 @@
       <c r="E98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>10768000</v>
+      <c r="F98" s="8" t="n">
+        <v>11000000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -6833,18 +6839,18 @@
       <c r="J98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M98" s="6" t="n">
-        <v>10768000</v>
+        <v>11000000</v>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
@@ -6883,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="8" t="n">
-        <v>4018000</v>
+        <v>4310000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -6895,7 +6901,7 @@
         <v>3890000</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>4870000</v>
+        <v>4703670</v>
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
@@ -6904,11 +6910,11 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>+128,000 ت از رتبه ۳ ترب (+3.3%)</t>
+          <t>+420,000 ت از رتبه ۳ ترب (+10.8%)</t>
         </is>
       </c>
       <c r="M99" s="6" t="n">
-        <v>4018000</v>
+        <v>4310000</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -6946,8 +6952,8 @@
       <c r="E100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="8" t="n">
-        <v>3866000</v>
+      <c r="F100" s="5" t="n">
+        <v>3390000</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>3580000</v>
@@ -6963,18 +6969,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K100" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>+286,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M100" s="6" t="n">
-        <v>3866000</v>
+        <v>3390000</v>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
@@ -7013,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="8" t="n">
-        <v>3370000</v>
+        <v>3120000</v>
       </c>
       <c r="G101" s="6" t="n">
         <v>2900000</v>
@@ -7036,11 +7042,11 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>+270,000 ت از رتبه ۳ ترب (+8.7%)</t>
+          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M101" s="6" t="n">
-        <v>3370000</v>
+        <v>3120000</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
@@ -7071,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>25920000</v>
+        <v>27470000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -7098,7 +7104,7 @@
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>25920000</v>
+        <v>27470000</v>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
@@ -7129,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>9900000</v>
+        <v>12060000</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -7162,7 +7168,7 @@
         </is>
       </c>
       <c r="M103" s="6" t="n">
-        <v>9900000</v>
+        <v>12060000</v>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
@@ -7201,7 +7207,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="8" t="n">
-        <v>4234000</v>
+        <v>4950000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -7222,11 +7228,11 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>+379,000 ت از رتبه ۳ ترب (+9.8%)</t>
+          <t>+1,095,000 ت از رتبه ۳ ترب (+28.4%)</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>4234000</v>
+        <v>4950000</v>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
@@ -7264,8 +7270,8 @@
       <c r="E105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="8" t="n">
-        <v>4730000</v>
+      <c r="F105" s="5" t="n">
+        <v>4440000</v>
       </c>
       <c r="G105" s="6" t="n">
         <v>4000000</v>
@@ -7279,18 +7285,18 @@
       <c r="J105" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K105" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>+31,000 ت از رتبه ۳ ترب (+0.7%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M105" s="6" t="n">
-        <v>4730000</v>
+        <v>4440000</v>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
@@ -7329,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="F106" s="8" t="n">
-        <v>14116000</v>
+        <v>13070000</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>7400000</v>
@@ -7352,11 +7358,11 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>+1,116,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+70,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M106" s="6" t="n">
-        <v>14116000</v>
+        <v>13070000</v>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
@@ -7468,8 +7474,8 @@
       <c r="E108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="8" t="n">
-        <v>10357000</v>
+      <c r="F108" s="5" t="n">
+        <v>9590000</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>7560000</v>
@@ -7483,18 +7489,18 @@
       <c r="J108" s="6" t="n">
         <v>14550000</v>
       </c>
-      <c r="K108" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>+658,000 ت از رتبه ۳ ترب (+6.8%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M108" s="6" t="n">
-        <v>10357000</v>
+        <v>9590000</v>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
@@ -7599,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="8" t="n">
-        <v>5962000</v>
+        <v>3600000</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>3580000</v>
@@ -7626,11 +7632,11 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>+2,382,000 ت از رتبه ۳ ترب (+66.5%)</t>
+          <t>+20,000 ت از رتبه ۳ ترب (+0.6%)</t>
         </is>
       </c>
       <c r="M110" s="6" t="n">
-        <v>5962000</v>
+        <v>3600000</v>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
@@ -7816,8 +7822,8 @@
       <c r="E113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="8" t="n">
-        <v>6772000</v>
+      <c r="F113" s="5" t="n">
+        <v>6220000</v>
       </c>
       <c r="G113" s="6" t="n">
         <v>5900000</v>
@@ -7831,18 +7837,18 @@
       <c r="J113" s="6" t="n">
         <v>7900000</v>
       </c>
-      <c r="K113" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>+322,000 ت از رتبه ۳ ترب (+5.0%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M113" s="6" t="n">
-        <v>6772000</v>
+        <v>6220000</v>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
@@ -7880,8 +7886,8 @@
       <c r="E114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="8" t="n">
-        <v>10951000</v>
+      <c r="F114" s="5" t="n">
+        <v>9440000</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>9000000</v>
@@ -7895,18 +7901,18 @@
       <c r="J114" s="6" t="n">
         <v>11290000</v>
       </c>
-      <c r="K114" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>+1,161,000 ت از رتبه ۳ ترب (+11.9%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M114" s="6" t="n">
-        <v>10951000</v>
+        <v>9440000</v>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -7944,8 +7950,8 @@
       <c r="E115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F115" s="8" t="n">
-        <v>10152000</v>
+      <c r="F115" s="5" t="n">
+        <v>9650000</v>
       </c>
       <c r="G115" s="6" t="n">
         <v>8900000</v>
@@ -7961,18 +7967,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K115" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>+352,000 ت از رتبه ۳ ترب (+3.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M115" s="6" t="n">
-        <v>10152000</v>
+        <v>9650000</v>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="8" t="n">
-        <v>3499000</v>
+        <v>3503000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8032,11 +8038,11 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>+511,000 ت از رتبه ۳ ترب (+17.1%)</t>
+          <t>+515,000 ت از رتبه ۳ ترب (+17.2%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3499000</v>
+        <v>3503000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8075,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="8" t="n">
-        <v>5314000</v>
+        <v>4920000</v>
       </c>
       <c r="G117" s="6" t="n">
         <v>4400000</v>
@@ -8100,11 +8106,11 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>+414,000 ت از رتبه ۳ ترب (+8.4%)</t>
+          <t>+20,000 ت از رتبه ۳ ترب (+0.4%)</t>
         </is>
       </c>
       <c r="M117" s="6" t="n">
-        <v>5314000</v>
+        <v>4920000</v>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
@@ -8143,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>6696000</v>
+        <v>6200000</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>5248000</v>
@@ -8170,7 +8176,7 @@
         </is>
       </c>
       <c r="M118" s="6" t="n">
-        <v>6696000</v>
+        <v>6200000</v>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
@@ -8209,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="8" t="n">
-        <v>9439000</v>
+        <v>12250000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -8230,11 +8236,11 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>+1,950,000 ت از رتبه ۳ ترب (+26.0%)</t>
+          <t>+4,761,000 ت از رتبه ۳ ترب (+63.6%)</t>
         </is>
       </c>
       <c r="M119" s="6" t="n">
-        <v>9439000</v>
+        <v>12250000</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -8272,8 +8278,8 @@
       <c r="E120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="8" t="n">
-        <v>6880000</v>
+      <c r="F120" s="5" t="n">
+        <v>6370000</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>5950000</v>
@@ -8289,18 +8295,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K120" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>+380,000 ت از رتبه ۳ ترب (+5.8%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M120" s="6" t="n">
-        <v>6880000</v>
+        <v>6370000</v>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
@@ -8339,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="F121" s="8" t="n">
-        <v>8143000</v>
+        <v>7540000</v>
       </c>
       <c r="G121" s="6" t="n">
         <v>6800000</v>
@@ -8362,11 +8368,11 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>+643,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M121" s="6" t="n">
-        <v>8143000</v>
+        <v>7540000</v>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
@@ -8400,8 +8406,8 @@
       <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="8" t="n">
-        <v>12528000</v>
+      <c r="F122" s="5" t="n">
+        <v>10970000</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>10800000</v>
@@ -8415,18 +8421,18 @@
       <c r="J122" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K122" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>+1,528,000 ت از رتبه ۳ ترب (+13.9%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M122" s="6" t="n">
-        <v>12528000</v>
+        <v>10970000</v>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
@@ -8464,8 +8470,8 @@
       <c r="E123" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="8" t="n">
-        <v>10314000</v>
+      <c r="F123" s="5" t="n">
+        <v>9550000</v>
       </c>
       <c r="G123" s="6" t="n">
         <v>8800000</v>
@@ -8479,18 +8485,18 @@
       <c r="J123" s="6" t="n">
         <v>18900000</v>
       </c>
-      <c r="K123" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>+414,000 ت از رتبه ۳ ترب (+4.2%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M123" s="6" t="n">
-        <v>10314000</v>
+        <v>9550000</v>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
@@ -8525,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>6479000</v>
+        <v>7140000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -8552,11 +8558,11 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>-3,121,000 ت از کف ترب (-32.5%)</t>
+          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
         </is>
       </c>
       <c r="M124" s="6" t="n">
-        <v>6479000</v>
+        <v>7140000</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
@@ -8595,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="F125" s="8" t="n">
-        <v>16697000</v>
+        <v>15460000</v>
       </c>
       <c r="G125" s="6" t="n">
         <v>13000000</v>
@@ -8618,11 +8624,11 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>+1,317,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+80,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M125" s="6" t="n">
-        <v>16697000</v>
+        <v>15460000</v>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
@@ -8660,8 +8666,8 @@
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="8" t="n">
-        <v>12528000</v>
+      <c r="F126" s="5" t="n">
+        <v>10970000</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>10800000</v>
@@ -8675,18 +8681,18 @@
       <c r="J126" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K126" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>+1,528,000 ت از رتبه ۳ ترب (+13.9%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M126" s="6" t="n">
-        <v>12528000</v>
+        <v>10970000</v>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
@@ -8798,8 +8804,8 @@
       <c r="E128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>10768000</v>
+      <c r="F128" s="8" t="n">
+        <v>11000000</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>7990000</v>
@@ -8813,18 +8819,18 @@
       <c r="J128" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K128" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+0.5%)</t>
         </is>
       </c>
       <c r="M128" s="6" t="n">
-        <v>10768000</v>
+        <v>11000000</v>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
@@ -8936,8 +8942,8 @@
       <c r="E130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="8" t="n">
-        <v>7927000</v>
+      <c r="F130" s="5" t="n">
+        <v>6770000</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>6690000</v>
@@ -8953,18 +8959,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K130" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>+1,077,000 ت از رتبه ۳ ترب (+15.7%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M130" s="6" t="n">
-        <v>7927000</v>
+        <v>6770000</v>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
@@ -9002,8 +9008,8 @@
       <c r="E131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="8" t="n">
-        <v>11070000</v>
+      <c r="F131" s="5" t="n">
+        <v>10250000</v>
       </c>
       <c r="G131" s="6" t="n">
         <v>9000000</v>
@@ -9019,18 +9025,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K131" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه ۳ ترب (+0.6%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M131" s="6" t="n">
-        <v>11070000</v>
+        <v>10250000</v>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
@@ -9068,8 +9074,8 @@
       <c r="E132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F132" s="8" t="n">
-        <v>13576000</v>
+      <c r="F132" s="5" t="n">
+        <v>11320000</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>9945000</v>
@@ -9085,18 +9091,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K132" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>+926,000 ت از رتبه ۳ ترب (+7.3%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M132" s="6" t="n">
-        <v>13576000</v>
+        <v>11320000</v>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
@@ -9134,8 +9140,8 @@
       <c r="E133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>11350000</v>
+      <c r="F133" s="8" t="n">
+        <v>16750000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9149,18 +9155,18 @@
       <c r="J133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K133" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K133" s="9" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+550,000 ت از رتبه ۳ ترب (+3.4%)</t>
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>11350000</v>
+        <v>16750000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9198,8 +9204,8 @@
       <c r="E134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F134" s="8" t="n">
-        <v>21492000</v>
+      <c r="F134" s="5" t="n">
+        <v>19750000</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>19000000</v>
@@ -9215,18 +9221,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K134" s="9" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>+1,592,000 ت از رتبه ۳ ترب (+8.0%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M134" s="6" t="n">
-        <v>21492000</v>
+        <v>19750000</v>
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -57,14 +57,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -619,7 +619,7 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10160000</v>
+        <v>10950000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9250000</v>
@@ -628,23 +628,23 @@
         <v>9900000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10160000</v>
+        <v>10290000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>11450000</v>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+660,000 ت از رتبه ۳ ترب (+6.4%)</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>1920240000</v>
+        <v>2069550000</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
@@ -682,8 +682,8 @@
       <c r="E3" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>20290000</v>
+      <c r="F3" s="8" t="n">
+        <v>20570000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>19990000</v>
@@ -692,12 +692,12 @@
         <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20290000</v>
+        <v>20570000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20590000</v>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>1278270000</v>
+        <v>1295910000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>14220000</v>
+        <v>16340000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14200000</v>
@@ -756,23 +756,23 @@
         <v>14200000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>14220000</v>
+        <v>14289000</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>+2,051,000 ت از رتبه ۳ ترب (+14.4%)</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>426600000</v>
+        <v>490200000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -810,33 +810,33 @@
       <c r="E5" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>7640000</v>
+      <c r="F5" s="5" t="n">
+        <v>10080000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5400000</v>
+        <v>5500000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5500000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5500000</v>
+        <v>5670103</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>6049000</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+        <v>5790000</v>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+2,140,000 ت از رتبه ۳ ترب (+38.9%)</t>
+          <t>+4,409,897 ت از رتبه ۳ ترب (+77.8%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>137520000</v>
+        <v>181440000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="8" t="n">
         <v>6530000</v>
       </c>
       <c r="G6" s="6" t="n">
@@ -889,7 +889,7 @@
       <c r="J6" s="6" t="n">
         <v>9560380</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -938,33 +938,33 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>4485000</v>
+      <c r="F7" s="5" t="n">
+        <v>4476000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4200000</v>
+        <v>4347000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>7599000</v>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
+        <v>4250000</v>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+285,000 ت از رتبه ۳ ترب (+6.8%)</t>
+          <t>+129,000 ت از رتبه ۳ ترب (+3.0%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>67275000</v>
+        <v>67140000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="8" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
@@ -1089,7 +1089,7 @@
       <c r="J9" s="6" t="n">
         <v>195000</v>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -1135,32 +1135,32 @@
         <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9640000</v>
+        <v>9790000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9300000</v>
+        <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9500000</v>
+        <v>9790000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>+140,000 ت از رتبه ۳ ترب (+1.5%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>106040000</v>
+        <v>107690000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       <c r="E11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="5" t="n">
         <v>7640000</v>
       </c>
       <c r="G11" s="6" t="n">
@@ -1211,9 +1211,9 @@
         <v>7600000</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>9450000</v>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
+        <v>10020000</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1262,22 +1262,22 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="8" t="n">
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4990000</v>
+        <v>4999000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5700000</v>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -1330,13 +1330,13 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>11800000</v>
+        <v>12000000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>12000000</v>
+        <v>13800000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>13100000</v>
+        <v>13900000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>-1,600,000 ت از کف ترب (-13.6%)</t>
+          <t>-1,800,000 ت از کف ترب (-15.0%)</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
@@ -1382,7 +1382,7 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="5" t="n">
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
@@ -1395,9 +1395,9 @@
         <v>11670000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
+        <v>20450000</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1446,33 +1446,33 @@
       <c r="E15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>7400000</v>
+      <c r="F15" s="5" t="n">
+        <v>8470000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7100000</v>
+        <v>7195000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7200000</v>
+        <v>7197000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8760000</v>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
+        <v>8880000</v>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+200,000 ت از رتبه ۳ ترب (+2.8%)</t>
+          <t>+1,273,000 ت از رتبه ۳ ترب (+17.7%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>51800000</v>
+        <v>59290000</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1510,22 +1510,22 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="8" t="n">
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>5190000</v>
+        <v>5400000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5200000</v>
+        <v>5445000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>6750000</v>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -1574,7 +1574,7 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="5" t="n">
         <v>12060000</v>
       </c>
       <c r="G17" s="6" t="n">
@@ -1595,7 +1595,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1644,7 +1644,7 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="5" t="n">
         <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
@@ -1661,7 +1661,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1711,32 +1711,32 @@
         <v>6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9640000</v>
+        <v>9790000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9300000</v>
+        <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9500000</v>
+        <v>9790000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>+140,000 ت از رتبه ۳ ترب (+1.5%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>57840000</v>
+        <v>58740000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="5" t="n">
         <v>7640000</v>
       </c>
       <c r="G21" s="6" t="n">
@@ -1853,9 +1853,9 @@
         <v>7600000</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>9450000</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
+        <v>10020000</v>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1904,7 +1904,7 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="5" t="n">
         <v>18590000</v>
       </c>
       <c r="G22" s="6" t="n">
@@ -1921,9 +1921,9 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>17865000</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
+        <v>15880000</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -1972,8 +1972,8 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>16750000</v>
+      <c r="F23" s="5" t="n">
+        <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7500000</v>
@@ -1987,18 +1987,18 @@
       <c r="J23" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>+3,450,000 ت از رتبه ۳ ترب (+25.9%)</t>
+          <t>+8,450,000 ت از رتبه ۳ ترب (+63.5%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>83750000</v>
+        <v>108750000</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -2036,33 +2036,33 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6490000</v>
+      <c r="F24" s="5" t="n">
+        <v>6900000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6099000</v>
+        <v>6200000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6200000</v>
+        <v>6400000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6400000</v>
+        <v>6449000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7421400</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+        <v>7725500</v>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه ۳ ترب (+1.4%)</t>
+          <t>+451,000 ت از رتبه ۳ ترب (+7.0%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>32450000</v>
+        <v>34500000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2100,29 +2100,29 @@
       <c r="E25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="8" t="n">
         <v>6990000</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="I25" s="6" t="n">
         <v>7480000</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>7500000</v>
-      </c>
       <c r="J25" s="6" t="n">
-        <v>15300000</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>15000000</v>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2174,7 +2174,7 @@
         <v>7980000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>9000000</v>
+        <v>8500000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
@@ -2224,29 +2224,29 @@
       <c r="E27" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="8" t="n">
         <v>15480000</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>12320000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>14500000</v>
+        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>15500000</v>
+        <v>16000000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M27" s="6" t="n">
@@ -2355,32 +2355,32 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>5070000</v>
+        <v>5270000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>5200000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5070000</v>
+        <v>5214550</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5150000</v>
+        <v>5220000</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>5812500</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+50,000 ت از رتبه ۳ ترب (+1.0%)</t>
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>20280000</v>
+        <v>21080000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2484,29 +2484,29 @@
       <c r="E31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F31" s="5" t="n">
         <v>28000000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>13000000</v>
+        <v>13900000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13900000</v>
+        <v>14000000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>14500000</v>
+        <v>14900000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>26990000</v>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
+        <v>27990000</v>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>+13,500,000 ت از رتبه ۳ ترب (+93.1%)</t>
+          <t>+13,100,000 ت از رتبه ۳ ترب (+87.9%)</t>
         </is>
       </c>
       <c r="M31" s="6" t="n">
@@ -2548,29 +2548,29 @@
       <c r="E32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="8" t="n">
         <v>11500000</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>11000000</v>
+        <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>11300000</v>
+        <v>11500000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11500000</v>
+        <v>11800000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M32" s="6" t="n">
@@ -2612,7 +2612,7 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="F33" s="5" t="n">
         <v>7140000</v>
       </c>
       <c r="G33" s="6" t="n">
@@ -2629,7 +2629,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2738,7 +2738,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="8" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -2757,7 +2757,7 @@
       <c r="J35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -2794,7 +2794,7 @@
       <c r="E36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="5" t="n">
         <v>8820000</v>
       </c>
       <c r="G36" s="6" t="n">
@@ -2809,7 +2809,7 @@
       <c r="J36" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2858,7 +2858,7 @@
       <c r="E37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="5" t="n">
         <v>8820000</v>
       </c>
       <c r="G37" s="6" t="n">
@@ -2873,7 +2873,7 @@
       <c r="J37" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -2922,33 +2922,33 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>16750000</v>
+      <c r="F38" s="8" t="n">
+        <v>17640000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>15800000</v>
+        <v>17640000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>16750000</v>
+        <v>17700000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>50250000</v>
+        <v>52920000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2986,33 +2986,33 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>4485000</v>
+      <c r="F39" s="5" t="n">
+        <v>4476000</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4200000</v>
+        <v>4347000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>7599000</v>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
+        <v>4250000</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+285,000 ت از رتبه ۳ ترب (+6.8%)</t>
+          <t>+129,000 ت از رتبه ۳ ترب (+3.0%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>13455000</v>
+        <v>13428000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       <c r="E40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="5" t="n">
         <v>18480000</v>
       </c>
       <c r="G40" s="6" t="n">
@@ -3067,7 +3067,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3108,7 +3108,7 @@
       <c r="E41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="5" t="n">
         <v>13570000</v>
       </c>
       <c r="G41" s="6" t="n">
@@ -3127,7 +3127,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -3242,7 +3242,7 @@
       <c r="E43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="8" t="n">
         <v>7140000</v>
       </c>
       <c r="G43" s="6" t="n">
@@ -3259,7 +3259,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -3380,8 +3380,8 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
-        <v>7750000</v>
+      <c r="F45" s="5" t="n">
+        <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -3397,18 +3397,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>+143,000 ت از رتبه ۳ ترب (+1.9%)</t>
+          <t>+8,000 ت از رتبه ۳ ترب (+0.1%)</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
-        <v>15500000</v>
+        <v>15230000</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
@@ -3461,7 +3461,7 @@
       <c r="J46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K46" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -3506,8 +3506,8 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>6490000</v>
+      <c r="F47" s="5" t="n">
+        <v>6900000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3519,20 +3519,20 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7421400</v>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
+        <v>7725500</v>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+792,000 ت از رتبه ۳ ترب (+13.9%)</t>
+          <t>+1,202,000 ت از رتبه ۳ ترب (+21.1%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>12980000</v>
+        <v>13800000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3570,8 +3570,8 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>9325000</v>
+      <c r="F48" s="5" t="n">
+        <v>9880000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -3585,18 +3585,18 @@
       <c r="J48" s="6" t="n">
         <v>13400000</v>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>+225,000 ت از رتبه ۳ ترب (+2.5%)</t>
+          <t>+780,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>18650000</v>
+        <v>19760000</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3634,8 +3634,8 @@
       <c r="E49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>3840000</v>
+      <c r="F49" s="5" t="n">
+        <v>4050000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -3649,18 +3649,18 @@
       <c r="J49" s="6" t="n">
         <v>4600000</v>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>+690,000 ت از رتبه ۳ ترب (+21.9%)</t>
+          <t>+900,000 ت از رتبه ۳ ترب (+28.6%)</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>7680000</v>
+        <v>8100000</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3698,8 +3698,8 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>9510000</v>
+      <c r="F50" s="5" t="n">
+        <v>9455000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -3715,18 +3715,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>+2,660,000 ت از رتبه ۳ ترب (+38.8%)</t>
+          <t>+2,605,000 ت از رتبه ۳ ترب (+38.0%)</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">
-        <v>19020000</v>
+        <v>18910000</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3764,8 +3764,8 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="8" t="n">
-        <v>16750000</v>
+      <c r="F51" s="5" t="n">
+        <v>17640000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3779,18 +3779,18 @@
       <c r="J51" s="6" t="n">
         <v>16750000</v>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>+3,850,000 ت از رتبه ۳ ترب (+29.8%)</t>
+          <t>+4,740,000 ت از رتبه ۳ ترب (+36.7%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>33500000</v>
+        <v>35280000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3828,8 +3828,8 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="8" t="n">
-        <v>12520000</v>
+      <c r="F52" s="5" t="n">
+        <v>19500000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -3843,18 +3843,18 @@
       <c r="J52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>+1,020,000 ت از رتبه ۳ ترب (+8.9%)</t>
+          <t>+8,000,000 ت از رتبه ۳ ترب (+69.6%)</t>
         </is>
       </c>
       <c r="M52" s="6" t="n">
-        <v>25040000</v>
+        <v>39000000</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3892,8 +3892,8 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="8" t="n">
-        <v>12250000</v>
+      <c r="F53" s="5" t="n">
+        <v>11000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -3907,18 +3907,18 @@
       <c r="J53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>+4,761,000 ت از رتبه ۳ ترب (+63.6%)</t>
+          <t>+3,511,000 ت از رتبه ۳ ترب (+46.9%)</t>
         </is>
       </c>
       <c r="M53" s="6" t="n">
-        <v>24500000</v>
+        <v>22000000</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
       <c r="E55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="F55" s="5" t="n">
         <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
@@ -4045,7 +4045,7 @@
       <c r="J55" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4094,8 +4094,8 @@
       <c r="E56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>9990000</v>
+      <c r="F56" s="5" t="n">
+        <v>10240000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4111,18 +4111,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>+4,040,000 ت از رتبه ۳ ترب (+67.9%)</t>
+          <t>+4,290,000 ت از رتبه ۳ ترب (+72.1%)</t>
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>19980000</v>
+        <v>20480000</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="8" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -4241,7 +4241,7 @@
       <c r="J58" s="6" t="n">
         <v>9900000</v>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K58" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -4286,7 +4286,7 @@
       <c r="E59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="8" t="n">
         <v>6150000</v>
       </c>
       <c r="G59" s="6" t="n">
@@ -4299,9 +4299,9 @@
         <v>6800000</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
+        <v>10000000</v>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4350,7 +4350,7 @@
       <c r="E60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="F60" s="5" t="n">
         <v>8340000</v>
       </c>
       <c r="G60" s="6" t="n">
@@ -4367,7 +4367,7 @@
       <c r="J60" s="6" t="n">
         <v>8486000</v>
       </c>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4416,7 +4416,7 @@
       <c r="E61" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="8" t="n">
         <v>8850000</v>
       </c>
       <c r="G61" s="6" t="n">
@@ -4433,7 +4433,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4482,8 +4482,8 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="8" t="n">
-        <v>7470000</v>
+      <c r="F62" s="5" t="n">
+        <v>4715000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4495,20 +4495,20 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>4905200</v>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
+        <v>5032600</v>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+3,520,000 ت از رتبه ۳ ترب (+89.1%)</t>
+          <t>+765,000 ت از رتبه ۳ ترب (+19.4%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>14940000</v>
+        <v>9430000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       <c r="E63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="F63" s="5" t="n">
         <v>22110000</v>
       </c>
       <c r="G63" s="6" t="n">
@@ -4561,9 +4561,9 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
+        <v>20000000</v>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4612,8 +4612,8 @@
       <c r="E64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="8" t="n">
-        <v>5070000</v>
+      <c r="F64" s="5" t="n">
+        <v>5270000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4627,18 +4627,18 @@
       <c r="J64" s="6" t="n">
         <v>5812500</v>
       </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه ۳ ترب (+2.4%)</t>
+          <t>+320,000 ت از رتبه ۳ ترب (+6.5%)</t>
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>10140000</v>
+        <v>10540000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
       <c r="E65" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="8" t="n">
         <v>2650000</v>
       </c>
       <c r="G65" s="6" t="n">
@@ -4693,7 +4693,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K65" s="7" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4742,7 +4742,7 @@
       <c r="E66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="8" t="n">
         <v>15600000</v>
       </c>
       <c r="G66" s="6" t="n">
@@ -4757,7 +4757,7 @@
       <c r="J66" s="6" t="n">
         <v>16019000</v>
       </c>
-      <c r="K66" s="7" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4798,7 +4798,7 @@
       <c r="E67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="F67" s="5" t="n">
         <v>4000000</v>
       </c>
       <c r="G67" s="6" t="n">
@@ -4819,7 +4819,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -4868,7 +4868,7 @@
       <c r="E68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="8" t="n">
         <v>3920000</v>
       </c>
       <c r="G68" s="6" t="n">
@@ -4883,7 +4883,7 @@
       <c r="J68" s="6" t="n">
         <v>4326110</v>
       </c>
-      <c r="K68" s="7" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4932,7 +4932,7 @@
       <c r="E69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="8" t="n">
         <v>13290000</v>
       </c>
       <c r="G69" s="6" t="n">
@@ -4949,7 +4949,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -4998,7 +4998,7 @@
       <c r="E70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="8" t="n">
+      <c r="F70" s="5" t="n">
         <v>9550000</v>
       </c>
       <c r="G70" s="6" t="n">
@@ -5017,7 +5017,7 @@
       <c r="J70" s="6" t="n">
         <v>15000000</v>
       </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5066,7 +5066,7 @@
       <c r="E71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="8" t="n">
+      <c r="F71" s="5" t="n">
         <v>7240000</v>
       </c>
       <c r="G71" s="6" t="n">
@@ -5083,7 +5083,7 @@
       <c r="J71" s="6" t="n">
         <v>9700000</v>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5132,7 +5132,7 @@
       <c r="E72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F72" s="8" t="n">
+      <c r="F72" s="5" t="n">
         <v>17590000</v>
       </c>
       <c r="G72" s="6" t="n">
@@ -5151,7 +5151,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K72" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5200,8 +5200,8 @@
       <c r="E73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="8" t="n">
-        <v>4310000</v>
+      <c r="F73" s="5" t="n">
+        <v>4450000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -5215,18 +5215,18 @@
       <c r="J73" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>+420,000 ت از رتبه ۳ ترب (+10.8%)</t>
+          <t>+560,000 ت از رتبه ۳ ترب (+14.4%)</t>
         </is>
       </c>
       <c r="M73" s="6" t="n">
-        <v>8620000</v>
+        <v>8900000</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -5264,8 +5264,8 @@
       <c r="E74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="8" t="n">
-        <v>12630000</v>
+      <c r="F74" s="5" t="n">
+        <v>12030000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -5279,18 +5279,18 @@
       <c r="J74" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>+3,430,000 ت از رتبه ۳ ترب (+37.3%)</t>
+          <t>+2,830,000 ت از رتبه ۳ ترب (+30.8%)</t>
         </is>
       </c>
       <c r="M74" s="6" t="n">
-        <v>12630000</v>
+        <v>12030000</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -5328,8 +5328,8 @@
       <c r="E75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="8" t="n">
-        <v>21750000</v>
+      <c r="F75" s="5" t="n">
+        <v>22000000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -5343,18 +5343,18 @@
       <c r="J75" s="6" t="n">
         <v>23900000</v>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>+19,305,000 ت از رتبه ۳ ترب (+789.6%)</t>
+          <t>+19,555,000 ت از رتبه ۳ ترب (+799.8%)</t>
         </is>
       </c>
       <c r="M75" s="6" t="n">
-        <v>21750000</v>
+        <v>22000000</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
       <c r="E76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="8" t="n">
+      <c r="F76" s="5" t="n">
         <v>27470000</v>
       </c>
       <c r="G76" s="6" t="n">
@@ -5403,7 +5403,7 @@
       <c r="J76" s="6" t="n">
         <v>36400000</v>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5448,8 +5448,8 @@
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>11060000</v>
+      <c r="F77" s="5" t="n">
+        <v>9990000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -5463,18 +5463,18 @@
       <c r="J77" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>+1,860,000 ت از رتبه ۳ ترب (+20.2%)</t>
+          <t>+790,000 ت از رتبه ۳ ترب (+8.6%)</t>
         </is>
       </c>
       <c r="M77" s="6" t="n">
-        <v>11060000</v>
+        <v>9990000</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -5512,8 +5512,8 @@
       <c r="E78" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="8" t="n">
-        <v>12630000</v>
+      <c r="F78" s="5" t="n">
+        <v>12030000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -5527,18 +5527,18 @@
       <c r="J78" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>+3,430,000 ت از رتبه ۳ ترب (+37.3%)</t>
+          <t>+2,830,000 ت از رتبه ۳ ترب (+30.8%)</t>
         </is>
       </c>
       <c r="M78" s="6" t="n">
-        <v>12630000</v>
+        <v>12030000</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
       <c r="E79" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="8" t="n">
+      <c r="F79" s="5" t="n">
         <v>4950000</v>
       </c>
       <c r="G79" s="6" t="n">
@@ -5589,9 +5589,9 @@
         <v>3855000</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>4824000</v>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
+        <v>4900000</v>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5640,8 +5640,8 @@
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="8" t="n">
-        <v>15390000</v>
+      <c r="F80" s="5" t="n">
+        <v>15485000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -5655,18 +5655,18 @@
       <c r="J80" s="6" t="n">
         <v>29987800</v>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>+400,000 ت از رتبه ۳ ترب (+2.7%)</t>
+          <t>+495,000 ت از رتبه ۳ ترب (+3.3%)</t>
         </is>
       </c>
       <c r="M80" s="6" t="n">
-        <v>15390000</v>
+        <v>15485000</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="5" t="n">
         <v>6495000</v>
       </c>
       <c r="G81" s="6" t="n">
@@ -5717,9 +5717,9 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>8760000</v>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
+        <v>8880000</v>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5768,7 +5768,7 @@
       <c r="E82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F82" s="8" t="n">
+      <c r="F82" s="5" t="n">
         <v>5980000</v>
       </c>
       <c r="G82" s="6" t="n">
@@ -5785,7 +5785,7 @@
       <c r="J82" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -5834,8 +5834,8 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="8" t="n">
-        <v>15520000</v>
+      <c r="F83" s="5" t="n">
+        <v>15760000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5847,20 +5847,20 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
+        <v>14300000</v>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>+3,720,000 ت از رتبه ۳ ترب (+31.5%)</t>
+          <t>+3,960,000 ت از رتبه ۳ ترب (+33.6%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>15520000</v>
+        <v>15760000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -5898,8 +5898,8 @@
       <c r="E84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F84" s="8" t="n">
-        <v>2670000</v>
+      <c r="F84" s="5" t="n">
+        <v>2687000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -5913,18 +5913,18 @@
       <c r="J84" s="6" t="n">
         <v>3795000</v>
       </c>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>+225,000 ت از رتبه ۳ ترب (+9.2%)</t>
+          <t>+242,000 ت از رتبه ۳ ترب (+9.9%)</t>
         </is>
       </c>
       <c r="M84" s="6" t="n">
-        <v>2670000</v>
+        <v>2687000</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="8" t="n">
+      <c r="F85" s="5" t="n">
         <v>12630000</v>
       </c>
       <c r="G85" s="6" t="n">
@@ -5973,7 +5973,7 @@
       <c r="J85" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6096,8 +6096,8 @@
       <c r="E87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F87" s="8" t="n">
-        <v>8250000</v>
+      <c r="F87" s="5" t="n">
+        <v>8270000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -6117,18 +6117,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="K87" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>+4,050,000 ت از رتبه ۳ ترب (+96.4%)</t>
+          <t>+4,070,000 ت از رتبه ۳ ترب (+96.9%)</t>
         </is>
       </c>
       <c r="M87" s="6" t="n">
-        <v>8250000</v>
+        <v>8270000</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       <c r="E88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="8" t="n">
+      <c r="F88" s="5" t="n">
         <v>7840000</v>
       </c>
       <c r="G88" s="6" t="n">
@@ -6183,7 +6183,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K88" s="9" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6232,7 +6232,7 @@
       <c r="E89" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="8" t="n">
+      <c r="F89" s="5" t="n">
         <v>8820000</v>
       </c>
       <c r="G89" s="6" t="n">
@@ -6247,7 +6247,7 @@
       <c r="J89" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="K89" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6296,7 +6296,7 @@
       <c r="E90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="8" t="n">
+      <c r="F90" s="5" t="n">
         <v>8820000</v>
       </c>
       <c r="G90" s="6" t="n">
@@ -6311,7 +6311,7 @@
       <c r="J90" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K90" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6360,8 +6360,8 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="8" t="n">
-        <v>7470000</v>
+      <c r="F91" s="5" t="n">
+        <v>4715000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6373,20 +6373,20 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>4905200</v>
-      </c>
-      <c r="K91" s="9" t="inlineStr">
+        <v>5032600</v>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>+3,520,000 ت از رتبه ۳ ترب (+89.1%)</t>
+          <t>+765,000 ت از رتبه ۳ ترب (+19.4%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>7470000</v>
+        <v>4715000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6424,8 +6424,8 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="8" t="n">
-        <v>3503000</v>
+      <c r="F92" s="5" t="n">
+        <v>3501000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6437,20 +6437,20 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>4119900</v>
-      </c>
-      <c r="K92" s="9" t="inlineStr">
+        <v>4242000</v>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>+515,000 ت از رتبه ۳ ترب (+17.2%)</t>
+          <t>+513,000 ت از رتبه ۳ ترب (+17.2%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>3503000</v>
+        <v>3501000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -6488,8 +6488,8 @@
       <c r="E93" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F93" s="8" t="n">
-        <v>7780000</v>
+      <c r="F93" s="5" t="n">
+        <v>7895000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -6503,18 +6503,18 @@
       <c r="J93" s="6" t="n">
         <v>8550000</v>
       </c>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="K93" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>+860,000 ت از رتبه ۳ ترب (+12.4%)</t>
+          <t>+975,000 ت از رتبه ۳ ترب (+14.1%)</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
-        <v>7780000</v>
+        <v>7895000</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="8" t="n">
+      <c r="F94" s="5" t="n">
         <v>5920000</v>
       </c>
       <c r="G94" s="6" t="n">
@@ -6571,7 +6571,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K94" s="9" t="inlineStr">
+      <c r="K94" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6620,8 +6620,8 @@
       <c r="E95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="8" t="n">
-        <v>24150000</v>
+      <c r="F95" s="5" t="n">
+        <v>24710000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -6635,18 +6635,18 @@
       <c r="J95" s="6" t="n">
         <v>27850000</v>
       </c>
-      <c r="K95" s="9" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>+2,800,000 ت از رتبه ۳ ترب (+13.1%)</t>
+          <t>+3,360,000 ت از رتبه ۳ ترب (+15.7%)</t>
         </is>
       </c>
       <c r="M95" s="6" t="n">
-        <v>24150000</v>
+        <v>24710000</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -6684,8 +6684,8 @@
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="8" t="n">
-        <v>4910000</v>
+      <c r="F96" s="5" t="n">
+        <v>4990000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -6705,18 +6705,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K96" s="9" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>+410,000 ت از رتبه ۳ ترب (+9.1%)</t>
+          <t>+490,000 ت از رتبه ۳ ترب (+10.9%)</t>
         </is>
       </c>
       <c r="M96" s="6" t="n">
-        <v>4910000</v>
+        <v>4990000</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
       <c r="E97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F97" s="8" t="n">
+      <c r="F97" s="5" t="n">
         <v>9550000</v>
       </c>
       <c r="G97" s="6" t="n">
@@ -6775,7 +6775,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="K97" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6824,7 +6824,7 @@
       <c r="E98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="5" t="n">
         <v>11000000</v>
       </c>
       <c r="G98" s="6" t="n">
@@ -6839,7 +6839,7 @@
       <c r="J98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="K98" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -6888,8 +6888,8 @@
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="8" t="n">
-        <v>4310000</v>
+      <c r="F99" s="5" t="n">
+        <v>4450000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -6903,18 +6903,18 @@
       <c r="J99" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="K99" s="9" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>+420,000 ت از رتبه ۳ ترب (+10.8%)</t>
+          <t>+560,000 ت از رتبه ۳ ترب (+14.4%)</t>
         </is>
       </c>
       <c r="M99" s="6" t="n">
-        <v>4310000</v>
+        <v>4450000</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
       <c r="E100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F100" s="8" t="n">
         <v>3390000</v>
       </c>
       <c r="G100" s="6" t="n">
@@ -6969,7 +6969,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="K100" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -7018,7 +7018,7 @@
       <c r="E101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F101" s="8" t="n">
+      <c r="F101" s="5" t="n">
         <v>3120000</v>
       </c>
       <c r="G101" s="6" t="n">
@@ -7035,7 +7035,7 @@
       <c r="J101" s="6" t="n">
         <v>3200000</v>
       </c>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="K101" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7076,7 +7076,7 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="5" t="n">
+      <c r="F102" s="8" t="n">
         <v>27470000</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -7093,7 +7093,7 @@
       <c r="J102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="K102" s="7" t="inlineStr">
+      <c r="K102" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -7206,7 +7206,7 @@
       <c r="E104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F104" s="8" t="n">
+      <c r="F104" s="5" t="n">
         <v>4950000</v>
       </c>
       <c r="G104" s="6" t="n">
@@ -7219,9 +7219,9 @@
         <v>3855000</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>4824000</v>
-      </c>
-      <c r="K104" s="9" t="inlineStr">
+        <v>4900000</v>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7270,7 +7270,7 @@
       <c r="E105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F105" s="5" t="n">
+      <c r="F105" s="8" t="n">
         <v>4440000</v>
       </c>
       <c r="G105" s="6" t="n">
@@ -7285,7 +7285,7 @@
       <c r="J105" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="K105" s="7" t="inlineStr">
+      <c r="K105" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -7334,7 +7334,7 @@
       <c r="E106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F106" s="8" t="n">
+      <c r="F106" s="5" t="n">
         <v>13070000</v>
       </c>
       <c r="G106" s="6" t="n">
@@ -7351,7 +7351,7 @@
       <c r="J106" s="6" t="n">
         <v>11000000</v>
       </c>
-      <c r="K106" s="9" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7474,7 +7474,7 @@
       <c r="E108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="5" t="n">
+      <c r="F108" s="8" t="n">
         <v>9590000</v>
       </c>
       <c r="G108" s="6" t="n">
@@ -7489,7 +7489,7 @@
       <c r="J108" s="6" t="n">
         <v>14550000</v>
       </c>
-      <c r="K108" s="7" t="inlineStr">
+      <c r="K108" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -7538,7 +7538,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F109" s="8" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -7559,7 +7559,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K109" s="7" t="inlineStr">
+      <c r="K109" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -7604,7 +7604,7 @@
       <c r="E110" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F110" s="8" t="n">
+      <c r="F110" s="5" t="n">
         <v>3600000</v>
       </c>
       <c r="G110" s="6" t="n">
@@ -7625,7 +7625,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="K110" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -7822,7 +7822,7 @@
       <c r="E113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="5" t="n">
+      <c r="F113" s="8" t="n">
         <v>6220000</v>
       </c>
       <c r="G113" s="6" t="n">
@@ -7837,7 +7837,7 @@
       <c r="J113" s="6" t="n">
         <v>7900000</v>
       </c>
-      <c r="K113" s="7" t="inlineStr">
+      <c r="K113" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -7886,7 +7886,7 @@
       <c r="E114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F114" s="8" t="n">
         <v>9440000</v>
       </c>
       <c r="G114" s="6" t="n">
@@ -7901,7 +7901,7 @@
       <c r="J114" s="6" t="n">
         <v>11290000</v>
       </c>
-      <c r="K114" s="7" t="inlineStr">
+      <c r="K114" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -7950,7 +7950,7 @@
       <c r="E115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F115" s="5" t="n">
+      <c r="F115" s="8" t="n">
         <v>9650000</v>
       </c>
       <c r="G115" s="6" t="n">
@@ -7967,7 +7967,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr">
+      <c r="K115" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8016,8 +8016,8 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="8" t="n">
-        <v>3503000</v>
+      <c r="F116" s="5" t="n">
+        <v>3501000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8029,20 +8029,20 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>4119900</v>
-      </c>
-      <c r="K116" s="9" t="inlineStr">
+        <v>4242000</v>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>+515,000 ت از رتبه ۳ ترب (+17.2%)</t>
+          <t>+513,000 ت از رتبه ۳ ترب (+17.2%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3503000</v>
+        <v>3501000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
       <c r="E117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F117" s="8" t="n">
+      <c r="F117" s="5" t="n">
         <v>4920000</v>
       </c>
       <c r="G117" s="6" t="n">
@@ -8099,7 +8099,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K117" s="9" t="inlineStr">
+      <c r="K117" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8148,7 +8148,7 @@
       <c r="E118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="5" t="n">
+      <c r="F118" s="8" t="n">
         <v>6200000</v>
       </c>
       <c r="G118" s="6" t="n">
@@ -8165,7 +8165,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K118" s="7" t="inlineStr">
+      <c r="K118" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8214,8 +8214,8 @@
       <c r="E119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="8" t="n">
-        <v>12250000</v>
+      <c r="F119" s="5" t="n">
+        <v>11000000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -8229,18 +8229,18 @@
       <c r="J119" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="K119" s="9" t="inlineStr">
+      <c r="K119" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>+4,761,000 ت از رتبه ۳ ترب (+63.6%)</t>
+          <t>+3,511,000 ت از رتبه ۳ ترب (+46.9%)</t>
         </is>
       </c>
       <c r="M119" s="6" t="n">
-        <v>12250000</v>
+        <v>11000000</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
       <c r="E120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="5" t="n">
+      <c r="F120" s="8" t="n">
         <v>6370000</v>
       </c>
       <c r="G120" s="6" t="n">
@@ -8295,7 +8295,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K120" s="7" t="inlineStr">
+      <c r="K120" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8344,7 +8344,7 @@
       <c r="E121" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F121" s="8" t="n">
+      <c r="F121" s="5" t="n">
         <v>7540000</v>
       </c>
       <c r="G121" s="6" t="n">
@@ -8361,7 +8361,7 @@
       <c r="J121" s="6" t="n">
         <v>9900000</v>
       </c>
-      <c r="K121" s="9" t="inlineStr">
+      <c r="K121" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8406,7 +8406,7 @@
       <c r="E122" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="5" t="n">
+      <c r="F122" s="8" t="n">
         <v>10970000</v>
       </c>
       <c r="G122" s="6" t="n">
@@ -8421,7 +8421,7 @@
       <c r="J122" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K122" s="7" t="inlineStr">
+      <c r="K122" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8470,7 +8470,7 @@
       <c r="E123" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="5" t="n">
+      <c r="F123" s="8" t="n">
         <v>9550000</v>
       </c>
       <c r="G123" s="6" t="n">
@@ -8485,7 +8485,7 @@
       <c r="J123" s="6" t="n">
         <v>18900000</v>
       </c>
-      <c r="K123" s="7" t="inlineStr">
+      <c r="K123" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8600,7 +8600,7 @@
       <c r="E125" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F125" s="8" t="n">
+      <c r="F125" s="5" t="n">
         <v>15460000</v>
       </c>
       <c r="G125" s="6" t="n">
@@ -8615,9 +8615,9 @@
         </is>
       </c>
       <c r="J125" s="6" t="n">
-        <v>17800000</v>
-      </c>
-      <c r="K125" s="9" t="inlineStr">
+        <v>17000000</v>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8666,7 +8666,7 @@
       <c r="E126" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F126" s="8" t="n">
         <v>10970000</v>
       </c>
       <c r="G126" s="6" t="n">
@@ -8681,7 +8681,7 @@
       <c r="J126" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K126" s="7" t="inlineStr">
+      <c r="K126" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -8804,7 +8804,7 @@
       <c r="E128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F128" s="8" t="n">
+      <c r="F128" s="5" t="n">
         <v>11000000</v>
       </c>
       <c r="G128" s="6" t="n">
@@ -8819,7 +8819,7 @@
       <c r="J128" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="K128" s="9" t="inlineStr">
+      <c r="K128" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
@@ -8942,7 +8942,7 @@
       <c r="E130" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="5" t="n">
+      <c r="F130" s="8" t="n">
         <v>6770000</v>
       </c>
       <c r="G130" s="6" t="n">
@@ -8959,7 +8959,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K130" s="7" t="inlineStr">
+      <c r="K130" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9008,7 +9008,7 @@
       <c r="E131" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="8" t="n">
         <v>10250000</v>
       </c>
       <c r="G131" s="6" t="n">
@@ -9025,7 +9025,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K131" s="7" t="inlineStr">
+      <c r="K131" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9074,7 +9074,7 @@
       <c r="E132" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F132" s="5" t="n">
+      <c r="F132" s="8" t="n">
         <v>11320000</v>
       </c>
       <c r="G132" s="6" t="n">
@@ -9091,7 +9091,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K132" s="7" t="inlineStr">
+      <c r="K132" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
@@ -9140,8 +9140,8 @@
       <c r="E133" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>16750000</v>
+      <c r="F133" s="5" t="n">
+        <v>21750000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -9155,18 +9155,18 @@
       <c r="J133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="K133" s="9" t="inlineStr">
+      <c r="K133" s="7" t="inlineStr">
         <is>
           <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>+550,000 ت از رتبه ۳ ترب (+3.4%)</t>
+          <t>+5,550,000 ت از رتبه ۳ ترب (+34.3%)</t>
         </is>
       </c>
       <c r="M133" s="6" t="n">
-        <v>16750000</v>
+        <v>21750000</v>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
       <c r="E134" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F134" s="5" t="n">
+      <c r="F134" s="8" t="n">
         <v>19750000</v>
       </c>
       <c r="G134" s="6" t="n">
@@ -9221,7 +9221,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K134" s="7" t="inlineStr">
+      <c r="K134" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -628,7 +628,7 @@
         <v>9900000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10290000</v>
+        <v>10140700</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>11450000</v>
@@ -640,7 +640,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>+660,000 ت از رتبه ۳ ترب (+6.4%)</t>
+          <t>+809,300 ت از رتبه ۳ ترب (+8.0%)</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
@@ -683,7 +683,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20570000</v>
+        <v>20580000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>19990000</v>
@@ -692,7 +692,7 @@
         <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20570000</v>
+        <v>20580000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20590000</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>1295910000</v>
+        <v>1296540000</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -746,33 +746,33 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>16340000</v>
+      <c r="F4" s="8" t="n">
+        <v>16680000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>14200000</v>
+        <v>14980000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>14200000</v>
+        <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>14289000</v>
+        <v>16680000</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>+2,051,000 ت از رتبه ۳ ترب (+14.4%)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>490200000</v>
+        <v>500400000</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         <v>18</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10080000</v>
+        <v>6370000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5500000</v>
+        <v>5400000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5500000</v>
@@ -832,11 +832,11 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>+4,409,897 ت از رتبه ۳ ترب (+77.8%)</t>
+          <t>+699,897 ت از رتبه ۳ ترب (+12.3%)</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>181440000</v>
+        <v>114660000</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4476000</v>
+        <v>4465000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4000000</v>
@@ -960,11 +960,11 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>+129,000 ت از رتبه ۳ ترب (+3.0%)</t>
+          <t>+118,000 ت از رتبه ۳ ترب (+2.7%)</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>67140000</v>
+        <v>66975000</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9790000</v>
+        <v>9795000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9200000</v>
+        <v>9300000</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9790000</v>
+        <v>9795000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>10950000</v>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>107690000</v>
+        <v>107745000</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7640000</v>
+        <v>7750000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1220,11 +1220,11 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>+150,000 ت از رتبه ۳ ترب (+2.0%)</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>84040000</v>
+        <v>85250000</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>4999000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5200000</v>
+        <v>5250000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5700000</v>
@@ -1330,13 +1330,13 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>12000000</v>
+        <v>13800000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>13800000</v>
+        <v>13900000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>13900000</v>
+        <v>14000000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>9500000</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>-1,800,000 ت از کف ترب (-15.0%)</t>
+          <t>-3,600,000 ت از کف ترب (-26.1%)</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
@@ -1389,13 +1389,13 @@
         <v>11500000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11500000</v>
+        <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>11670000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>20450000</v>
+        <v>20850000</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
         <v>8470000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6500000</v>
+        <v>7195000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7195000</v>
+        <v>7197000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7197000</v>
+        <v>7300000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8880000</v>
+        <v>8860000</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>+1,273,000 ت از رتبه ۳ ترب (+17.7%)</t>
+          <t>+1,170,000 ت از رتبه ۳ ترب (+16.0%)</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
@@ -1711,16 +1711,16 @@
         <v>6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9790000</v>
+        <v>9795000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9200000</v>
+        <v>9300000</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9790000</v>
+        <v>9795000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>10950000</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>58740000</v>
+        <v>58770000</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>15880000</v>
+        <v>19885220</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
         <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9660000</v>
+        <v>9050000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>13300000</v>
+        <v>9400000</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>7652540</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>+8,450,000 ت از رتبه ۳ ترب (+63.5%)</t>
+          <t>+12,350,000 ت از رتبه ۳ ترب (+131.4%)</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
@@ -2037,19 +2037,19 @@
         <v>5</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>6900000</v>
+        <v>6670000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>6200000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6400000</v>
+        <v>6449000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6449000</v>
+        <v>6550000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7725500</v>
+        <v>7594700</v>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -2058,11 +2058,11 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>+451,000 ت از رتبه ۳ ترب (+7.0%)</t>
+          <t>+120,000 ت از رتبه ۳ ترب (+1.8%)</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>34500000</v>
+        <v>33350000</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -2107,22 +2107,22 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6900000</v>
+        <v>7500000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7480000</v>
+        <v>8290000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>15000000</v>
+        <v>14600000</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (مجاز)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (مجاز)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
@@ -2168,13 +2168,13 @@
         <v>7690000</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>7890000</v>
+        <v>8500000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7980000</v>
+        <v>8900000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>5400000</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>-200,000 ت از کف ترب (-2.5%)</t>
+          <t>-810,000 ت از کف ترب (-9.5%)</t>
         </is>
       </c>
       <c r="M26" s="6" t="n">
@@ -2355,19 +2355,19 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>5270000</v>
+        <v>5250000</v>
       </c>
       <c r="G29" s="6" t="n">
+        <v>5190000</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>5199000</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="H29" s="6" t="n">
-        <v>5214550</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>5220000</v>
-      </c>
       <c r="J29" s="6" t="n">
-        <v>5812500</v>
+        <v>6250000</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>21080000</v>
+        <v>21000000</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -2488,16 +2488,16 @@
         <v>28000000</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>13900000</v>
+        <v>14000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>14000000</v>
+        <v>14900000</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>14900000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>27990000</v>
+        <v>27300000</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>7140000</v>
+        <v>7060000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
@@ -2636,11 +2636,11 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>+141,000 ت از رتبه ۳ ترب (+2.0%)</t>
+          <t>+61,000 ت از رتبه ۳ ترب (+0.9%)</t>
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>21420000</v>
+        <v>21180000</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2923,32 +2923,32 @@
         <v>3</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17640000</v>
+        <v>17720000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17640000</v>
+        <v>17700000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17700000</v>
+        <v>17720000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>16790000</v>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (مجاز)</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
-        <v>52920000</v>
+        <v>53160000</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4476000</v>
+        <v>4465000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>4000000</v>
@@ -3008,11 +3008,11 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>+129,000 ت از رتبه ۳ ترب (+3.0%)</t>
+          <t>+118,000 ت از رتبه ۳ ترب (+2.7%)</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>13428000</v>
+        <v>13395000</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7880000</v>
+        <v>7500000</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>7615000</v>
+        <v>7611000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -3404,11 +3404,11 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه ۳ ترب (+0.1%)</t>
+          <t>+4,000 ت از رتبه ۳ ترب (+0.1%)</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
-        <v>15230000</v>
+        <v>15222000</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>6900000</v>
+        <v>6670000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3519,7 +3519,7 @@
         <v>5698000</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7725500</v>
+        <v>7594700</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
@@ -3528,11 +3528,11 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>+1,202,000 ت از رتبه ۳ ترب (+21.1%)</t>
+          <t>+972,000 ت از رتبه ۳ ترب (+17.1%)</t>
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>13800000</v>
+        <v>13340000</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>9880000</v>
+        <v>9940000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -3583,7 +3583,7 @@
         <v>9100000</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>13400000</v>
+        <v>14500000</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
@@ -3592,11 +3592,11 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>+780,000 ت از رتبه ۳ ترب (+8.6%)</t>
+          <t>+840,000 ت از رتبه ۳ ترب (+9.2%)</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>19760000</v>
+        <v>19880000</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>4050000</v>
+        <v>3840000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -3656,11 +3656,11 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>+900,000 ت از رتبه ۳ ترب (+28.6%)</t>
+          <t>+690,000 ت از رتبه ۳ ترب (+21.9%)</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>8100000</v>
+        <v>7680000</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9455000</v>
+        <v>9452000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>+2,605,000 ت از رتبه ۳ ترب (+38.0%)</t>
+          <t>+2,602,000 ت از رتبه ۳ ترب (+38.0%)</t>
         </is>
       </c>
       <c r="M50" s="6" t="n">
-        <v>18910000</v>
+        <v>18904000</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17640000</v>
+        <v>17720000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -3786,11 +3786,11 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>+4,740,000 ت از رتبه ۳ ترب (+36.7%)</t>
+          <t>+4,820,000 ت از رتبه ۳ ترب (+37.4%)</t>
         </is>
       </c>
       <c r="M51" s="6" t="n">
-        <v>35280000</v>
+        <v>35440000</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>19500000</v>
+        <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -3850,11 +3850,11 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>+8,000,000 ت از رتبه ۳ ترب (+69.6%)</t>
+          <t>+850,000 ت از رتبه ۳ ترب (+7.4%)</t>
         </is>
       </c>
       <c r="M52" s="6" t="n">
-        <v>39000000</v>
+        <v>24700000</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>11000000</v>
+        <v>10500000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -3914,11 +3914,11 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>+3,511,000 ت از رتبه ۳ ترب (+46.9%)</t>
+          <t>+3,011,000 ت از رتبه ۳ ترب (+40.2%)</t>
         </is>
       </c>
       <c r="M53" s="6" t="n">
-        <v>22000000</v>
+        <v>21000000</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10240000</v>
+        <v>10290000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>+4,290,000 ت از رتبه ۳ ترب (+72.1%)</t>
+          <t>+4,340,000 ت از رتبه ۳ ترب (+72.9%)</t>
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>20480000</v>
+        <v>20580000</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>6800000</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>4715000</v>
+        <v>4720000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -4495,7 +4495,7 @@
         <v>3950000</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>5032600</v>
+        <v>5750000</v>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
@@ -4504,11 +4504,11 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>+765,000 ت از رتبه ۳ ترب (+19.4%)</t>
+          <t>+770,000 ت از رتبه ۳ ترب (+19.5%)</t>
         </is>
       </c>
       <c r="M62" s="6" t="n">
-        <v>9430000</v>
+        <v>9440000</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>20000000</v>
+        <v>19200000</v>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5270000</v>
+        <v>5250000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -4625,7 +4625,7 @@
         <v>4950000</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>5812500</v>
+        <v>6250000</v>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
@@ -4634,11 +4634,11 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>+320,000 ت از رتبه ۳ ترب (+6.5%)</t>
+          <t>+300,000 ت از رتبه ۳ ترب (+6.1%)</t>
         </is>
       </c>
       <c r="M64" s="6" t="n">
-        <v>10540000</v>
+        <v>10500000</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4450000</v>
+        <v>4460000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -5213,7 +5213,7 @@
         <v>3890000</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>4703670</v>
+        <v>4870000</v>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
@@ -5222,11 +5222,11 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>+560,000 ت از رتبه ۳ ترب (+14.4%)</t>
+          <t>+570,000 ت از رتبه ۳ ترب (+14.7%)</t>
         </is>
       </c>
       <c r="M73" s="6" t="n">
-        <v>8900000</v>
+        <v>8920000</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>12030000</v>
+        <v>12010000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -5286,11 +5286,11 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>+2,830,000 ت از رتبه ۳ ترب (+30.8%)</t>
+          <t>+2,810,000 ت از رتبه ۳ ترب (+30.5%)</t>
         </is>
       </c>
       <c r="M74" s="6" t="n">
-        <v>12030000</v>
+        <v>12010000</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12030000</v>
+        <v>12010000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -5534,11 +5534,11 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>+2,830,000 ت از رتبه ۳ ترب (+30.8%)</t>
+          <t>+2,810,000 ت از رتبه ۳ ترب (+30.5%)</t>
         </is>
       </c>
       <c r="M78" s="6" t="n">
-        <v>12030000</v>
+        <v>12010000</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15485000</v>
+        <v>15495000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -5662,11 +5662,11 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>+495,000 ت از رتبه ۳ ترب (+3.3%)</t>
+          <t>+505,000 ت از رتبه ۳ ترب (+3.4%)</t>
         </is>
       </c>
       <c r="M80" s="6" t="n">
-        <v>15485000</v>
+        <v>15495000</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>6200000</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>8880000</v>
+        <v>8860000</v>
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>15760000</v>
+        <v>15780000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -5847,7 +5847,7 @@
         <v>11800000</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>14300000</v>
+        <v>39000000</v>
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
@@ -5856,11 +5856,11 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>+3,960,000 ت از رتبه ۳ ترب (+33.6%)</t>
+          <t>+3,980,000 ت از رتبه ۳ ترب (+33.7%)</t>
         </is>
       </c>
       <c r="M83" s="6" t="n">
-        <v>15760000</v>
+        <v>15780000</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2687000</v>
+        <v>2660000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -5920,11 +5920,11 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>+242,000 ت از رتبه ۳ ترب (+9.9%)</t>
+          <t>+215,000 ت از رتبه ۳ ترب (+8.8%)</t>
         </is>
       </c>
       <c r="M84" s="6" t="n">
-        <v>2687000</v>
+        <v>2660000</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>4715000</v>
+        <v>4720000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -6373,7 +6373,7 @@
         <v>3950000</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>5032600</v>
+        <v>5750000</v>
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
@@ -6382,11 +6382,11 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>+765,000 ت از رتبه ۳ ترب (+19.4%)</t>
+          <t>+770,000 ت از رتبه ۳ ترب (+19.5%)</t>
         </is>
       </c>
       <c r="M91" s="6" t="n">
-        <v>4715000</v>
+        <v>4720000</v>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3501000</v>
+        <v>3508000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -6437,7 +6437,7 @@
         <v>2988000</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>4242000</v>
+        <v>4214400</v>
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
@@ -6446,11 +6446,11 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>+513,000 ت از رتبه ۳ ترب (+17.2%)</t>
+          <t>+520,000 ت از رتبه ۳ ترب (+17.4%)</t>
         </is>
       </c>
       <c r="M92" s="6" t="n">
-        <v>3501000</v>
+        <v>3508000</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7895000</v>
+        <v>7979500</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -6510,11 +6510,11 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>+975,000 ت از رتبه ۳ ترب (+14.1%)</t>
+          <t>+1,059,500 ت از رتبه ۳ ترب (+15.3%)</t>
         </is>
       </c>
       <c r="M93" s="6" t="n">
-        <v>7895000</v>
+        <v>7979500</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -6552,8 +6552,8 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>5920000</v>
+      <c r="F94" s="8" t="n">
+        <v>5800000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -6571,18 +6571,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="K94" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۳ رتبه اول</t>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>+31,000 ت از رتبه ۳ ترب (+0.5%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="M94" s="6" t="n">
-        <v>5920000</v>
+        <v>5800000</v>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>24710000</v>
+        <v>24750000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -6642,11 +6642,11 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>+3,360,000 ت از رتبه ۳ ترب (+15.7%)</t>
+          <t>+3,400,000 ت از رتبه ۳ ترب (+15.9%)</t>
         </is>
       </c>
       <c r="M95" s="6" t="n">
-        <v>24710000</v>
+        <v>24750000</v>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>4990000</v>
+        <v>5010000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -6712,11 +6712,11 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>+490,000 ت از رتبه ۳ ترب (+10.9%)</t>
+          <t>+510,000 ت از رتبه ۳ ترب (+11.3%)</t>
         </is>
       </c>
       <c r="M96" s="6" t="n">
-        <v>4990000</v>
+        <v>5010000</v>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4450000</v>
+        <v>4460000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -6901,7 +6901,7 @@
         <v>3890000</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>4703670</v>
+        <v>4870000</v>
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
@@ -6910,11 +6910,11 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>+560,000 ت از رتبه ۳ ترب (+14.4%)</t>
+          <t>+570,000 ت از رتبه ۳ ترب (+14.7%)</t>
         </is>
       </c>
       <c r="M99" s="6" t="n">
-        <v>4450000</v>
+        <v>4460000</v>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3501000</v>
+        <v>3508000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -8029,7 +8029,7 @@
         <v>2988000</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>4242000</v>
+        <v>4214400</v>
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
@@ -8038,11 +8038,11 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>+513,000 ت از رتبه ۳ ترب (+17.2%)</t>
+          <t>+520,000 ت از رتبه ۳ ترب (+17.4%)</t>
         </is>
       </c>
       <c r="M116" s="6" t="n">
-        <v>3501000</v>
+        <v>3508000</v>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>11000000</v>
+        <v>10500000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -8236,11 +8236,11 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>+3,511,000 ت از رتبه ۳ ترب (+46.9%)</t>
+          <t>+3,011,000 ت از رتبه ۳ ترب (+40.2%)</t>
         </is>
       </c>
       <c r="M119" s="6" t="n">
-        <v>11000000</v>
+        <v>10500000</v>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>7140000</v>
+        <v>7060000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -8558,11 +8558,11 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
+          <t>-2,540,000 ت از کف ترب (-26.5%)</t>
         </is>
       </c>
       <c r="M124" s="6" t="n">
-        <v>7140000</v>
+        <v>7060000</v>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مانیتورینگ ۵ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="مانیتورینگ ۵ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,14 +63,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3E8FF"/>
-        <bgColor rgb="00F3E8FF"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,26 +636,22 @@
         <v>10950000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9200000</v>
+        <v>9250000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9250000</v>
+        <v>9900000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>10140700</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>10290000</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>10400000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>10280000</v>
+        <v>11450000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -664,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+16.5%)</t>
+          <t>+550,000 ت از رتبه 5 ترب (+5.3%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -708,39 +704,35 @@
       <c r="E3" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>20580000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14590000</v>
+        <v>19990000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>14990000</v>
+        <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15499000</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>20580000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>20590000</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>20790000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>20590000</v>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>+5,081,000 ت از رتبه 3 ترب (+32.8%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -784,39 +776,35 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="8" t="n">
         <v>16680000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>12899000</v>
+        <v>14980000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12990000</v>
+        <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12990000</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>16680000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>17028000</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>17190000</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>12990000</v>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>17190000</v>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+3,690,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -864,23 +852,19 @@
         <v>6370000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4500000</v>
+        <v>5500000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4800000</v>
+        <v>5670103</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5690000</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>5700000</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>5790000</v>
@@ -892,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+1,370,000 ت از رتبه 3 ترب (+27.4%)</t>
+          <t>+670,000 ت از رتبه 5 ترب (+11.8%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -936,11 +920,11 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="8" t="n">
         <v>6530000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6400000</v>
+        <v>7350000</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>6450000</v>
@@ -959,16 +943,16 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>7460210</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9560380</v>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1012,39 +996,35 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="8" t="n">
         <v>4465000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3950000</v>
+        <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3995000</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4347000</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4465000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+470,000 ت از رتبه 3 ترب (+11.8%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1075,7 +1055,7 @@
           <t>2144</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1088,10 +1068,8 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F8" s="6" t="n">
+        <v>1760000</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1125,16 +1103,16 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>22880000</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1172,47 +1150,35 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="G9" s="6" t="n">
+        <v>97000</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>106300</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>116379</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>129600</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1252,39 +1218,35 @@
       <c r="E10" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="8" t="n">
         <v>9795000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8900000</v>
+        <v>9300000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9000000</v>
+        <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9795000</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>9880000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1332,17 +1294,13 @@
         <v>7750000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6799000</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1313,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>8220000</v>
+        <v>10558090</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -1364,7 +1322,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+1,850,000 ت از رتبه 1 ترب (+31.4%)</t>
+          <t>+150,000 ت از رتبه 3 ترب (+2.0%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1395,7 +1353,7 @@
           <t>2121</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1408,51 +1366,39 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F12" s="8" t="n">
+        <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7265700</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>4600000</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4999000</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>49500000</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1490,39 +1436,35 @@
       <c r="E13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>9100000</v>
+        <v>13800000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9500000</v>
+        <v>13900000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>14000000</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>15330000</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>17880000</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>-3,600,000 ت از کف ترب (-26.1%)</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1545,7 +1487,7 @@
           <t>1953</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1558,45 +1500,39 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11480000</v>
+        <v>11470000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11590000</v>
+        <v>11500000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>14179000</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>11500000</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>11600000</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>11670000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>22099150</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+8,180,000 ت از رتبه 5 ترب (+70.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0</v>
+        <v>158800000</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
@@ -1640,26 +1576,22 @@
         <v>8470000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6200000</v>
+        <v>7195000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6295000</v>
+        <v>7297000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7300000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>7860000</v>
+        <v>8860000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1668,7 +1600,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+2,170,000 ت از رتبه 3 ترب (+34.4%)</t>
+          <t>+1,070,000 ت از رتبه 5 ترب (+14.5%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1699,7 +1631,7 @@
           <t>1964</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1712,45 +1644,39 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F16" s="8" t="n">
+        <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4195000</v>
+        <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4200000</v>
+        <v>5400000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4290000</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5445000</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>5597000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>32340000</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -1790,13 +1716,11 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>12060000</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G17" s="6" t="n">
+        <v>12000000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1823,14 +1747,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>+60,000 ت از رتبه 1 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -1861,7 +1785,7 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1874,47 +1798,41 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F18" s="8" t="n">
+        <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9250000</v>
+        <v>9420000</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9500000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>12870000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0</v>
+        <v>57720000</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -1941,7 +1859,7 @@
           <t>1814</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1954,39 +1872,35 @@
       <c r="E19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="8" t="n">
         <v>9795000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>8900000</v>
+        <v>9300000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9000000</v>
+        <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9795000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>9880000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2017,7 +1931,7 @@
           <t>2559</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2030,13 +1944,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F20" s="11" t="n">
+        <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2980000</v>
+        <v>4000000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -2059,18 +1971,18 @@
       <c r="L20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>-13,000 ت از کف ترب (-0.3%)</t>
         </is>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0</v>
+        <v>23196000</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
@@ -2114,17 +2026,13 @@
         <v>7640000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6799000</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2137,7 +2045,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>8220000</v>
+        <v>10558090</v>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
@@ -2146,7 +2054,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>+1,740,000 ت از رتبه 1 ترب (+29.5%)</t>
+          <t>+40,000 ت از رتبه 3 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -2194,7 +2102,7 @@
         <v>18590000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>15300000</v>
+        <v>18000000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16890000</v>
+        <v>19885220</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2226,7 +2134,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>+3,290,000 ت از رتبه 1 ترب (+21.5%)</t>
+          <t>+590,000 ت از رتبه 1 ترب (+3.3%)</t>
         </is>
       </c>
       <c r="O22" s="6" t="n">
@@ -2270,39 +2178,35 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="8" t="n">
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7800000</v>
+        <v>7500000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8090000</v>
+        <v>9050000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>16200000</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9470000</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>30200000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>6902400</v>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>7652540</v>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>+5,550,000 ت از رتبه 3 ترب (+34.3%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2333,7 +2237,7 @@
           <t>1714</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2346,45 +2250,39 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F24" s="8" t="n">
+        <v>6670000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5616000</v>
+        <v>6200000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5650000</v>
+        <v>6449000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6550000</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>6799000</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>6950000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7686300</v>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>33350000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2309,7 @@
           <t>2071</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2433,23 +2331,19 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6980000</v>
+        <v>7500000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8290000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>8500000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>12590000</v>
+        <v>14600000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2489,7 +2383,7 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2508,23 +2402,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>6900000</v>
+        <v>8500000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7400000</v>
+        <v>8900000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7980000</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9000000</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>9400000</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>9550000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2563,7 +2453,7 @@
           <t>2420</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2582,18 +2472,16 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>8300000</v>
+        <v>12320000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>9200000</v>
+        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>16000000</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>20500000</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -2637,7 +2525,7 @@
           <t>2167</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2656,7 +2544,7 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6500000</v>
+        <v>7600000</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2734,39 +2622,35 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="8" t="n">
         <v>5250000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>5190000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4980000</v>
+        <v>5200000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5220000</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>5250000</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>5276880</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>5790000</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>6450000</v>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+250,000 ت از رتبه 3 ترب (+5.0%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2875,7 +2759,7 @@
           <t>1759</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2894,26 +2778,22 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22950000</v>
+        <v>14000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>23000000</v>
+        <v>14899000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>14900000</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>15000000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>29900000</v>
+        <v>27300000</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2953,7 +2833,7 @@
           <t>1862</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2972,23 +2852,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10799000</v>
+        <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>10800000</v>
+        <v>11500000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>11800000</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>19500000</v>
@@ -3044,45 +2920,37 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="8" t="n">
         <v>7060000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>9600000</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6000000</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>7060000</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>7300000</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-2,540,000 ت از کف ترب (-26.5%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -3113,7 +2981,7 @@
           <t>1930</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3132,27 +3000,19 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8700000</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>9889000</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>9889000</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3189,7 +3049,7 @@
       <c r="B35" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3202,7 +3062,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -3231,7 +3091,7 @@
       <c r="L35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -3257,7 +3117,7 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3274,26 +3134,22 @@
         <v>8820000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H36" s="6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="I36" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="I36" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J36" s="6" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>7489000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7150000</v>
+        <v>7400000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3302,7 +3158,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,820,000 ت از رتبه 3 ترب (+26.0%)</t>
+          <t>+1,331,000 ت از رتبه 5 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -3333,7 +3189,7 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3350,26 +3206,22 @@
         <v>8820000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6500000</v>
+        <v>6700000</v>
       </c>
       <c r="H37" s="6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="I37" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="I37" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J37" s="6" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>7489000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7150000</v>
+        <v>7400000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3378,7 +3230,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,820,000 ت از رتبه 3 ترب (+26.0%)</t>
+          <t>+1,331,000 ت از رتبه 5 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -3409,7 +3261,7 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3422,41 +3274,35 @@
       <c r="E38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="8" t="n">
         <v>17720000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11880000</v>
+        <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>11890000</v>
+        <v>17700000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13200000</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>17720000</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>17750000</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>16790000</v>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+4,520,000 ت از رتبه 3 ترب (+34.2%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3487,7 +3333,7 @@
           <t>1753</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3500,39 +3346,35 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="8" t="n">
         <v>4465000</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3900000</v>
+        <v>4000000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>3950000</v>
+        <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3995000</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4347000</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>4465000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+470,000 ت از رتبه 3 ترب (+11.8%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3563,7 +3405,7 @@
           <t>2420</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3635,7 +3477,7 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3717,7 +3559,7 @@
           <t>2139</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3736,7 +3578,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3797,7 +3639,7 @@
           <t>2133</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3822,17 +3664,13 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7500000</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8064550</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8489000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3715,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4052,7 +3890,7 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
@@ -4077,7 +3915,7 @@
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="10" t="inlineStr">
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
@@ -4124,10 +3962,8 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F47" s="5" t="n">
+        <v>6670000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -4149,20 +3985,20 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7686300</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+972,000 ت از رتبه 3 ترب (+17.1%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>13340000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4225,7 +4061,7 @@
         </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>11000000</v>
+        <v>14500000</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
@@ -4301,7 +4137,7 @@
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>4085000</v>
+        <v>4600000</v>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
@@ -4454,10 +4290,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L51" s="6" t="n">
+        <v>16750000</v>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
@@ -4532,10 +4366,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L52" s="6" t="n">
+        <v>13000000</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -4889,7 +4721,7 @@
       <c r="B57" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4961,7 +4793,7 @@
       <c r="B58" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4974,7 +4806,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="8" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -5000,12 +4832,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="L58" s="6" t="n">
+        <v>7911200</v>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -5039,7 +4869,7 @@
           <t>1775</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5077,7 +4907,7 @@
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>8075000</v>
+        <v>11000000</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -5117,7 +4947,7 @@
           <t>1902</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5156,10 +4986,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L60" s="6" t="n">
+        <v>8486000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5199,7 +5027,7 @@
           <t>3231</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5279,7 +5107,7 @@
           <t>2092</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5292,10 +5120,8 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>4720000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5317,20 +5143,20 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>5780000</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+770,000 ت از رتبه 3 ترب (+19.5%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0</v>
+        <v>9440000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5357,7 +5183,7 @@
           <t>1926</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5397,7 +5223,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>8075000</v>
+        <v>19200000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5437,7 +5263,7 @@
           <t>1819</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5473,7 +5299,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>5500000</v>
+        <v>6450000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5513,7 +5339,7 @@
           <t>2066</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5593,7 +5419,7 @@
           <t>1942</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5663,7 +5489,7 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5747,7 +5573,7 @@
           <t>3240</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5785,7 +5611,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>3866860</v>
+        <v>4326110</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5825,7 +5651,7 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5905,7 +5731,7 @@
           <t>1885</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5944,10 +5770,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L70" s="6" t="n">
+        <v>15000000</v>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
@@ -5987,7 +5811,7 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6027,7 +5851,7 @@
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>6377900</v>
+        <v>9700000</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -6067,7 +5891,7 @@
           <t>1914</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6149,7 +5973,7 @@
           <t>2127</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6185,7 +6009,7 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>5200000</v>
+        <v>4870000</v>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
@@ -6261,7 +6085,7 @@
         </is>
       </c>
       <c r="L74" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
@@ -6481,7 +6305,7 @@
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
@@ -6557,7 +6381,7 @@
         </is>
       </c>
       <c r="L78" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
@@ -6633,7 +6457,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>4630000</v>
+        <v>4900000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6709,7 +6533,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>24980000</v>
+        <v>29987800</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6785,7 +6609,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>7660000</v>
+        <v>8860000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6863,7 +6687,7 @@
         </is>
       </c>
       <c r="L82" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
@@ -6939,7 +6763,7 @@
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>14300000</v>
+        <v>39000000</v>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
@@ -7087,7 +6911,7 @@
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
@@ -7409,7 +7233,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>6950000</v>
+        <v>7400000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7485,7 +7309,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>6950000</v>
+        <v>7400000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7538,10 +7362,8 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F91" s="5" t="n">
+        <v>4720000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7563,20 +7385,20 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>5780000</v>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+770,000 ت از رتبه 3 ترب (+19.5%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>0</v>
+        <v>4720000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7461,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>3324800</v>
+        <v>4239400</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7715,7 +7537,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>7850000</v>
+        <v>8550000</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7768,7 +7590,7 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="9" t="n">
+      <c r="F94" s="8" t="n">
         <v>5800000</v>
       </c>
       <c r="G94" s="6" t="n">
@@ -7797,7 +7619,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M94" s="10" t="inlineStr">
+      <c r="M94" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -8187,7 +8009,7 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>5200000</v>
+        <v>4870000</v>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
@@ -8227,7 +8049,7 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8307,7 +8129,7 @@
           <t>3250</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8379,7 +8201,7 @@
           <t>3229</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8392,7 +8214,7 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="9" t="n">
+      <c r="F102" s="8" t="n">
         <v>27470000</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -8419,7 +8241,7 @@
       <c r="L102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="M102" s="10" t="inlineStr">
+      <c r="M102" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -8449,7 +8271,7 @@
           <t>1840</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8533,7 +8355,7 @@
           <t>2554</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8569,7 +8391,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>4630000</v>
+        <v>4900000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8609,7 +8431,7 @@
           <t>3227</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8647,7 +8469,7 @@
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>5300000</v>
+        <v>7100000</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8509,7 @@
           <t>3232</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8767,7 +8589,7 @@
           <t>3242</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8853,7 +8675,7 @@
           <t>1868</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8891,7 +8713,7 @@
         </is>
       </c>
       <c r="L108" s="6" t="n">
-        <v>16990000</v>
+        <v>14550000</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -8929,7 +8751,7 @@
       <c r="B109" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8942,7 +8764,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F109" s="8" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -8973,7 +8795,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M109" s="10" t="inlineStr">
+      <c r="M109" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -9007,7 +8829,7 @@
           <t>3228</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9091,7 +8913,7 @@
           <t>3233</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9177,7 +8999,7 @@
           <t>3251</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9263,7 +9085,7 @@
           <t>1948</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9341,7 +9163,7 @@
           <t>1783</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9379,7 +9201,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11000000</v>
+        <v>11290000</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9419,7 +9241,7 @@
           <t>2082</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9499,7 +9321,7 @@
           <t>1809</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9535,7 +9357,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>3324800</v>
+        <v>4239400</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9575,7 +9397,7 @@
           <t>3239</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9657,7 +9479,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9737,7 +9559,7 @@
           <t>2115</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9813,7 +9635,7 @@
           <t>2563</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9893,7 +9715,7 @@
           <t>2567</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9969,7 +9791,7 @@
           <t>1862</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10047,7 +9869,7 @@
           <t>1846</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10121,7 +9943,7 @@
           <t>1851</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10203,7 +10025,7 @@
           <t>3244</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10242,10 +10064,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L125" s="6" t="n">
+        <v>17000000</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -10285,7 +10105,7 @@
           <t>2566</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10363,7 +10183,7 @@
           <t>2150</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10449,7 +10269,7 @@
           <t>1879</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10525,7 +10345,7 @@
           <t>1908</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10611,7 +10431,7 @@
           <t>2558</t>
         </is>
       </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10691,7 +10511,7 @@
           <t>2052</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10771,7 +10591,7 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10851,7 +10671,7 @@
           <t>1770</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10887,7 +10707,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="n">
-        <v>6902400</v>
+        <v>7652540</v>
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>
@@ -10927,7 +10747,7 @@
           <t>3236</t>
         </is>
       </c>
-      <c r="C134" s="8" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -642,13 +642,13 @@
         <v>9900000</v>
       </c>
       <c r="I2" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>10140700</v>
       </c>
-      <c r="J2" s="6" t="n">
-        <v>10290000</v>
-      </c>
       <c r="K2" s="6" t="n">
-        <v>10400000</v>
+        <v>10200000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>11450000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+550,000 ت از رتبه 5 ترب (+5.3%)</t>
+          <t>+750,000 ت از رتبه 5 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -864,7 +864,7 @@
         <v>5700000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5700000</v>
+        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>5790000</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+670,000 ت از رتبه 5 ترب (+11.8%)</t>
+          <t>+570,000 ت از رتبه 5 ترب (+9.8%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -1504,16 +1504,16 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11470000</v>
+        <v>11500000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11500000</v>
+        <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11500000</v>
+        <v>11670000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11600000</v>
+        <v>11670000</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>11670000</v>
@@ -1657,10 +1657,10 @@
         <v>5445000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5500000</v>
+        <v>5597000</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5597000</v>
+        <v>5605000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>4900000</v>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4150000</v>
+        <v>3150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3664,13 +3664,17 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8064550</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>8489000</v>
+        <v>7289000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -639,19 +639,19 @@
         <v>9250000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9900000</v>
+        <v>9964340</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10140700</v>
+        <v>10200000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10200000</v>
+        <v>10290000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>11450000</v>
+        <v>12000000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+750,000 ت از رتبه 5 ترب (+7.4%)</t>
+          <t>+660,000 ت از رتبه 5 ترب (+6.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20580000</v>
+        <v>20585000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>19990000</v>
@@ -714,7 +714,7 @@
         <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20580000</v>
+        <v>20585000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20590000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1296540000</v>
+        <v>1296855000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16680000</v>
+        <v>16850000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14980000</v>
@@ -786,13 +786,13 @@
         <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16680000</v>
+        <v>16850000</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>17028000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>17190000</v>
+        <v>17100000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>500400000</v>
+        <v>505500000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,25 +849,25 @@
         <v>18</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6370000</v>
+        <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>5670103</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>5690000</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>5700000</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>5800000</v>
-      </c>
       <c r="L5" s="6" t="n">
-        <v>5790000</v>
+        <v>6850000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 5 ترب (+9.8%)</t>
+          <t>+450,000 ت از رتبه 5 ترب (+7.9%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114660000</v>
+        <v>110700000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9560380</v>
+        <v>9559730</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>4465000</v>
+        <v>4520000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4000000</v>
@@ -1006,29 +1006,29 @@
         <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4347000</v>
+        <v>4500000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4350000</v>
+        <v>4520000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4465000</v>
+        <v>4550000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>66975000</v>
+        <v>67800000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>106300</v>
+        <v>108300</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>116379</v>
@@ -1219,16 +1219,16 @@
         <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9795000</v>
+        <v>9797000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9300000</v>
+        <v>9400000</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9795000</v>
+        <v>9797000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9800000</v>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>107745000</v>
+        <v>107767000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7750000</v>
+        <v>7720000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>10558090</v>
+        <v>13513760</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه 3 ترب (+2.0%)</t>
+          <t>+120,000 ت از رتبه 3 ترب (+1.6%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>85250000</v>
+        <v>84920000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         <v>4999000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5250000</v>
+        <v>5400000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5400000</v>
+        <v>5700000</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>5700000</v>
@@ -1519,7 +1519,7 @@
         <v>11670000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22099150</v>
+        <v>20850000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1573,25 +1573,25 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8470000</v>
+        <v>7880000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7195000</v>
+        <v>7270000</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>7294000</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>7297000</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>7300000</v>
-      </c>
       <c r="J15" s="6" t="n">
-        <v>7300000</v>
+        <v>7400000</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8860000</v>
+        <v>8806600</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1600,11 +1600,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+1,070,000 ت از رتبه 5 ترب (+14.5%)</t>
+          <t>+480,000 ت از رتبه 5 ترب (+6.5%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>59290000</v>
+        <v>55160000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>10000000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>12870000</v>
+        <v>12950000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1873,16 +1873,16 @@
         <v>6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9795000</v>
+        <v>9797000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9300000</v>
+        <v>9400000</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9795000</v>
+        <v>9797000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9800000</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>58770000</v>
+        <v>58782000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>10558090</v>
+        <v>13513760</v>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>19885220</v>
+        <v>18300000</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2182,16 +2182,16 @@
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7500000</v>
+        <v>9050000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9050000</v>
+        <v>9470000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9470000</v>
+        <v>13300000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>13300000</v>
+        <v>30200000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>30200000</v>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2250,8 +2250,8 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6670000</v>
+      <c r="F24" s="5" t="n">
+        <v>7290000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>6200000</v>
@@ -2263,26 +2263,26 @@
         <v>6550000</v>
       </c>
       <c r="J24" s="6" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="K24" s="6" t="n">
         <v>6799000</v>
       </c>
-      <c r="K24" s="6" t="n">
-        <v>6950000</v>
-      </c>
       <c r="L24" s="6" t="n">
-        <v>7686300</v>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>6390000</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+491,000 ت از رتبه 5 ترب (+7.2%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>33350000</v>
+        <v>36450000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2402,19 +2402,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
+        <v>8415000</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>8500000</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="6" t="n">
         <v>8900000</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>9000000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>9400000</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>9550000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2623,7 +2623,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>5250000</v>
+        <v>5260000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5190000</v>
@@ -2635,10 +2635,10 @@
         <v>5220000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5250000</v>
+        <v>5260000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5276880</v>
+        <v>5282000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6450000</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21000000</v>
+        <v>21040000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>14900000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>15000000</v>
+        <v>14900000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2858,13 +2858,13 @@
         <v>11500000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11800000</v>
+        <v>12500000</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>12500000</v>
+        <v>12650000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12500000</v>
+        <v>12700000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>19500000</v>
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
@@ -2933,7 +2933,7 @@
         <v>6999000</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>7300000</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="O33" s="6" t="n">
-        <v>21180000</v>
+        <v>21420000</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
@@ -3134,19 +3134,19 @@
         <v>8820000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6700000</v>
+        <v>6950000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>6900000</v>
+        <v>7000000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7300000</v>
+        <v>7500000</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>7400000</v>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,331,000 ت از رتبه 5 ترب (+17.8%)</t>
+          <t>+1,320,000 ت از رتبه 5 ترب (+17.6%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -3206,19 +3206,19 @@
         <v>8820000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6700000</v>
+        <v>6950000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>6900000</v>
+        <v>7000000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7300000</v>
+        <v>7500000</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>7400000</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,331,000 ت از رتبه 5 ترب (+17.8%)</t>
+          <t>+1,320,000 ت از رتبه 5 ترب (+17.6%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -3347,7 +3347,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>4465000</v>
+        <v>4520000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>4000000</v>
@@ -3356,29 +3356,29 @@
         <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4347000</v>
+        <v>4500000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4350000</v>
+        <v>4520000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4465000</v>
+        <v>4550000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>13395000</v>
+        <v>13560000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3664,17 +3664,13 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7500000</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8064550</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8489000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3819,7 +3815,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>7611000</v>
+        <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -3852,11 +3848,11 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+4,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
-        <v>15222000</v>
+        <v>15230000</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -3967,7 +3963,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>6670000</v>
+        <v>7290000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3989,7 +3985,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>7686300</v>
+        <v>6390000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3998,11 +3994,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+972,000 ت از رتبه 3 ترب (+17.1%)</t>
+          <t>+1,592,000 ت از رتبه 3 ترب (+27.9%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13340000</v>
+        <v>14580000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4043,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>9940000</v>
+        <v>11650000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4074,11 +4070,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+840,000 ت از رتبه 3 ترب (+9.2%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+28.0%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>19880000</v>
+        <v>23300000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4119,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3840000</v>
+        <v>3940000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -4150,11 +4146,11 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+690,000 ت از رتبه 3 ترب (+21.9%)</t>
+          <t>+790,000 ت از رتبه 3 ترب (+25.1%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
-        <v>7680000</v>
+        <v>7880000</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -4294,8 +4290,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L51" s="6" t="n">
-        <v>16750000</v>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
@@ -4349,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>12350000</v>
+        <v>12270000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4380,11 +4378,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
+          <t>+770,000 ت از رتبه 3 ترب (+6.7%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>24700000</v>
+        <v>24540000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4663,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10290000</v>
+        <v>10340000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4696,11 +4694,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,340,000 ت از رتبه 3 ترب (+72.9%)</t>
+          <t>+4,390,000 ت از رتبه 3 ترب (+73.8%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>20580000</v>
+        <v>20680000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -5125,7 +5123,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>4720000</v>
+        <v>4840000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5147,7 +5145,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5780000</v>
+        <v>5690000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5156,11 +5154,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+770,000 ت از رتبه 3 ترب (+19.5%)</t>
+          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>9440000</v>
+        <v>9680000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5281,7 +5279,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5250000</v>
+        <v>5260000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5312,11 +5310,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 3 ترب (+6.1%)</t>
+          <t>+310,000 ت از رتبه 3 ترب (+6.3%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>10500000</v>
+        <v>10520000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5512,7 +5510,7 @@
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>3980000</v>
+        <v>6408230</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -5615,7 +5613,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4326110</v>
+        <v>4260710</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5991,7 +5989,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4460000</v>
+        <v>4470000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6013,7 +6011,7 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>4870000</v>
+        <v>4703670</v>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
@@ -6022,11 +6020,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+580,000 ت از رتبه 3 ترب (+14.9%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>8920000</v>
+        <v>8940000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6067,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -6098,11 +6096,11 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>+2,810,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
@@ -6143,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>22000000</v>
+        <v>21740000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6174,11 +6172,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,555,000 ت از رتبه 3 ترب (+799.8%)</t>
+          <t>+19,295,000 ت از رتبه 3 ترب (+789.2%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>22000000</v>
+        <v>21740000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6287,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>9990000</v>
+        <v>10495000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6318,11 +6316,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+790,000 ت از رتبه 3 ترب (+8.6%)</t>
+          <t>+1,295,000 ت از رتبه 3 ترب (+14.1%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>9990000</v>
+        <v>10495000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6439,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4950000</v>
+        <v>4490000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6470,11 +6468,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+1,095,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>+635,000 ت از رتبه 3 ترب (+16.5%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4950000</v>
+        <v>4490000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6515,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15495000</v>
+        <v>15497000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6546,11 +6544,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+505,000 ت از رتبه 3 ترب (+3.4%)</t>
+          <t>+507,000 ت از رتبه 3 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15495000</v>
+        <v>15497000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6745,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>15780000</v>
+        <v>17840000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6776,11 +6774,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+3,980,000 ت از رتبه 3 ترب (+33.7%)</t>
+          <t>+6,040,000 ت از رتبه 3 ترب (+51.2%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>15780000</v>
+        <v>17840000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6821,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2660000</v>
+        <v>2655000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6852,11 +6850,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+215,000 ت از رتبه 3 ترب (+8.8%)</t>
+          <t>+210,000 ت از رتبه 3 ترب (+8.6%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2660000</v>
+        <v>2655000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -7367,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>4720000</v>
+        <v>4840000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7389,7 +7387,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5780000</v>
+        <v>5690000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7398,11 +7396,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+770,000 ت از رتبه 3 ترب (+19.5%)</t>
+          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>4720000</v>
+        <v>4840000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7443,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3508000</v>
+        <v>3515000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7465,7 +7463,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4239400</v>
+        <v>4283400</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7474,11 +7472,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+520,000 ت از رتبه 3 ترب (+17.4%)</t>
+          <t>+527,000 ت از رتبه 3 ترب (+17.6%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3508000</v>
+        <v>3515000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7519,7 +7517,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7979500</v>
+        <v>7920000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7550,11 +7548,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+1,059,500 ت از رتبه 3 ترب (+15.3%)</t>
+          <t>+1,000,000 ت از رتبه 3 ترب (+14.5%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7979500</v>
+        <v>7920000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7991,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4460000</v>
+        <v>4470000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8013,7 +8011,7 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>4870000</v>
+        <v>4703670</v>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
@@ -8022,11 +8020,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+580,000 ت از رتبه 3 ترب (+14.9%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4460000</v>
+        <v>4470000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8373,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4950000</v>
+        <v>4490000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8404,11 +8402,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+1,095,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>+635,000 ت از رتبه 3 ترب (+16.5%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4950000</v>
+        <v>4490000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -8473,7 +8471,7 @@
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>7100000</v>
+        <v>8100000</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -9205,7 +9203,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11290000</v>
+        <v>11590000</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9339,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3508000</v>
+        <v>3515000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9361,7 +9359,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4239400</v>
+        <v>4283400</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9370,11 +9368,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+520,000 ت از رتبه 3 ترب (+17.4%)</t>
+          <t>+527,000 ت از رتبه 3 ترب (+17.6%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3508000</v>
+        <v>3515000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9961,7 +9959,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -9998,11 +9996,11 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-2,540,000 ت از کف ترب (-26.5%)</t>
+          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
         </is>
       </c>
       <c r="O124" s="6" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -633,16 +633,16 @@
         <v>189</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10950000</v>
+        <v>11390000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9250000</v>
+        <v>9964340</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9964340</v>
+        <v>10000000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10000000</v>
+        <v>10200000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>10200000</v>
@@ -660,11 +660,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+660,000 ت از رتبه 5 ترب (+6.4%)</t>
+          <t>+1,100,000 ت از رتبه 5 ترب (+10.7%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2069550000</v>
+        <v>2152710000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20585000</v>
+        <v>20430000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>19990000</v>
@@ -714,29 +714,29 @@
         <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20585000</v>
+        <v>20290000</v>
       </c>
       <c r="J3" s="6" t="n">
+        <v>20430000</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>20590000</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>20790000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>20590000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1296855000</v>
+        <v>1287090000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16850000</v>
+        <v>16750000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14980000</v>
@@ -786,29 +786,29 @@
         <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16850000</v>
+        <v>16650000</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>16750000</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>17028000</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>17100000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>505500000</v>
+        <v>502500000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -855,19 +855,19 @@
         <v>5400000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5500000</v>
+        <v>5670103</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5670103</v>
+        <v>5690000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5690000</v>
+        <v>5800000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5700000</v>
+        <v>5850000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>6850000</v>
+        <v>6800000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+450,000 ت از رتبه 5 ترب (+7.9%)</t>
+          <t>+300,000 ت از رتبه 5 ترب (+5.1%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -996,8 +996,8 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>4520000</v>
+      <c r="F7" s="5" t="n">
+        <v>4640000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4000000</v>
@@ -1006,29 +1006,29 @@
         <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4500000</v>
+        <v>4460000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4520000</v>
+        <v>4550000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4550000</v>
+        <v>4595000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>67800000</v>
+        <v>69600000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9797000</v>
+        <v>9798000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9400000</v>
@@ -1228,7 +1228,7 @@
         <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9797000</v>
+        <v>9798000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9800000</v>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>107767000</v>
+        <v>107778000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>11</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7720000</v>
+        <v>7760000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه 3 ترب (+1.6%)</t>
+          <t>+160,000 ت از رتبه 3 ترب (+2.1%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>84920000</v>
+        <v>85360000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4999000</v>
+        <v>5300000</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5400000</v>
@@ -1443,10 +1443,10 @@
         <v>13800000</v>
       </c>
       <c r="H13" s="6" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="I13" s="6" t="n">
         <v>13900000</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>14000000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>15330000</v>
@@ -1519,7 +1519,7 @@
         <v>11670000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>20850000</v>
+        <v>21500000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7880000</v>
+        <v>7930000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>7270000</v>
@@ -1591,7 +1591,7 @@
         <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8806600</v>
+        <v>8860000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1600,11 +1600,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+480,000 ت از رتبه 5 ترب (+6.5%)</t>
+          <t>+530,000 ت از رتبه 5 ترب (+7.2%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>55160000</v>
+        <v>55510000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1654,13 +1654,13 @@
         <v>5400000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5445000</v>
+        <v>5597000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5597000</v>
+        <v>5605000</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5605000</v>
+        <v>5680000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>4900000</v>
@@ -1873,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9797000</v>
+        <v>9798000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9400000</v>
@@ -1882,7 +1882,7 @@
         <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9797000</v>
+        <v>9798000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9800000</v>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>58782000</v>
+        <v>58788000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>18300000</v>
+        <v>17405210</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2182,31 +2182,31 @@
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>9050000</v>
+        <v>9470000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>9470000</v>
+        <v>13300000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>13300000</v>
+        <v>30200000</v>
       </c>
       <c r="J23" s="6" t="n">
         <v>30200000</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>30200000</v>
+        <v>40200000</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>7652540</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2251,25 +2251,25 @@
         <v>5</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>7290000</v>
+        <v>7470000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6200000</v>
+        <v>6449000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6449000</v>
+        <v>6550000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6550000</v>
+        <v>6597000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6597000</v>
+        <v>6950000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>6799000</v>
+        <v>6990000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>6390000</v>
+        <v>7747400</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -2278,11 +2278,11 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+491,000 ت از رتبه 5 ترب (+7.2%)</t>
+          <t>+480,000 ت از رتبه 5 ترب (+6.9%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>36450000</v>
+        <v>37350000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2331,19 +2331,19 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>7500000</v>
+        <v>8290000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8290000</v>
+        <v>8400000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8400000</v>
+        <v>8500000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8500000</v>
+        <v>8800000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14600000</v>
+        <v>14700000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2405,16 +2405,16 @@
         <v>8415000</v>
       </c>
       <c r="H26" s="6" t="n">
+        <v>8499000</v>
+      </c>
+      <c r="I26" s="6" t="n">
         <v>8500000</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>8900000</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="6" t="n">
         <v>9000000</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>9400000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2622,8 +2622,8 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5260000</v>
+      <c r="F29" s="5" t="n">
+        <v>5380000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5190000</v>
@@ -2635,26 +2635,26 @@
         <v>5220000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5260000</v>
+        <v>5282000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5282000</v>
+        <v>5300000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6450000</v>
       </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+80,000 ت از رتبه 5 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21040000</v>
+        <v>21520000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>11500000</v>
+        <v>12500000</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>12500000</v>
@@ -2864,7 +2864,7 @@
         <v>12650000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12700000</v>
+        <v>12650000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>19500000</v>
@@ -3131,16 +3131,16 @@
         <v>3</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7000000</v>
+        <v>7300000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7300000</v>
+        <v>7489000</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>7500000</v>
@@ -3158,11 +3158,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,320,000 ت از رتبه 5 ترب (+17.6%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>26460000</v>
+        <v>30300000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3203,16 +3203,16 @@
         <v>3</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7000000</v>
+        <v>7300000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7300000</v>
+        <v>7489000</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>7500000</v>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,320,000 ت از رتبه 5 ترب (+17.6%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>26460000</v>
+        <v>30300000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17720000</v>
+        <v>17730000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>14500000</v>
@@ -3284,7 +3284,7 @@
         <v>17700000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17720000</v>
+        <v>17730000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>17750000</v>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>53160000</v>
+        <v>53190000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3346,8 +3346,8 @@
       <c r="E39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>4520000</v>
+      <c r="F39" s="5" t="n">
+        <v>4640000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>4000000</v>
@@ -3356,29 +3356,29 @@
         <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4500000</v>
+        <v>4460000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4520000</v>
+        <v>4550000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4550000</v>
+        <v>4595000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>13560000</v>
+        <v>13920000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3814,22 +3814,20 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7600000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7615000</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>7893100</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -3841,14 +3839,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3890,39 +3888,35 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>2839550</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>4160000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4300000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>4500000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+300,000 ت از رتبه 5 ترب (+6.7%)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3963,7 +3957,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7290000</v>
+        <v>7470000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3985,7 +3979,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>6390000</v>
+        <v>7747400</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3994,11 +3988,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,592,000 ت از رتبه 3 ترب (+27.9%)</t>
+          <t>+1,772,000 ت از رتبه 3 ترب (+31.1%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14580000</v>
+        <v>14940000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4039,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>11650000</v>
+        <v>12700000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4070,11 +4064,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+2,550,000 ت از رتبه 3 ترب (+28.0%)</t>
+          <t>+3,600,000 ت از رتبه 3 ترب (+39.6%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>23300000</v>
+        <v>25400000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4115,7 +4109,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3940000</v>
+        <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -4146,11 +4140,11 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+790,000 ت از رتبه 3 ترب (+25.1%)</t>
+          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
-        <v>7880000</v>
+        <v>8790000</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -4269,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17720000</v>
+        <v>17730000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4302,11 +4296,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+4,820,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>+4,830,000 ت از رتبه 3 ترب (+37.4%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>35440000</v>
+        <v>35460000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4347,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>12270000</v>
+        <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4378,11 +4372,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+770,000 ت از رتبه 3 ترب (+6.7%)</t>
+          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>24540000</v>
+        <v>24700000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>10500000</v>
+        <v>11250000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4454,11 +4448,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+3,011,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>21000000</v>
+        <v>22500000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4661,7 +4655,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10340000</v>
+        <v>10390000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4694,11 +4688,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,390,000 ت از رتبه 3 ترب (+73.8%)</t>
+          <t>+4,440,000 ت از رتبه 3 ترب (+74.6%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>20680000</v>
+        <v>20780000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4989,7 +4983,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>8486000</v>
+        <v>8299990</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5145,7 +5139,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5690000</v>
+        <v>4758000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5279,7 +5273,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5260000</v>
+        <v>5380000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5310,11 +5304,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+310,000 ت از رتبه 3 ترب (+6.3%)</t>
+          <t>+430,000 ت از رتبه 3 ترب (+8.7%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>10520000</v>
+        <v>10760000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5510,7 +5504,7 @@
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>6408230</v>
+        <v>3980000</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -5773,7 +5767,7 @@
         </is>
       </c>
       <c r="L70" s="6" t="n">
-        <v>15000000</v>
+        <v>16000000</v>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
@@ -5989,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4470000</v>
+        <v>4475000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6020,11 +6014,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+580,000 ت از رتبه 3 ترب (+14.9%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>8940000</v>
+        <v>8950000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6213,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6244,11 +6238,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+11,870,000 ت از رتبه 3 ترب (+76.1%)</t>
+          <t>+11,770,000 ت از رتبه 3 ترب (+75.4%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6285,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>10495000</v>
+        <v>10740000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6316,11 +6310,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,295,000 ت از رتبه 3 ترب (+14.1%)</t>
+          <t>+1,540,000 ت از رتبه 3 ترب (+16.7%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>10495000</v>
+        <v>10740000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6437,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4490000</v>
+        <v>4540000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6459,7 +6453,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>4900000</v>
+        <v>4894000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6468,11 +6462,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+635,000 ت از رتبه 3 ترب (+16.5%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4490000</v>
+        <v>4540000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6513,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15497000</v>
+        <v>15498000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6535,7 +6529,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>29987800</v>
+        <v>30126400</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6544,11 +6538,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+507,000 ت از رتبه 3 ترب (+3.4%)</t>
+          <t>+508,000 ت از رتبه 3 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15497000</v>
+        <v>15498000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6589,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>6495000</v>
+        <v>6500000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -6620,11 +6614,11 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+4.8%)</t>
+          <t>+300,000 ت از رتبه 3 ترب (+4.8%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>6495000</v>
+        <v>6500000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -6743,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>17840000</v>
+        <v>22200000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6765,7 +6759,7 @@
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>39000000</v>
+        <v>38000000</v>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
@@ -6774,11 +6768,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+6,040,000 ت از رتبه 3 ترب (+51.2%)</t>
+          <t>+10,400,000 ت از رتبه 3 ترب (+88.1%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>17840000</v>
+        <v>22200000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6819,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2655000</v>
+        <v>2652000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6850,11 +6844,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+210,000 ت از رتبه 3 ترب (+8.6%)</t>
+          <t>+207,000 ت از رتبه 3 ترب (+8.5%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2655000</v>
+        <v>2652000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -7213,7 +7207,7 @@
         <v>1</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7244,11 +7238,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+1,870,000 ت از رتبه 3 ترب (+26.9%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7289,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7320,11 +7314,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+1,870,000 ت از رتبه 3 ترب (+26.9%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7387,7 +7381,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5690000</v>
+        <v>4758000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7441,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3515000</v>
+        <v>3501000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7463,7 +7457,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4283400</v>
+        <v>3597000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7472,11 +7466,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+527,000 ت از رتبه 3 ترب (+17.6%)</t>
+          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3515000</v>
+        <v>3501000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7517,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7920000</v>
+        <v>7900000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7548,11 +7542,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+1,000,000 ت از رتبه 3 ترب (+14.5%)</t>
+          <t>+980,000 ت از رتبه 3 ترب (+14.2%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7920000</v>
+        <v>7900000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7593,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -7632,7 +7626,7 @@
         </is>
       </c>
       <c r="O94" s="6" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
@@ -7749,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5010000</v>
+        <v>5040000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7786,11 +7780,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+510,000 ت از رتبه 1 ترب (+11.3%)</t>
+          <t>+540,000 ت از رتبه 1 ترب (+12.0%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5010000</v>
+        <v>5040000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7989,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4470000</v>
+        <v>4475000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8020,11 +8014,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+580,000 ت از رتبه 3 ترب (+14.9%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4470000</v>
+        <v>4475000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8211,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8254,7 +8248,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -8371,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4490000</v>
+        <v>4540000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8393,7 +8387,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>4900000</v>
+        <v>4894000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8402,11 +8396,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+635,000 ت از رتبه 3 ترب (+16.5%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4490000</v>
+        <v>4540000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9337,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3515000</v>
+        <v>3501000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9359,7 +9353,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4283400</v>
+        <v>4400000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9368,11 +9362,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+527,000 ت از رتبه 3 ترب (+17.6%)</t>
+          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3515000</v>
+        <v>3501000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9575,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>10500000</v>
+        <v>11250000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9606,11 +9600,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+3,011,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>10500000</v>
+        <v>11250000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10950000</v>
+        <v>11390000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9200000</v>
@@ -664,11 +664,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+16.5%)</t>
+          <t>+1,990,000 ت از رتبه 3 ترب (+21.2%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2069550000</v>
+        <v>2141320000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>20580000</v>
+        <v>20430000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>14590000</v>
@@ -740,15 +740,15 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>+5,081,000 ت از رتبه 3 ترب (+32.8%)</t>
+          <t>+4,931,000 ت از رتبه 3 ترب (+31.8%)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1296540000</v>
+        <v>1287090000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1834</t>
+          <t>https://royaldigi.ir/product/netbox-mobo-edition/</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>16680000</v>
+        <v>16750000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>12899000</v>
@@ -816,15 +816,15 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+3,690,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>+3,760,000 ت از رتبه 3 ترب (+28.9%)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>500400000</v>
+        <v>502500000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1828</t>
+          <t>https://royaldigi.ir/product/netbox-shine-s/</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6370000</v>
+        <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4500000</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+1,370,000 ت از رتبه 3 ترب (+27.4%)</t>
+          <t>+1,150,000 ت از رتبه 3 ترب (+23.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114660000</v>
+        <v>104550000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4465000</v>
+        <v>4640000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3900000</v>
@@ -1044,11 +1044,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+470,000 ت از رتبه 3 ترب (+11.8%)</t>
+          <t>+645,000 ت از رتبه 3 ترب (+16.1%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>66975000</v>
+        <v>69600000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>9795000</v>
+        <v>9798000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>8900000</v>
@@ -1284,11 +1284,11 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>+298,000 ت از رتبه 3 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>107745000</v>
+        <v>97980000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7750000</v>
+        <v>7760000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>5900000</v>
@@ -1364,11 +1364,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+1,850,000 ت از رتبه 1 ترب (+31.4%)</t>
+          <t>+1,860,000 ت از رتبه 1 ترب (+31.5%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>85250000</v>
+        <v>15520000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8470000</v>
+        <v>7930000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6200000</v>
@@ -1668,11 +1668,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+2,170,000 ت از رتبه 3 ترب (+34.4%)</t>
+          <t>+1,630,000 ت از رتبه 3 ترب (+25.9%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>59290000</v>
+        <v>39650000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1964</t>
+          <t>https://royaldigi.ir/product/alcatel-bt71/</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1840</t>
+          <t>https://royaldigi.ir/product/netbox-prime/</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>9795000</v>
+        <v>9798000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>8900000</v>
@@ -1986,15 +1986,15 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>+298,000 ت از رتبه 3 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>58770000</v>
+        <v>97980000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1814</t>
+          <t>https://royaldigi.ir/product/irancell-tf-i60-s1/</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2559</t>
+          <t>https://royaldigi.ir/product/irancell-fd-m40-g1/</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1714</t>
+          <t>https://royaldigi.ir/product/tp-link-archer-c50/</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>5250000</v>
+        <v>5380000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>4950000</v>
@@ -2766,11 +2766,11 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+250,000 ت از رتبه 3 ترب (+5.0%)</t>
+          <t>+380,000 ت از رتبه 3 ترب (+7.6%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21000000</v>
+        <v>21520000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3238</t>
+          <t>https://royaldigi.ir/product/cp108-n3004g-lte-cpe/</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -3045,7 +3045,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>9600000</v>
@@ -3082,11 +3082,11 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-2,540,000 ت از کف ترب (-26.5%)</t>
+          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
-        <v>21180000</v>
+        <v>21420000</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1930</t>
+          <t>https://royaldigi.ir/product/d-link-dwr-981/</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6500000</v>
@@ -3302,15 +3302,15 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,820,000 ت از رتبه 3 ترب (+26.0%)</t>
+          <t>+3,100,000 ت از رتبه 3 ترب (+44.3%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>26460000</v>
+        <v>20200000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1958</t>
+          <t>https://royaldigi.ir/product/utel-l443/</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6500000</v>
@@ -3378,15 +3378,15 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,820,000 ت از رتبه 3 ترب (+26.0%)</t>
+          <t>+3,100,000 ت از رتبه 3 ترب (+44.3%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>26460000</v>
+        <v>20200000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1958</t>
+          <t>https://royaldigi.ir/product/utel-l443/</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>17720000</v>
+        <v>17730000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>11880000</v>
@@ -3456,15 +3456,15 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+4,520,000 ت از رتبه 3 ترب (+34.2%)</t>
+          <t>+4,530,000 ت از رتبه 3 ترب (+34.3%)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>53160000</v>
+        <v>35460000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2013</t>
+          <t>https://royaldigi.ir/product/irancell-tf-i60-g1/</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4465000</v>
+        <v>4640000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>3900000</v>
@@ -3532,15 +3532,15 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+470,000 ت از رتبه 3 ترب (+11.8%)</t>
+          <t>+645,000 ت از رتبه 3 ترب (+16.1%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>13395000</v>
+        <v>69600000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1753</t>
+          <t>https://royaldigi.ir/product/d-link-dsl-124/</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -3623,7 +3623,11 @@
           <t>https://royaldigi.ir/product/huawei-e5785-330-mobile-wifi-elite-2/</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/8d1a9fa5-d864-4570-878e-374382235a85/%D9%85%D9%88%D8%AF%D9%85-%D9%87%D9%88%D8%A7%D9%88%DB%8C-%D9%85%D8%AF%D9%84-e5785-330/</t>
+        </is>
+      </c>
       <c r="R40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -3977,7 +3981,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>7611000</v>
+        <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
@@ -4010,11 +4014,11 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+4,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
-        <v>15222000</v>
+        <v>15230000</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -4203,7 +4207,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>9940000</v>
+        <v>12700000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4234,11 +4238,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+840,000 ت از رتبه 3 ترب (+9.2%)</t>
+          <t>+3,600,000 ت از رتبه 3 ترب (+39.6%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>19880000</v>
+        <v>25400000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4276,10 +4280,10 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3840000</v>
+        <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -4310,11 +4314,11 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+690,000 ت از رتبه 3 ترب (+21.9%)</t>
+          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
-        <v>7680000</v>
+        <v>4395000</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -4433,7 +4437,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17720000</v>
+        <v>17730000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4466,11 +4470,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+4,820,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>+4,830,000 ت از رتبه 3 ترب (+37.4%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>35440000</v>
+        <v>35460000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4589,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>10500000</v>
+        <v>11250000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4620,11 +4624,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+3,011,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>21000000</v>
+        <v>22500000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4748,7 +4752,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>11000000</v>
@@ -4786,7 +4790,7 @@
         </is>
       </c>
       <c r="O55" s="6" t="n">
-        <v>22000000</v>
+        <v>33000000</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
@@ -4827,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10290000</v>
+        <v>10390000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4860,11 +4864,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,340,000 ت از رتبه 3 ترب (+72.9%)</t>
+          <t>+4,440,000 ت از رتبه 3 ترب (+74.6%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>20580000</v>
+        <v>20780000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -5256,7 +5260,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3231</t>
+          <t>https://royaldigi.ir/product/d-link-dwr-m961v/</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -5334,7 +5338,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2092</t>
+          <t>https://royaldigi.ir/product/tp-link-td-w8961n/</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -5448,10 +5452,10 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5250000</v>
+        <v>5380000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5482,15 +5486,15 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 3 ترب (+6.1%)</t>
+          <t>+430,000 ت از رتبه 3 ترب (+8.7%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>10500000</v>
+        <v>21520000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1819</t>
+          <t>https://royaldigi.ir/product/irancell-fd-i40-b2/</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -5802,7 +5806,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3240</t>
+          <t>https://royaldigi.ir/product/huawei-echolife-hg8546m/</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -5916,7 +5920,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>9550000</v>
@@ -5960,11 +5964,11 @@
         </is>
       </c>
       <c r="O70" s="6" t="n">
-        <v>19100000</v>
+        <v>9550000</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1885</t>
+          <t>https://royaldigi.ir/product/huawei-e5577c/</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -6126,7 +6130,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1914</t>
+          <t>https://royaldigi.ir/product/huawei-e5783-330/</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -6160,10 +6164,10 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6194,15 +6198,15 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>8920000</v>
+        <v>4475000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2127</t>
+          <t>https://royaldigi.ir/product/vodafone-r228t/</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -6239,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -6270,15 +6274,15 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>+2,810,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2553</t>
+          <t>https://royaldigi.ir/product/tp-link-tl-wa901n/</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -6315,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>22000000</v>
+        <v>21740000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6346,15 +6350,15 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,555,000 ت از رتبه 3 ترب (+799.8%)</t>
+          <t>+19,295,000 ت از رتبه 3 ترب (+789.2%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>22000000</v>
+        <v>21740000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2552</t>
+          <t>https://royaldigi.ir/product/tp-link-eap225-v3/</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -6387,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6418,15 +6422,15 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+11,870,000 ت از رتبه 3 ترب (+76.1%)</t>
+          <t>+11,770,000 ت از رتبه 3 ترب (+75.4%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3229</t>
+          <t>https://royaldigi.ir/product/tp-link-omada-eap245-v3/</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -6459,7 +6463,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>9990000</v>
+        <v>10740000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6490,15 +6494,15 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+790,000 ت از رتبه 3 ترب (+8.6%)</t>
+          <t>+1,540,000 ت از رتبه 3 ترب (+16.7%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>9990000</v>
+        <v>10740000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2551</t>
+          <t>https://royaldigi.ir/product/tp-link-eap110-outdoor/</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -6611,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4950000</v>
+        <v>4540000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6642,15 +6646,15 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+1,095,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4950000</v>
+        <v>4540000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2554</t>
+          <t>https://royaldigi.ir/product/tp-link-tl-wr840n/</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -6687,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15495000</v>
+        <v>15498000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6718,11 +6722,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+505,000 ت از رتبه 3 ترب (+3.4%)</t>
+          <t>+508,000 ت از رتبه 3 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15495000</v>
+        <v>15498000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6763,7 +6767,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>6495000</v>
+        <v>6500000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -6794,15 +6798,15 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+4.8%)</t>
+          <t>+300,000 ت از رتبه 3 ترب (+4.8%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>6495000</v>
+        <v>6500000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2555</t>
+          <t>https://royaldigi.ir/product/tp-link-archer-c6/</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -6917,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>15780000</v>
+        <v>22200000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6948,15 +6952,15 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+3,980,000 ت از رتبه 3 ترب (+33.7%)</t>
+          <t>+10,400,000 ت از رتبه 3 ترب (+88.1%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>15780000</v>
+        <v>22200000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3245</t>
+          <t>https://royaldigi.ir/product/dlink-dir-x3000z-vodafone/</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -6993,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2660000</v>
+        <v>2652000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -7024,15 +7028,15 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+215,000 ت از رتبه 3 ترب (+8.8%)</t>
+          <t>+207,000 ت از رتبه 3 ترب (+8.5%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2660000</v>
+        <v>2652000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2556</t>
+          <t>https://royaldigi.ir/product/d-link-dgs-1005a/</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -7104,7 +7108,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2568</t>
+          <t>https://royaldigi.ir/product/tp-link-re200/</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -7190,7 +7194,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3243</t>
+          <t>https://royaldigi.ir/product/bvot-u20/</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -7272,7 +7276,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2565</t>
+          <t>https://royaldigi.ir/product/huawei-carfi-e8377/</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -7384,10 +7388,10 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7418,11 +7422,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+1,870,000 ت از رتبه 3 ترب (+26.9%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>8820000</v>
+        <v>20200000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7460,10 +7464,10 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>8820000</v>
+        <v>10100000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7494,11 +7498,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+1,870,000 ت از رتبه 3 ترب (+26.9%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>8820000</v>
+        <v>20200000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7617,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3508000</v>
+        <v>3501000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7648,11 +7652,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+520,000 ت از رتبه 3 ترب (+17.4%)</t>
+          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3508000</v>
+        <v>3501000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7979500</v>
+        <v>7900000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7724,15 +7728,15 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+1,059,500 ت از رتبه 3 ترب (+15.3%)</t>
+          <t>+980,000 ت از رتبه 3 ترب (+14.2%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7979500</v>
+        <v>7900000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2162</t>
+          <t>https://royaldigi.ir/product/utel-g442/</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -7769,7 +7773,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -7808,7 +7812,7 @@
         </is>
       </c>
       <c r="O94" s="6" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
@@ -7925,7 +7929,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5010000</v>
+        <v>5040000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7962,11 +7966,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+510,000 ت از رتبه 1 ترب (+11.3%)</t>
+          <t>+540,000 ت از رتبه 1 ترب (+12.0%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5010000</v>
+        <v>5040000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8052,7 +8056,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1885</t>
+          <t>https://royaldigi.ir/product/huawei-e5577c/</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -8086,7 +8090,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5" t="n">
         <v>11000000</v>
@@ -8124,7 +8128,7 @@
         </is>
       </c>
       <c r="O98" s="6" t="n">
-        <v>11000000</v>
+        <v>33000000</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
@@ -8165,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8196,11 +8200,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8284,7 +8288,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1997</t>
+          <t>https://royaldigi.ir/product/irancell-dt-350/</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -8364,10 +8368,14 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3250</t>
-        </is>
-      </c>
-      <c r="Q101" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/mikrotik-rb750r2/</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/fdd3ab52-7612-4fc0-8237-40c7fa31655e/%D8%B1%D9%88%D8%AA%D8%B1-%D9%85%DB%8C%DA%A9%D8%B1%D9%88%D8%AA%DB%8C%DA%A9-%D9%85%D8%AF%D9%84-hex-lite-_-rb750gr2/</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
@@ -8393,7 +8401,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8430,14 +8438,18 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27470000</v>
+        <v>27370000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3229</t>
-        </is>
-      </c>
-      <c r="Q102" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/tp-link-omada-eap245-v3/</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/9207040a-f0f8-40af-b983-93881477740e/</t>
+        </is>
+      </c>
       <c r="R102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
@@ -8460,7 +8472,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>12060000</v>
@@ -8506,11 +8518,11 @@
         </is>
       </c>
       <c r="O103" s="6" t="n">
-        <v>12060000</v>
+        <v>72360000</v>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1840</t>
+          <t>https://royaldigi.ir/product/netbox-prime/</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -8547,7 +8559,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4950000</v>
+        <v>4540000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8578,15 +8590,15 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+1,095,000 ت از رتبه 3 ترب (+28.4%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4950000</v>
+        <v>4540000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2554</t>
+          <t>https://royaldigi.ir/product/tp-link-tl-wr840n/</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -8664,7 +8676,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3227</t>
+          <t>https://royaldigi.ir/product/d-link-des-1008a/</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -8744,7 +8756,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3232</t>
+          <t>https://royaldigi.ir/product/alcatel-linkzone-mw70vk-cat-7/</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -8830,7 +8842,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3242</t>
+          <t>https://royaldigi.ir/product/jazz-mf673/</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -8908,7 +8920,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1868</t>
+          <t>https://royaldigi.ir/product/tp-link-m7200/</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -9068,7 +9080,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3228</t>
+          <t>https://royaldigi.ir/product/irancell-gp-2101-plus/</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -9154,7 +9166,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3233</t>
+          <t>https://royaldigi.ir/product/asiacell-speedoo-huawei-e352/</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -9240,7 +9252,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3251</t>
+          <t>https://royaldigi.ir/product/%d9%85%d9%88%d8%af%d9%85-%d8%b1%d9%88%d8%aa%d8%b1-4-5g-lte-%d8%af%d9%88-%d8%a8%d8%a7%d9%86%d8%af%d9%87-%d9%86%d8%b2%d8%aa%da%a9-naztech-nzt-gtx1000/</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -9513,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3508000</v>
+        <v>3501000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9544,15 +9556,15 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+520,000 ت از رتبه 3 ترب (+17.4%)</t>
+          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3508000</v>
+        <v>3501000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1809</t>
+          <t>https://royaldigi.ir/product/neterbit-nsl-122/</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -9634,7 +9646,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3239</t>
+          <t>https://royaldigi.ir/product/huawei-hg655d-n300/</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -9748,10 +9760,10 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>10500000</v>
+        <v>11250000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9782,15 +9794,15 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+3,011,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>10500000</v>
+        <v>22500000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2115</t>
+          <t>https://royaldigi.ir/product/d-link-dwr-m921/</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -9870,7 +9882,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2563</t>
+          <t>https://royaldigi.ir/product/mobinnet-mn-4200-n/</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -9950,7 +9962,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2567</t>
+          <t>https://royaldigi.ir/product/huawei-speed-wi-fi-home-l01s/</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -10132,10 +10144,10 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>7060000</v>
+        <v>7140000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -10172,15 +10184,15 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-2,540,000 ت از کف ترب (-26.5%)</t>
+          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
         </is>
       </c>
       <c r="O124" s="6" t="n">
-        <v>7060000</v>
+        <v>21420000</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1851</t>
+          <t>https://royaldigi.ir/product/tp-link-xn020-g3/</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -10262,7 +10274,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3244</t>
+          <t>https://royaldigi.ir/product/zlt-x20-ooredoo/</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -10340,7 +10352,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2566</t>
+          <t>https://royaldigi.ir/product/huawei-b2368/</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -10460,7 +10472,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F128" s="5" t="n">
         <v>11000000</v>
@@ -10498,11 +10510,11 @@
         </is>
       </c>
       <c r="O128" s="6" t="n">
-        <v>11000000</v>
+        <v>33000000</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1879</t>
+          <t>https://royaldigi.ir/product/huawei-e5573-320/</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -10668,7 +10680,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2558</t>
+          <t>https://royaldigi.ir/product/irancell-fd-m40-b1/</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -10862,7 +10874,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F133" s="5" t="n">
         <v>21750000</v>
@@ -10900,11 +10912,11 @@
         </is>
       </c>
       <c r="O133" s="6" t="n">
-        <v>21750000</v>
+        <v>108750000</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1770</t>
+          <t>https://royaldigi.ir/product/naztech-hope/</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -10984,7 +10996,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3236</t>
+          <t>https://royaldigi.ir/product/huawei-b622-335/</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -11070,10 +11082,14 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1975</t>
-        </is>
-      </c>
-      <c r="Q135" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/alcatel-linkzone-mw40v/</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/698b55f2-da18-42c9-a207-63d2803d366d/%D9%85%D9%88%D8%AF%D9%85-%D8%AC%DB%8C%D8%A8%DB%8C-%D8%A7%D9%84%DA%A9%D8%A7%D8%AA%D9%84-linkzone-mw40v-4g/</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
@@ -11140,10 +11156,14 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1973</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/d-link-dwr-930m/</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3c5544f1-2704-4dcb-a918-a41d404325f8/%D9%85%D9%88%D8%AF%D9%85-4g-%D9%82%D8%A7%D8%A8%D9%84-%D8%AD%D9%85%D9%84-%D8%AF%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-%D9%85%D8%AF%D9%84-dwr-930m/</t>
+        </is>
+      </c>
       <c r="R136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
@@ -11212,10 +11232,14 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2057</t>
-        </is>
-      </c>
-      <c r="Q137" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/d-link-dwr-933v/</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/613960de-720e-4f00-afd5-3ce32b01df80/%D9%85%D9%88%D8%AF%D9%85-%D8%B1%D9%88%D8%AA%D8%B1-%D8%A8%DB%8C-%D8%B3%DB%8C%D9%85-%D8%AF%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-%D9%85%D8%AF%D9%84-dwr-933v-4g-lte/</t>
+        </is>
+      </c>
       <c r="R137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
@@ -11282,10 +11306,14 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2076</t>
-        </is>
-      </c>
-      <c r="Q138" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/d-link-dwr-m920/</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/7b905a85-31a3-4aa4-8cb0-c623df59507d/%D9%85%D9%88%D8%AF%D9%85-%D8%AF%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-%D9%85%D8%AF%D9%84-dwr-m920/</t>
+        </is>
+      </c>
       <c r="R138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
@@ -11352,10 +11380,14 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2562</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/huawei-du-h155-380/</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/354d19d6-5474-4b53-9f5b-b9f05a183533/</t>
+        </is>
+      </c>
       <c r="R139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
@@ -11502,10 +11534,14 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2550</t>
-        </is>
-      </c>
-      <c r="Q141" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/huawei-w435-md-500b/</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/b5042640-6b61-4817-a0be-4907f7544b91/%D8%A7%D9%86%D8%AA%D9%86-%D8%AA%D9%82%D9%88%DB%8C%D8%AA%DB%8C-%D9%85%D9%88%D8%AF%D9%85-%D8%AC%DB%8C%D8%A8%DB%8C-%D9%85%D8%AF%D9%84-w435/</t>
+        </is>
+      </c>
       <c r="R141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
@@ -11580,10 +11616,14 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2031</t>
-        </is>
-      </c>
-      <c r="Q142" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/irancell-fd-i40-g1/</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/0531db72-7b60-4ae7-addb-bbca662a8e5f/%D9%85%D9%88%D8%AF%D9%85-%D8%B1%D9%88%D9%85%DB%8C%D8%B2%DB%8C-3g-4g-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%D8%B3%D9%84-%D9%85%D8%AF%D9%84-fd-i40-g1/</t>
+        </is>
+      </c>
       <c r="R142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
@@ -11652,10 +11692,14 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2040</t>
-        </is>
-      </c>
-      <c r="Q143" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/irancell-lh92/</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/6891435a-41ca-47e6-b6a9-644c3e5898cf/%D9%85%D9%88%D8%AF%D9%85-%D9%87%D9%85%D8%B1%D8%A7%D9%87-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%D8%B3%D9%84-%D9%85%D8%AF%D9%84-lh92-4g/</t>
+        </is>
+      </c>
       <c r="R143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
@@ -11724,10 +11768,14 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2046</t>
-        </is>
-      </c>
-      <c r="Q144" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/irancell-lh96/</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3c985055-6674-4b5c-a5d3-f5424578c734/</t>
+        </is>
+      </c>
       <c r="R144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
@@ -11791,7 +11839,11 @@
         <v>0</v>
       </c>
       <c r="P145" s="2" t="inlineStr"/>
-      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3f4bb37d-893b-4742-9309-51abed232a46/%D9%85%D9%88%D8%AF%D9%85-%D8%A7%DB%8C%D8%B1%D8%A7%D9%86%D8%B3%D9%84-%D9%85%D8%AF%D9%84-tf-i60-s1/</t>
+        </is>
+      </c>
       <c r="R145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
@@ -11866,7 +11918,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2142</t>
+          <t>https://royaldigi.ir/product/irancell-uroad-ss10/</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr"/>
@@ -11938,10 +11990,14 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3247</t>
-        </is>
-      </c>
-      <c r="Q147" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/klpda18dbi-25m/</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3b1d3d63-2b36-4c4c-83b6-2007823f990a/</t>
+        </is>
+      </c>
       <c r="R147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
@@ -12009,7 +12065,11 @@
         <v>0</v>
       </c>
       <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/653303c6-07f7-418e-a988-912f2750e386/</t>
+        </is>
+      </c>
       <c r="R148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
@@ -12078,10 +12138,14 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1932</t>
-        </is>
-      </c>
-      <c r="Q149" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/mci-ha4300/</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/1628d055-6111-40b9-810a-3c5b8b93910c/</t>
+        </is>
+      </c>
       <c r="R149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
@@ -12156,7 +12220,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2557</t>
+          <t>https://royaldigi.ir/product/mp-link-mp-4844/</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr"/>
@@ -12234,10 +12298,14 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2561</t>
-        </is>
-      </c>
-      <c r="Q151" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/necton-lc-02/</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/a3154f97-1352-4361-b244-6899a5746f89/%D9%85%D9%88%D8%AF%D9%85-%D8%B1%D9%88%D9%85%DB%8C%D8%B2%DB%8C-%D9%86%DA%A9%D8%AA%D9%88%D9%86-%D9%85%D8%AF%D9%84-lc02-td-lte-45g/</t>
+        </is>
+      </c>
       <c r="R151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
@@ -12304,10 +12372,14 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1897</t>
-        </is>
-      </c>
-      <c r="Q152" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/tp-link-eap110/</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/65306660-8430-4e3a-9669-02685764d852/</t>
+        </is>
+      </c>
       <c r="R152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
@@ -12374,10 +12446,14 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2560</t>
-        </is>
-      </c>
-      <c r="Q153" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/ugalink-ug-4221/</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/e3427f1b-3f2d-4874-a690-366551b74f07/</t>
+        </is>
+      </c>
       <c r="R153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
@@ -12444,10 +12520,14 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=1737</t>
-        </is>
-      </c>
-      <c r="Q154" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/zte-mc801a/</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/94833b95-d250-482f-870b-53c847d17482/</t>
+        </is>
+      </c>
       <c r="R154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
@@ -12522,10 +12602,14 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3249</t>
-        </is>
-      </c>
-      <c r="Q155" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/ubiquiti-uap-ac-lr/</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/a4773c33-652a-4340-9a28-112349195325/</t>
+        </is>
+      </c>
       <c r="R155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
@@ -12600,10 +12684,14 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3237</t>
-        </is>
-      </c>
-      <c r="Q156" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/%d8%a8%d8%a7%d8%aa%d8%b1%db%8c-%d9%85%d9%88%d8%af%d9%85-m40-g1-%d9%85%d8%af%d9%84-l816-%d8%b8%d8%b1%d9%81%db%8c%d8%aa-2100mah/</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/8525b6a7-0130-47ec-a472-88f5a2b16624/</t>
+        </is>
+      </c>
       <c r="R156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
@@ -12681,7 +12769,11 @@
           <t>https://royaldigi.ir/product/tp-link-tl-wr941nd/</t>
         </is>
       </c>
-      <c r="Q157" s="2" t="inlineStr"/>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/a46c3786-ab3d-4e09-8471-3cb415de2742/%D8%B1%D9%88%D8%AA%D8%B1-%D8%A8%DB%8C-%D8%B3%DB%8C%D9%85-%D8%AA%DA%A9-%D8%A8%D8%A7%D9%86%D8%AF%D9%87-%D8%AA%DB%8C-%D9%BE%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-tp-link-tl-wr941nd-%D8%A7%DA%A9%D8%A8%D9%86%D8%AF/</t>
+        </is>
+      </c>
       <c r="R157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
@@ -12759,7 +12851,11 @@
           <t>https://royaldigi.ir/product/tp-link-archer-ax3000/</t>
         </is>
       </c>
-      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3e2f8716-b861-494b-900a-33da78c9db29/%D8%B1%D9%88%D8%AA%D8%B1-%D8%A8%DB%8C-%D8%B3%DB%8C%D9%85-%D8%AA%DB%8C-%D9%BE%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-%D9%85%D8%AF%D9%84-archer-ax55-%D8%B8%D8%B1%D9%81%DB%8C%D8%AA-ax3000/</t>
+        </is>
+      </c>
       <c r="R158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
@@ -12837,7 +12933,11 @@
           <t>https://royaldigi.ir/product/tp-link-archer-c60-v3/</t>
         </is>
       </c>
-      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/5d00374d-afa7-42ac-9f67-3ccba7601c8f/%D8%B1%D9%88%D8%AA%D8%B1-%D8%A8%DB%8C-%D8%B3%DB%8C%D9%85-%D8%AA%DB%8C-%D9%BE%DB%8C-%D9%84%DB%8C%D9%86%DA%A9-archer-c60-ac1350-%D8%AF%D9%88-%D8%A8%D8%A7%D9%86%D8%AF/</t>
+        </is>
+      </c>
       <c r="R159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
@@ -12912,10 +13012,14 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=3248</t>
-        </is>
-      </c>
-      <c r="Q160" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/%da%a9%d8%a7%d8%a8%d9%84-%d9%85%d8%a8%d8%af%d9%84-%d8%a7%d9%81%d8%b2%d8%a7%db%8c%d9%86%d8%af%d9%87-%d9%88%d9%84%d8%aa%d8%a7%da%98-usb-5v-%d8%a8%d9%87-dc-12v-%d9%85%d8%ae%d8%b5%d9%88%d8%b5-%d9%85%d9%88/</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3547f32d-209e-4c3e-8686-35e670d8a57e/</t>
+        </is>
+      </c>
       <c r="R160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
@@ -12993,7 +13097,11 @@
           <t>https://royaldigi.ir/product/huawei-hg553/</t>
         </is>
       </c>
-      <c r="Q161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3c14cd83-c864-4316-9203-e3e3e6ca32b9/%D9%85%D9%88%D8%AF%D9%85-%D8%B1%D9%88%D8%AA%D8%B1-adsl-%D9%88%D8%AF%D8%A7%D9%81%D9%88%D9%86-%D9%85%D8%AF%D9%84-vodafone-hg553/</t>
+        </is>
+      </c>
       <c r="R161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
@@ -13071,7 +13179,11 @@
           <t>https://royaldigi.ir/product/naztech-nzt-tdx1000/</t>
         </is>
       </c>
-      <c r="Q162" s="2" t="inlineStr"/>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3b1e326c-95ea-402a-9218-47209f98457c/</t>
+        </is>
+      </c>
       <c r="R162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
@@ -13146,10 +13258,14 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>https://royaldigi.ir/?p=2564</t>
-        </is>
-      </c>
-      <c r="Q163" s="2" t="inlineStr"/>
+          <t>https://royaldigi.ir/product/huawei-b612s-25d/</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/8233f2c5-5552-411a-b6e8-232a5118742d/</t>
+        </is>
+      </c>
       <c r="R163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
@@ -13227,7 +13343,11 @@
           <t>https://royaldigi.ir/product/tp-link-xx230v/</t>
         </is>
       </c>
-      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/23114068-d8a7-d985-d8af-d985-d981-db-8c-d8a8-d8b1-d986-d988-d8b1-db-8c-d8aa-db-8c-d9-be-d9-84-db-8c-d9-86-da-a9-d9-85-d8af-d9-84-xx230v-ax1800-d8af-d988-d8a8-d8a7-d9-86-d8af-wi-fi-6/</t>
+        </is>
+      </c>
       <c r="R164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
@@ -13305,7 +13425,11 @@
           <t>https://royaldigi.ir/product/mci-mc-i110/</t>
         </is>
       </c>
-      <c r="Q165" s="2" t="inlineStr"/>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/653303c6-07f7-418e-a988-912f2750e386/</t>
+        </is>
+      </c>
       <c r="R165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
@@ -13383,7 +13507,11 @@
           <t>https://royaldigi.ir/product/huawei-e5785-320/</t>
         </is>
       </c>
-      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3b118b62-0943-41a4-96d2-8b4317f22557/</t>
+        </is>
+      </c>
       <c r="R166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
@@ -13461,7 +13589,11 @@
           <t>https://royaldigi.ir/product/huawei-e5785-320-stc/</t>
         </is>
       </c>
-      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>https://torob.com/p/3b118b62-0943-41a4-96d2-8b4317f22557/</t>
+        </is>
+      </c>
       <c r="R167" s="2" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مانیتورینگ ۵ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="مانیتورینگ ۵ فروشنده ترب" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,14 +63,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3E8FF"/>
-        <bgColor rgb="00F3E8FF"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
+        <fgColor rgb="00F3E8FF"/>
+        <bgColor rgb="00F3E8FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,10 +115,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,26 +636,22 @@
         <v>11390000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9200000</v>
+        <v>9964340</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9250000</v>
+        <v>10000000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>10200000</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>10290000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>10280000</v>
+        <v>12000000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -664,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+1,990,000 ت از رتبه 3 ترب (+21.2%)</t>
+          <t>+1,100,000 ت از رتبه 5 ترب (+10.7%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -708,39 +704,35 @@
       <c r="E3" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>20430000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>14590000</v>
+        <v>19990000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>14990000</v>
+        <v>20000000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15499000</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>20290000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>20430000</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>20590000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>20590000</v>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>+4,931,000 ت از رتبه 3 ترب (+31.8%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -784,39 +776,35 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="8" t="n">
         <v>16750000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>12899000</v>
+        <v>14980000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12990000</v>
+        <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>12990000</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>16650000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>16750000</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>17028000</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>12990000</v>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>17190000</v>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+3,760,000 ت از رتبه 3 ترب (+28.9%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -864,26 +852,22 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4500000</v>
+        <v>5099999</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4800000</v>
+        <v>5400000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5670103</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>5690000</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>5790000</v>
+        <v>6800000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -892,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+1,150,000 ت از رتبه 3 ترب (+23.0%)</t>
+          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -936,11 +920,11 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="8" t="n">
         <v>6530000</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6400000</v>
+        <v>7350000</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>6450000</v>
@@ -959,16 +943,16 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>7460210</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9560670</v>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1016,23 +1000,19 @@
         <v>4640000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3900000</v>
+        <v>1890000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3950000</v>
+        <v>4000000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3995000</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4200000</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>4460000</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>4550000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1044,7 +1024,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+645,000 ت از رتبه 3 ترب (+16.1%)</t>
+          <t>+90,000 ت از رتبه 5 ترب (+2.0%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1075,7 +1055,7 @@
           <t>2144</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1088,10 +1068,8 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F8" s="6" t="n">
+        <v>1760000</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1125,16 +1103,16 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>22880000</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1172,47 +1150,35 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="8" t="n">
         <v>100000</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="G9" s="6" t="n">
+        <v>97000</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>116379</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>129600</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>195000</v>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1252,39 +1218,35 @@
       <c r="E10" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="8" t="n">
         <v>9798000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>8900000</v>
+        <v>9400000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9000000</v>
+        <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9798000</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>9800000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>+298,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1332,17 +1294,13 @@
         <v>7760000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6799000</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1313,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>8220000</v>
+        <v>13513760</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -1364,7 +1322,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+1,860,000 ت از رتبه 1 ترب (+31.5%)</t>
+          <t>+160,000 ت از رتبه 3 ترب (+2.1%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1395,7 +1353,7 @@
           <t>2121</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1408,51 +1366,39 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F12" s="8" t="n">
+        <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>7265700</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>4600000</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>49500000</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1490,39 +1436,35 @@
       <c r="E13" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>9100000</v>
+        <v>13800000</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9500000</v>
+        <v>13800000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>10200000</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>13900000</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>15330000</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>17880000</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>-3,600,000 ت از کف ترب (-26.1%)</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1545,7 +1487,7 @@
           <t>1953</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1558,45 +1500,39 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11480000</v>
+        <v>11500000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11590000</v>
+        <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>14179000</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>11670000</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>11670000</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>11670000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>20900000</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+8,180,000 ت از رتبه 5 ترب (+70.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0</v>
+        <v>158800000</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
@@ -1640,26 +1576,22 @@
         <v>7930000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6200000</v>
+        <v>7270000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>6295000</v>
+        <v>7294000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7297000</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>7860000</v>
+        <v>8880000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1668,7 +1600,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+1,630,000 ت از رتبه 3 ترب (+25.9%)</t>
+          <t>+530,000 ت از رتبه 5 ترب (+7.2%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1699,7 +1631,7 @@
           <t>1964</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1712,45 +1644,39 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F16" s="8" t="n">
+        <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4195000</v>
+        <v>4600000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>4200000</v>
+        <v>5000000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4290000</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5400000</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>5597000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>32340000</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -1790,13 +1716,11 @@
       <c r="E17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>12060000</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G17" s="6" t="n">
+        <v>12000000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1823,14 +1747,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در ترب</t>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>+60,000 ت از رتبه 1 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
@@ -1861,7 +1785,7 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1874,47 +1798,41 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F18" s="8" t="n">
+        <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9250000</v>
+        <v>9420000</v>
       </c>
       <c r="H18" s="6" t="n">
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9500000</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>12950000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0</v>
+        <v>57720000</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -1941,7 +1859,7 @@
           <t>1814</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -1954,39 +1872,35 @@
       <c r="E19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="8" t="n">
         <v>9798000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>8900000</v>
+        <v>9400000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9000000</v>
+        <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9798000</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>9800000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9800000</v>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>+298,000 ت از رتبه 3 ترب (+3.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2017,7 +1931,7 @@
           <t>2559</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2030,13 +1944,11 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F20" s="11" t="n">
+        <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>2980000</v>
+        <v>4000000</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>3879000</v>
@@ -2059,18 +1971,18 @@
       <c r="L20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>-13,000 ت از کف ترب (-0.3%)</t>
         </is>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0</v>
+        <v>23196000</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
@@ -2114,17 +2026,13 @@
         <v>7640000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6799000</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2137,7 +2045,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>8220000</v>
+        <v>13513760</v>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
@@ -2146,7 +2054,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>+1,740,000 ت از رتبه 1 ترب (+29.5%)</t>
+          <t>+40,000 ت از رتبه 3 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -2194,7 +2102,7 @@
         <v>18590000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>15300000</v>
+        <v>18000000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2217,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16890000</v>
+        <v>17452870</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2226,7 +2134,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>+3,290,000 ت از رتبه 1 ترب (+21.5%)</t>
+          <t>+590,000 ت از رتبه 1 ترب (+3.3%)</t>
         </is>
       </c>
       <c r="O22" s="6" t="n">
@@ -2270,39 +2178,35 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="8" t="n">
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>7800000</v>
+        <v>9470000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8090000</v>
+        <v>13300000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>16200000</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>30200000</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>40200000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>6902400</v>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>7652540</v>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>+5,550,000 ت از رتبه 3 ترب (+34.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2333,7 +2237,7 @@
           <t>1714</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2346,45 +2250,39 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F24" s="5" t="n">
+        <v>7470000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>5616000</v>
+        <v>6440000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>5650000</v>
+        <v>6550000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6790000</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>6950000</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>6990000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7813800</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+480,000 ت از رتبه 5 ترب (+6.9%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>37350000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2309,7 @@
           <t>2071</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2433,23 +2331,19 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6980000</v>
+        <v>8200000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8290000</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>8800000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>12590000</v>
+        <v>14700000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2489,7 +2383,7 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2508,23 +2402,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>6900000</v>
+        <v>8400000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>7400000</v>
+        <v>8415000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7980000</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8499000</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>9000000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2563,7 +2453,7 @@
           <t>2420</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2582,18 +2472,16 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>8300000</v>
+        <v>12320000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>9200000</v>
+        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>16000000</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>20500000</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -2637,7 +2525,7 @@
           <t>2167</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2656,7 +2544,7 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>6500000</v>
+        <v>7600000</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2738,26 +2626,22 @@
         <v>5380000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>5190000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>4980000</v>
+        <v>5200000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5220000</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>5282000</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>5300000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>5790000</v>
+        <v>6450000</v>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
@@ -2766,7 +2650,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+380,000 ت از رتبه 3 ترب (+7.6%)</t>
+          <t>+80,000 ت از رتبه 5 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2875,7 +2759,7 @@
           <t>1759</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2894,26 +2778,22 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>22950000</v>
+        <v>14000000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>23000000</v>
+        <v>14899000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>14900000</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>15000000</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>29900000</v>
+        <v>27300000</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -2953,7 +2833,7 @@
           <t>1862</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -2972,23 +2852,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>10799000</v>
+        <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>10800000</v>
+        <v>12500000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12500000</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>12650000</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>12650000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>19500000</v>
@@ -3044,45 +2920,37 @@
       <c r="E33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="8" t="n">
         <v>7140000</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>9600000</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6000000</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>7140000</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>7300000</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -3113,7 +2981,7 @@
           <t>1930</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3132,27 +3000,19 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8700000</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>9440000</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>9889000</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>9889000</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3189,7 +3049,7 @@
       <c r="B35" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3202,7 +3062,7 @@
       <c r="E35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>2500000</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -3231,7 +3091,7 @@
       <c r="L35" s="6" t="n">
         <v>3305000</v>
       </c>
-      <c r="M35" s="10" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -3257,7 +3117,7 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3274,26 +3134,22 @@
         <v>10100000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6500000</v>
+        <v>6950000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7489000</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7150000</v>
+        <v>7650000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3302,7 +3158,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+3,100,000 ت از رتبه 3 ترب (+44.3%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -3333,7 +3189,7 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3350,26 +3206,22 @@
         <v>10100000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6500000</v>
+        <v>6950000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7489000</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7150000</v>
+        <v>7650000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3378,7 +3230,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+3,100,000 ت از رتبه 3 ترب (+44.3%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -3409,7 +3261,7 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3422,41 +3274,35 @@
       <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="8" t="n">
         <v>17730000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11880000</v>
+        <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>11890000</v>
+        <v>15500000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>13200000</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>17700000</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>17730000</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>17750000</v>
+      </c>
+      <c r="L38" s="6" t="n">
+        <v>16790000</v>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+4,530,000 ت از رتبه 3 ترب (+34.3%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3487,7 +3333,7 @@
           <t>1753</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3504,23 +3350,19 @@
         <v>4640000</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>3900000</v>
+        <v>1890000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>3950000</v>
+        <v>4000000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3995000</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4200000</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>4460000</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>4550000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3532,7 +3374,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+645,000 ت از رتبه 3 ترب (+16.1%)</t>
+          <t>+90,000 ت از رتبه 5 ترب (+2.0%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3563,7 +3405,7 @@
           <t>2420</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3582,18 +3424,16 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>8300000</v>
+        <v>12320000</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>9200000</v>
+        <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>16000000</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>20500000</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -3639,7 +3479,7 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3721,7 +3561,7 @@
           <t>2139</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3740,7 +3580,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3801,7 +3641,7 @@
           <t>2133</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3826,17 +3666,13 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7500000</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8064550</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8489000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3881,7 +3717,7 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -3980,22 +3816,20 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7600000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7615000</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>7893100</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4007,14 +3841,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -4056,39 +3890,35 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>3498000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4500000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>15300000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="10" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -4128,45 +3958,39 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F47" s="5" t="n">
+        <v>7470000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5616000</v>
+        <v>6440000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5650000</v>
+        <v>6550000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6790000</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>6950000</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>6990000</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>7069000</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7813800</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+480,000 ت از رتبه 5 ترب (+6.9%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>14940000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4210,26 +4034,22 @@
         <v>12700000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>8700000</v>
+        <v>9300000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>8900000</v>
+        <v>9900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>10600000</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>11650000</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>12000000</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>11000000</v>
+        <v>14500000</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
@@ -4238,7 +4058,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,600,000 ت از رتبه 3 ترب (+39.6%)</t>
+          <t>+700,000 ت از رتبه 5 ترب (+5.8%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -4286,26 +4106,22 @@
         <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3140000</v>
+        <v>14000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>3149000</v>
+        <v>15000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>15000</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>3350000</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>4085000</v>
+        <v>4600000</v>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
@@ -4314,7 +4130,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>+1,045,000 ت از رتبه 5 ترب (+31.2%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4358,41 +4174,37 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="8" t="n">
         <v>9452000</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>6690000</v>
+        <v>7200000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>6700000</v>
+        <v>7999000</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>6850000</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8489000</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>9452000</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+2,602,000 ت از رتبه 3 ترب (+38.0%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -4436,41 +4248,37 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="8" t="n">
         <v>17730000</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>11890000</v>
+        <v>14500000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>11900000</v>
+        <v>15500000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>12900000</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>17700000</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>17730000</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>17750000</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+4,830,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -4536,10 +4344,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L52" s="6" t="n">
+        <v>13000000</v>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -4893,7 +4699,7 @@
       <c r="B57" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="C57" s="8" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4965,7 +4771,7 @@
       <c r="B58" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -4978,7 +4784,7 @@
       <c r="E58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F58" s="8" t="n">
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -5004,12 +4810,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="L58" s="6" t="n">
+        <v>7911200</v>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -5043,7 +4847,7 @@
           <t>1775</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5081,7 +4885,7 @@
         </is>
       </c>
       <c r="L59" s="6" t="n">
-        <v>8075000</v>
+        <v>11000000</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -5121,7 +4925,7 @@
           <t>1902</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5160,10 +4964,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L60" s="6" t="n">
+        <v>8295990</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5203,7 +5005,7 @@
           <t>3231</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5283,7 +5085,7 @@
           <t>2092</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5296,10 +5098,8 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>4840000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5321,20 +5121,20 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>4758000</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0</v>
+        <v>9680000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5161,7 @@
           <t>1926</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5401,7 +5201,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>8075000</v>
+        <v>19200000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5441,7 +5241,7 @@
           <t>1819</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5477,7 +5277,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>5500000</v>
+        <v>6450000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5517,7 +5317,7 @@
           <t>2066</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5597,7 +5397,7 @@
           <t>1942</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5667,7 +5467,7 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5751,7 +5551,7 @@
           <t>3240</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5789,7 +5589,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>3866860</v>
+        <v>4260710</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5829,7 +5629,7 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5909,7 +5709,7 @@
           <t>1885</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -5948,10 +5748,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L70" s="6" t="n">
+        <v>16000000</v>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
@@ -5991,7 +5789,7 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6031,7 +5829,7 @@
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>6377900</v>
+        <v>9700000</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -6071,7 +5869,7 @@
           <t>1914</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6153,7 +5951,7 @@
           <t>2127</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -6189,7 +5987,7 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>5200000</v>
+        <v>4703670</v>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
@@ -6265,7 +6063,7 @@
         </is>
       </c>
       <c r="L74" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
@@ -6485,7 +6283,7 @@
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
@@ -6561,7 +6359,7 @@
         </is>
       </c>
       <c r="L78" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
@@ -6637,7 +6435,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>4630000</v>
+        <v>5200000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6713,7 +6511,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>24980000</v>
+        <v>30126400</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6789,7 +6587,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>7660000</v>
+        <v>8880000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6867,7 +6665,7 @@
         </is>
       </c>
       <c r="L82" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
@@ -6943,7 +6741,7 @@
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>14300000</v>
+        <v>38000000</v>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
@@ -7091,7 +6889,7 @@
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>13300000</v>
+        <v>18000000</v>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
@@ -7413,7 +7211,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>6950000</v>
+        <v>7650000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7489,7 +7287,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>6950000</v>
+        <v>7650000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7542,10 +7340,8 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F91" s="5" t="n">
+        <v>4840000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7567,20 +7363,20 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>4582400</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>4758000</v>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>0</v>
+        <v>4840000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7643,7 +7439,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>3324800</v>
+        <v>3597000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7719,7 +7515,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>7850000</v>
+        <v>8550000</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7772,7 +7568,7 @@
       <c r="E94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="9" t="n">
+      <c r="F94" s="8" t="n">
         <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
@@ -7801,7 +7597,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M94" s="10" t="inlineStr">
+      <c r="M94" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -8191,7 +7987,7 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>5200000</v>
+        <v>4703670</v>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
@@ -8231,7 +8027,7 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
+      <c r="C100" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8311,7 +8107,7 @@
           <t>3250</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8387,7 +8183,7 @@
           <t>3229</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8400,7 +8196,7 @@
       <c r="E102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F102" s="9" t="n">
+      <c r="F102" s="8" t="n">
         <v>27370000</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -8427,7 +8223,7 @@
       <c r="L102" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="M102" s="10" t="inlineStr">
+      <c r="M102" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
@@ -8461,7 +8257,7 @@
           <t>1840</t>
         </is>
       </c>
-      <c r="C103" s="8" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8545,7 +8341,7 @@
           <t>2554</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8581,7 +8377,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>4630000</v>
+        <v>5200000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8621,7 +8417,7 @@
           <t>3227</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8659,7 +8455,7 @@
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>5300000</v>
+        <v>8100000</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -8699,7 +8495,7 @@
           <t>3232</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C106" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8779,7 +8575,7 @@
           <t>3242</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8865,7 +8661,7 @@
           <t>1868</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C108" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8903,7 +8699,7 @@
         </is>
       </c>
       <c r="L108" s="6" t="n">
-        <v>16990000</v>
+        <v>14550000</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -8941,7 +8737,7 @@
       <c r="B109" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -8954,7 +8750,7 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F109" s="8" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -8985,7 +8781,7 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M109" s="10" t="inlineStr">
+      <c r="M109" s="9" t="inlineStr">
         <is>
           <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
@@ -9019,7 +8815,7 @@
           <t>3228</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9103,7 +8899,7 @@
           <t>3233</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9189,7 +8985,7 @@
           <t>3251</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9275,7 +9071,7 @@
           <t>1948</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9353,7 +9149,7 @@
           <t>1783</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9391,7 +9187,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11000000</v>
+        <v>11590000</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9431,7 +9227,7 @@
           <t>2082</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9511,7 +9307,7 @@
           <t>1809</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9547,7 +9343,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>3324800</v>
+        <v>3597000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9587,7 +9383,7 @@
           <t>3239</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9669,7 +9465,7 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C118" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9749,7 +9545,7 @@
           <t>2115</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9825,7 +9621,7 @@
           <t>2563</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9905,7 +9701,7 @@
           <t>2567</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -9981,7 +9777,7 @@
           <t>1862</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C122" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10059,7 +9855,7 @@
           <t>1846</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10133,7 +9929,7 @@
           <t>1851</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10215,7 +10011,7 @@
           <t>3244</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10254,10 +10050,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L125" s="6" t="n">
+        <v>16000000</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -10297,7 +10091,7 @@
           <t>2566</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10375,7 +10169,7 @@
           <t>2150</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C127" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10461,7 +10255,7 @@
           <t>1879</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10537,7 +10331,7 @@
           <t>1908</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10623,7 +10417,7 @@
           <t>2558</t>
         </is>
       </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10703,7 +10497,7 @@
           <t>2052</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10783,7 +10577,7 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr">
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10863,7 +10657,7 @@
           <t>1770</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>
@@ -10899,7 +10693,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="n">
-        <v>6902400</v>
+        <v>7652540</v>
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>
@@ -10939,7 +10733,7 @@
           <t>3236</t>
         </is>
       </c>
-      <c r="C134" s="8" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>کالای استوک</t>
         </is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -511,7 +511,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="43" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
@@ -636,13 +636,13 @@
         <v>11390000</v>
       </c>
       <c r="G2" s="6" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="I2" s="6" t="n">
         <v>9964340</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>10200000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>10200000</v>
@@ -717,7 +717,7 @@
         <v>20290000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20430000</v>
+        <v>20360000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>20590000</v>
@@ -727,12 +727,12 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -776,7 +776,7 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="5" t="n">
         <v>16750000</v>
       </c>
       <c r="G4" s="6" t="n">
@@ -786,25 +786,25 @@
         <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
+        <v>16245000</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>16440000</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>16650000</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>16750000</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>17028000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+100,000 ت از رتبه 5 ترب (+0.6%)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -852,19 +852,19 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5099999</v>
+        <v>4950000</v>
       </c>
       <c r="H5" s="6" t="n">
+        <v>4989000</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>4990000</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <v>5670103</v>
-      </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>5690000</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>6800000</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
+          <t>+460,000 ت از رتبه 5 ترب (+8.1%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -1009,10 +1009,10 @@
         <v>4200000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4460000</v>
+        <v>4550000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4550000</v>
+        <v>4595000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه 5 ترب (+2.0%)</t>
+          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1068,8 +1068,10 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>1760000</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1103,16 +1105,16 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در ترب</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
-        <v>22880000</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1160,13 +1162,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>129600</v>
+        <v>130810</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1228,7 +1230,7 @@
         <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9798000</v>
+        <v>9799000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9800000</v>
@@ -1237,7 +1239,7 @@
         <v>9800000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9800000</v>
+        <v>9450000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1366,39 +1368,41 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="n">
-        <v>4950000</v>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>4900000</v>
+        <v>5199000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5400000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5700000</v>
+        <v>5699000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5700000</v>
       </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
-        <v>49500000</v>
+        <v>0</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1440,7 +1444,7 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>13800000</v>
+        <v>13500000</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>13800000</v>
@@ -1464,7 +1468,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-3,600,000 ت از کف ترب (-26.1%)</t>
+          <t>-3,300,000 ت از کف ترب (-24.4%)</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1500,8 +1504,10 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>19850000</v>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G14" s="6" t="n">
         <v>11500000</v>
@@ -1521,18 +1527,18 @@
       <c r="L14" s="6" t="n">
         <v>20900000</v>
       </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+8,180,000 ت از رتبه 5 ترب (+70.1%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
-        <v>158800000</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
@@ -1576,22 +1582,22 @@
         <v>7930000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7270000</v>
+        <v>6200000</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>7290000</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>7294000</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>7297000</v>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>7400000</v>
-      </c>
       <c r="K15" s="6" t="n">
-        <v>7400000</v>
+        <v>7300000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8880000</v>
+        <v>8840000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1600,7 +1606,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+530,000 ت از رتبه 5 ترب (+7.2%)</t>
+          <t>+630,000 ت از رتبه 5 ترب (+8.6%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1644,8 +1650,10 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>4620000</v>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G16" s="6" t="n">
         <v>4600000</v>
@@ -1657,26 +1665,26 @@
         <v>5400000</v>
       </c>
       <c r="J16" s="6" t="n">
+        <v>5445000</v>
+      </c>
+      <c r="K16" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="K16" s="6" t="n">
-        <v>5597000</v>
-      </c>
       <c r="L16" s="6" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>6100000</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
-        <v>32340000</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -1798,8 +1806,10 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>9620000</v>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G18" s="6" t="n">
         <v>9420000</v>
@@ -1808,31 +1818,31 @@
         <v>9500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>9500000</v>
+        <v>10000000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>10000000</v>
+        <v>12500000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>12950000</v>
+        <v>18000000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
-        <v>57720000</v>
+        <v>0</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -1882,7 +1892,7 @@
         <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9798000</v>
+        <v>9799000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9800000</v>
@@ -1891,7 +1901,7 @@
         <v>9800000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9800000</v>
+        <v>9450000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -1944,8 +1954,10 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>3866000</v>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G20" s="6" t="n">
         <v>4000000</v>
@@ -1971,18 +1983,18 @@
       <c r="L20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="M20" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-13,000 ت از کف ترب (-0.3%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O20" s="6" t="n">
-        <v>23196000</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2137,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17452870</v>
+        <v>19275040</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2182,31 +2194,31 @@
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>9470000</v>
+        <v>7490000</v>
       </c>
       <c r="H23" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>9590000</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>30200000</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>30200000</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>40200000</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>7652540</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2250,8 +2262,10 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>7470000</v>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G24" s="6" t="n">
         <v>6440000</v>
@@ -2271,18 +2285,18 @@
       <c r="L24" s="6" t="n">
         <v>7813800</v>
       </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+480,000 ت از رتبه 5 ترب (+6.9%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>37350000</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2331,16 +2345,16 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="J25" s="6" t="n">
         <v>8200000</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>8290000</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>8400000</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>8800000</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>14700000</v>
@@ -2405,16 +2419,16 @@
         <v>8400000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>8415000</v>
+        <v>8499000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8499000</v>
+        <v>8500000</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8500000</v>
+        <v>9000000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>9000000</v>
+        <v>9389000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2478,7 +2492,7 @@
         <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>16000000</v>
+        <v>17900000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>20500000</v>
@@ -2626,19 +2640,19 @@
         <v>5380000</v>
       </c>
       <c r="G29" s="6" t="n">
+        <v>4950000</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>5190000</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>5220000</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>5282000</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>5300000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6450000</v>
@@ -2650,7 +2664,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+80,000 ت از رتبه 5 ترب (+1.5%)</t>
+          <t>+160,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2778,19 +2792,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
+        <v>13900000</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>14000000</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>14899000</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>14900000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>14900000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>15000000</v>
+        <v>14900000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2861,7 +2875,7 @@
         <v>12500000</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>12650000</v>
+        <v>12500000</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>12650000</v>
@@ -2936,7 +2950,7 @@
         <v>7140000</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>7300000</v>
+        <v>8000000</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -3278,31 +3292,31 @@
         <v>17730000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>14500000</v>
+        <v>17710000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>15500000</v>
+        <v>17750000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17700000</v>
+        <v>17999000</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>17730000</v>
+        <v>18000000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>17750000</v>
+        <v>18500000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>16790000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3359,10 +3373,10 @@
         <v>4200000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4460000</v>
+        <v>4550000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4550000</v>
+        <v>4595000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3374,7 +3388,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه 5 ترب (+2.0%)</t>
+          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3430,7 +3444,7 @@
         <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>16000000</v>
+        <v>17900000</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>20500000</v>
@@ -3672,7 +3686,7 @@
         <v>8064550</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8489000</v>
+        <v>8480000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3897,10 +3911,10 @@
         <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>3498000</v>
+        <v>4500000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4500000</v>
+        <v>6200000</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>11000000</v>
@@ -3913,12 +3927,12 @@
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3958,8 +3972,10 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="5" t="n">
-        <v>7470000</v>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G47" s="6" t="n">
         <v>6440000</v>
@@ -3979,18 +3995,18 @@
       <c r="L47" s="6" t="n">
         <v>7813800</v>
       </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+480,000 ت از رتبه 5 ترب (+6.9%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14940000</v>
+        <v>0</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4043,10 +4059,10 @@
         <v>10600000</v>
       </c>
       <c r="J48" s="6" t="n">
+        <v>11120000</v>
+      </c>
+      <c r="K48" s="6" t="n">
         <v>11650000</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>12000000</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>14500000</v>
@@ -4058,7 +4074,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+700,000 ت از رتبه 5 ترب (+5.8%)</t>
+          <t>+1,050,000 ت از رتبه 5 ترب (+9.0%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -4178,19 +4194,19 @@
         <v>9452000</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>7200000</v>
+        <v>7999000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>7999000</v>
+        <v>8489000</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>8489000</v>
+        <v>9450000</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>9450000</v>
+        <v>9452000</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>9452000</v>
+        <v>9500000</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -4199,12 +4215,12 @@
       </c>
       <c r="M50" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -4252,19 +4268,19 @@
         <v>17730000</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>14500000</v>
+        <v>17710000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>15500000</v>
+        <v>17750000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>17700000</v>
+        <v>17999000</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>17730000</v>
+        <v>18000000</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>17750000</v>
+        <v>18500000</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -4273,12 +4289,12 @@
       </c>
       <c r="M51" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -4322,39 +4338,35 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="8" t="n">
         <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>11400000</v>
+        <v>11500000</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12200000</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>12350000</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>12850000</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -4402,23 +4414,19 @@
         <v>11250000</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>6750000</v>
+        <v>7000000</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>7000000</v>
+        <v>7489000</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>7489000</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8000000</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>10620000</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>13700000</v>
@@ -4430,7 +4438,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
+          <t>+630,000 ت از رتبه 5 ترب (+5.9%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -4564,23 +4572,19 @@
         <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>7990000</v>
+        <v>399000</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>9000000</v>
+        <v>545000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>10950000</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>650000</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>765000</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>890000</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>9300000</v>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+10,110,000 ت از رتبه 5 ترب (+1136.0%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -4636,17 +4640,17 @@
       <c r="E56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="8" t="n">
         <v>10390000</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>5800000</v>
+        <v>6592000</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>5900000</v>
+        <v>9936000</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>5950000</v>
+        <v>10440000</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4663,14 +4667,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M56" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,440,000 ت از رتبه 3 ترب (+74.6%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
@@ -4788,17 +4792,13 @@
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4180000</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>6489000</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4815,12 +4815,12 @@
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O58" s="6" t="n">
@@ -4866,18 +4866,16 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>4600000</v>
+        <v>8100000</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>5500000</v>
+        <v>10000000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12700000</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>13248000</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -4944,28 +4942,22 @@
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>6460000</v>
+        <v>4500000</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5700000</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>6280000</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>6500000</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>8295990</v>
+        <v>7849990</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5024,10 +5016,10 @@
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>8500000</v>
+        <v>13000000</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>8700000</v>
+        <v>16480000</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>9000000</v>
@@ -5098,43 +5090,41 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>4840000</v>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3900000</v>
+        <v>3500000</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>3940000</v>
+        <v>4100000</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>3950000</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4380000</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>4500000</v>
       </c>
       <c r="L62" s="6" t="n">
-        <v>4758000</v>
-      </c>
-      <c r="M62" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>5950000</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>9680000</v>
+        <v>0</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5180,15 +5170,13 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>21500000</v>
+        <v>20000000</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="I63" s="6" t="n">
+        <v>22162000</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5201,7 +5189,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>19200000</v>
+        <v>20000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5258,23 +5246,19 @@
         <v>5380000</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>4600000</v>
+        <v>4950000</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>4950000</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>5190000</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>5220000</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>6450000</v>
@@ -5286,7 +5270,7 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+430,000 ت از رتبه 3 ترب (+8.7%)</t>
+          <t>+160,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
@@ -5486,12 +5470,10 @@
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>3980000</v>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6408230</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>6489000</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -5570,23 +5552,19 @@
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3620000</v>
+        <v>3700000</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>3741000</v>
+        <v>4000000</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>4100000</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4200000</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>4350000</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>4700000</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>4260710</v>
@@ -5651,20 +5629,16 @@
         <v>10000000</v>
       </c>
       <c r="H69" s="6" t="n">
+        <v>10659330</v>
+      </c>
+      <c r="I69" s="6" t="n">
         <v>10989000</v>
       </c>
-      <c r="I69" s="6" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J69" s="6" t="n">
+        <v>11210000</v>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>12840000</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -5726,7 +5700,7 @@
         <v>9550000</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>7200000</v>
+        <v>9500000</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -5758,7 +5732,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
+          <t>+50,000 ت از رتبه 1 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O70" s="6" t="n">
@@ -5829,7 +5803,7 @@
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>9700000</v>
+        <v>11000000</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5888,10 +5862,10 @@
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>11000000</v>
+        <v>12500000</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>17500000</v>
+        <v>18900000</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -5964,39 +5938,35 @@
       <c r="E73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="8" t="n">
         <v>4475000</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>3290000</v>
+        <v>3889253</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>3700000</v>
+        <v>4450000</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>3890000</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4480000</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>4489000</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>4489000</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="M73" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
@@ -6040,39 +6010,35 @@
       <c r="E74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="8" t="n">
         <v>12005000</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>8999000</v>
+        <v>9900000</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>9000000</v>
+        <v>10200000</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12000000</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>12005000</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="M74" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
@@ -6120,23 +6086,19 @@
         <v>21740000</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>2350000</v>
+        <v>700000</v>
       </c>
       <c r="H75" s="6" t="n">
         <v>2400000</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>2445000</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>2500000</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>2649000</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>2649500</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>23900000</v>
@@ -6148,7 +6110,7 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,295,000 ت از رتبه 3 ترب (+789.2%)</t>
+          <t>+19,090,500 ت از رتبه 5 ترب (+720.5%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
@@ -6195,20 +6157,16 @@
         <v>10000000</v>
       </c>
       <c r="H76" s="6" t="n">
+        <v>10659330</v>
+      </c>
+      <c r="I76" s="6" t="n">
         <v>10989000</v>
       </c>
-      <c r="I76" s="6" t="n">
-        <v>15600000</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J76" s="6" t="n">
+        <v>11210000</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>12840000</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>36400000</v>
@@ -6220,7 +6178,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+11,770,000 ت از رتبه 3 ترب (+75.4%)</t>
+          <t>+14,530,000 ت از رتبه 5 ترب (+113.2%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
@@ -6260,39 +6218,35 @@
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="8" t="n">
         <v>10740000</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>8999000</v>
+        <v>9900000</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>9000000</v>
+        <v>10200000</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12000000</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>12005000</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="M77" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,540,000 ت از رتبه 3 ترب (+16.7%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
@@ -6340,23 +6294,19 @@
         <v>12010000</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>8999000</v>
+        <v>9900000</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>9000000</v>
+        <v>10200000</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12000000</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>12005000</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>18000000</v>
@@ -6368,7 +6318,7 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+2,810,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+5,000 ت از رتبه 5 ترب (+0.0%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
@@ -6416,23 +6366,19 @@
         <v>4540000</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>3750000</v>
+        <v>4200000</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>3800000</v>
+        <v>4400000</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>3855000</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4498000</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>4498000</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>4499000</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>5200000</v>
@@ -6444,7 +6390,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+41,000 ت از رتبه 5 ترب (+0.9%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
@@ -6488,39 +6434,35 @@
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="8" t="n">
         <v>15498000</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>14700000</v>
+        <v>14999000</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>14989000</v>
+        <v>15490000</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>14990000</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>15499000</v>
+      </c>
+      <c r="J80" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>15500000</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>30126400</v>
       </c>
-      <c r="M80" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M80" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+508,000 ت از رتبه 3 ترب (+3.4%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
@@ -6564,39 +6506,35 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="8" t="n">
         <v>6500000</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>6190000</v>
+        <v>6200000</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>6198000</v>
+        <v>7290000</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7294000</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>7297000</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>7300000</v>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8880000</v>
-      </c>
-      <c r="M81" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>8860000</v>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 3 ترب (+4.8%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
@@ -6718,39 +6656,35 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="8" t="n">
         <v>22200000</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>10000000</v>
+        <v>15490000</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>10900000</v>
+        <v>23000000</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>11800000</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>23350000</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>25900000</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>38000000</v>
       </c>
-      <c r="M83" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M83" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+10,400,000 ت از رتبه 3 ترب (+88.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
@@ -6798,23 +6732,19 @@
         <v>2652000</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>2350000</v>
+        <v>700000</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>2400000</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>2445000</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>2500000</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>2649000</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>2649500</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>3795000</v>
@@ -6826,7 +6756,7 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+207,000 ت از رتبه 3 ترب (+8.5%)</t>
+          <t>+2,500 ت از رتبه 5 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
@@ -6870,23 +6800,19 @@
         <v>12630000</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>8999000</v>
+        <v>9900000</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>9000000</v>
+        <v>10200000</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>9200000</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12000000</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>12005000</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>18000000</v>
@@ -6898,7 +6824,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>+3,430,000 ت از رتبه 3 ترب (+37.3%)</t>
+          <t>+625,000 ت از رتبه 5 ترب (+5.2%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
@@ -6947,10 +6873,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="G86" s="6" t="n">
+        <v>4000000</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -7114,7 +7038,7 @@
         <v>7840000</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>5800000</v>
+        <v>7000000</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>5980000</v>
@@ -7192,23 +7116,19 @@
         <v>10100000</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>6400000</v>
+        <v>6950000</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>6590000</v>
+        <v>7300000</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7489000</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>7500000</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>7650000</v>
@@ -7220,7 +7140,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
@@ -7268,23 +7188,19 @@
         <v>10100000</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>6400000</v>
+        <v>6950000</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>6590000</v>
+        <v>7300000</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7489000</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>7500000</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>7650000</v>
@@ -7296,7 +7212,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
@@ -7340,43 +7256,41 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>4840000</v>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="G91" s="6" t="n">
-        <v>3900000</v>
+        <v>3500000</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>3940000</v>
+        <v>4100000</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>3950000</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4380000</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>4500000</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>4758000</v>
-      </c>
-      <c r="M91" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>5950000</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+890,000 ت از رتبه 3 ترب (+22.5%)</t>
+          <t>ناموجود در رویال</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>4840000</v>
+        <v>0</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7416,39 +7330,35 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="8" t="n">
         <v>3501000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>2950000</v>
+        <v>3500000</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>2988000</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>3500000</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>3549000</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>3597000</v>
       </c>
       <c r="L92" s="6" t="n">
-        <v>3597000</v>
-      </c>
-      <c r="M92" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>4300000</v>
+      </c>
+      <c r="M92" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
@@ -7496,23 +7406,19 @@
         <v>7900000</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>6898000</v>
+        <v>7900</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>6899000</v>
+        <v>7850000</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>6920000</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7880000</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>7885000</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>7899000</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>8550000</v>
@@ -7524,7 +7430,7 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+980,000 ت از رتبه 3 ترب (+14.2%)</t>
+          <t>+1,000 ت از رتبه 5 ترب (+0.0%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
@@ -7572,21 +7478,17 @@
         <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>3580000</v>
+        <v>3980000</v>
       </c>
       <c r="H94" s="6" t="n">
+        <v>5594550</v>
+      </c>
+      <c r="I94" s="6" t="n">
+        <v>5712330</v>
+      </c>
+      <c r="J94" s="6" t="n">
         <v>5889000</v>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -7599,12 +7501,12 @@
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O94" s="6" t="n">
@@ -7648,39 +7550,35 @@
       <c r="E95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F95" s="8" t="n">
         <v>24750000</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>19800000</v>
+        <v>21490000</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>21000000</v>
+        <v>23500000</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>21350000</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>23990000</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>25000000</v>
       </c>
       <c r="L95" s="6" t="n">
-        <v>27800000</v>
-      </c>
-      <c r="M95" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>27700000</v>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+3,400,000 ت از رتبه 3 ترب (+15.9%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
@@ -7724,16 +7622,14 @@
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F96" s="8" t="n">
         <v>5040000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="H96" s="6" t="n">
+        <v>5070000</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -7755,14 +7651,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M96" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M96" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+540,000 ت از رتبه 1 ترب (+12.0%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
@@ -7810,7 +7706,7 @@
         <v>9550000</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>7200000</v>
+        <v>9500000</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -7844,7 +7740,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
+          <t>+50,000 ت از رتبه 1 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O97" s="6" t="n">
@@ -7888,14 +7784,14 @@
       <c r="E98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="F98" s="8" t="n">
         <v>11000000</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>7990000</v>
+        <v>11000000</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>9000000</v>
+        <v>14900000</v>
       </c>
       <c r="I98" s="6" t="n">
         <v>10950000</v>
@@ -7913,14 +7809,14 @@
       <c r="L98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O98" s="6" t="n">
@@ -7964,39 +7860,35 @@
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F99" s="8" t="n">
         <v>4475000</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>3290000</v>
+        <v>3889253</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>3700000</v>
+        <v>4450000</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>3890000</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4480000</v>
+      </c>
+      <c r="J99" s="6" t="n">
+        <v>4489000</v>
+      </c>
+      <c r="K99" s="6" t="n">
+        <v>4489000</v>
       </c>
       <c r="L99" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="M99" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M99" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
@@ -8046,10 +7938,10 @@
         </is>
       </c>
       <c r="G100" s="6" t="n">
-        <v>3580000</v>
+        <v>3680000</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>3200000</v>
+        <v>5989000</v>
       </c>
       <c r="I100" s="6" t="n">
         <v>3580000</v>
@@ -8126,25 +8018,19 @@
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>2900000</v>
+        <v>1890000</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8600000</v>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>8999000</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="K101" s="6" t="n">
+        <v>11230000</v>
       </c>
       <c r="L101" s="6" t="n">
         <v>3200000</v>
@@ -8358,23 +8244,19 @@
         <v>4540000</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>3750000</v>
+        <v>4200000</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>3800000</v>
+        <v>4400000</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>3855000</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4498000</v>
+      </c>
+      <c r="J104" s="6" t="n">
+        <v>4498000</v>
+      </c>
+      <c r="K104" s="6" t="n">
+        <v>4499000</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>5200000</v>
@@ -8386,7 +8268,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+41,000 ت از رتبه 5 ترب (+0.9%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
@@ -8436,23 +8318,19 @@
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>4000000</v>
+        <v>2900000</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>4200000</v>
+        <v>4400000</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>4699000</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4800000</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="K105" s="6" t="n">
+        <v>4900000</v>
       </c>
       <c r="L105" s="6" t="n">
         <v>8100000</v>
@@ -8680,23 +8558,19 @@
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>7560000</v>
+        <v>9950000</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>9500000</v>
+        <v>10700000</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>9699000</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>10800000</v>
+      </c>
+      <c r="J108" s="6" t="n">
+        <v>13490000</v>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>14900000</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>14550000</v>
@@ -8750,11 +8624,11 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="8" t="n">
+      <c r="F109" s="11" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>2250000</v>
+        <v>2550000</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -8781,14 +8655,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M109" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>-300,000 ت از کف ترب (-11.8%)</t>
         </is>
       </c>
       <c r="O109" s="6" t="n">
@@ -8834,12 +8708,10 @@
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>3580000</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>3680000</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>5989000</v>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -9090,23 +8962,19 @@
         </is>
       </c>
       <c r="G113" s="6" t="n">
-        <v>5900000</v>
+        <v>5850000</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>6000000</v>
+        <v>6150000</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>6450000</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6500000</v>
+      </c>
+      <c r="J113" s="6" t="n">
+        <v>6992000</v>
+      </c>
+      <c r="K113" s="6" t="n">
+        <v>7800000</v>
       </c>
       <c r="L113" s="6" t="n">
         <v>7900000</v>
@@ -9168,26 +9036,22 @@
         </is>
       </c>
       <c r="G114" s="6" t="n">
-        <v>9000000</v>
+        <v>9320000</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>9100000</v>
+        <v>9400000</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>9790000</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9400000</v>
+      </c>
+      <c r="J114" s="6" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>9800000</v>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11590000</v>
+        <v>11544740</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9246,23 +9110,19 @@
         </is>
       </c>
       <c r="G115" s="6" t="n">
-        <v>8900000</v>
+        <v>8750000</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>9500000</v>
+        <v>9300000</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9300000</v>
+      </c>
+      <c r="J115" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K115" s="6" t="n">
+        <v>10250000</v>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
@@ -9320,39 +9180,35 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="5" t="n">
+      <c r="F116" s="8" t="n">
         <v>3501000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>2950000</v>
+        <v>3500000</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>2988000</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>3500000</v>
+      </c>
+      <c r="J116" s="6" t="n">
+        <v>3549000</v>
+      </c>
+      <c r="K116" s="6" t="n">
+        <v>3597000</v>
       </c>
       <c r="L116" s="6" t="n">
-        <v>3597000</v>
-      </c>
-      <c r="M116" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>4300000</v>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+513,000 ت از رتبه 3 ترب (+17.2%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
@@ -9405,7 +9261,7 @@
         <v>4400000</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>4900000</v>
+        <v>5500000</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -9484,23 +9340,19 @@
         </is>
       </c>
       <c r="G118" s="6" t="n">
-        <v>5248000</v>
+        <v>5500000</v>
       </c>
       <c r="H118" s="6" t="n">
-        <v>5500000</v>
+        <v>6900000</v>
       </c>
       <c r="I118" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6989000</v>
+      </c>
+      <c r="J118" s="6" t="n">
+        <v>6989000</v>
+      </c>
+      <c r="K118" s="6" t="n">
+        <v>7000000</v>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
@@ -9562,23 +9414,19 @@
         <v>11250000</v>
       </c>
       <c r="G119" s="6" t="n">
-        <v>6750000</v>
+        <v>7000000</v>
       </c>
       <c r="H119" s="6" t="n">
-        <v>7000000</v>
+        <v>7489000</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>7489000</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8000000</v>
+      </c>
+      <c r="J119" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K119" s="6" t="n">
+        <v>10620000</v>
       </c>
       <c r="L119" s="6" t="n">
         <v>13700000</v>
@@ -9590,7 +9438,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+3,761,000 ت از رتبه 3 ترب (+50.2%)</t>
+          <t>+630,000 ت از رتبه 5 ترب (+5.9%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
@@ -9643,20 +9491,16 @@
         <v>5950000</v>
       </c>
       <c r="H120" s="6" t="n">
-        <v>6250000</v>
+        <v>6500000</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8140000</v>
+      </c>
+      <c r="J120" s="6" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="K120" s="6" t="n">
+        <v>81400000</v>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
@@ -9796,23 +9640,19 @@
         </is>
       </c>
       <c r="G122" s="6" t="n">
-        <v>10800000</v>
+        <v>11300000</v>
       </c>
       <c r="H122" s="6" t="n">
-        <v>10950000</v>
+        <v>12500000</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12500000</v>
+      </c>
+      <c r="J122" s="6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="K122" s="6" t="n">
+        <v>12650000</v>
       </c>
       <c r="L122" s="6" t="n">
         <v>19500000</v>
@@ -10110,23 +9950,19 @@
         </is>
       </c>
       <c r="G126" s="6" t="n">
-        <v>10800000</v>
+        <v>11300000</v>
       </c>
       <c r="H126" s="6" t="n">
-        <v>10950000</v>
+        <v>12500000</v>
       </c>
       <c r="I126" s="6" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12500000</v>
+      </c>
+      <c r="J126" s="6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="K126" s="6" t="n">
+        <v>12650000</v>
       </c>
       <c r="L126" s="6" t="n">
         <v>19500000</v>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -511,7 +511,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="43" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
@@ -633,7 +633,7 @@
         <v>188</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>11390000</v>
+        <v>10860000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>9500000</v>
@@ -648,7 +648,7 @@
         <v>10200000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10290000</v>
+        <v>10500000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12000000</v>
@@ -660,11 +660,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+1,100,000 ت از رتبه 5 ترب (+10.7%)</t>
+          <t>+360,000 ت از رتبه 5 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2141320000</v>
+        <v>2041680000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -705,38 +705,38 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20430000</v>
+        <v>19690000</v>
       </c>
       <c r="G3" s="6" t="n">
+        <v>17760000</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>19429693</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>19590000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>19990000</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>20290000</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>20360000</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>20590000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>20590000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1287090000</v>
+        <v>1240470000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -776,8 +776,8 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>16750000</v>
+      <c r="F4" s="8" t="n">
+        <v>16290000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14980000</v>
@@ -789,7 +789,7 @@
         <v>16245000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>16440000</v>
+        <v>16290000</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>16650000</v>
@@ -797,18 +797,18 @@
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+100,000 ت از رتبه 5 ترب (+0.6%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>502500000</v>
+        <v>488700000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,22 +849,22 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6150000</v>
+        <v>5840000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4950000</v>
+        <v>5149000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>4989000</v>
+        <v>5200000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4990000</v>
+        <v>5690000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5400000</v>
+        <v>5700000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5690000</v>
+        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>6800000</v>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+460,000 ت از رتبه 5 ترب (+8.1%)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.7%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>104550000</v>
+        <v>99280000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -920,8 +920,8 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>6530000</v>
+      <c r="F6" s="5" t="n">
+        <v>7990000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>7350000</v>
@@ -943,20 +943,20 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9560670</v>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+        <v>9494730</v>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+640,000 ت از رتبه 3 ترب (+8.7%)</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>111010000</v>
+        <v>135830000</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4640000</v>
+        <v>4880000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1009,10 +1009,10 @@
         <v>4200000</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4550000</v>
+        <v>4599936</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4595000</v>
+        <v>4695000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
+          <t>+185,000 ت از رتبه 5 ترب (+3.9%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>69600000</v>
+        <v>73200000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1068,10 +1068,8 @@
       <c r="E8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F8" s="6" t="n">
+        <v>1760000</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1105,16 +1103,16 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>ناموجود در ترب</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>22880000</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1162,13 +1160,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>116379</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>129600</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>130810</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1221,7 +1219,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9798000</v>
+        <v>9570000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9400000</v>
@@ -1230,7 +1228,7 @@
         <v>9500000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9799000</v>
+        <v>9570000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9800000</v>
@@ -1252,7 +1250,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>97980000</v>
+        <v>95700000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1293,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7760000</v>
+        <v>7755000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1324,11 +1322,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+160,000 ت از رتبه 3 ترب (+2.1%)</t>
+          <t>+155,000 ت از رتبه 3 ترب (+2.0%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>15520000</v>
+        <v>15510000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1368,10 +1366,8 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F12" s="8" t="n">
+        <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>4600000</v>
@@ -1386,23 +1382,23 @@
         <v>5400000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5699000</v>
+        <v>5690000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5700000</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0</v>
+        <v>49500000</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1500,8 @@
       <c r="E14" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F14" s="5" t="n">
+        <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>11500000</v>
@@ -1525,20 +1519,20 @@
         <v>11670000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>20900000</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>21300000</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+8,180,000 ت از رتبه 5 ترب (+70.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0</v>
+        <v>158800000</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
@@ -1578,39 +1572,39 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="5" t="n">
-        <v>7930000</v>
+      <c r="F15" s="8" t="n">
+        <v>7299000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6200000</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>7284000</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>7290000</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7294000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7297000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7300000</v>
+        <v>7299000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8840000</v>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>8113910</v>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+630,000 ت از رتبه 5 ترب (+8.6%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>39650000</v>
+        <v>36495000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1650,10 +1644,8 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F16" s="8" t="n">
+        <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>4600000</v>
@@ -1671,20 +1663,20 @@
         <v>5500000</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>6100000</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>4900000</v>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>32340000</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -1806,10 +1798,8 @@
       <c r="E18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F18" s="8" t="n">
+        <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>9420000</v>
@@ -1831,18 +1821,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0</v>
+        <v>57720000</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -1883,7 +1873,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9798000</v>
+        <v>9570000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9400000</v>
@@ -1892,7 +1882,7 @@
         <v>9500000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9799000</v>
+        <v>9570000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9800000</v>
@@ -1914,7 +1904,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>97980000</v>
+        <v>95700000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -1954,10 +1944,8 @@
       <c r="E20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F20" s="11" t="n">
+        <v>3866000</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>4000000</v>
@@ -1983,18 +1971,18 @@
       <c r="L20" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>-13,000 ت از کف ترب (-0.3%)</t>
         </is>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0</v>
+        <v>23196000</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
@@ -2137,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>19275040</v>
+        <v>21320000</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2191,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>21750000</v>
+        <v>11440000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7490000</v>
@@ -2213,16 +2201,16 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
-        <v>108750000</v>
+        <v>57200000</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
@@ -2262,41 +2250,39 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F24" s="8" t="n">
+        <v>6950000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>6440000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6550000</v>
+        <v>6790000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6790000</v>
+        <v>6950000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6950000</v>
+        <v>6990000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>6990000</v>
+        <v>6999000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>7813800</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7783800</v>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>34750000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2354,7 +2340,7 @@
         <v>8200000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8290000</v>
+        <v>8400000</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>14700000</v>
@@ -2428,7 +2414,7 @@
         <v>9000000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>9389000</v>
+        <v>9000000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2495,7 +2481,7 @@
         <v>17900000</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>20500000</v>
+        <v>20600000</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -2636,39 +2622,39 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>5380000</v>
+      <c r="F29" s="8" t="n">
+        <v>5260000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>4950000</v>
+        <v>5190000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5190000</v>
+        <v>5220000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5200000</v>
+        <v>5260000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5220000</v>
+        <v>5282000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6450000</v>
       </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+160,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21520000</v>
+        <v>21040000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2792,19 +2778,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
+        <v>13899000</v>
+      </c>
+      <c r="H31" s="6" t="n">
         <v>13900000</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>14000000</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>14899000</v>
-      </c>
       <c r="J31" s="6" t="n">
-        <v>14900000</v>
+        <v>14490000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14900000</v>
+        <v>14820000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -3020,13 +3006,13 @@
         <v>9440000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9440000</v>
+        <v>9889000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>9889000</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>9889000</v>
+        <v>14160000</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3145,16 +3131,16 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>10100000</v>
+        <v>9090000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7300000</v>
+        <v>7489000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>7500000</v>
@@ -3163,7 +3149,7 @@
         <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7650000</v>
+        <v>7400000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3172,11 +3158,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>+1,590,000 ت از رتبه 5 ترب (+21.2%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>20200000</v>
+        <v>18180000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3217,16 +3203,16 @@
         <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>10100000</v>
+        <v>9090000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6950000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7300000</v>
+        <v>7489000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>7500000</v>
@@ -3235,7 +3221,7 @@
         <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7650000</v>
+        <v>7400000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3244,11 +3230,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>+1,590,000 ت از رتبه 5 ترب (+21.2%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>20200000</v>
+        <v>18180000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3289,16 +3275,16 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17730000</v>
+        <v>17999750</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>17710000</v>
+        <v>17750000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17750000</v>
+        <v>17999000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17999000</v>
+        <v>17999750</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>18000000</v>
@@ -3311,16 +3297,16 @@
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>35460000</v>
+        <v>35999500</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3361,7 +3347,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4640000</v>
+        <v>4880000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3373,10 +3359,10 @@
         <v>4200000</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4550000</v>
+        <v>4599936</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4595000</v>
+        <v>4695000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3388,11 +3374,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+45,000 ت از رتبه 5 ترب (+1.0%)</t>
+          <t>+185,000 ت از رتبه 5 ترب (+3.9%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>69600000</v>
+        <v>73200000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3433,7 @@
         <v>17900000</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>20500000</v>
+        <v>20600000</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -3594,7 +3580,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4150000</v>
+        <v>3150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3680,13 +3666,17 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8064550</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>8480000</v>
+        <v>7289000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3830,20 +3820,22 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7600000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7615000</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -3855,14 +3847,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3908,19 +3900,23 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>45500</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4500000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>15300000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
@@ -3972,41 +3968,43 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F47" s="5" t="n">
+        <v>6950000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>6440000</v>
+        <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6550000</v>
+        <v>5650000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6790000</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>6990000</v>
+        <v>5698000</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>7813800</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>7783800</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+1,252,000 ت از رتبه 3 ترب (+22.0%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>13900000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4047,22 +4045,26 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12700000</v>
+        <v>11650000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>9300000</v>
+        <v>8700000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>9900000</v>
+        <v>8900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>10600000</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>11120000</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>11650000</v>
+        <v>9100000</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L48" s="6" t="n">
         <v>14500000</v>
@@ -4074,11 +4076,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+1,050,000 ت از رتبه 5 ترب (+9.0%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+28.0%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>25400000</v>
+        <v>23300000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4122,19 +4124,23 @@
         <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>14000</v>
+        <v>3140000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15000</v>
+        <v>3149000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>3350000</v>
+        <v>3150000</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L49" s="6" t="n">
         <v>4600000</v>
@@ -4146,7 +4152,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+1,045,000 ت از رتبه 5 ترب (+31.2%)</t>
+          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4190,41 +4196,45 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>9452000</v>
+      <c r="F50" s="5" t="n">
+        <v>9450500</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>7999000</v>
+        <v>6690000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>8489000</v>
+        <v>6700000</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>9450000</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>9452000</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>9500000</v>
+        <v>6850000</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+2,600,500 ت از رتبه 3 ترب (+38.0%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18904000</v>
+        <v>18901000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4264,41 +4274,45 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="8" t="n">
-        <v>17730000</v>
+      <c r="F51" s="5" t="n">
+        <v>17999750</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>17710000</v>
+        <v>11890000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>17750000</v>
+        <v>11900000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>17999000</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>18500000</v>
+        <v>12900000</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+5,099,750 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>35460000</v>
+        <v>35999500</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4338,35 +4352,39 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="5" t="n">
         <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
       </c>
       <c r="H52" s="6" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="I52" s="6" t="n">
         <v>11500000</v>
       </c>
-      <c r="I52" s="6" t="n">
-        <v>12200000</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>12350000</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>12850000</v>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -4411,22 +4429,26 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>11250000</v>
+        <v>10150000</v>
       </c>
       <c r="G53" s="6" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="H53" s="6" t="n">
         <v>7000000</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="I53" s="6" t="n">
         <v>7489000</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>10620000</v>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L53" s="6" t="n">
         <v>13700000</v>
@@ -4438,11 +4460,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+630,000 ت از رتبه 5 ترب (+5.9%)</t>
+          <t>+2,661,000 ت از رتبه 3 ترب (+35.5%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>22500000</v>
+        <v>20300000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4572,19 +4594,23 @@
         <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>399000</v>
+        <v>7990000</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>545000</v>
+        <v>9000000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>650000</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>765000</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>890000</v>
+        <v>10950000</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L55" s="6" t="n">
         <v>9300000</v>
@@ -4596,7 +4622,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+10,110,000 ت از رتبه 5 ترب (+1136.0%)</t>
+          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -4640,17 +4666,17 @@
       <c r="E56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>10390000</v>
+      <c r="F56" s="5" t="n">
+        <v>10540000</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>6592000</v>
+        <v>5800000</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>9936000</v>
+        <v>5900000</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>10440000</v>
+        <v>5950000</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4667,18 +4693,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M56" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+4,590,000 ت از رتبه 3 ترب (+77.1%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>20780000</v>
+        <v>21080000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4818,17 @@
         <v>4500000</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>4180000</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>6489000</v>
+        <v>4500000</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4811,16 +4841,16 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>7911200</v>
+        <v>9900000</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="O58" s="6" t="n">
@@ -4866,16 +4896,18 @@
         </is>
       </c>
       <c r="G59" s="6" t="n">
-        <v>8100000</v>
+        <v>4600000</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>10000000</v>
+        <v>5500000</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>12700000</v>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>13248000</v>
+        <v>6800000</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -4942,22 +4974,28 @@
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>4500000</v>
+        <v>6460000</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>6280000</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>6500000</v>
+        <v>8300000</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7849990</v>
+        <v>7270000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5016,10 +5054,10 @@
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>13000000</v>
+        <v>8500000</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>16480000</v>
+        <v>8700000</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>9000000</v>
@@ -5090,41 +5128,43 @@
       <c r="E62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>4999500</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>3500000</v>
+        <v>3900000</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>4100000</v>
+        <v>3940000</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>4380000</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>4500000</v>
+        <v>3950000</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5950000</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>5990000</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+1,049,500 ت از رتبه 3 ترب (+26.6%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>0</v>
+        <v>9999000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5170,13 +5210,15 @@
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>20000000</v>
+        <v>21500000</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>22000000</v>
       </c>
-      <c r="I63" s="6" t="n">
-        <v>22162000</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5243,22 +5285,26 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5380000</v>
+        <v>5260000</v>
       </c>
       <c r="G64" s="6" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="I64" s="6" t="n">
         <v>4950000</v>
       </c>
-      <c r="H64" s="6" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="I64" s="6" t="n">
-        <v>5190000</v>
-      </c>
-      <c r="J64" s="6" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>5220000</v>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L64" s="6" t="n">
         <v>6450000</v>
@@ -5270,11 +5316,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+160,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>+310,000 ت از رتبه 3 ترب (+6.3%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21520000</v>
+        <v>21040000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5470,10 +5516,12 @@
         </is>
       </c>
       <c r="G67" s="6" t="n">
-        <v>6408230</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>6489000</v>
+        <v>3980000</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -5552,19 +5600,23 @@
         </is>
       </c>
       <c r="G68" s="6" t="n">
-        <v>3700000</v>
+        <v>3620000</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>4000000</v>
+        <v>3741000</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="J68" s="6" t="n">
-        <v>4350000</v>
-      </c>
-      <c r="K68" s="6" t="n">
-        <v>4700000</v>
+        <v>4100000</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L68" s="6" t="n">
         <v>4260710</v>
@@ -5629,16 +5681,20 @@
         <v>10000000</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>10659330</v>
+        <v>10989000</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>10989000</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>11210000</v>
-      </c>
-      <c r="K69" s="6" t="n">
-        <v>12840000</v>
+        <v>15600000</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -5700,7 +5756,7 @@
         <v>9550000</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>9500000</v>
+        <v>7200000</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5788,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 1 ترب (+0.5%)</t>
+          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
         </is>
       </c>
       <c r="O70" s="6" t="n">
@@ -5803,7 +5859,7 @@
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>11000000</v>
+        <v>9700000</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5862,10 +5918,10 @@
         </is>
       </c>
       <c r="G72" s="6" t="n">
-        <v>12500000</v>
+        <v>11000000</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>18900000</v>
+        <v>17500000</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -5938,39 +5994,43 @@
       <c r="E73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="8" t="n">
-        <v>4475000</v>
+      <c r="F73" s="5" t="n">
+        <v>4486000</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>3889253</v>
+        <v>3290000</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>4450000</v>
+        <v>3700000</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>4480000</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>4489000</v>
-      </c>
-      <c r="K73" s="6" t="n">
-        <v>4489000</v>
+        <v>3890000</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L73" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="M73" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+596,000 ت از رتبه 3 ترب (+15.3%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4475000</v>
+        <v>4486000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6010,35 +6070,39 @@
       <c r="E74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="8" t="n">
+      <c r="F74" s="5" t="n">
         <v>12005000</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>9900000</v>
+        <v>8999000</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>10200000</v>
+        <v>9000000</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>12005000</v>
+        <v>9200000</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L74" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="M74" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
@@ -6083,22 +6147,26 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>21740000</v>
+        <v>21720000</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>700000</v>
+        <v>2350000</v>
       </c>
       <c r="H75" s="6" t="n">
         <v>2400000</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>2649000</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>2649500</v>
+        <v>2445000</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L75" s="6" t="n">
         <v>23900000</v>
@@ -6110,11 +6178,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,090,500 ت از رتبه 5 ترب (+720.5%)</t>
+          <t>+19,275,000 ت از رتبه 3 ترب (+788.3%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>21740000</v>
+        <v>21720000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6151,22 +6219,26 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="H76" s="6" t="n">
-        <v>10659330</v>
+        <v>10989000</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>10989000</v>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>11210000</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>12840000</v>
+        <v>15600000</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L76" s="6" t="n">
         <v>36400000</v>
@@ -6178,11 +6250,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+14,530,000 ت از رتبه 5 ترب (+113.2%)</t>
+          <t>+12,370,000 ت از رتبه 3 ترب (+79.3%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6218,39 +6290,43 @@
       <c r="E77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>10740000</v>
+      <c r="F77" s="5" t="n">
+        <v>10750000</v>
       </c>
       <c r="G77" s="6" t="n">
-        <v>9900000</v>
+        <v>8999000</v>
       </c>
       <c r="H77" s="6" t="n">
-        <v>10200000</v>
+        <v>9000000</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>12005000</v>
+        <v>9200000</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L77" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="M77" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+1,550,000 ت از رتبه 3 ترب (+16.8%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>10740000</v>
+        <v>10750000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6291,22 +6367,26 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="G78" s="6" t="n">
-        <v>9900000</v>
+        <v>8999000</v>
       </c>
       <c r="H78" s="6" t="n">
-        <v>10200000</v>
+        <v>9000000</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="J78" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="K78" s="6" t="n">
-        <v>12005000</v>
+        <v>9200000</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L78" s="6" t="n">
         <v>18000000</v>
@@ -6318,11 +6398,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+5,000 ت از رتبه 5 ترب (+0.0%)</t>
+          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12010000</v>
+        <v>12005000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6366,19 +6446,23 @@
         <v>4540000</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>4200000</v>
+        <v>3750000</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>4400000</v>
+        <v>3800000</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="K79" s="6" t="n">
-        <v>4499000</v>
+        <v>3855000</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L79" s="6" t="n">
         <v>5200000</v>
@@ -6390,7 +6474,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+41,000 ت از رتبه 5 ترب (+0.9%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
@@ -6434,39 +6518,43 @@
       <c r="E80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="8" t="n">
-        <v>15498000</v>
+      <c r="F80" s="5" t="n">
+        <v>15500000</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>14999000</v>
+        <v>14700000</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>15490000</v>
+        <v>14989000</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>15499000</v>
-      </c>
-      <c r="J80" s="6" t="n">
-        <v>15500000</v>
-      </c>
-      <c r="K80" s="6" t="n">
-        <v>15500000</v>
+        <v>14990000</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L80" s="6" t="n">
         <v>30126400</v>
       </c>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+510,000 ت از رتبه 3 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15498000</v>
+        <v>15500000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6506,39 +6594,43 @@
       <c r="E81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="8" t="n">
-        <v>6500000</v>
+      <c r="F81" s="5" t="n">
+        <v>7950000</v>
       </c>
       <c r="G81" s="6" t="n">
+        <v>6190000</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>6198000</v>
+      </c>
+      <c r="I81" s="6" t="n">
         <v>6200000</v>
       </c>
-      <c r="H81" s="6" t="n">
-        <v>7290000</v>
-      </c>
-      <c r="I81" s="6" t="n">
-        <v>7294000</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>7297000</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>7300000</v>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8860000</v>
-      </c>
-      <c r="M81" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>8113910</v>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+1,750,000 ت از رتبه 3 ترب (+28.2%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>6500000</v>
+        <v>7950000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -6579,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>5980000</v>
+        <v>6040000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6612,11 +6704,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه 2 ترب (+0.5%)</t>
+          <t>+90,000 ت از رتبه 2 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>5980000</v>
+        <v>6040000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6656,39 +6748,43 @@
       <c r="E83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="8" t="n">
-        <v>22200000</v>
+      <c r="F83" s="5" t="n">
+        <v>24210000</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>15490000</v>
+        <v>10000000</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>23000000</v>
+        <v>10900000</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>23350000</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>25900000</v>
+        <v>11800000</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L83" s="6" t="n">
         <v>38000000</v>
       </c>
-      <c r="M83" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+12,410,000 ت از رتبه 3 ترب (+105.2%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22200000</v>
+        <v>24210000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6729,22 +6825,26 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2652000</v>
+        <v>2642000</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>700000</v>
+        <v>2350000</v>
       </c>
       <c r="H84" s="6" t="n">
         <v>2400000</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>2649000</v>
-      </c>
-      <c r="K84" s="6" t="n">
-        <v>2649500</v>
+        <v>2445000</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L84" s="6" t="n">
         <v>3795000</v>
@@ -6756,11 +6856,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+2,500 ت از رتبه 5 ترب (+0.1%)</t>
+          <t>+197,000 ت از رتبه 3 ترب (+8.1%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2652000</v>
+        <v>2642000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6796,39 +6896,43 @@
       <c r="E85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>12630000</v>
+      <c r="F85" s="11" t="n">
+        <v>7340000</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>9900000</v>
+        <v>8999000</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>10200000</v>
+        <v>9000000</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="K85" s="6" t="n">
-        <v>12005000</v>
+        <v>9200000</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L85" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="M85" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>+625,000 ت از رتبه 5 ترب (+5.2%)</t>
+          <t>-1,659,000 ت از کف ترب (-18.4%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>12630000</v>
+        <v>7340000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -6873,8 +6977,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="G86" s="6" t="n">
-        <v>4000000</v>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -7038,7 +7144,7 @@
         <v>7840000</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>7000000</v>
+        <v>5800000</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>5980000</v>
@@ -7113,25 +7219,29 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>10100000</v>
+        <v>9090000</v>
       </c>
       <c r="G89" s="6" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>6590000</v>
+      </c>
+      <c r="I89" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="H89" s="6" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="I89" s="6" t="n">
-        <v>7489000</v>
-      </c>
-      <c r="J89" s="6" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="K89" s="6" t="n">
-        <v>7500000</v>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7650000</v>
+        <v>7400000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7140,11 +7250,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>+2,140,000 ت از رتبه 3 ترب (+30.8%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>20200000</v>
+        <v>18180000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7185,25 +7295,29 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>10100000</v>
+        <v>9090000</v>
       </c>
       <c r="G90" s="6" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>6590000</v>
+      </c>
+      <c r="I90" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="H90" s="6" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="I90" s="6" t="n">
-        <v>7489000</v>
-      </c>
-      <c r="J90" s="6" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="K90" s="6" t="n">
-        <v>7500000</v>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7650000</v>
+        <v>7400000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7212,11 +7326,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>+2,140,000 ت از رتبه 3 ترب (+30.8%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>20200000</v>
+        <v>18180000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7256,41 +7370,43 @@
       <c r="E91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="F91" s="5" t="n">
+        <v>4999500</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>3500000</v>
+        <v>3900000</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>4100000</v>
+        <v>3940000</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>4380000</v>
-      </c>
-      <c r="J91" s="6" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="K91" s="6" t="n">
-        <v>4500000</v>
+        <v>3950000</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5950000</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود در رویال</t>
+        <v>5990000</v>
+      </c>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>ناموجود در رویال</t>
+          <t>+1,049,500 ت از رتبه 3 ترب (+26.6%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>0</v>
+        <v>4999500</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7330,39 +7446,43 @@
       <c r="E92" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="8" t="n">
-        <v>3501000</v>
+      <c r="F92" s="5" t="n">
+        <v>3615000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
       </c>
       <c r="H92" s="6" t="n">
-        <v>3500000</v>
+        <v>2950000</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="J92" s="6" t="n">
-        <v>3549000</v>
-      </c>
-      <c r="K92" s="6" t="n">
-        <v>3597000</v>
+        <v>2988000</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="M92" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>4314600</v>
+      </c>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+627,000 ت از رتبه 3 ترب (+21.0%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3501000</v>
+        <v>3615000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7403,22 +7523,26 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7900000</v>
+        <v>7894000</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>7900</v>
+        <v>6898000</v>
       </c>
       <c r="H93" s="6" t="n">
-        <v>7850000</v>
+        <v>6899000</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>7880000</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>7885000</v>
-      </c>
-      <c r="K93" s="6" t="n">
-        <v>7899000</v>
+        <v>6920000</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L93" s="6" t="n">
         <v>8550000</v>
@@ -7430,11 +7554,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+1,000 ت از رتبه 5 ترب (+0.0%)</t>
+          <t>+974,000 ت از رتبه 3 ترب (+14.1%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7900000</v>
+        <v>7894000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7478,17 +7602,21 @@
         <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>3980000</v>
+        <v>3580000</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>5594550</v>
-      </c>
-      <c r="I94" s="6" t="n">
-        <v>5712330</v>
-      </c>
-      <c r="J94" s="6" t="n">
         <v>5889000</v>
       </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -7501,12 +7629,12 @@
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O94" s="6" t="n">
@@ -7550,39 +7678,43 @@
       <c r="E95" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F95" s="8" t="n">
-        <v>24750000</v>
+      <c r="F95" s="5" t="n">
+        <v>24900000</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>21490000</v>
+        <v>19800000</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>23500000</v>
+        <v>21000000</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>23990000</v>
-      </c>
-      <c r="J95" s="6" t="n">
-        <v>24800000</v>
-      </c>
-      <c r="K95" s="6" t="n">
-        <v>25000000</v>
+        <v>21350000</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>27700000</v>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>27600000</v>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+3,550,000 ت از رتبه 3 ترب (+16.6%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>24750000</v>
+        <v>24900000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7622,14 +7754,16 @@
       <c r="E96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F96" s="8" t="n">
-        <v>5040000</v>
+      <c r="F96" s="5" t="n">
+        <v>5130000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
       </c>
-      <c r="H96" s="6" t="n">
-        <v>5070000</v>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -7651,18 +7785,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M96" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+630,000 ت از رتبه 1 ترب (+14.0%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5040000</v>
+        <v>5130000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7706,7 +7840,7 @@
         <v>9550000</v>
       </c>
       <c r="G97" s="6" t="n">
-        <v>9500000</v>
+        <v>7200000</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
@@ -7740,7 +7874,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 1 ترب (+0.5%)</t>
+          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
         </is>
       </c>
       <c r="O97" s="6" t="n">
@@ -7784,14 +7918,14 @@
       <c r="E98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="F98" s="8" t="n">
+      <c r="F98" s="5" t="n">
         <v>11000000</v>
       </c>
       <c r="G98" s="6" t="n">
-        <v>11000000</v>
+        <v>7990000</v>
       </c>
       <c r="H98" s="6" t="n">
-        <v>14900000</v>
+        <v>9000000</v>
       </c>
       <c r="I98" s="6" t="n">
         <v>10950000</v>
@@ -7809,14 +7943,14 @@
       <c r="L98" s="6" t="n">
         <v>9300000</v>
       </c>
-      <c r="M98" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O98" s="6" t="n">
@@ -7860,39 +7994,43 @@
       <c r="E99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="8" t="n">
-        <v>4475000</v>
+      <c r="F99" s="5" t="n">
+        <v>4486000</v>
       </c>
       <c r="G99" s="6" t="n">
-        <v>3889253</v>
+        <v>3290000</v>
       </c>
       <c r="H99" s="6" t="n">
-        <v>4450000</v>
+        <v>3700000</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>4480000</v>
-      </c>
-      <c r="J99" s="6" t="n">
-        <v>4489000</v>
-      </c>
-      <c r="K99" s="6" t="n">
-        <v>4489000</v>
+        <v>3890000</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L99" s="6" t="n">
         <v>4703670</v>
       </c>
-      <c r="M99" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+596,000 ت از رتبه 3 ترب (+15.3%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4475000</v>
+        <v>4486000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -7938,10 +8076,10 @@
         </is>
       </c>
       <c r="G100" s="6" t="n">
-        <v>3680000</v>
+        <v>3580000</v>
       </c>
       <c r="H100" s="6" t="n">
-        <v>5989000</v>
+        <v>3200000</v>
       </c>
       <c r="I100" s="6" t="n">
         <v>3580000</v>
@@ -8018,19 +8156,25 @@
         </is>
       </c>
       <c r="G101" s="6" t="n">
-        <v>1890000</v>
+        <v>2900000</v>
       </c>
       <c r="H101" s="6" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="I101" s="6" t="n">
-        <v>8999000</v>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>10900000</v>
-      </c>
-      <c r="K101" s="6" t="n">
-        <v>11230000</v>
+        <v>3100000</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L101" s="6" t="n">
         <v>3200000</v>
@@ -8083,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8120,7 +8264,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -8244,19 +8388,23 @@
         <v>4540000</v>
       </c>
       <c r="G104" s="6" t="n">
-        <v>4200000</v>
+        <v>3750000</v>
       </c>
       <c r="H104" s="6" t="n">
-        <v>4400000</v>
+        <v>3800000</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="J104" s="6" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="K104" s="6" t="n">
-        <v>4499000</v>
+        <v>3855000</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L104" s="6" t="n">
         <v>5200000</v>
@@ -8268,7 +8416,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+41,000 ت از رتبه 5 ترب (+0.9%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
@@ -8318,19 +8466,23 @@
         </is>
       </c>
       <c r="G105" s="6" t="n">
-        <v>2900000</v>
+        <v>4000000</v>
       </c>
       <c r="H105" s="6" t="n">
-        <v>4400000</v>
+        <v>4200000</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J105" s="6" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="K105" s="6" t="n">
-        <v>4900000</v>
+        <v>4699000</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L105" s="6" t="n">
         <v>8100000</v>
@@ -8558,19 +8710,23 @@
         </is>
       </c>
       <c r="G108" s="6" t="n">
-        <v>9950000</v>
+        <v>7560000</v>
       </c>
       <c r="H108" s="6" t="n">
-        <v>10700000</v>
+        <v>9500000</v>
       </c>
       <c r="I108" s="6" t="n">
-        <v>10800000</v>
-      </c>
-      <c r="J108" s="6" t="n">
-        <v>13490000</v>
-      </c>
-      <c r="K108" s="6" t="n">
-        <v>14900000</v>
+        <v>9699000</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L108" s="6" t="n">
         <v>14550000</v>
@@ -8624,11 +8780,11 @@
       <c r="E109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F109" s="11" t="n">
+      <c r="F109" s="8" t="n">
         <v>2250000</v>
       </c>
       <c r="G109" s="6" t="n">
-        <v>2550000</v>
+        <v>2250000</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
@@ -8655,14 +8811,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M109" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-300,000 ت از کف ترب (-11.8%)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="O109" s="6" t="n">
@@ -8708,10 +8864,12 @@
         </is>
       </c>
       <c r="G110" s="6" t="n">
-        <v>3680000</v>
-      </c>
-      <c r="H110" s="6" t="n">
-        <v>5989000</v>
+        <v>3580000</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -8962,19 +9120,23 @@
         </is>
       </c>
       <c r="G113" s="6" t="n">
-        <v>5850000</v>
+        <v>5900000</v>
       </c>
       <c r="H113" s="6" t="n">
-        <v>6150000</v>
+        <v>6000000</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="J113" s="6" t="n">
-        <v>6992000</v>
-      </c>
-      <c r="K113" s="6" t="n">
-        <v>7800000</v>
+        <v>6450000</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L113" s="6" t="n">
         <v>7900000</v>
@@ -9036,19 +9198,23 @@
         </is>
       </c>
       <c r="G114" s="6" t="n">
-        <v>9320000</v>
+        <v>9000000</v>
       </c>
       <c r="H114" s="6" t="n">
-        <v>9400000</v>
+        <v>9100000</v>
       </c>
       <c r="I114" s="6" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="J114" s="6" t="n">
-        <v>9700000</v>
-      </c>
-      <c r="K114" s="6" t="n">
-        <v>9800000</v>
+        <v>9790000</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L114" s="6" t="n">
         <v>11544740</v>
@@ -9110,19 +9276,23 @@
         </is>
       </c>
       <c r="G115" s="6" t="n">
-        <v>8750000</v>
+        <v>8900000</v>
       </c>
       <c r="H115" s="6" t="n">
-        <v>9300000</v>
+        <v>9500000</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>9300000</v>
-      </c>
-      <c r="J115" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K115" s="6" t="n">
-        <v>10250000</v>
+        <v>9800000</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
@@ -9180,39 +9350,43 @@
       <c r="E116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="8" t="n">
-        <v>3501000</v>
+      <c r="F116" s="5" t="n">
+        <v>3615000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
       </c>
       <c r="H116" s="6" t="n">
-        <v>3500000</v>
+        <v>2950000</v>
       </c>
       <c r="I116" s="6" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="J116" s="6" t="n">
-        <v>3549000</v>
-      </c>
-      <c r="K116" s="6" t="n">
-        <v>3597000</v>
+        <v>2988000</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="M116" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>4314600</v>
+      </c>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+627,000 ت از رتبه 3 ترب (+21.0%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3501000</v>
+        <v>3615000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9261,7 +9435,7 @@
         <v>4400000</v>
       </c>
       <c r="H117" s="6" t="n">
-        <v>5500000</v>
+        <v>4900000</v>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -9340,19 +9514,23 @@
         </is>
       </c>
       <c r="G118" s="6" t="n">
+        <v>5248000</v>
+      </c>
+      <c r="H118" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="H118" s="6" t="n">
+      <c r="I118" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="I118" s="6" t="n">
-        <v>6989000</v>
-      </c>
-      <c r="J118" s="6" t="n">
-        <v>6989000</v>
-      </c>
-      <c r="K118" s="6" t="n">
-        <v>7000000</v>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
@@ -9411,22 +9589,26 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>11250000</v>
+        <v>10150000</v>
       </c>
       <c r="G119" s="6" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="H119" s="6" t="n">
         <v>7000000</v>
       </c>
-      <c r="H119" s="6" t="n">
+      <c r="I119" s="6" t="n">
         <v>7489000</v>
       </c>
-      <c r="I119" s="6" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J119" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K119" s="6" t="n">
-        <v>10620000</v>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L119" s="6" t="n">
         <v>13700000</v>
@@ -9438,11 +9620,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+630,000 ت از رتبه 5 ترب (+5.9%)</t>
+          <t>+2,661,000 ت از رتبه 3 ترب (+35.5%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>22500000</v>
+        <v>20300000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9491,16 +9673,20 @@
         <v>5950000</v>
       </c>
       <c r="H120" s="6" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="I120" s="6" t="n">
         <v>6500000</v>
       </c>
-      <c r="I120" s="6" t="n">
-        <v>8140000</v>
-      </c>
-      <c r="J120" s="6" t="n">
-        <v>8900000</v>
-      </c>
-      <c r="K120" s="6" t="n">
-        <v>81400000</v>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
@@ -9640,19 +9826,23 @@
         </is>
       </c>
       <c r="G122" s="6" t="n">
-        <v>11300000</v>
+        <v>10800000</v>
       </c>
       <c r="H122" s="6" t="n">
-        <v>12500000</v>
+        <v>10950000</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="J122" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="K122" s="6" t="n">
-        <v>12650000</v>
+        <v>11000000</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L122" s="6" t="n">
         <v>19500000</v>
@@ -9950,19 +10140,23 @@
         </is>
       </c>
       <c r="G126" s="6" t="n">
-        <v>11300000</v>
+        <v>10800000</v>
       </c>
       <c r="H126" s="6" t="n">
-        <v>12500000</v>
+        <v>10950000</v>
       </c>
       <c r="I126" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="J126" s="6" t="n">
-        <v>12500000</v>
-      </c>
-      <c r="K126" s="6" t="n">
-        <v>12650000</v>
+        <v>11000000</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L126" s="6" t="n">
         <v>19500000</v>
@@ -10506,8 +10700,8 @@
       <c r="E133" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>21750000</v>
+      <c r="F133" s="8" t="n">
+        <v>11440000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -10531,18 +10725,18 @@
       <c r="L133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="M133" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M133" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>+5,550,000 ت از رتبه 3 ترب (+34.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O133" s="6" t="n">
-        <v>108750000</v>
+        <v>57200000</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -511,7 +511,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="43" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="41" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
@@ -636,19 +636,19 @@
         <v>10860000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>9500000</v>
+        <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9900000</v>
+        <v>10500000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>9964340</v>
+        <v>10500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10200000</v>
+        <v>10581600</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10500000</v>
+        <v>10700000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12000000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+360,000 ت از رتبه 5 ترب (+3.4%)</t>
+          <t>+160,000 ت از رتبه 5 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>19690000</v>
+        <v>19640000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>17760000</v>
@@ -717,13 +717,13 @@
         <v>19590000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19690000</v>
+        <v>19640000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>19990000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>20590000</v>
+        <v>21190000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1240470000</v>
+        <v>1237320000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16290000</v>
+        <v>16260000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14980000</v>
@@ -789,7 +789,7 @@
         <v>16245000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>16290000</v>
+        <v>16260000</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>16650000</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>488700000</v>
+        <v>487800000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5840000</v>
+        <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5149000</v>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.7%)</t>
+          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>99280000</v>
+        <v>104550000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -920,14 +920,14 @@
       <c r="E6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="8" t="n">
         <v>7990000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>7350000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>6450000</v>
+        <v>9500000</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>6500000</v>
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9494730</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9561330</v>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>+640,000 ت از رتبه 3 ترب (+8.7%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -997,22 +997,22 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4880000</v>
+        <v>4910000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4200000</v>
+        <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4599936</v>
+        <v>4695000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4695000</v>
+        <v>4700000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+185,000 ت از رتبه 5 ترب (+3.9%)</t>
+          <t>+210,000 ت از رتبه 5 ترب (+4.5%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>73200000</v>
+        <v>73650000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1160,13 +1160,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>129600</v>
+        <v>130810</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1219,19 +1219,19 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9570000</v>
+        <v>9480000</v>
       </c>
       <c r="G10" s="6" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>9400000</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>9570000</v>
-      </c>
       <c r="J10" s="6" t="n">
-        <v>9800000</v>
+        <v>9480000</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>9800000</v>
@@ -1241,16 +1241,16 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>95700000</v>
+        <v>94800000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7755000</v>
+        <v>10120000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+155,000 ت از رتبه 3 ترب (+2.0%)</t>
+          <t>+2,520,000 ت از رتبه 3 ترب (+33.2%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>15510000</v>
+        <v>20240000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1366,35 +1366,35 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="11" t="n">
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4600000</v>
+        <v>5199000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5199000</v>
+        <v>5200000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5200000</v>
+        <v>5400000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5400000</v>
+        <v>5600000</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>5690000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>6000000</v>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-249,000 ت از کف ترب (-4.8%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1449,7 +1449,7 @@
         <v>13900000</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>15330000</v>
+        <v>15000000</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>17880000</v>
@@ -1510,16 +1510,16 @@
         <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11670000</v>
+        <v>13310000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11670000</v>
+        <v>14590000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>11670000</v>
+        <v>14590000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21300000</v>
+        <v>21000000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+8,180,000 ت از رتبه 5 ترب (+70.1%)</t>
+          <t>+5,260,000 ت از رتبه 5 ترب (+36.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1573,7 +1573,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>7299000</v>
+        <v>7299500</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6200000</v>
@@ -1588,7 +1588,7 @@
         <v>7297000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7299000</v>
+        <v>7299500</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>8113910</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>36495000</v>
+        <v>36497500</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1873,19 +1873,19 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9570000</v>
+        <v>9480000</v>
       </c>
       <c r="G19" s="6" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>9400000</v>
       </c>
-      <c r="H19" s="6" t="n">
-        <v>9500000</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>9570000</v>
-      </c>
       <c r="J19" s="6" t="n">
-        <v>9800000</v>
+        <v>9480000</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>9800000</v>
@@ -1895,16 +1895,16 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>95700000</v>
+        <v>94800000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>21320000</v>
+        <v>19277950</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>11440000</v>
+        <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7490000</v>
@@ -2201,16 +2201,16 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
-        <v>57200000</v>
+        <v>108750000</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
@@ -2251,38 +2251,38 @@
         <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>6950000</v>
+        <v>6870000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>6440000</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>6790000</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="J24" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>6990000</v>
       </c>
-      <c r="K24" s="6" t="n">
-        <v>6999000</v>
-      </c>
       <c r="L24" s="6" t="n">
-        <v>7783800</v>
+        <v>6160800</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>34750000</v>
+        <v>34350000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>8400000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>14700000</v>
+        <v>15000000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>5282000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6450000</v>
+        <v>6350000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2778,19 +2778,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>13899000</v>
+        <v>13799000</v>
       </c>
       <c r="H31" s="6" t="n">
+        <v>13800000</v>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>13900000</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>14000000</v>
-      </c>
       <c r="J31" s="6" t="n">
-        <v>14490000</v>
+        <v>14290000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14820000</v>
+        <v>14300000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -3006,13 +3006,13 @@
         <v>9440000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9889000</v>
+        <v>9440000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>9889000</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>14160000</v>
+        <v>9889000</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3131,10 +3131,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>9090000</v>
+        <v>10100000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>7489000</v>
@@ -3158,11 +3158,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,590,000 ت از رتبه 5 ترب (+21.2%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>18180000</v>
+        <v>20200000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>9090000</v>
+        <v>10100000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6950000</v>
+        <v>7300000</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>7489000</v>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,590,000 ت از رتبه 5 ترب (+21.2%)</t>
+          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>18180000</v>
+        <v>20200000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17999750</v>
+        <v>17999875</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>17750000</v>
@@ -3284,7 +3284,7 @@
         <v>17999000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17999750</v>
+        <v>17999875</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>18000000</v>
@@ -3293,7 +3293,7 @@
         <v>18500000</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>16790000</v>
+        <v>17790000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>35999500</v>
+        <v>35999750</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3347,22 +3347,22 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4880000</v>
+        <v>4910000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4000000</v>
+        <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4200000</v>
+        <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4599936</v>
+        <v>4695000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4695000</v>
+        <v>4700000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3374,11 +3374,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+185,000 ت از رتبه 5 ترب (+3.9%)</t>
+          <t>+210,000 ت از رتبه 5 ترب (+4.5%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>73200000</v>
+        <v>73650000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3666,17 +3666,13 @@
         <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7500000</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8064550</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8480000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3820,17 +3816,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3847,14 +3843,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3896,39 +3892,35 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>1210000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>2839550</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4080000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>4350000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+450,000 ت از رتبه 5 ترب (+10.3%)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3968,43 +3960,39 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="8" t="n">
+        <v>6870000</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>6440000</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>6790000</v>
+      </c>
+      <c r="J47" s="6" t="n">
         <v>6950000</v>
       </c>
-      <c r="G47" s="6" t="n">
-        <v>5616000</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>5650000</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="K47" s="6" t="n">
+        <v>6990000</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>7783800</v>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>6160800</v>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,252,000 ت از رتبه 3 ترب (+22.0%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13900000</v>
+        <v>13740000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4044,43 +4032,39 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>11650000</v>
+      <c r="F48" s="8" t="n">
+        <v>12470000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>8700000</v>
+        <v>12100000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>8900000</v>
+        <v>12450000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12470000</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>12499000</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>12500000</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>14450000</v>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+2,550,000 ت از رتبه 3 ترب (+28.0%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>23300000</v>
+        <v>24940000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4124,23 +4108,19 @@
         <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3140000</v>
+        <v>14000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>3149000</v>
+        <v>15000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>15000</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>3499000</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>4600000</v>
@@ -4152,7 +4132,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>+896,000 ت از رتبه 5 ترب (+25.6%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4196,45 +4176,41 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>9450500</v>
+      <c r="F50" s="8" t="n">
+        <v>9420000</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>6690000</v>
+        <v>7999000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>6700000</v>
+        <v>8489000</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>6850000</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>9400000</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>9420000</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>9450000</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M50" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+2,600,500 ت از رتبه 3 ترب (+38.0%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18901000</v>
+        <v>18840000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4274,45 +4250,39 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>17999750</v>
+      <c r="F51" s="8" t="n">
+        <v>17999875</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>11890000</v>
+        <v>17750000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>11900000</v>
+        <v>17999000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>12900000</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>17999875</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>17750000</v>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+5,099,750 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>35999500</v>
+        <v>35999750</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4352,39 +4322,35 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="8" t="n">
         <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>11400000</v>
+        <v>11500000</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>11500000</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12350000</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>12850000</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>18000000</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="M52" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -4428,43 +4394,39 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>10150000</v>
+      <c r="F53" s="8" t="n">
+        <v>10070000</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>6750000</v>
+        <v>7000000</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>7000000</v>
+        <v>7489000</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>7489000</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8000000</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>10070000</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="M53" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+2,661,000 ت از رتبه 3 ترب (+35.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>20300000</v>
+        <v>20140000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4594,23 +4556,19 @@
         <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>7990000</v>
+        <v>399000</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>9000000</v>
+        <v>545000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>10950000</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>650000</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>765000</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>890000</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>9300000</v>
@@ -4622,7 +4580,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+10,110,000 ت از رتبه 5 ترب (+1136.0%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -4667,7 +4625,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10540000</v>
+        <v>10590000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4700,11 +4658,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,590,000 ت از رتبه 3 ترب (+77.1%)</t>
+          <t>+4,640,000 ت از رتبه 3 ترب (+78.0%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>21080000</v>
+        <v>21180000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4841,7 +4799,7 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>9900000</v>
+        <v>8990000</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
@@ -4995,7 +4953,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7270000</v>
+        <v>7600000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5151,7 +5109,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5990000</v>
+        <v>6000000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5307,7 +5265,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6450000</v>
+        <v>6350000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5995,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4486000</v>
+        <v>4489000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6026,11 +5984,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+596,000 ت از رتبه 3 ترب (+15.3%)</t>
+          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4486000</v>
+        <v>4489000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6671,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6040000</v>
+        <v>6070000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6704,11 +6662,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+90,000 ت از رتبه 2 ترب (+1.5%)</t>
+          <t>+120,000 ت از رتبه 2 ترب (+2.0%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6040000</v>
+        <v>6070000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6749,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>24210000</v>
+        <v>24850000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6780,11 +6738,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+12,410,000 ت از رتبه 3 ترب (+105.2%)</t>
+          <t>+13,050,000 ت از رتبه 3 ترب (+110.6%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>24210000</v>
+        <v>24850000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6825,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2642000</v>
+        <v>2641000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6856,11 +6814,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+197,000 ت از رتبه 3 ترب (+8.1%)</t>
+          <t>+196,000 ت از رتبه 3 ترب (+8.0%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2642000</v>
+        <v>2641000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -7059,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>8270000</v>
+        <v>7990000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -7096,11 +7054,11 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>+4,070,000 ت از رتبه 1 ترب (+96.9%)</t>
+          <t>+3,790,000 ت از رتبه 1 ترب (+90.2%)</t>
         </is>
       </c>
       <c r="O87" s="6" t="n">
-        <v>8270000</v>
+        <v>7990000</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
@@ -7219,7 +7177,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>9090000</v>
+        <v>10100000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7250,11 +7208,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+2,140,000 ت از رتبه 3 ترب (+30.8%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>18180000</v>
+        <v>20200000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7295,7 +7253,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>9090000</v>
+        <v>10100000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7326,11 +7284,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+2,140,000 ت از رتبه 3 ترب (+30.8%)</t>
+          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>18180000</v>
+        <v>20200000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7393,7 +7351,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5990000</v>
+        <v>6000000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7447,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3615000</v>
+        <v>3710000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7469,7 +7427,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4314600</v>
+        <v>4300000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7478,11 +7436,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+627,000 ت از رتبه 3 ترب (+21.0%)</t>
+          <t>+722,000 ت از رتبه 3 ترب (+24.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3615000</v>
+        <v>3710000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7523,7 +7481,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7894000</v>
+        <v>7885000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7554,11 +7512,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+974,000 ت از رتبه 3 ترب (+14.1%)</t>
+          <t>+965,000 ت از رتبه 3 ترب (+13.9%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7894000</v>
+        <v>7885000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7755,7 +7713,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5130000</v>
+        <v>5160000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7792,11 +7750,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+630,000 ت از رتبه 1 ترب (+14.0%)</t>
+          <t>+660,000 ت از رتبه 1 ترب (+14.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5130000</v>
+        <v>5160000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7995,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4486000</v>
+        <v>4489000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8026,11 +7984,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+596,000 ت از رتبه 3 ترب (+15.3%)</t>
+          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4486000</v>
+        <v>4489000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -9351,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3615000</v>
+        <v>3710000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9373,7 +9331,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4314600</v>
+        <v>4300000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9382,11 +9340,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+627,000 ت از رتبه 3 ترب (+21.0%)</t>
+          <t>+722,000 ت از رتبه 3 ترب (+24.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3615000</v>
+        <v>3710000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9547,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>10150000</v>
+        <v>10070000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9620,11 +9578,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+2,661,000 ت از رتبه 3 ترب (+35.5%)</t>
+          <t>+2,581,000 ت از رتبه 3 ترب (+34.5%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>20300000</v>
+        <v>20140000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -10700,8 +10658,8 @@
       <c r="E133" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>11440000</v>
+      <c r="F133" s="5" t="n">
+        <v>21750000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -10725,18 +10683,18 @@
       <c r="L133" s="6" t="n">
         <v>7652540</v>
       </c>
-      <c r="M133" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+5,550,000 ت از رتبه 3 ترب (+34.3%)</t>
         </is>
       </c>
       <c r="O133" s="6" t="n">
-        <v>57200000</v>
+        <v>108750000</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -511,7 +511,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="43" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
     <col width="50" customWidth="1" min="17" max="17"/>
@@ -639,19 +639,19 @@
         <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10500000</v>
+        <v>10300000</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>10500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10581600</v>
+        <v>10500000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10700000</v>
+        <v>10500000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>12000000</v>
+        <v>11950000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+160,000 ت از رتبه 5 ترب (+1.5%)</t>
+          <t>+360,000 ت از رتبه 5 ترب (+3.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -714,25 +714,25 @@
         <v>19429693</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19590000</v>
+        <v>19640000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19640000</v>
+        <v>19990000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>19990000</v>
+        <v>20000000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>21190000</v>
+        <v>18490000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -786,10 +786,10 @@
         <v>15390000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16245000</v>
+        <v>16260000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>16260000</v>
+        <v>16330500</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>16650000</v>
@@ -799,12 +799,12 @@
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -852,16 +852,16 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5149000</v>
+        <v>5200000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5200000</v>
+        <v>5690000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5690000</v>
+        <v>5700000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5700000</v>
+        <v>5790000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>5800000</v>
@@ -1160,13 +1160,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>116379</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>129600</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>130810</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1225,28 +1225,28 @@
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9380000</v>
+        <v>9400000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9400000</v>
+        <v>9480000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9480000</v>
+        <v>9800000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9800000</v>
+        <v>9880000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>9450000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1510,16 +1510,16 @@
         <v>11600000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>13310000</v>
+        <v>13300000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>14590000</v>
+        <v>13300000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>14590000</v>
+        <v>13300000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21000000</v>
+        <v>21200000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+5,260,000 ت از رتبه 5 ترب (+36.1%)</t>
+          <t>+6,550,000 ت از رتبه 5 ترب (+49.2%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1579,28 +1579,28 @@
         <v>6200000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7284000</v>
+        <v>7290000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7290000</v>
+        <v>7299500</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7297000</v>
+        <v>7300000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7299500</v>
+        <v>7399000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8113910</v>
+        <v>9300000</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1644,35 +1644,35 @@
       <c r="E16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="11" t="n">
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>4600000</v>
+        <v>5000000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>5000000</v>
+        <v>5300000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5400000</v>
+        <v>5445000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5445000</v>
+        <v>5500000</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5500000</v>
+        <v>5597000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>4900000</v>
       </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-380,000 ت از کف ترب (-7.6%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1802,16 +1802,16 @@
         <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>9420000</v>
+        <v>9500000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>9500000</v>
+        <v>9800000</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>12500000</v>
+        <v>14500000</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>18000000</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -1879,28 +1879,28 @@
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9380000</v>
+        <v>9400000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9400000</v>
+        <v>9480000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9480000</v>
+        <v>9800000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9800000</v>
+        <v>9880000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>9450000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>19277950</v>
+        <v>16057670</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>13300000</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>30200000</v>
+        <v>40200000</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>7652540</v>
@@ -2251,16 +2251,16 @@
         <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>6870000</v>
+        <v>6920000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6440000</v>
+        <v>6597000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6597000</v>
+        <v>6790000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6790000</v>
+        <v>6900000</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>6950000</v>
@@ -2269,7 +2269,7 @@
         <v>6990000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>6160800</v>
+        <v>8299000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>34350000</v>
+        <v>34600000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2334,13 +2334,13 @@
         <v>6900000</v>
       </c>
       <c r="I25" s="6" t="n">
+        <v>6980000</v>
+      </c>
+      <c r="J25" s="6" t="n">
         <v>7500000</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>8200000</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>8400000</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>15000000</v>
@@ -2478,15 +2478,13 @@
         <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>17900000</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>20600000</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2641,7 +2639,7 @@
         <v>5282000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6350000</v>
+        <v>6950000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2855,7 +2853,7 @@
         <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>12500000</v>
+        <v>11800000</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>12500000</v>
@@ -2864,7 +2862,7 @@
         <v>12500000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12650000</v>
+        <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>19500000</v>
@@ -3134,13 +3132,13 @@
         <v>10100000</v>
       </c>
       <c r="G36" s="6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>7300000</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="6" t="n">
         <v>7489000</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="J36" s="6" t="n">
         <v>7500000</v>
@@ -3206,13 +3204,13 @@
         <v>10100000</v>
       </c>
       <c r="G37" s="6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>7300000</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="6" t="n">
         <v>7489000</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="J37" s="6" t="n">
         <v>7500000</v>
@@ -3281,28 +3279,28 @@
         <v>17750000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17999000</v>
+        <v>17999875</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17999875</v>
+        <v>18000000</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>18000000</v>
+        <v>18500000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>18500000</v>
+        <v>19000000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3430,15 +3428,13 @@
         <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="J40" s="6" t="n">
         <v>17900000</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>20600000</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3663,10 +3659,10 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7500000</v>
+        <v>8000000</v>
       </c>
       <c r="J43" s="6" t="n">
         <v>8064550</v>
@@ -3816,17 +3812,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7600000</v>
+        <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7615000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3843,14 +3839,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3892,35 +3888,39 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>1210000</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>2839550</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4080000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>4350000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>+450,000 ت از رتبه 5 ترب (+10.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3960,39 +3960,43 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>6870000</v>
+      <c r="F47" s="5" t="n">
+        <v>6920000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>6440000</v>
+        <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6597000</v>
+        <v>5650000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6790000</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>6990000</v>
+        <v>5698000</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>6160800</v>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>8299000</v>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+1,222,000 ت از رتبه 3 ترب (+21.4%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13740000</v>
+        <v>13840000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4032,39 +4036,43 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>12470000</v>
+      <c r="F48" s="5" t="n">
+        <v>12480000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>12100000</v>
+        <v>8700000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>12450000</v>
+        <v>8900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>12470000</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>12499000</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>12500000</v>
+        <v>9100000</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L48" s="6" t="n">
         <v>14450000</v>
       </c>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+3,380,000 ت از رتبه 3 ترب (+37.1%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>24940000</v>
+        <v>24960000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4108,19 +4116,23 @@
         <v>4395000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>14000</v>
+        <v>3140000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15000</v>
+        <v>3149000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>3499000</v>
+        <v>3150000</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L49" s="6" t="n">
         <v>4600000</v>
@@ -4132,7 +4144,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+896,000 ت از رتبه 5 ترب (+25.6%)</t>
+          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4176,37 +4188,41 @@
       <c r="E50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="5" t="n">
         <v>9420000</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>7999000</v>
+        <v>6690000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>8489000</v>
+        <v>6700000</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>9400000</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>9420000</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>9450000</v>
+        <v>6850000</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+2,570,000 ت از رتبه 3 ترب (+37.5%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -4250,35 +4266,39 @@
       <c r="E51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="F51" s="5" t="n">
         <v>17999875</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>17750000</v>
+        <v>11890000</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>17999000</v>
+        <v>11900000</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>17999875</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>18500000</v>
+        <v>12900000</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L51" s="6" t="n">
         <v>17750000</v>
       </c>
-      <c r="M51" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+5,099,875 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -4322,35 +4342,39 @@
       <c r="E52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="5" t="n">
         <v>12350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
       </c>
       <c r="H52" s="6" t="n">
+        <v>11400000</v>
+      </c>
+      <c r="I52" s="6" t="n">
         <v>11500000</v>
       </c>
-      <c r="I52" s="6" t="n">
-        <v>12350000</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>12850000</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>18000000</v>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L52" s="6" t="n">
         <v>13000000</v>
       </c>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -4394,35 +4418,39 @@
       <c r="E53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="F53" s="5" t="n">
         <v>10070000</v>
       </c>
       <c r="G53" s="6" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="H53" s="6" t="n">
         <v>7000000</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="I53" s="6" t="n">
         <v>7489000</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>10070000</v>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L53" s="6" t="n">
         <v>13700000</v>
       </c>
-      <c r="M53" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+2,581,000 ت از رتبه 3 ترب (+34.5%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -4556,19 +4584,23 @@
         <v>11000000</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>399000</v>
+        <v>7990000</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>545000</v>
+        <v>9000000</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>650000</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>765000</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>890000</v>
+        <v>10950000</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L55" s="6" t="n">
         <v>9300000</v>
@@ -4580,7 +4612,7 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+10,110,000 ت از رتبه 5 ترب (+1136.0%)</t>
+          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -4953,7 +4985,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7600000</v>
+        <v>7229990</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5109,7 +5141,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>6000000</v>
+        <v>5990000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5265,7 +5297,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6350000</v>
+        <v>6950000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5577,7 +5609,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4260710</v>
+        <v>4176870</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -6575,7 +6607,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8113910</v>
+        <v>9300000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -7351,7 +7383,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>6000000</v>
+        <v>5990000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7503,7 +7535,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8550000</v>
+        <v>8044480</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -9175,7 +9207,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11544740</v>
+        <v>11533150</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -708,31 +708,31 @@
         <v>19640000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>17760000</v>
+        <v>18490000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>19429693</v>
+        <v>19640000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19640000</v>
+        <v>19990000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>19990000</v>
+        <v>20000000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20000000</v>
+        <v>20130500</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -783,28 +783,28 @@
         <v>14980000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>15390000</v>
+        <v>16260000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16260000</v>
+        <v>16330500</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>16330500</v>
+        <v>16650000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>16650000</v>
+        <v>17028000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -852,22 +852,22 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5200000</v>
+        <v>5100000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5690000</v>
       </c>
       <c r="I5" s="6" t="n">
+        <v>5690000</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>5700000</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>5790000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>6800000</v>
+        <v>6850000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9561330</v>
+        <v>9559820</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="8" t="n">
         <v>4910000</v>
       </c>
       <c r="G7" s="6" t="n">
@@ -1009,22 +1009,22 @@
         <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4695000</v>
+        <v>4700000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4700000</v>
+        <v>4910000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+210,000 ت از رتبه 5 ترب (+4.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1231,13 +1231,13 @@
         <v>9480000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9800000</v>
+        <v>9880000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9880000</v>
+        <v>9999000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9450000</v>
+        <v>10950000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1299,8 +1299,10 @@
       <c r="H11" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="I11" s="6" t="n">
-        <v>7600000</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1322,7 +1324,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+2,520,000 ت از رتبه 3 ترب (+33.2%)</t>
+          <t>+2,520,000 ت از رتبه 2 ترب (+33.2%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1385,7 +1387,7 @@
         <v>5690000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>6000000</v>
+        <v>5900000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1519,7 +1521,7 @@
         <v>13300000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21200000</v>
+        <v>22719520</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1591,7 +1593,7 @@
         <v>7399000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>9300000</v>
+        <v>8690000</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -1663,7 +1665,7 @@
         <v>5597000</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>4900000</v>
+        <v>5900000</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -1885,13 +1887,13 @@
         <v>9480000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9800000</v>
+        <v>9880000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9880000</v>
+        <v>9999000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9450000</v>
+        <v>10950000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -2031,8 +2033,10 @@
       <c r="H21" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="I21" s="6" t="n">
-        <v>7600000</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2054,7 +2058,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+40,000 ت از رتبه 2 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -2125,7 +2129,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16057670</v>
+        <v>18500000</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2194,10 +2198,10 @@
         <v>13300000</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>40200000</v>
+        <v>30200000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>7652540</v>
+        <v>7600000</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
@@ -2254,31 +2258,31 @@
         <v>6920000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6597000</v>
+        <v>6790000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6790000</v>
+        <v>6900000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6900000</v>
+        <v>6950000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6950000</v>
+        <v>6990000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>6990000</v>
+        <v>6999000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>8299000</v>
+        <v>9333000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2331,19 +2335,19 @@
         <v>6500000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6900000</v>
+        <v>6980000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6980000</v>
+        <v>7500000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7500000</v>
+        <v>8200000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8200000</v>
+        <v>8800000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15000000</v>
+        <v>17000000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2478,13 +2482,15 @@
         <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>15500000</v>
+        <v>17900000</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>17900000</v>
-      </c>
-      <c r="K27" s="6" t="n">
         <v>20600000</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2639,7 +2645,7 @@
         <v>5282000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6950000</v>
+        <v>6649000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2782,13 +2788,13 @@
         <v>13800000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13900000</v>
+        <v>14300000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>14290000</v>
+        <v>14820000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14300000</v>
+        <v>14900000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -3344,7 +3350,7 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="8" t="n">
         <v>4910000</v>
       </c>
       <c r="G39" s="6" t="n">
@@ -3357,22 +3363,22 @@
         <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4695000</v>
+        <v>4700000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4700000</v>
+        <v>4910000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+210,000 ت از رتبه 5 ترب (+4.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3428,13 +3434,15 @@
         <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15500000</v>
+        <v>17900000</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>17900000</v>
-      </c>
-      <c r="K40" s="6" t="n">
         <v>20600000</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3576,7 +3584,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4150000</v>
+        <v>3150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3659,16 +3667,20 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7500000</v>
+        <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8064550</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>8480000</v>
+        <v>7289000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3995,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>8299000</v>
+        <v>9333000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -4985,7 +4997,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7229990</v>
+        <v>7500000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5141,7 +5153,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5990000</v>
+        <v>6000000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5297,7 +5309,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6950000</v>
+        <v>6649000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -6607,7 +6619,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>9300000</v>
+        <v>8690000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -7383,7 +7395,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5990000</v>
+        <v>6000000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7459,7 +7471,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4300000</v>
+        <v>4270000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -9207,7 +9219,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11533150</v>
+        <v>11841910</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9363,7 +9375,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4300000</v>
+        <v>4270000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -10713,7 +10725,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="n">
-        <v>7652540</v>
+        <v>7600000</v>
       </c>
       <c r="M133" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -633,16 +633,16 @@
         <v>188</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>10860000</v>
+        <v>13410000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="I2" s="6" t="n">
         <v>10300000</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>10500000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>10500000</v>
@@ -660,11 +660,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+360,000 ت از رتبه 5 ترب (+3.4%)</t>
+          <t>+2,910,000 ت از رتبه 5 ترب (+27.7%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2041680000</v>
+        <v>2521080000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -705,38 +705,38 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>19640000</v>
+        <v>19997000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>19640000</v>
+        <v>19990000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19990000</v>
+        <v>19997000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20000000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20130500</v>
+        <v>20131000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1237320000</v>
+        <v>1259811000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,38 +777,38 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16260000</v>
+        <v>17050000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>14980000</v>
+        <v>16331000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>16260000</v>
+        <v>16650000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16330500</v>
+        <v>17028000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>16650000</v>
+        <v>17050000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>17028000</v>
+        <v>17190000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>487800000</v>
+        <v>511500000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,22 +849,22 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6150000</v>
+        <v>6030000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5100000</v>
+        <v>5400000</v>
       </c>
       <c r="H5" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>5679000</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>5680000</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>5690000</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>5690000</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>5700000</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>6850000</v>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
+          <t>+340,000 ت از رتبه 5 ترب (+6.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>104550000</v>
+        <v>102510000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -996,8 +996,8 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>4910000</v>
+      <c r="F7" s="5" t="n">
+        <v>5070000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1012,23 +1012,23 @@
         <v>4700000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4910000</v>
+        <v>4950000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+120,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>73650000</v>
+        <v>76050000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1160,13 +1160,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>101200</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>108300</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>116379</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>129600</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1219,7 +1219,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9480000</v>
+        <v>9680000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1228,7 +1228,7 @@
         <v>9400000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9480000</v>
+        <v>9680000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9880000</v>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>94800000</v>
+        <v>96800000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>10120000</v>
+        <v>7710000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1324,11 +1324,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+2,520,000 ت از رتبه 2 ترب (+33.2%)</t>
+          <t>+110,000 ت از رتبه 2 ترب (+1.4%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>20240000</v>
+        <v>15420000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1509,19 +1509,19 @@
         <v>11500000</v>
       </c>
       <c r="H14" s="6" t="n">
+        <v>11599000</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>11599000</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>11599000</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>11600000</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>13300000</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>13300000</v>
-      </c>
       <c r="L14" s="6" t="n">
-        <v>22719520</v>
+        <v>20900000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,550,000 ت از رتبه 5 ترب (+49.2%)</t>
+          <t>+8,250,000 ت از رتبه 5 ترب (+71.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1574,39 +1574,39 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>7299500</v>
+      <c r="F15" s="5" t="n">
+        <v>7700000</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>6200000</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>7283000</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>7290000</v>
       </c>
-      <c r="I15" s="6" t="n">
-        <v>7299500</v>
-      </c>
       <c r="J15" s="6" t="n">
-        <v>7300000</v>
+        <v>7399000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7399000</v>
+        <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8690000</v>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+        <v>8542300</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+300,000 ت از رتبه 5 ترب (+4.1%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>36497500</v>
+        <v>38500000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>12060000</v>
+        <v>13070000</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>12000000</v>
+        <v>13000000</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1756,11 +1756,11 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>+60,000 ت از رتبه 1 ترب (+0.5%)</t>
+          <t>+70,000 ت از رتبه 1 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O17" s="6" t="n">
-        <v>72360000</v>
+        <v>78420000</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9480000</v>
+        <v>9680000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1884,7 +1884,7 @@
         <v>9400000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9480000</v>
+        <v>9680000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9880000</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>94800000</v>
+        <v>96800000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>18500000</v>
+        <v>17584770</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="5" t="n">
         <v>21750000</v>
       </c>
       <c r="G23" s="6" t="n">
@@ -2192,25 +2192,25 @@
         <v>7500000</v>
       </c>
       <c r="I23" s="6" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>9590000</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>13300000</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>30200000</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="M23" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+8,450,000 ت از رتبه 5 ترب (+63.5%)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2255,16 +2255,16 @@
         <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>6920000</v>
+        <v>6994000</v>
       </c>
       <c r="G24" s="6" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>6790000</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="6" t="n">
         <v>6900000</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>6950000</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>6990000</v>
@@ -2273,20 +2273,20 @@
         <v>6999000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9333000</v>
+        <v>9965000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>34600000</v>
+        <v>34970000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2482,15 +2482,13 @@
         <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>17900000</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="6" t="n">
         <v>20600000</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2626,8 +2624,8 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5260000</v>
+      <c r="F29" s="5" t="n">
+        <v>5380000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5190000</v>
@@ -2639,26 +2637,26 @@
         <v>5220000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5260000</v>
+        <v>5282000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5282000</v>
+        <v>5340000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6649000</v>
       </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.7%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21040000</v>
+        <v>21520000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2788,13 +2786,13 @@
         <v>13800000</v>
       </c>
       <c r="I31" s="6" t="n">
+        <v>14290000</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>14300000</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>14820000</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>14900000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2925,7 +2923,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>7140000</v>
+        <v>7020000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
@@ -2937,7 +2935,7 @@
         <v>6999000</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>7140000</v>
+        <v>7020000</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>8000000</v>
@@ -2958,7 +2956,7 @@
         </is>
       </c>
       <c r="O33" s="6" t="n">
-        <v>21420000</v>
+        <v>21060000</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
@@ -3134,8 +3132,8 @@
       <c r="E36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>10100000</v>
+      <c r="F36" s="8" t="n">
+        <v>7491000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>7000000</v>
@@ -3147,26 +3145,26 @@
         <v>7489000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7500000</v>
+        <v>7491000</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7400000</v>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>7950000</v>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>20200000</v>
+        <v>14982000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3206,8 +3204,8 @@
       <c r="E37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>10100000</v>
+      <c r="F37" s="8" t="n">
+        <v>7491000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>7000000</v>
@@ -3219,26 +3217,26 @@
         <v>7489000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7500000</v>
+        <v>7491000</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7400000</v>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>7950000</v>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+2,600,000 ت از رتبه 5 ترب (+34.7%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>20200000</v>
+        <v>14982000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3279,16 +3277,16 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17999875</v>
+        <v>18370000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>17750000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>17999875</v>
+        <v>18000000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>18000000</v>
+        <v>18370000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>18500000</v>
@@ -3301,16 +3299,16 @@
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>35999750</v>
+        <v>36740000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3350,8 +3348,8 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>4910000</v>
+      <c r="F39" s="5" t="n">
+        <v>5070000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3366,23 +3364,23 @@
         <v>4700000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4910000</v>
+        <v>4950000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+120,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>73650000</v>
+        <v>76050000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3434,15 +3432,13 @@
         <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="J40" s="6" t="n">
         <v>17900000</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>20600000</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3584,7 +3580,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3667,20 +3663,16 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8064550</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8480000</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8489000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3973,7 +3965,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>6920000</v>
+        <v>6994000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3995,7 +3987,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9333000</v>
+        <v>9965000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -4004,11 +3996,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,222,000 ت از رتبه 3 ترب (+21.4%)</t>
+          <t>+1,296,000 ت از رتبه 3 ترب (+22.7%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13840000</v>
+        <v>13988000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4049,7 +4041,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12480000</v>
+        <v>12494000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4071,7 +4063,7 @@
         </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>14450000</v>
+        <v>15900000</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
@@ -4080,11 +4072,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,380,000 ت از رتبه 3 ترب (+37.1%)</t>
+          <t>+3,394,000 ت از رتبه 3 ترب (+37.3%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>24960000</v>
+        <v>24988000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4125,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>4395000</v>
+        <v>3499500</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -4147,7 +4139,7 @@
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>4600000</v>
+        <v>4570000</v>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
@@ -4156,11 +4148,11 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+1,245,000 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>+349,500 ت از رتبه 3 ترب (+11.1%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
-        <v>4395000</v>
+        <v>3499500</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -4201,7 +4193,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9420000</v>
+        <v>9405000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4234,11 +4226,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+2,570,000 ت از رتبه 3 ترب (+37.5%)</t>
+          <t>+2,555,000 ت از رتبه 3 ترب (+37.3%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18840000</v>
+        <v>18810000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4279,7 +4271,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17999875</v>
+        <v>18370000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4310,11 +4302,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+5,099,875 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>+5,470,000 ت از رتبه 3 ترب (+42.4%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>35999750</v>
+        <v>36740000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4355,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>12350000</v>
+        <v>16710000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4376,8 +4368,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L52" s="6" t="n">
-        <v>13000000</v>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
@@ -4386,11 +4380,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+850,000 ت از رتبه 3 ترب (+7.4%)</t>
+          <t>+5,210,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>24700000</v>
+        <v>33420000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4425,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>10070000</v>
+        <v>8510000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4462,11 +4456,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+2,581,000 ت از رتبه 3 ترب (+34.5%)</t>
+          <t>+1,021,000 ت از رتبه 3 ترب (+13.6%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>20140000</v>
+        <v>17020000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4593,7 +4587,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>11000000</v>
+        <v>15040000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -4624,11 +4618,11 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
-        <v>33000000</v>
+        <v>45120000</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
@@ -4669,7 +4663,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10590000</v>
+        <v>10690000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4702,11 +4696,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,640,000 ت از رتبه 3 ترب (+78.0%)</t>
+          <t>+4,740,000 ت از رتبه 3 ترب (+79.7%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>21180000</v>
+        <v>21380000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4997,7 +4991,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7500000</v>
+        <v>7350000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5131,7 +5125,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>4999500</v>
+        <v>5200000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5162,11 +5156,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,049,500 ت از رتبه 3 ترب (+26.6%)</t>
+          <t>+1,250,000 ت از رتبه 3 ترب (+31.6%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>9999000</v>
+        <v>10400000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5287,7 +5281,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5260000</v>
+        <v>5380000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5318,11 +5312,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+310,000 ت از رتبه 3 ترب (+6.3%)</t>
+          <t>+430,000 ت از رتبه 3 ترب (+8.7%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21040000</v>
+        <v>21520000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4489000</v>
+        <v>4460000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6028,11 +6022,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
+          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4489000</v>
+        <v>4460000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6149,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>21720000</v>
+        <v>22240000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6180,11 +6174,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,275,000 ت از رتبه 3 ترب (+788.3%)</t>
+          <t>+19,795,000 ت از رتبه 3 ترب (+809.6%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>21720000</v>
+        <v>22240000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6293,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>10750000</v>
+        <v>11750000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6324,11 +6318,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+16.8%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+27.7%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>10750000</v>
+        <v>11750000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6369,7 +6363,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12005000</v>
+        <v>12008000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -6400,11 +6394,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+2,808,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12005000</v>
+        <v>12008000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6521,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15500000</v>
+        <v>15550000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6543,7 +6537,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>30126400</v>
+        <v>25000000</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6552,11 +6546,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+510,000 ت از رتبه 3 ترب (+3.4%)</t>
+          <t>+560,000 ت از رتبه 3 ترب (+3.7%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15500000</v>
+        <v>15550000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6597,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>7950000</v>
+        <v>7590000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -6619,7 +6613,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8690000</v>
+        <v>8542300</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6628,11 +6622,11 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+1,750,000 ت از رتبه 3 ترب (+28.2%)</t>
+          <t>+1,390,000 ت از رتبه 3 ترب (+22.4%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>7950000</v>
+        <v>7590000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -6673,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6070000</v>
+        <v>6130000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6706,11 +6700,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه 2 ترب (+2.0%)</t>
+          <t>+180,000 ت از رتبه 2 ترب (+3.0%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6070000</v>
+        <v>6130000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6751,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>24850000</v>
+        <v>23920000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6782,11 +6776,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+13,050,000 ت از رتبه 3 ترب (+110.6%)</t>
+          <t>+12,120,000 ت از رتبه 3 ترب (+102.7%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>24850000</v>
+        <v>23920000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6827,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2641000</v>
+        <v>2640500</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6858,11 +6852,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+196,000 ت از رتبه 3 ترب (+8.0%)</t>
+          <t>+195,500 ت از رتبه 3 ترب (+8.0%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2641000</v>
+        <v>2640500</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -7061,7 +7055,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>7990000</v>
+        <v>8300000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -7098,11 +7092,11 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>+3,790,000 ت از رتبه 1 ترب (+90.2%)</t>
+          <t>+4,100,000 ت از رتبه 1 ترب (+97.6%)</t>
         </is>
       </c>
       <c r="O87" s="6" t="n">
-        <v>7990000</v>
+        <v>8300000</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
@@ -7221,7 +7215,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>10100000</v>
+        <v>7491000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7243,7 +7237,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7252,11 +7246,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+541,000 ت از رتبه 3 ترب (+7.8%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>20200000</v>
+        <v>14982000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7297,7 +7291,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>10100000</v>
+        <v>7491000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7319,7 +7313,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7328,11 +7322,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+3,150,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+541,000 ت از رتبه 3 ترب (+7.8%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>20200000</v>
+        <v>14982000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7373,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>4999500</v>
+        <v>5200000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7395,7 +7389,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>6000000</v>
+        <v>4582400</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7404,11 +7398,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,049,500 ت از رتبه 3 ترب (+26.6%)</t>
+          <t>+1,250,000 ت از رتبه 3 ترب (+31.6%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>4999500</v>
+        <v>5200000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7449,7 +7443,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3710000</v>
+        <v>3740000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7471,7 +7465,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4270000</v>
+        <v>3324800</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7480,11 +7474,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+722,000 ت از رتبه 3 ترب (+24.2%)</t>
+          <t>+752,000 ت از رتبه 3 ترب (+25.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3710000</v>
+        <v>3740000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7525,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7885000</v>
+        <v>7930000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7547,7 +7541,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8044480</v>
+        <v>8437890</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7556,11 +7550,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+965,000 ت از رتبه 3 ترب (+13.9%)</t>
+          <t>+1,010,000 ت از رتبه 3 ترب (+14.6%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7885000</v>
+        <v>7930000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7601,7 +7595,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5889000</v>
+        <v>5800000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -7640,7 +7634,7 @@
         </is>
       </c>
       <c r="O94" s="6" t="n">
-        <v>5889000</v>
+        <v>5800000</v>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
@@ -7681,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>24900000</v>
+        <v>26670000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7712,11 +7706,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+3,550,000 ت از رتبه 3 ترب (+16.6%)</t>
+          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>24900000</v>
+        <v>26670000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5160000</v>
+        <v>5220000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7794,11 +7788,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+660,000 ت از رتبه 1 ترب (+14.7%)</t>
+          <t>+720,000 ت از رتبه 1 ترب (+16.0%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5160000</v>
+        <v>5220000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7921,7 +7915,7 @@
         <v>3</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>11000000</v>
+        <v>15040000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -7952,11 +7946,11 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
         </is>
       </c>
       <c r="O98" s="6" t="n">
-        <v>33000000</v>
+        <v>45120000</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
@@ -7997,7 +7991,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4489000</v>
+        <v>4460000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8028,11 +8022,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
+          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4489000</v>
+        <v>4460000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8303,7 +8297,7 @@
         <v>6</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>12060000</v>
+        <v>13070000</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -8346,7 +8340,7 @@
         </is>
       </c>
       <c r="O103" s="6" t="n">
-        <v>72360000</v>
+        <v>78420000</v>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
@@ -9353,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3710000</v>
+        <v>3740000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9375,7 +9369,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4270000</v>
+        <v>4350000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9384,11 +9378,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+722,000 ت از رتبه 3 ترب (+24.2%)</t>
+          <t>+752,000 ت از رتبه 3 ترب (+25.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3710000</v>
+        <v>3740000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9591,7 +9585,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>10070000</v>
+        <v>8510000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9622,11 +9616,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+2,581,000 ت از رتبه 3 ترب (+34.5%)</t>
+          <t>+1,021,000 ت از رتبه 3 ترب (+13.6%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>20140000</v>
+        <v>17020000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9975,7 +9969,7 @@
         <v>3</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>7140000</v>
+        <v>7020000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -10012,11 +10006,11 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-2,460,000 ت از کف ترب (-25.6%)</t>
+          <t>-2,580,000 ت از کف ترب (-26.9%)</t>
         </is>
       </c>
       <c r="O124" s="6" t="n">
-        <v>21420000</v>
+        <v>21060000</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
@@ -10301,7 +10295,7 @@
         <v>3</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>11000000</v>
+        <v>15040000</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>7990000</v>
@@ -10332,11 +10326,11 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 3 ترب (+0.5%)</t>
+          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
         </is>
       </c>
       <c r="O128" s="6" t="n">
-        <v>33000000</v>
+        <v>45120000</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -636,22 +636,22 @@
         <v>13410000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10200000</v>
+        <v>10000000</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>10200000</v>
       </c>
       <c r="I2" s="6" t="n">
+        <v>10200000</v>
+      </c>
+      <c r="J2" s="6" t="n">
         <v>10300000</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>10500000</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>10500000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>11950000</v>
+        <v>12100000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         <v>19997000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20000000</v>
+        <v>20131000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20131000</v>
+        <v>20290000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18490000</v>
@@ -780,31 +780,31 @@
         <v>17050000</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>15390000</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>16331000</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>16650000</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>17028000</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>17050000</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>17190000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -858,16 +858,16 @@
         <v>5500000</v>
       </c>
       <c r="I5" s="6" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>5679000</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>5680000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>5690000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>6850000</v>
+        <v>6950000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
         <v>7350000</v>
       </c>
       <c r="H6" s="6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>9500000</v>
       </c>
-      <c r="I6" s="6" t="n">
-        <v>6500000</v>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9559820</v>
+        <v>9697100</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1009,10 +1009,10 @@
         <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
+        <v>4695000</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>4700000</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4950000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+370,000 ت از رتبه 5 ترب (+7.9%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1234,7 +1234,7 @@
         <v>9880000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9999000</v>
+        <v>9900000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>10950000</v>
@@ -1372,22 +1372,22 @@
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5199000</v>
+        <v>5149000</v>
       </c>
       <c r="H12" s="6" t="n">
+        <v>5150000</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>5200000</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>5400000</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>5600000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5690000</v>
+        <v>5600000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5900000</v>
+        <v>5700000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-249,000 ت از کف ترب (-4.8%)</t>
+          <t>-199,000 ت از کف ترب (-3.9%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1506,7 +1506,7 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11500000</v>
+        <v>11599000</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>11599000</v>
@@ -1515,13 +1515,13 @@
         <v>11599000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11599000</v>
+        <v>11600000</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>11600000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>20900000</v>
+        <v>21500000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>6200000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7283000</v>
+        <v>7280000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7290000</v>
+        <v>7399000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7399000</v>
+        <v>7400000</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8542300</v>
+        <v>8200000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1650,22 +1650,22 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5000000</v>
+        <v>5200000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
       <c r="I16" s="6" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>5445000</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>5500000</v>
       </c>
-      <c r="K16" s="6" t="n">
-        <v>5597000</v>
-      </c>
       <c r="L16" s="6" t="n">
-        <v>5900000</v>
+        <v>5800000</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-380,000 ت از کف ترب (-7.6%)</t>
+          <t>-580,000 ت از کف ترب (-11.2%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1890,7 +1890,7 @@
         <v>9880000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9999000</v>
+        <v>9900000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>10950000</v>
@@ -2106,7 +2106,7 @@
         <v>18590000</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>18000000</v>
+        <v>15500000</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17584770</v>
+        <v>17795730</v>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>+590,000 ت از رتبه 1 ترب (+3.3%)</t>
+          <t>+3,090,000 ت از رتبه 1 ترب (+19.9%)</t>
         </is>
       </c>
       <c r="O22" s="6" t="n">
@@ -2267,22 +2267,22 @@
         <v>6900000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6990000</v>
+        <v>6999000</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>6999000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9965000</v>
+        <v>9211000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2643,7 +2643,7 @@
         <v>5340000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6649000</v>
+        <v>6950000</v>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>14300000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14820000</v>
+        <v>14500000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2857,7 +2857,7 @@
         <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>11800000</v>
+        <v>12500000</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>12500000</v>
@@ -2866,10 +2866,10 @@
         <v>12500000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12500000</v>
+        <v>12650000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>19500000</v>
+        <v>19490000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
+        <v>4695000</v>
+      </c>
+      <c r="K39" s="6" t="n">
         <v>4700000</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4950000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+120,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+370,000 ت از رتبه 5 ترب (+7.9%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3432,13 +3432,15 @@
         <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15500000</v>
+        <v>17900000</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>17900000</v>
-      </c>
-      <c r="K40" s="6" t="n">
         <v>20600000</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3816,17 +3818,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3843,14 +3845,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3896,35 +3898,31 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>4140000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4300000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>6950000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3964,39 +3962,35 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="8" t="n">
         <v>6994000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5616000</v>
+        <v>6597000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5650000</v>
+        <v>6790000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6900000</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>6999000</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>6999000</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9965000</v>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9211000</v>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,296,000 ت از رتبه 3 ترب (+22.7%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -4063,7 +4057,7 @@
         </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>15900000</v>
+        <v>15800000</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
@@ -5147,7 +5141,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>6000000</v>
+        <v>5860000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5303,7 +5297,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6649000</v>
+        <v>6950000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -6461,7 +6455,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>5200000</v>
+        <v>5600000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6537,7 +6531,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>25000000</v>
+        <v>22200000</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6613,7 +6607,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8542300</v>
+        <v>8200000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -7389,7 +7383,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>4582400</v>
+        <v>5860000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7465,7 +7459,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>3324800</v>
+        <v>4280000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7541,7 +7535,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8437890</v>
+        <v>8335730</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -8403,7 +8397,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>5200000</v>
+        <v>5600000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -9213,7 +9207,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11841910</v>
+        <v>11391720</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9369,7 +9363,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4350000</v>
+        <v>4280000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9841,7 +9835,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>19500000</v>
+        <v>19490000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10155,7 +10149,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>19500000</v>
+        <v>19490000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -645,7 +645,7 @@
         <v>10200000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10300000</v>
+        <v>10200000</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>10500000</v>
@@ -705,38 +705,38 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>19997000</v>
+        <v>20020000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="H3" s="6" t="n">
+        <v>19784300</v>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>19990000</v>
       </c>
-      <c r="I3" s="6" t="n">
-        <v>19997000</v>
-      </c>
       <c r="J3" s="6" t="n">
+        <v>20020000</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>20131000</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>20290000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1259811000</v>
+        <v>1261260000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -776,39 +776,39 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>17050000</v>
+      <c r="F4" s="5" t="n">
+        <v>16650000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>15390000</v>
+        <v>14990000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>16331000</v>
+        <v>15191000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>16650000</v>
+        <v>15360000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>17028000</v>
+        <v>15700000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>17050000</v>
+        <v>15790000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+860,000 ت از رتبه 5 ترب (+5.4%)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>511500000</v>
+        <v>499500000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,25 +849,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6030000</v>
+        <v>6210000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5400000</v>
+        <v>5679000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5500000</v>
+        <v>5690000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5500000</v>
+        <v>5700000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5679000</v>
+        <v>5700000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5690000</v>
+        <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>6950000</v>
+        <v>6850000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+340,000 ت از رتبه 5 ترب (+6.0%)</t>
+          <t>+410,000 ت از رتبه 5 ترب (+7.1%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>102510000</v>
+        <v>105570000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7990000</v>
+        <v>7999000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>7350000</v>
@@ -930,7 +930,7 @@
         <v>8000000</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9697100</v>
+        <v>9559160</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>135830000</v>
+        <v>135983000</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>5070000</v>
+        <v>4960000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+370,000 ت از رتبه 5 ترب (+7.9%)</t>
+          <t>+260,000 ت از رتبه 5 ترب (+5.5%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>76050000</v>
+        <v>74400000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         <v>101200</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1219,25 +1219,25 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9680000</v>
+        <v>9890000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9400000</v>
+        <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9680000</v>
+        <v>9890000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9900000</v>
+        <v>9999000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>10950000</v>
+        <v>10200000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>96800000</v>
+        <v>98900000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7710000</v>
+        <v>7890000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1299,10 +1299,8 @@
       <c r="H11" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="I11" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1324,11 +1322,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+110,000 ت از رتبه 2 ترب (+1.4%)</t>
+          <t>+290,000 ت از رتبه 3 ترب (+3.8%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>15420000</v>
+        <v>15780000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1385,7 @@
         <v>5600000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5700000</v>
+        <v>5600000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1506,22 +1504,22 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11599000</v>
+        <v>13310000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11599000</v>
+        <v>13490000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11599000</v>
+        <v>13490000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11600000</v>
+        <v>13500000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>11600000</v>
+        <v>13700000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21500000</v>
+        <v>22450000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1530,7 +1528,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+8,250,000 ت از رتبه 5 ترب (+71.1%)</t>
+          <t>+6,150,000 ت از رتبه 5 ترب (+44.9%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1578,7 +1576,7 @@
         <v>7700000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>6200000</v>
+        <v>7273000</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>7280000</v>
@@ -1593,7 +1591,7 @@
         <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8200000</v>
+        <v>9070000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1650,13 +1648,13 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5200000</v>
+        <v>5199000</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>5200000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5200000</v>
+        <v>5350000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>5445000</v>
@@ -1665,7 +1663,7 @@
         <v>5500000</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>5800000</v>
+        <v>5790000</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -1674,7 +1672,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-580,000 ت از کف ترب (-11.2%)</t>
+          <t>-579,000 ت از کف ترب (-11.1%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1875,25 +1873,25 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9680000</v>
+        <v>9890000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9400000</v>
+        <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9680000</v>
+        <v>9890000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9900000</v>
+        <v>9999000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>10950000</v>
+        <v>10200000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -1906,7 +1904,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>96800000</v>
+        <v>98900000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2024,8 +2022,8 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="5" t="n">
-        <v>7640000</v>
+      <c r="F21" s="8" t="n">
+        <v>7450000</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>6799000</v>
@@ -2033,10 +2031,8 @@
       <c r="H21" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="I21" s="6" t="n">
+        <v>7600000</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2051,18 +2047,18 @@
       <c r="L21" s="6" t="n">
         <v>13513760</v>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 2 ترب (+0.5%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
-        <v>38200000</v>
+        <v>37250000</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
@@ -2102,8 +2098,8 @@
       <c r="E22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="5" t="n">
-        <v>18590000</v>
+      <c r="F22" s="11" t="n">
+        <v>14690000</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>15500000</v>
@@ -2131,18 +2127,18 @@
       <c r="L22" s="6" t="n">
         <v>17795730</v>
       </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>+3,090,000 ت از رتبه 1 ترب (+19.9%)</t>
+          <t>-810,000 ت از کف ترب (-5.2%)</t>
         </is>
       </c>
       <c r="O22" s="6" t="n">
-        <v>92950000</v>
+        <v>73450000</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
@@ -2182,8 +2178,8 @@
       <c r="E23" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>21750000</v>
+      <c r="F23" s="8" t="n">
+        <v>11350000</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>7490000</v>
@@ -2195,7 +2191,7 @@
         <v>7500000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>9590000</v>
+        <v>9400000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>13300000</v>
@@ -2203,18 +2199,18 @@
       <c r="L23" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>+8,450,000 ت از رتبه 5 ترب (+63.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
-        <v>108750000</v>
+        <v>56750000</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
@@ -2254,39 +2250,39 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6994000</v>
+      <c r="F24" s="5" t="n">
+        <v>7320000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6597000</v>
+        <v>6790000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6790000</v>
+        <v>6900000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6900000</v>
+        <v>7100000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6999000</v>
+        <v>7100000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>6999000</v>
+        <v>7100000</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>9211000</v>
       </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+220,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>34970000</v>
+        <v>36600000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2406,19 +2402,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
+        <v>8390000</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>8400000</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="6" t="n">
         <v>8499000</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="J26" s="6" t="n">
         <v>8500000</v>
       </c>
-      <c r="J26" s="6" t="n">
-        <v>9000000</v>
-      </c>
       <c r="K26" s="6" t="n">
-        <v>9000000</v>
+        <v>8500000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2476,10 +2472,10 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>12320000</v>
+        <v>10800000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>15500000</v>
+        <v>11000000</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>15500000</v>
@@ -2624,39 +2620,39 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
-        <v>5380000</v>
+      <c r="F29" s="8" t="n">
+        <v>5410000</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>5190000</v>
+        <v>5200000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5200000</v>
+        <v>5220000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5220000</v>
+        <v>5282000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5282000</v>
+        <v>5340000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5340000</v>
+        <v>5410000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>6649000</v>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.7%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21520000</v>
+        <v>21640000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2780,19 +2776,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>13799000</v>
+        <v>12990000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13800000</v>
+        <v>13000000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>14290000</v>
+        <v>13400000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>14300000</v>
+        <v>13700000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>14500000</v>
+        <v>13700000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2857,7 +2853,7 @@
         <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>12500000</v>
+        <v>12497000</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>12500000</v>
@@ -2866,10 +2862,10 @@
         <v>12500000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12650000</v>
+        <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>19490000</v>
+        <v>19290000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2919,7 @@
         <v>3</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>7020000</v>
+        <v>7550000</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>6000000</v>
@@ -2935,7 +2931,7 @@
         <v>6999000</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>7020000</v>
+        <v>7550000</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>8000000</v>
@@ -2956,7 +2952,7 @@
         </is>
       </c>
       <c r="O33" s="6" t="n">
-        <v>21060000</v>
+        <v>22650000</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
@@ -3011,7 +3007,7 @@
         <v>9440000</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9889000</v>
+        <v>9592330</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>9889000</v>
@@ -3136,31 +3132,31 @@
         <v>7491000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>7000000</v>
+        <v>6900000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7300000</v>
+        <v>7491000</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7491000</v>
+        <v>7500000</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7950000</v>
+        <v>7400000</v>
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
@@ -3208,31 +3204,31 @@
         <v>7491000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>7000000</v>
+        <v>6900000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7300000</v>
+        <v>7491000</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>7489000</v>
+        <v>7500000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7491000</v>
+        <v>7500000</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7950000</v>
+        <v>7400000</v>
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
@@ -3276,39 +3272,39 @@
       <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>18370000</v>
+      <c r="F38" s="5" t="n">
+        <v>20250000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>17750000</v>
+        <v>18498000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>18000000</v>
+        <v>18500000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>18370000</v>
+        <v>19000000</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>18500000</v>
+        <v>19500000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19000000</v>
+        <v>19650000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
       </c>
-      <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+600,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>36740000</v>
+        <v>40500000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3349,7 +3345,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>5070000</v>
+        <v>4960000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3376,11 +3372,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+370,000 ت از رتبه 5 ترب (+7.9%)</t>
+          <t>+260,000 ت از رتبه 5 ترب (+5.5%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>76050000</v>
+        <v>74400000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3426,21 +3422,19 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>12320000</v>
+        <v>10800000</v>
       </c>
       <c r="H40" s="6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I40" s="6" t="n">
         <v>15500000</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="J40" s="6" t="n">
         <v>17900000</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="6" t="n">
         <v>20600000</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3671,10 +3665,10 @@
         <v>8064550</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>8480000</v>
+        <v>8489000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8489000</v>
+        <v>8500000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3819,13 +3813,13 @@
         <v>2</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>7615000</v>
+        <v>7750000</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7615000</v>
+        <v>7750000</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>7893100</v>
@@ -3856,7 +3850,7 @@
         </is>
       </c>
       <c r="O45" s="6" t="n">
-        <v>15230000</v>
+        <v>15500000</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -3894,11 +3888,11 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>45500</v>
+        <v>2839550</v>
       </c>
       <c r="H46" s="6" t="n">
         <v>4140000</v>
@@ -3907,22 +3901,22 @@
         <v>4300000</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>6100000</v>
+        <v>4350000</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>6950000</v>
+        <v>4500000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+300,000 ت از رتبه 5 ترب (+6.7%)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3962,39 +3956,43 @@
       <c r="E47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>6994000</v>
+      <c r="F47" s="5" t="n">
+        <v>7320000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>6597000</v>
+        <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6790000</v>
+        <v>5650000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>6999000</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>6999000</v>
+        <v>5698000</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L47" s="6" t="n">
         <v>9211000</v>
       </c>
-      <c r="M47" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+1,622,000 ت از رتبه 3 ترب (+28.5%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13988000</v>
+        <v>14640000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4035,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12494000</v>
+        <v>12600000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4066,11 +4064,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,394,000 ت از رتبه 3 ترب (+37.3%)</t>
+          <t>+3,500,000 ت از رتبه 3 ترب (+38.5%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>24988000</v>
+        <v>25200000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4111,7 +4109,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>3499500</v>
+        <v>3500000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>3140000</v>
@@ -4142,11 +4140,11 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+349,500 ت از رتبه 3 ترب (+11.1%)</t>
+          <t>+350,000 ت از رتبه 3 ترب (+11.1%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
-        <v>3499500</v>
+        <v>3500000</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -4187,7 +4185,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9405000</v>
+        <v>9402000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4220,11 +4218,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+2,555,000 ت از رتبه 3 ترب (+37.3%)</t>
+          <t>+2,552,000 ت از رتبه 3 ترب (+37.3%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18810000</v>
+        <v>18804000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4265,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>18370000</v>
+        <v>20250000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4296,11 +4294,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+5,470,000 ت از رتبه 3 ترب (+42.4%)</t>
+          <t>+7,350,000 ت از رتبه 3 ترب (+57.0%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>36740000</v>
+        <v>40500000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4341,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>16710000</v>
+        <v>18370000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4374,11 +4372,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+5,210,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+6,870,000 ت از رتبه 3 ترب (+59.7%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>33420000</v>
+        <v>36740000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4419,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>8510000</v>
+        <v>8120000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4441,7 +4439,7 @@
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>13700000</v>
+        <v>23000000</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -4450,11 +4448,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+1,021,000 ت از رتبه 3 ترب (+13.6%)</t>
+          <t>+631,000 ت از رتبه 3 ترب (+8.4%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>17020000</v>
+        <v>16240000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4581,7 +4579,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>15040000</v>
+        <v>14500000</v>
       </c>
       <c r="G55" s="6" t="n">
         <v>7990000</v>
@@ -4612,11 +4610,11 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>+3,550,000 ت از رتبه 3 ترب (+32.4%)</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
-        <v>45120000</v>
+        <v>43500000</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
@@ -4657,7 +4655,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10690000</v>
+        <v>10330000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4690,11 +4688,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,740,000 ت از رتبه 3 ترب (+79.7%)</t>
+          <t>+4,380,000 ت از رتبه 3 ترب (+73.6%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>21380000</v>
+        <v>20660000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -4985,7 +4983,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7350000</v>
+        <v>7300000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5141,7 +5139,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5860000</v>
+        <v>6100000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5221,7 +5219,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>20000000</v>
+        <v>19000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5275,7 +5273,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5380000</v>
+        <v>5410000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5297,7 +5295,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6950000</v>
+        <v>6649000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5306,11 +5304,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+430,000 ت از رتبه 3 ترب (+8.7%)</t>
+          <t>+460,000 ت از رتبه 3 ترب (+9.3%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21520000</v>
+        <v>21640000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5609,7 +5607,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4176870</v>
+        <v>4150000</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -5743,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>9550000</v>
+        <v>11550000</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>7200000</v>
@@ -5778,11 +5776,11 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
+          <t>+4,350,000 ت از رتبه 1 ترب (+60.4%)</t>
         </is>
       </c>
       <c r="O70" s="6" t="n">
-        <v>9550000</v>
+        <v>11550000</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
@@ -5985,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6016,11 +6014,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6061,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>12005000</v>
+        <v>11100000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -6092,11 +6090,11 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+1,900,000 ت از رتبه 3 ترب (+20.7%)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
-        <v>12005000</v>
+        <v>11100000</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
@@ -6137,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>22240000</v>
+        <v>23470000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6168,11 +6166,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+19,795,000 ت از رتبه 3 ترب (+809.6%)</t>
+          <t>+21,025,000 ت از رتبه 3 ترب (+859.9%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>22240000</v>
+        <v>23470000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6207,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27970000</v>
+        <v>27370000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6240,11 +6238,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+12,370,000 ت از رتبه 3 ترب (+79.3%)</t>
+          <t>+11,770,000 ت از رتبه 3 ترب (+75.4%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27970000</v>
+        <v>27370000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6281,7 +6279,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>11750000</v>
+        <v>10540000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6312,11 +6310,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+2,550,000 ت از رتبه 3 ترب (+27.7%)</t>
+          <t>+1,340,000 ت از رتبه 3 ترب (+14.6%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>11750000</v>
+        <v>10540000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6357,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12008000</v>
+        <v>12004000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -6388,11 +6386,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+2,808,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+2,804,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12008000</v>
+        <v>12004000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6433,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4540000</v>
+        <v>4750000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6455,7 +6453,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>5600000</v>
+        <v>5700000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6464,11 +6462,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+895,000 ت از رتبه 3 ترب (+23.2%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4540000</v>
+        <v>4750000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6509,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15550000</v>
+        <v>15860000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6540,11 +6538,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+560,000 ت از رتبه 3 ترب (+3.7%)</t>
+          <t>+870,000 ت از رتبه 3 ترب (+5.8%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15550000</v>
+        <v>15860000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6585,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>7590000</v>
+        <v>7950000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -6607,7 +6605,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8200000</v>
+        <v>9070000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6616,11 +6614,11 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+1,390,000 ت از رتبه 3 ترب (+22.4%)</t>
+          <t>+1,750,000 ت از رتبه 3 ترب (+28.2%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>7590000</v>
+        <v>7950000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -6661,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6130000</v>
+        <v>6190000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6694,11 +6692,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+180,000 ت از رتبه 2 ترب (+3.0%)</t>
+          <t>+240,000 ت از رتبه 2 ترب (+4.0%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6130000</v>
+        <v>6190000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>23920000</v>
+        <v>22500000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6770,11 +6768,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+12,120,000 ت از رتبه 3 ترب (+102.7%)</t>
+          <t>+10,700,000 ت از رتبه 3 ترب (+90.7%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>23920000</v>
+        <v>22500000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6815,7 +6813,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2640500</v>
+        <v>2640125</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6846,11 +6844,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+195,500 ت از رتبه 3 ترب (+8.0%)</t>
+          <t>+195,125 ت از رتبه 3 ترب (+8.0%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2640500</v>
+        <v>2640125</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6887,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>7340000</v>
+        <v>7650000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6918,11 +6916,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-1,659,000 ت از کف ترب (-18.4%)</t>
+          <t>-1,349,000 ت از کف ترب (-15.0%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>7340000</v>
+        <v>7650000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7049,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>8300000</v>
+        <v>6150000</v>
       </c>
       <c r="G87" s="6" t="n">
         <v>4200000</v>
@@ -7086,11 +7084,11 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>+4,100,000 ت از رتبه 1 ترب (+97.6%)</t>
+          <t>+1,950,000 ت از رتبه 1 ترب (+46.4%)</t>
         </is>
       </c>
       <c r="O87" s="6" t="n">
-        <v>8300000</v>
+        <v>6150000</v>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
@@ -7231,7 +7229,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7950000</v>
+        <v>7400000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7307,7 +7305,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7950000</v>
+        <v>7400000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7383,7 +7381,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5860000</v>
+        <v>6100000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7437,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3740000</v>
+        <v>3795000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7459,7 +7457,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4280000</v>
+        <v>4320000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7468,11 +7466,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+752,000 ت از رتبه 3 ترب (+25.2%)</t>
+          <t>+807,000 ت از رتبه 3 ترب (+27.0%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3740000</v>
+        <v>3795000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7513,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>7930000</v>
+        <v>7990000</v>
       </c>
       <c r="G93" s="6" t="n">
         <v>6898000</v>
@@ -7535,7 +7533,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8335730</v>
+        <v>8424450</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7544,11 +7542,11 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>+1,010,000 ت از رتبه 3 ترب (+14.6%)</t>
+          <t>+1,070,000 ت از رتبه 3 ترب (+15.5%)</t>
         </is>
       </c>
       <c r="O93" s="6" t="n">
-        <v>7930000</v>
+        <v>7990000</v>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
@@ -7589,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="8" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>3580000</v>
@@ -7628,7 +7626,7 @@
         </is>
       </c>
       <c r="O94" s="6" t="n">
-        <v>5800000</v>
+        <v>5889000</v>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
@@ -7669,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>26670000</v>
+        <v>26699000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7700,11 +7698,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
+          <t>+5,349,000 ت از رتبه 3 ترب (+25.1%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>26670000</v>
+        <v>26699000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7745,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5220000</v>
+        <v>5280000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7782,11 +7780,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+720,000 ت از رتبه 1 ترب (+16.0%)</t>
+          <t>+780,000 ت از رتبه 1 ترب (+17.3%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5220000</v>
+        <v>5280000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7827,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>9550000</v>
+        <v>11550000</v>
       </c>
       <c r="G97" s="6" t="n">
         <v>7200000</v>
@@ -7864,11 +7862,11 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>+2,350,000 ت از رتبه 1 ترب (+32.6%)</t>
+          <t>+4,350,000 ت از رتبه 1 ترب (+60.4%)</t>
         </is>
       </c>
       <c r="O97" s="6" t="n">
-        <v>9550000</v>
+        <v>11550000</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
@@ -7909,7 +7907,7 @@
         <v>3</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>15040000</v>
+        <v>14500000</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>7990000</v>
@@ -7940,11 +7938,11 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>+3,550,000 ت از رتبه 3 ترب (+32.4%)</t>
         </is>
       </c>
       <c r="O98" s="6" t="n">
-        <v>45120000</v>
+        <v>43500000</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
@@ -7985,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8016,11 +8014,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 3 ترب (+14.7%)</t>
+          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4460000</v>
+        <v>4475000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27970000</v>
+        <v>27370000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8254,7 +8252,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27970000</v>
+        <v>27370000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -8375,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4540000</v>
+        <v>4750000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8397,7 +8395,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>5600000</v>
+        <v>5700000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8406,11 +8404,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+895,000 ت از رتبه 3 ترب (+23.2%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4540000</v>
+        <v>4750000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -8475,7 +8473,7 @@
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>8100000</v>
+        <v>8080000</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -9341,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3740000</v>
+        <v>3795000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9363,7 +9361,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4280000</v>
+        <v>4320000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9372,11 +9370,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+752,000 ت از رتبه 3 ترب (+25.2%)</t>
+          <t>+807,000 ت از رتبه 3 ترب (+27.0%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3740000</v>
+        <v>3795000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9579,7 +9577,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>8510000</v>
+        <v>8120000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9601,7 +9599,7 @@
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>13700000</v>
+        <v>23000000</v>
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
@@ -9610,11 +9608,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+1,021,000 ت از رتبه 3 ترب (+13.6%)</t>
+          <t>+631,000 ت از رتبه 3 ترب (+8.4%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>17020000</v>
+        <v>16240000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9835,7 +9833,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>19490000</v>
+        <v>19290000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -9963,7 +9961,7 @@
         <v>3</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>7020000</v>
+        <v>7550000</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>9600000</v>
@@ -10000,11 +9998,11 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-2,580,000 ت از کف ترب (-26.9%)</t>
+          <t>-2,050,000 ت از کف ترب (-21.4%)</t>
         </is>
       </c>
       <c r="O124" s="6" t="n">
-        <v>21060000</v>
+        <v>22650000</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
@@ -10149,7 +10147,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>19490000</v>
+        <v>19290000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -10289,7 +10287,7 @@
         <v>3</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>15040000</v>
+        <v>14500000</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>7990000</v>
@@ -10320,11 +10318,11 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>+4,090,000 ت از رتبه 3 ترب (+37.4%)</t>
+          <t>+3,550,000 ت از رتبه 3 ترب (+32.4%)</t>
         </is>
       </c>
       <c r="O128" s="6" t="n">
-        <v>45120000</v>
+        <v>43500000</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
@@ -10690,8 +10688,8 @@
       <c r="E133" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>21750000</v>
+      <c r="F133" s="8" t="n">
+        <v>11350000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -10715,18 +10713,18 @@
       <c r="L133" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="M133" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M133" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>+5,550,000 ت از رتبه 3 ترب (+34.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O133" s="6" t="n">
-        <v>108750000</v>
+        <v>56750000</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -636,19 +636,19 @@
         <v>13410000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10000000</v>
+        <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>10200000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10200000</v>
+        <v>10500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10200000</v>
+        <v>10500000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10500000</v>
+        <v>10800000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12100000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+2,910,000 ت از رتبه 5 ترب (+27.7%)</t>
+          <t>+2,610,000 ت از رتبه 5 ترب (+24.2%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -705,38 +705,38 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20020000</v>
+        <v>20060000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>19784300</v>
+        <v>19990000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>19990000</v>
+        <v>20060000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20020000</v>
+        <v>20131000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20131000</v>
+        <v>20290000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18490000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1261260000</v>
+        <v>1263780000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,22 +777,22 @@
         <v>30</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>16650000</v>
+        <v>16830000</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>13620000</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>14990000</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>15191000</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>15360000</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>15700000</v>
-      </c>
       <c r="K4" s="6" t="n">
-        <v>15790000</v>
+        <v>15390000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
@@ -804,11 +804,11 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+860,000 ت از رتبه 5 ترب (+5.4%)</t>
+          <t>+1,440,000 ت از رتبه 5 ترب (+9.4%)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>499500000</v>
+        <v>504900000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6210000</v>
+        <v>6900000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5679000</v>
@@ -858,16 +858,16 @@
         <v>5690000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5700000</v>
+        <v>5800000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5700000</v>
+        <v>6000000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5800000</v>
+        <v>6000000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>6850000</v>
+        <v>6950000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+410,000 ت از رتبه 5 ترب (+7.1%)</t>
+          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>105570000</v>
+        <v>117300000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -930,12 +930,10 @@
         <v>8000000</v>
       </c>
       <c r="I6" s="6" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="J6" s="6" t="n">
         <v>8500000</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -997,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4960000</v>
+        <v>4760000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1009,10 +1007,10 @@
         <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
+        <v>4690000</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>4695000</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4700000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1024,11 +1022,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+260,000 ت از رتبه 5 ترب (+5.5%)</t>
+          <t>+65,000 ت از رتبه 5 ترب (+1.4%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>74400000</v>
+        <v>71400000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1163,10 +1161,10 @@
         <v>101200</v>
       </c>
       <c r="J9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>116379</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>129600</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1237,7 +1235,7 @@
         <v>9999000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>10200000</v>
+        <v>10000000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1379,13 +1377,13 @@
         <v>5200000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5600000</v>
+        <v>5300000</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>5600000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5600000</v>
+        <v>5700000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1504,22 +1502,22 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>13310000</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <v>13490000</v>
-      </c>
       <c r="I14" s="6" t="n">
-        <v>13490000</v>
+        <v>13340000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>13500000</v>
+        <v>13340000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13700000</v>
+        <v>13400000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22450000</v>
+        <v>21900000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1528,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,150,000 ت از رتبه 5 ترب (+44.9%)</t>
+          <t>+6,450,000 ت از رتبه 5 ترب (+48.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1573,13 +1571,13 @@
         <v>5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7700000</v>
+        <v>7440000</v>
       </c>
       <c r="G15" s="6" t="n">
+        <v>7270000</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>7273000</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>7280000</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>7399000</v>
@@ -1591,7 +1589,7 @@
         <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>9070000</v>
+        <v>8460000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1600,11 +1598,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 5 ترب (+4.1%)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>38500000</v>
+        <v>37200000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1663,7 +1661,7 @@
         <v>5500000</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>5790000</v>
+        <v>5800000</v>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
@@ -1802,10 +1800,10 @@
         <v>9620000</v>
       </c>
       <c r="G18" s="6" t="n">
+        <v>9450000</v>
+      </c>
+      <c r="H18" s="6" t="n">
         <v>9500000</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>9800000</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>10000000</v>
@@ -1823,12 +1821,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -1891,7 +1889,7 @@
         <v>9999000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>10200000</v>
+        <v>10000000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -2179,13 +2177,13 @@
         <v>5</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>11350000</v>
+        <v>7539000</v>
       </c>
       <c r="G23" s="6" t="n">
+        <v>7480000</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>7490000</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>7500000</v>
@@ -2201,16 +2199,16 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
-        <v>56750000</v>
+        <v>37695000</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
@@ -2266,10 +2264,10 @@
         <v>7100000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>7100000</v>
+        <v>7150000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9211000</v>
+        <v>9157000</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -2278,7 +2276,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+220,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>+170,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2340,10 +2338,10 @@
         <v>8200000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8800000</v>
+        <v>8600000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>17000000</v>
+        <v>16000000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2621,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>5410000</v>
+        <v>5400000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5200000</v>
@@ -2636,7 +2634,7 @@
         <v>5340000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5410000</v>
+        <v>5400000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6649000</v>
@@ -2652,7 +2650,7 @@
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21640000</v>
+        <v>21600000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -3128,14 +3126,14 @@
       <c r="E36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>7491000</v>
+      <c r="F36" s="5" t="n">
+        <v>8500000</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>6900000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7491000</v>
+        <v>7500000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>7500000</v>
@@ -3144,23 +3142,23 @@
         <v>7500000</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>7500000</v>
+        <v>7580000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+920,000 ت از رتبه 5 ترب (+12.1%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>14982000</v>
+        <v>17000000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3200,14 +3198,14 @@
       <c r="E37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="8" t="n">
-        <v>7491000</v>
+      <c r="F37" s="5" t="n">
+        <v>8500000</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>6900000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7491000</v>
+        <v>7500000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>7500000</v>
@@ -3216,23 +3214,23 @@
         <v>7500000</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>7500000</v>
+        <v>7580000</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>7400000</v>
       </c>
-      <c r="M37" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+920,000 ت از رتبه 5 ترب (+12.1%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>14982000</v>
+        <v>17000000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>20250000</v>
+        <v>22000000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>18498000</v>
@@ -3288,7 +3286,7 @@
         <v>19500000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19650000</v>
+        <v>21900000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
@@ -3300,11 +3298,11 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+600,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>+100,000 ت از رتبه 5 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>40500000</v>
+        <v>44000000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3343,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4960000</v>
+        <v>4760000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3357,10 +3355,10 @@
         <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
+        <v>4690000</v>
+      </c>
+      <c r="K39" s="6" t="n">
         <v>4695000</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4700000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3372,11 +3370,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+260,000 ت از رتبه 5 ترب (+5.5%)</t>
+          <t>+65,000 ت از رتبه 5 ترب (+1.4%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>74400000</v>
+        <v>71400000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3576,7 +3574,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4150000</v>
+        <v>3150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3659,16 +3657,20 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8064550</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8489000</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>8500000</v>
+        <v>7289000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3812,17 +3814,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
-        <v>7750000</v>
+      <c r="F45" s="5" t="n">
+        <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7600000</v>
+        <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7750000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3839,18 +3841,18 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
-        <v>15500000</v>
+        <v>15230000</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -3888,35 +3890,39 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>2839550</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4140000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>4350000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>4500000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 5 ترب (+6.7%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3979,7 +3985,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9211000</v>
+        <v>9157000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -4033,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12600000</v>
+        <v>12699000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4064,11 +4070,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,500,000 ت از رتبه 3 ترب (+38.5%)</t>
+          <t>+3,599,000 ت از رتبه 3 ترب (+39.5%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>25200000</v>
+        <v>25398000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4263,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>20250000</v>
+        <v>22000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4294,11 +4300,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+7,350,000 ت از رتبه 3 ترب (+57.0%)</t>
+          <t>+9,100,000 ت از رتبه 3 ترب (+70.5%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>40500000</v>
+        <v>44000000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4339,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>18370000</v>
+        <v>16710000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4372,11 +4378,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,870,000 ت از رتبه 3 ترب (+59.7%)</t>
+          <t>+5,210,000 ت از رتبه 3 ترب (+45.3%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>36740000</v>
+        <v>33420000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4417,7 +4423,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>8120000</v>
+        <v>10000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4448,11 +4454,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+631,000 ت از رتبه 3 ترب (+8.4%)</t>
+          <t>+2,511,000 ت از رتبه 3 ترب (+33.5%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>16240000</v>
+        <v>20000000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4655,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>10330000</v>
+        <v>9890000</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>5800000</v>
@@ -4688,11 +4694,11 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>+4,380,000 ت از رتبه 3 ترب (+73.6%)</t>
+          <t>+3,940,000 ت از رتبه 3 ترب (+66.2%)</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
-        <v>20660000</v>
+        <v>19780000</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
@@ -5219,7 +5225,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>19000000</v>
+        <v>19300000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5273,7 +5279,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5410000</v>
+        <v>5400000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5304,11 +5310,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+460,000 ت از رتبه 3 ترب (+9.3%)</t>
+          <t>+450,000 ت از رتبه 3 ترب (+9.1%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21640000</v>
+        <v>21600000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5983,7 +5989,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4475000</v>
+        <v>4489000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6014,11 +6020,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
+          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4475000</v>
+        <v>4489000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6059,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>11100000</v>
+        <v>12005000</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>8999000</v>
@@ -6090,11 +6096,11 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>+1,900,000 ت از رتبه 3 ترب (+20.7%)</t>
+          <t>+2,805,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O74" s="6" t="n">
-        <v>11100000</v>
+        <v>12005000</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
@@ -6135,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>23470000</v>
+        <v>23000000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6166,11 +6172,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+21,025,000 ت از رتبه 3 ترب (+859.9%)</t>
+          <t>+20,555,000 ت از رتبه 3 ترب (+840.7%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>23470000</v>
+        <v>23000000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6207,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6238,11 +6244,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+11,770,000 ت از رتبه 3 ترب (+75.4%)</t>
+          <t>+12,370,000 ت از رتبه 3 ترب (+79.3%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6279,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>10540000</v>
+        <v>11050000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6310,11 +6316,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,340,000 ت از رتبه 3 ترب (+14.6%)</t>
+          <t>+1,850,000 ت از رتبه 3 ترب (+20.1%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>10540000</v>
+        <v>11050000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6355,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12004000</v>
+        <v>12009000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -6386,11 +6392,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+2,804,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+2,809,000 ت از رتبه 3 ترب (+30.5%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12004000</v>
+        <v>12009000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6431,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4750000</v>
+        <v>5200000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6453,7 +6459,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>5700000</v>
+        <v>5600000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6462,11 +6468,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+895,000 ت از رتبه 3 ترب (+23.2%)</t>
+          <t>+1,345,000 ت از رتبه 3 ترب (+34.9%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4750000</v>
+        <v>5200000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6507,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15860000</v>
+        <v>15780000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6538,11 +6544,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+870,000 ت از رتبه 3 ترب (+5.8%)</t>
+          <t>+790,000 ت از رتبه 3 ترب (+5.3%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15860000</v>
+        <v>15780000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6605,7 +6611,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>9070000</v>
+        <v>8460000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6659,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6190000</v>
+        <v>6250000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6692,11 +6698,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+240,000 ت از رتبه 2 ترب (+4.0%)</t>
+          <t>+300,000 ت از رتبه 2 ترب (+5.0%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6190000</v>
+        <v>6250000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6737,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22500000</v>
+        <v>22870000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6768,11 +6774,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+10,700,000 ت از رتبه 3 ترب (+90.7%)</t>
+          <t>+11,070,000 ت از رتبه 3 ترب (+93.8%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22500000</v>
+        <v>22870000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2640125</v>
+        <v>2730000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6844,11 +6850,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+195,125 ت از رتبه 3 ترب (+8.0%)</t>
+          <t>+285,000 ت از رتبه 3 ترب (+11.7%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2640125</v>
+        <v>2730000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6885,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>7650000</v>
+        <v>7270000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6916,11 +6922,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-1,349,000 ت از کف ترب (-15.0%)</t>
+          <t>-1,729,000 ت از کف ترب (-19.2%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>7650000</v>
+        <v>7270000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7213,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>7491000</v>
+        <v>8500000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7238,11 +7244,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+541,000 ت از رتبه 3 ترب (+7.8%)</t>
+          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>14982000</v>
+        <v>17000000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7283,7 +7289,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>7491000</v>
+        <v>8500000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7314,11 +7320,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+541,000 ت از رتبه 3 ترب (+7.8%)</t>
+          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>14982000</v>
+        <v>17000000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7435,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3795000</v>
+        <v>3782000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7466,11 +7472,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+807,000 ت از رتبه 3 ترب (+27.0%)</t>
+          <t>+794,000 ت از رتبه 3 ترب (+26.6%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3795000</v>
+        <v>3782000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7743,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5280000</v>
+        <v>5340000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7780,11 +7786,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+780,000 ت از رتبه 1 ترب (+17.3%)</t>
+          <t>+840,000 ت از رتبه 1 ترب (+18.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5280000</v>
+        <v>5340000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7983,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4475000</v>
+        <v>4489000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8014,11 +8020,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+585,000 ت از رتبه 3 ترب (+15.0%)</t>
+          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4475000</v>
+        <v>4489000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8252,7 +8258,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27370000</v>
+        <v>27970000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -8373,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4750000</v>
+        <v>5200000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8395,7 +8401,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>5700000</v>
+        <v>5600000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8404,11 +8410,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+895,000 ت از رتبه 3 ترب (+23.2%)</t>
+          <t>+1,345,000 ت از رتبه 3 ترب (+34.9%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4750000</v>
+        <v>5200000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -8473,7 +8479,7 @@
         </is>
       </c>
       <c r="L105" s="6" t="n">
-        <v>8080000</v>
+        <v>8100000</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
@@ -9339,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3795000</v>
+        <v>3782000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9370,11 +9376,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+807,000 ت از رتبه 3 ترب (+27.0%)</t>
+          <t>+794,000 ت از رتبه 3 ترب (+26.6%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3795000</v>
+        <v>3782000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9577,7 +9583,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>8120000</v>
+        <v>10000000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9608,11 +9614,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+631,000 ت از رتبه 3 ترب (+8.4%)</t>
+          <t>+2,511,000 ت از رتبه 3 ترب (+33.5%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>16240000</v>
+        <v>20000000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -10472,10 +10478,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L130" s="6" t="n">
+        <v>6950000</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -10688,8 +10692,8 @@
       <c r="E133" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>11350000</v>
+      <c r="F133" s="11" t="n">
+        <v>7539000</v>
       </c>
       <c r="G133" s="6" t="n">
         <v>7800000</v>
@@ -10713,18 +10717,18 @@
       <c r="L133" s="6" t="n">
         <v>7600000</v>
       </c>
-      <c r="M133" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>-261,000 ت از کف ترب (-3.3%)</t>
         </is>
       </c>
       <c r="O133" s="6" t="n">
-        <v>56750000</v>
+        <v>37695000</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -633,7 +633,7 @@
         <v>188</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>13410000</v>
+        <v>12780000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>10200000</v>
@@ -645,13 +645,13 @@
         <v>10500000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10500000</v>
+        <v>10769000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10800000</v>
+        <v>10769000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>12100000</v>
+        <v>12200000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -660,11 +660,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+2,610,000 ت از رتبه 5 ترب (+24.2%)</t>
+          <t>+2,011,000 ت از رتبه 5 ترب (+18.7%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2521080000</v>
+        <v>2402640000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20060000</v>
+        <v>20090000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18490000</v>
@@ -714,7 +714,7 @@
         <v>19990000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20060000</v>
+        <v>20090000</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>20131000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1263780000</v>
+        <v>1265670000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -849,25 +849,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6900000</v>
+        <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>5650000</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>5679000</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>5690000</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>5800000</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>6000000</v>
-      </c>
       <c r="L5" s="6" t="n">
-        <v>6950000</v>
+        <v>7150000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
+          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>117300000</v>
+        <v>104550000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9559160</v>
+        <v>9370000</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4760000</v>
+        <v>4730000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1022,11 +1022,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+65,000 ت از رتبه 5 ترب (+1.4%)</t>
+          <t>+35,000 ت از رتبه 5 ترب (+0.7%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>71400000</v>
+        <v>70950000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1217,16 +1217,16 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9890000</v>
+        <v>9885000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>9880000</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>9890000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9900000</v>
@@ -1239,16 +1239,16 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>98900000</v>
+        <v>98850000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1368,22 +1368,22 @@
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5149000</v>
+        <v>4960000</v>
       </c>
       <c r="H12" s="6" t="n">
+        <v>5130000</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>5145000</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>5150000</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>5600000</v>
-      </c>
       <c r="L12" s="6" t="n">
-        <v>5700000</v>
+        <v>5390000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-199,000 ت از کف ترب (-3.9%)</t>
+          <t>-10,000 ت از کف ترب (-0.2%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1505,19 +1505,19 @@
         <v>12000000</v>
       </c>
       <c r="H14" s="6" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>13310000</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>13340000</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>13340000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13400000</v>
+        <v>13340000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21900000</v>
+        <v>21800000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,450,000 ت از رتبه 5 ترب (+48.1%)</t>
+          <t>+6,510,000 ت از رتبه 5 ترب (+48.8%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1570,35 +1570,35 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="8" t="n">
         <v>7440000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7270000</v>
+        <v>7380000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7273000</v>
+        <v>7399000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7399000</v>
+        <v>7400000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7400000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7400000</v>
+        <v>7440000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8460000</v>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>8400000</v>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1646,19 +1646,19 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5199000</v>
+        <v>5200000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>5200000</v>
+        <v>5350000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5350000</v>
+        <v>5400000</v>
       </c>
       <c r="J16" s="6" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="K16" s="6" t="n">
         <v>5445000</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>5500000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>5800000</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-579,000 ت از کف ترب (-11.1%)</t>
+          <t>-580,000 ت از کف ترب (-11.2%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1803,16 +1803,16 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>9500000</v>
+        <v>10000000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>10000000</v>
+        <v>14500000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>14500000</v>
+        <v>18000000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>18000000</v>
+        <v>18900000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O18" s="6" t="n">
@@ -1871,16 +1871,16 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9890000</v>
+        <v>9885000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>9880000</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>9890000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9900000</v>
@@ -1893,16 +1893,16 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>98900000</v>
+        <v>98850000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>7150000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9157000</v>
+        <v>9201000</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>8200000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8600000</v>
+        <v>8300000</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>16000000</v>
@@ -2400,19 +2400,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>8390000</v>
+        <v>8300000</v>
       </c>
       <c r="H26" s="6" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="K26" s="6" t="n">
         <v>8400000</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>8499000</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>8500000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2619,25 +2619,25 @@
         <v>4</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>5400000</v>
+        <v>5470000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5200000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5220000</v>
+        <v>5340000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5282000</v>
+        <v>5400000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5340000</v>
+        <v>5450000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5400000</v>
+        <v>5470000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6649000</v>
+        <v>7150000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21600000</v>
+        <v>21880000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2780,13 +2780,13 @@
         <v>13000000</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13400000</v>
+        <v>13700000</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>13700000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>13700000</v>
+        <v>13799000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2863,7 +2863,7 @@
         <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>19290000</v>
+        <v>19090000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>8700000</v>
+        <v>9440000</v>
       </c>
       <c r="H34" s="6" t="n">
         <v>9440000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9440000</v>
+        <v>9592330</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9592330</v>
+        <v>9889000</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>9889000</v>
+        <v>14160000</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3127,10 +3127,10 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6900000</v>
+        <v>7250000</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>7500000</v>
@@ -3145,7 +3145,7 @@
         <v>7580000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+920,000 ت از رتبه 5 ترب (+12.1%)</t>
+          <t>+1,920,000 ت از رتبه 5 ترب (+25.3%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
         <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6900000</v>
+        <v>7250000</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>7500000</v>
@@ -3217,7 +3217,7 @@
         <v>7580000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3226,11 +3226,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+920,000 ت از رتبه 5 ترب (+12.1%)</t>
+          <t>+1,920,000 ت از رتبه 5 ترب (+25.3%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3270,39 +3270,39 @@
       <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>22000000</v>
+      <c r="F38" s="8" t="n">
+        <v>21950000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>18498000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>18500000</v>
+        <v>19000000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>19000000</v>
+        <v>21900000</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>19500000</v>
+        <v>21950000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>21900000</v>
+        <v>22000000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
       </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+100,000 ت از رتبه 5 ترب (+0.5%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>44000000</v>
+        <v>43900000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4760000</v>
+        <v>4730000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+65,000 ت از رتبه 5 ترب (+1.4%)</t>
+          <t>+35,000 ت از رتبه 5 ترب (+0.7%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>71400000</v>
+        <v>70950000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3657,20 +3657,16 @@
         <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7000000</v>
+        <v>8000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8064550</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8489000</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>8500000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3814,17 +3810,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3841,14 +3837,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3894,23 +3890,19 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>4300000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6950000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>7350000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>7900000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
@@ -3966,26 +3958,22 @@
         <v>7320000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5616000</v>
+        <v>6790000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5650000</v>
+        <v>6900000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>7100000</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>7150000</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9157000</v>
+        <v>9201000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3994,7 +3982,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,622,000 ت از رتبه 3 ترب (+28.5%)</t>
+          <t>+170,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -4038,43 +4026,39 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="8" t="n">
+        <v>12699500</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>12100000</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="I48" s="6" t="n">
         <v>12699000</v>
       </c>
-      <c r="G48" s="6" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>8900000</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="J48" s="6" t="n">
+        <v>12699500</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>12750000</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>15800000</v>
       </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,599,000 ت از رتبه 3 ترب (+39.5%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>25398000</v>
+        <v>25399000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4114,39 +4098,35 @@
       <c r="E49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="8" t="n">
         <v>3500000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>3140000</v>
+        <v>14000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>3149000</v>
+        <v>15000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>3150000</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>15000</v>
+      </c>
+      <c r="J49" s="6" t="n">
+        <v>2250000</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>3500000</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>4570000</v>
       </c>
-      <c r="M49" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>+350,000 ت از رتبه 3 ترب (+11.1%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4191,7 +4171,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>9402000</v>
+        <v>8350000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4224,11 +4204,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+2,552,000 ت از رتبه 3 ترب (+37.3%)</t>
+          <t>+1,500,000 ت از رتبه 3 ترب (+21.9%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18804000</v>
+        <v>16700000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4269,7 +4249,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>22000000</v>
+        <v>21950000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4300,11 +4280,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+9,100,000 ت از رتبه 3 ترب (+70.5%)</t>
+          <t>+9,050,000 ت از رتبه 3 ترب (+70.2%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>44000000</v>
+        <v>43900000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4345,7 +4325,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>16710000</v>
+        <v>17350000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4378,11 +4358,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+5,210,000 ت از رتبه 3 ترب (+45.3%)</t>
+          <t>+5,850,000 ت از رتبه 3 ترب (+50.9%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>33420000</v>
+        <v>34700000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4403,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4454,11 +4434,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+2,511,000 ت از رتبه 3 ترب (+33.5%)</t>
+          <t>+3,511,000 ت از رتبه 3 ترب (+46.9%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>20000000</v>
+        <v>22000000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -5123,7 +5103,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5200000</v>
+        <v>5270000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5145,7 +5125,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>6100000</v>
+        <v>5990000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5154,11 +5134,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,250,000 ت از رتبه 3 ترب (+31.6%)</t>
+          <t>+1,320,000 ت از رتبه 3 ترب (+33.4%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10400000</v>
+        <v>10540000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5225,7 +5205,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>19300000</v>
+        <v>19000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5279,7 +5259,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5400000</v>
+        <v>5470000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5301,7 +5281,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6649000</v>
+        <v>7150000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5310,11 +5290,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+450,000 ت از رتبه 3 ترب (+9.1%)</t>
+          <t>+520,000 ت از رتبه 3 ترب (+10.5%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21600000</v>
+        <v>21880000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -6285,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>11050000</v>
+        <v>10990000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6316,11 +6296,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,850,000 ت از رتبه 3 ترب (+20.1%)</t>
+          <t>+1,790,000 ت از رتبه 3 ترب (+19.5%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>11050000</v>
+        <v>10990000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6437,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>5200000</v>
+        <v>4850000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6468,11 +6448,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+1,345,000 ت از رتبه 3 ترب (+34.9%)</t>
+          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>5200000</v>
+        <v>4850000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6513,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15780000</v>
+        <v>15840000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6544,11 +6524,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+790,000 ت از رتبه 3 ترب (+5.3%)</t>
+          <t>+850,000 ت از رتبه 3 ترب (+5.7%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15780000</v>
+        <v>15840000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6611,7 +6591,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8460000</v>
+        <v>8400000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6665,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6250000</v>
+        <v>6280000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6698,11 +6678,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+300,000 ت از رتبه 2 ترب (+5.0%)</t>
+          <t>+330,000 ت از رتبه 2 ترب (+5.5%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6250000</v>
+        <v>6280000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6743,7 +6723,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22870000</v>
+        <v>22930000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6774,11 +6754,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,070,000 ت از رتبه 3 ترب (+93.8%)</t>
+          <t>+11,130,000 ت از رتبه 3 ترب (+94.3%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22870000</v>
+        <v>22930000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6819,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2730000</v>
+        <v>2740000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6850,11 +6830,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+285,000 ت از رتبه 3 ترب (+11.7%)</t>
+          <t>+295,000 ت از رتبه 3 ترب (+12.1%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2730000</v>
+        <v>2740000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6891,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>7270000</v>
+        <v>7400000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6922,11 +6902,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-1,729,000 ت از کف ترب (-19.2%)</t>
+          <t>-1,599,000 ت از کف ترب (-17.8%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>7270000</v>
+        <v>7400000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7213,7 +7193,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7235,7 +7215,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7244,11 +7224,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7289,7 +7269,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7311,7 +7291,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7400000</v>
+        <v>7950000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7320,11 +7300,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7365,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5200000</v>
+        <v>5270000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7387,7 +7367,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>6100000</v>
+        <v>5990000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7396,11 +7376,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,250,000 ت از رتبه 3 ترب (+31.6%)</t>
+          <t>+1,320,000 ت از رتبه 3 ترب (+33.4%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5200000</v>
+        <v>5270000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7441,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3782000</v>
+        <v>3790000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7463,7 +7443,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4320000</v>
+        <v>4184900</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7472,11 +7452,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+794,000 ت از رتبه 3 ترب (+26.6%)</t>
+          <t>+802,000 ت از رتبه 3 ترب (+26.8%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3782000</v>
+        <v>3790000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7539,7 +7519,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8424450</v>
+        <v>8335730</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7673,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>26699000</v>
+        <v>27340000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7704,11 +7684,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,349,000 ت از رتبه 3 ترب (+25.1%)</t>
+          <t>+5,990,000 ت از رتبه 3 ترب (+28.1%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>26699000</v>
+        <v>27340000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7749,7 +7729,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5340000</v>
+        <v>5370000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7786,11 +7766,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+840,000 ت از رتبه 1 ترب (+18.7%)</t>
+          <t>+870,000 ت از رتبه 1 ترب (+19.3%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5340000</v>
+        <v>5370000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8379,7 +8359,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>5200000</v>
+        <v>4850000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8410,11 +8390,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+1,345,000 ت از رتبه 3 ترب (+34.9%)</t>
+          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>5200000</v>
+        <v>4850000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9211,7 +9191,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11391720</v>
+        <v>11350000</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9345,7 +9325,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3782000</v>
+        <v>3790000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9367,7 +9347,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4320000</v>
+        <v>4184900</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9376,11 +9356,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+794,000 ت از رتبه 3 ترب (+26.6%)</t>
+          <t>+802,000 ت از رتبه 3 ترب (+26.8%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3782000</v>
+        <v>3790000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9583,7 +9563,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9614,11 +9594,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+2,511,000 ت از رتبه 3 ترب (+33.5%)</t>
+          <t>+3,511,000 ت از رتبه 3 ترب (+46.9%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>20000000</v>
+        <v>22000000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9839,7 +9819,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>19290000</v>
+        <v>19090000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10153,7 +10133,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>19290000</v>
+        <v>19090000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -639,16 +639,16 @@
         <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10200000</v>
+        <v>10769000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10500000</v>
+        <v>10769000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10769000</v>
+        <v>10800000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10769000</v>
+        <v>10950000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12200000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+2,011,000 ت از رتبه 5 ترب (+18.7%)</t>
+          <t>+1,830,000 ت از رتبه 5 ترب (+16.7%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -708,31 +708,31 @@
         <v>20090000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>18490000</v>
+        <v>19990000</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>19990000</v>
+        <v>20090000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20090000</v>
+        <v>20131000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20131000</v>
+        <v>20290000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20290000</v>
+        <v>20790000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>18490000</v>
+        <v>21190000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -852,22 +852,22 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5600000</v>
+        <v>5650000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5650000</v>
+        <v>5679000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5679000</v>
+        <v>5690000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5690000</v>
+        <v>5700000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>5800000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>7150000</v>
+        <v>5790000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9370000</v>
+        <v>8467000</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -998,19 +998,19 @@
         <v>4730000</v>
       </c>
       <c r="G7" s="6" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1890000</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>4599936</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>4690000</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4695000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+35,000 ت از رتبه 5 ترب (+0.7%)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.9%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1158,13 +1158,13 @@
         <v>100000</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>101200</v>
+        <v>108300</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1223,28 +1223,28 @@
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9380000</v>
+        <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9900000</v>
+        <v>9999000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9999000</v>
+        <v>10000000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1368,7 +1368,7 @@
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4960000</v>
+        <v>5090000</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>5130000</v>
@@ -1383,7 +1383,7 @@
         <v>5200000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5390000</v>
+        <v>5400000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-10,000 ت از کف ترب (-0.2%)</t>
+          <t>-140,000 ت از کف ترب (-2.8%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1502,22 +1502,22 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>11990000</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>11990000</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>12000000</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="J14" s="6" t="n">
         <v>13300000</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>13310000</v>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>13340000</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>13340000</v>
-      </c>
       <c r="L14" s="6" t="n">
-        <v>21800000</v>
+        <v>21900000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,510,000 ت از رتبه 5 ترب (+48.8%)</t>
+          <t>+6,540,000 ت از رتبه 5 ترب (+49.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1574,13 +1574,13 @@
         <v>7440000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7380000</v>
+        <v>1550000</v>
       </c>
       <c r="H15" s="6" t="n">
+        <v>7340000</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>7399000</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7400000</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>7400000</v>
@@ -1589,7 +1589,7 @@
         <v>7440000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8400000</v>
+        <v>8460000</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -1646,19 +1646,19 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5200000</v>
+        <v>5340000</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>5350000</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5400000</v>
+        <v>5399000</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>5400000</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5445000</v>
+        <v>5400000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>5800000</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-580,000 ت از کف ترب (-11.2%)</t>
+          <t>-720,000 ت از کف ترب (-13.5%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1877,28 +1877,28 @@
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9380000</v>
+        <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9900000</v>
+        <v>9999000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9999000</v>
+        <v>10000000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17795730</v>
+        <v>17147290</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>7500000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>9400000</v>
+        <v>9590000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>13300000</v>
@@ -2252,22 +2252,22 @@
         <v>7320000</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>6790000</v>
+        <v>4500000</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>6845000</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>7100000</v>
       </c>
-      <c r="J24" s="6" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>7150000</v>
-      </c>
       <c r="L24" s="6" t="n">
-        <v>9201000</v>
+        <v>9077000</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+170,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+220,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2338,10 +2338,10 @@
         <v>8200000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8300000</v>
+        <v>8600000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>16000000</v>
+        <v>15900000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2400,19 +2400,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>8300000</v>
+        <v>8390000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>8300000</v>
+        <v>8400000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8300000</v>
+        <v>8499000</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8300000</v>
+        <v>8500000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>8400000</v>
+        <v>8500000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2479,10 +2479,10 @@
         <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="K27" s="6" t="n">
         <v>17900000</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>20600000</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2637,7 +2637,7 @@
         <v>5470000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>7150000</v>
+        <v>6800000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2774,19 +2774,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12990000</v>
+        <v>13690000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13000000</v>
+        <v>13700000</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>13700000</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>13700000</v>
+        <v>13799000</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>13799000</v>
+        <v>14220000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -3145,7 +3145,7 @@
         <v>7580000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>7950000</v>
+        <v>8399990</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>7580000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>7950000</v>
+        <v>8399990</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3274,31 +3274,31 @@
         <v>21950000</v>
       </c>
       <c r="G38" s="6" t="n">
+        <v>12989000</v>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>18498000</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>19000000</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="J38" s="6" t="n">
         <v>21900000</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="6" t="n">
         <v>21950000</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>22000000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3346,19 +3346,19 @@
         <v>4730000</v>
       </c>
       <c r="G39" s="6" t="n">
+        <v>1390000</v>
+      </c>
+      <c r="H39" s="6" t="n">
         <v>1890000</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>4599936</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>4690000</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4695000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+35,000 ت از رتبه 5 ترب (+0.7%)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.9%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3429,10 +3429,10 @@
         <v>15500000</v>
       </c>
       <c r="J40" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="K40" s="6" t="n">
         <v>17900000</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>20600000</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4300000</v>
+        <v>2050000</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>6950000</v>
@@ -3958,22 +3958,26 @@
         <v>7320000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>6790000</v>
+        <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6900000</v>
+        <v>5650000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>7150000</v>
+        <v>5698000</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9201000</v>
+        <v>9077000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3982,7 +3986,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+170,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+1,622,000 ت از رتبه 3 ترب (+28.5%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -4026,35 +4030,39 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="5" t="n">
         <v>12699500</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>12100000</v>
+        <v>8700000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>12500000</v>
+        <v>8900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>12699000</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>12699500</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>12750000</v>
+        <v>9100000</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>15800000</v>
-      </c>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>15700000</v>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+3,599,500 ت از رتبه 3 ترب (+39.6%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -4098,35 +4106,39 @@
       <c r="E49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="F49" s="5" t="n">
         <v>3500000</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>14000</v>
+        <v>3140000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>15000</v>
+        <v>3149000</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J49" s="6" t="n">
-        <v>2250000</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>3500000</v>
+        <v>3150000</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L49" s="6" t="n">
         <v>4570000</v>
       </c>
-      <c r="M49" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+350,000 ت از رتبه 3 ترب (+11.1%)</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -4815,7 +4827,7 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>8990000</v>
+        <v>9900000</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
@@ -5281,7 +5293,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>7150000</v>
+        <v>6800000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -6515,7 +6527,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>22200000</v>
+        <v>22250000</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6591,7 +6603,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8400000</v>
+        <v>8460000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -7215,7 +7227,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>7950000</v>
+        <v>8399990</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7291,7 +7303,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>7950000</v>
+        <v>8399990</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7443,7 +7455,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4184900</v>
+        <v>4120000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -9191,7 +9203,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11350000</v>
+        <v>11294100</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9347,7 +9359,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4184900</v>
+        <v>4120000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -651,7 +651,7 @@
         <v>10950000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>12200000</v>
+        <v>12900000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -708,31 +708,31 @@
         <v>20090000</v>
       </c>
       <c r="G3" s="6" t="n">
+        <v>18990000</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>19990000</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>20090000</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>20131000</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>20290000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>20790000</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>21190000</v>
+        <v>18990000</v>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
@@ -852,22 +852,22 @@
         <v>6150000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5650000</v>
+        <v>5679000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5679000</v>
+        <v>5690000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5690000</v>
+        <v>5800000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5700000</v>
+        <v>5800000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5800000</v>
+        <v>6000000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>5790000</v>
+        <v>7250000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+350,000 ت از رتبه 5 ترب (+6.0%)</t>
+          <t>+150,000 ت از رتبه 5 ترب (+2.5%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>8467000</v>
+        <v>9370000</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -1004,13 +1004,13 @@
         <v>1890000</v>
       </c>
       <c r="I7" s="6" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>4599936</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4690000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.9%)</t>
+          <t>+130,064 ت از رتبه 5 ترب (+2.8%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1152,31 +1152,31 @@
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>97000</v>
+        <v>100000</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>100000</v>
+        <v>108300</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>129600</v>
+        <v>131500</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۱ ترب (کف قیمت)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1226,7 +1226,7 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9900000</v>
+        <v>9885000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9999000</v>
@@ -1374,16 +1374,16 @@
         <v>5130000</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>5145000</v>
+        <v>5150000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5150000</v>
+        <v>5200000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5200000</v>
+        <v>5300000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5400000</v>
+        <v>5300000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1502,13 +1502,13 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11990000</v>
+        <v>13300000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11990000</v>
+        <v>13300000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>12000000</v>
+        <v>13300000</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>13300000</v>
@@ -1517,7 +1517,7 @@
         <v>13310000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21900000</v>
+        <v>21000000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="5" t="n">
         <v>7440000</v>
       </c>
       <c r="G15" s="6" t="n">
@@ -1586,19 +1586,19 @@
         <v>7400000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7440000</v>
+        <v>7400000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8460000</v>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+        <v>9120000</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+40,000 ت از رتبه 5 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1646,7 +1646,7 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5340000</v>
+        <v>5200000</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>5350000</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-720,000 ت از کف ترب (-13.5%)</t>
+          <t>-580,000 ت از کف ترب (-11.2%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1880,7 +1880,7 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9900000</v>
+        <v>9885000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9999000</v>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17147290</v>
+        <v>17255580</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         <v>7490000</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>7500000</v>
+        <v>8800000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>9590000</v>
+        <v>9790000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>13300000</v>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O23" s="6" t="n">
@@ -2267,7 +2267,7 @@
         <v>7100000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9077000</v>
+        <v>9087000</v>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
@@ -2406,13 +2406,13 @@
         <v>8400000</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>8499000</v>
+        <v>8500000</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>8500000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>8500000</v>
+        <v>8800000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
+        <v>13599000</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>13600000</v>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>13690000</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>13700000</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>13700000</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>13799000</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>14220000</v>
@@ -2996,19 +2996,21 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>9440000</v>
+        <v>9592330</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9440000</v>
+        <v>9889000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9592330</v>
+        <v>10440000</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9889000</v>
-      </c>
-      <c r="K34" s="6" t="n">
         <v>14160000</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L34" s="6" t="n">
         <v>7100000</v>
@@ -3130,7 +3132,7 @@
         <v>9500000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>7250000</v>
+        <v>7000000</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>7500000</v>
@@ -3145,7 +3147,7 @@
         <v>7580000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>8399990</v>
+        <v>8500000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3202,7 +3204,7 @@
         <v>9500000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>7250000</v>
+        <v>7000000</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>7500000</v>
@@ -3217,7 +3219,7 @@
         <v>7580000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>8399990</v>
+        <v>8500000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3270,7 +3272,7 @@
       <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="5" t="n">
         <v>21950000</v>
       </c>
       <c r="G38" s="6" t="n">
@@ -3283,22 +3285,22 @@
         <v>19000000</v>
       </c>
       <c r="J38" s="6" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="K38" s="6" t="n">
         <v>21900000</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>21950000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>17790000</v>
       </c>
-      <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+50,000 ت از رتبه 5 ترب (+0.2%)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -3352,13 +3354,13 @@
         <v>1890000</v>
       </c>
       <c r="I39" s="6" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="J39" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="6" t="n">
         <v>4599936</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4690000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
@@ -3370,7 +3372,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.9%)</t>
+          <t>+130,064 ت از رتبه 5 ترب (+2.8%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
@@ -3660,13 +3662,13 @@
         <v>8000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8064550</v>
+        <v>8489000</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>8489000</v>
+        <v>8500000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8500000</v>
+        <v>8900000</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3810,17 +3812,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7600000</v>
+        <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7615000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3837,14 +3839,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3890,19 +3892,23 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>45500</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>2050000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>6950000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>7350000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>7900000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
@@ -3977,7 +3983,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9077000</v>
+        <v>9087000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -5137,7 +5143,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5990000</v>
+        <v>5860000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -6451,7 +6457,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6603,7 +6609,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8460000</v>
+        <v>9120000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -7227,7 +7233,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>8399990</v>
+        <v>8500000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7303,7 +7309,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>8399990</v>
+        <v>8500000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7379,7 +7385,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5990000</v>
+        <v>5860000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7687,7 +7693,7 @@
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>27600000</v>
+        <v>27700000</v>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
@@ -8393,7 +8399,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -633,7 +633,7 @@
         <v>188</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>12780000</v>
+        <v>11210000</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>10200000</v>
@@ -660,11 +660,11 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+1,830,000 ت از رتبه 5 ترب (+16.7%)</t>
+          <t>+260,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
-        <v>2402640000</v>
+        <v>2107480000</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20090000</v>
+        <v>20690000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -714,10 +714,10 @@
         <v>19990000</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>20090000</v>
+        <v>20131000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20131000</v>
+        <v>20510000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>20790000</v>
@@ -727,16 +727,16 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1265670000</v>
+        <v>1303470000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6150000</v>
+        <v>6900000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5679000</v>
+        <v>5650000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5690000</v>
@@ -861,13 +861,13 @@
         <v>5800000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5800000</v>
+        <v>6000000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>7250000</v>
+        <v>7300000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه 5 ترب (+2.5%)</t>
+          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>104550000</v>
+        <v>117300000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>9370000</v>
+        <v>8763180</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -994,39 +994,39 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>4730000</v>
+      <c r="F7" s="8" t="n">
+        <v>4780000</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1390000</v>
+        <v>1890000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1890000</v>
+        <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3900000</v>
+        <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4200000</v>
+        <v>4695000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4599936</v>
+        <v>4780000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+130,064 ت از رتبه 5 ترب (+2.8%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>70950000</v>
+        <v>71700000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         <v>100000</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>116379</v>
+        <v>131500</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>129600</v>
+        <v>134750</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>131500</v>
+        <v>136100</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9885000</v>
+        <v>9895000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,13 +1226,13 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9885000</v>
+        <v>9895000</v>
       </c>
       <c r="J10" s="6" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>9999000</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>10000000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>10000000</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>98850000</v>
+        <v>98950000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1374,13 +1374,13 @@
         <v>5130000</v>
       </c>
       <c r="I12" s="6" t="n">
+        <v>5145000</v>
+      </c>
+      <c r="J12" s="6" t="n">
         <v>5150000</v>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>5200000</v>
-      </c>
       <c r="K12" s="6" t="n">
-        <v>5300000</v>
+        <v>5199000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5300000</v>
@@ -1450,7 +1450,7 @@
         <v>15000000</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>17880000</v>
+        <v>17250000</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>9500000</v>
@@ -1514,10 +1514,10 @@
         <v>13300000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13310000</v>
+        <v>13300000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21000000</v>
+        <v>21350000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,540,000 ت از رتبه 5 ترب (+49.1%)</t>
+          <t>+6,550,000 ت از رتبه 5 ترب (+49.2%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1571,13 +1571,13 @@
         <v>5</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7440000</v>
+        <v>7499000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1550000</v>
+        <v>7340000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7340000</v>
+        <v>7398000</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>7399000</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+40,000 ت از رتبه 5 ترب (+0.5%)</t>
+          <t>+99,000 ت از رتبه 5 ترب (+1.3%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>37200000</v>
+        <v>37495000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1649,13 +1649,13 @@
         <v>5200000</v>
       </c>
       <c r="H16" s="6" t="n">
+        <v>5339000</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>5340000</v>
+      </c>
+      <c r="J16" s="6" t="n">
         <v>5350000</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>5399000</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>5400000</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>5400000</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9885000</v>
+        <v>9895000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,13 +1880,13 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9885000</v>
+        <v>9895000</v>
       </c>
       <c r="J19" s="6" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>9999000</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>10000000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>10000000</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>98850000</v>
+        <v>98950000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>13300000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>7600000</v>
+        <v>7800000</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
@@ -2248,8 +2248,8 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>7320000</v>
+      <c r="F24" s="8" t="n">
+        <v>7050000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
@@ -2267,20 +2267,20 @@
         <v>7100000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9087000</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>9186000</v>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+220,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>36600000</v>
+        <v>35250000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2618,8 +2618,8 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5470000</v>
+      <c r="F29" s="5" t="n">
+        <v>5650000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5200000</v>
@@ -2634,23 +2634,23 @@
         <v>5450000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5470000</v>
+        <v>5500000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6800000</v>
       </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+150,000 ت از رتبه 5 ترب (+2.7%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>21880000</v>
+        <v>22600000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2774,19 +2774,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
+        <v>12990000</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>13599000</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>13600000</v>
       </c>
-      <c r="I31" s="6" t="n">
-        <v>13690000</v>
-      </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>13700000</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>14220000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>9592330</v>
+        <v>9889000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9889000</v>
+        <v>10650000</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>10440000</v>
+        <v>10650000</v>
       </c>
       <c r="J34" s="6" t="n">
         <v>14160000</v>
@@ -3272,8 +3272,8 @@
       <c r="E38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>21950000</v>
+      <c r="F38" s="8" t="n">
+        <v>19120000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>12989000</v>
@@ -3285,26 +3285,26 @@
         <v>19000000</v>
       </c>
       <c r="J38" s="6" t="n">
+        <v>19120000</v>
+      </c>
+      <c r="K38" s="6" t="n">
         <v>19500000</v>
       </c>
-      <c r="K38" s="6" t="n">
-        <v>21900000</v>
-      </c>
       <c r="L38" s="6" t="n">
-        <v>17790000</v>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>18690000</v>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>+50,000 ت از رتبه 5 ترب (+0.2%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>43900000</v>
+        <v>38240000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3344,39 +3344,39 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>4730000</v>
+      <c r="F39" s="8" t="n">
+        <v>4780000</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>1390000</v>
+        <v>1890000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1890000</v>
+        <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3900000</v>
+        <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4200000</v>
+        <v>4695000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4599936</v>
+        <v>4780000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+130,064 ت از رتبه 5 ترب (+2.8%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>70950000</v>
+        <v>71700000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3812,17 +3812,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3888,39 +3888,35 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="5" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
+        <v>2839550</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>3260000</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="J46" s="6" t="n">
         <v>4400000</v>
       </c>
-      <c r="H46" s="6" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="K46" s="6" t="n">
+        <v>4469000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>+331,000 ت از رتبه 5 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3961,7 +3957,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7320000</v>
+        <v>7050000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3983,7 +3979,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9087000</v>
+        <v>9186000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3992,11 +3988,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,622,000 ت از رتبه 3 ترب (+28.5%)</t>
+          <t>+1,352,000 ت از رتبه 3 ترب (+23.7%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14640000</v>
+        <v>14100000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4037,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12699500</v>
+        <v>12799000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4068,11 +4064,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,599,500 ت از رتبه 3 ترب (+39.6%)</t>
+          <t>+3,699,000 ت از رتبه 3 ترب (+40.6%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>25399000</v>
+        <v>25598000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4189,7 +4185,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>8350000</v>
+        <v>8690000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4222,11 +4218,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+1,500,000 ت از رتبه 3 ترب (+21.9%)</t>
+          <t>+1,840,000 ت از رتبه 3 ترب (+26.9%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>16700000</v>
+        <v>17380000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4267,7 +4263,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>21950000</v>
+        <v>19120000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4289,7 +4285,7 @@
         </is>
       </c>
       <c r="L51" s="6" t="n">
-        <v>17750000</v>
+        <v>18750000</v>
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
@@ -4298,11 +4294,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+9,050,000 ت از رتبه 3 ترب (+70.2%)</t>
+          <t>+6,220,000 ت از رتبه 3 ترب (+48.2%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>43900000</v>
+        <v>38240000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4343,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17350000</v>
+        <v>17830000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4376,11 +4372,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+5,850,000 ت از رتبه 3 ترب (+50.9%)</t>
+          <t>+6,330,000 ت از رتبه 3 ترب (+55.0%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>34700000</v>
+        <v>35660000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4421,7 +4417,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>11000000</v>
+        <v>7950000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4452,11 +4448,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+3,511,000 ت از رتبه 3 ترب (+46.9%)</t>
+          <t>+461,000 ت از رتبه 3 ترب (+6.2%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>22000000</v>
+        <v>15900000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -5121,7 +5117,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5270000</v>
+        <v>5140000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5152,11 +5148,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,320,000 ت از رتبه 3 ترب (+33.4%)</t>
+          <t>+1,190,000 ت از رتبه 3 ترب (+30.1%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10540000</v>
+        <v>10280000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5277,7 +5273,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5470000</v>
+        <v>5650000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5308,11 +5304,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+520,000 ت از رتبه 3 ترب (+10.5%)</t>
+          <t>+700,000 ت از رتبه 3 ترب (+14.1%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>21880000</v>
+        <v>22600000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -6009,7 +6005,7 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>4703670</v>
+        <v>4700000</v>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
@@ -6435,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4850000</v>
+        <v>4540000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6457,7 +6453,7 @@
         </is>
       </c>
       <c r="L79" s="6" t="n">
-        <v>5000000</v>
+        <v>5600000</v>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
@@ -6466,11 +6462,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4850000</v>
+        <v>4540000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6511,7 +6507,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15840000</v>
+        <v>15770000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6542,11 +6538,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+850,000 ت از رتبه 3 ترب (+5.7%)</t>
+          <t>+780,000 ت از رتبه 3 ترب (+5.2%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15840000</v>
+        <v>15770000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6587,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>7950000</v>
+        <v>8099000</v>
       </c>
       <c r="G81" s="6" t="n">
         <v>6190000</v>
@@ -6618,11 +6614,11 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>+1,750,000 ت از رتبه 3 ترب (+28.2%)</t>
+          <t>+1,899,000 ت از رتبه 3 ترب (+30.6%)</t>
         </is>
       </c>
       <c r="O81" s="6" t="n">
-        <v>7950000</v>
+        <v>8099000</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
@@ -6663,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6280000</v>
+        <v>6340000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6696,11 +6692,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+330,000 ت از رتبه 2 ترب (+5.5%)</t>
+          <t>+390,000 ت از رتبه 2 ترب (+6.6%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6280000</v>
+        <v>6340000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6741,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22930000</v>
+        <v>22980000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6772,11 +6768,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,130,000 ت از رتبه 3 ترب (+94.3%)</t>
+          <t>+11,180,000 ت از رتبه 3 ترب (+94.7%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22930000</v>
+        <v>22980000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6889,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>7400000</v>
+        <v>5710000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6920,11 +6916,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-1,599,000 ت از کف ترب (-17.8%)</t>
+          <t>-3,289,000 ت از کف ترب (-36.5%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>7400000</v>
+        <v>5710000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7363,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5270000</v>
+        <v>5140000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7394,11 +7390,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,320,000 ت از رتبه 3 ترب (+33.4%)</t>
+          <t>+1,190,000 ت از رتبه 3 ترب (+30.1%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5270000</v>
+        <v>5140000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7439,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3790000</v>
+        <v>3885000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7470,11 +7466,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+802,000 ت از رتبه 3 ترب (+26.8%)</t>
+          <t>+897,000 ت از رتبه 3 ترب (+30.0%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3790000</v>
+        <v>3885000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7537,7 +7533,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8335730</v>
+        <v>8330600</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7671,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>27340000</v>
+        <v>26670000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7693,7 +7689,7 @@
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>27700000</v>
+        <v>27900000</v>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
@@ -7702,11 +7698,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,990,000 ت از رتبه 3 ترب (+28.1%)</t>
+          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>27340000</v>
+        <v>26670000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7747,7 +7743,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5370000</v>
+        <v>5430000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7784,11 +7780,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+870,000 ت از رتبه 1 ترب (+19.3%)</t>
+          <t>+930,000 ت از رتبه 1 ترب (+20.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5370000</v>
+        <v>5430000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8009,7 +8005,7 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>4703670</v>
+        <v>4700000</v>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
@@ -8377,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4850000</v>
+        <v>4540000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8399,7 +8395,7 @@
         </is>
       </c>
       <c r="L104" s="6" t="n">
-        <v>5000000</v>
+        <v>5600000</v>
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
@@ -8408,11 +8404,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
+          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4850000</v>
+        <v>4540000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9343,7 +9339,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3790000</v>
+        <v>3885000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9374,11 +9370,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+802,000 ت از رتبه 3 ترب (+26.8%)</t>
+          <t>+897,000 ت از رتبه 3 ترب (+30.0%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3790000</v>
+        <v>3885000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9577,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>11000000</v>
+        <v>7950000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9612,11 +9608,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+3,511,000 ت از رتبه 3 ترب (+46.9%)</t>
+          <t>+461,000 ت از رتبه 3 ترب (+6.2%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>22000000</v>
+        <v>15900000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9837,7 +9833,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>19090000</v>
+        <v>19000000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10151,7 +10147,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>19090000</v>
+        <v>19000000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -10476,8 +10472,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L130" s="6" t="n">
-        <v>6950000</v>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
@@ -10713,7 +10711,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="n">
-        <v>7600000</v>
+        <v>7800000</v>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -639,16 +639,16 @@
         <v>10200000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10769000</v>
+        <v>10500000</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>10769000</v>
       </c>
       <c r="J2" s="6" t="n">
+        <v>10769000</v>
+      </c>
+      <c r="K2" s="6" t="n">
         <v>10800000</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>10950000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12900000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+260,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+410,000 ت از رتبه 5 ترب (+3.8%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20690000</v>
+        <v>20510000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -727,16 +727,16 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1303470000</v>
+        <v>1292130000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -776,20 +776,20 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>16830000</v>
+      <c r="F4" s="8" t="n">
+        <v>15365000</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>13620000</v>
+        <v>14990000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>14990000</v>
+        <v>15191000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>15191000</v>
+        <v>15360000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>15360000</v>
+        <v>15365000</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>15390000</v>
@@ -797,18 +797,18 @@
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+1,440,000 ت از رتبه 5 ترب (+9.4%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>504900000</v>
+        <v>460950000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -849,25 +849,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6900000</v>
+        <v>10080000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5650000</v>
+        <v>5690000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5690000</v>
+        <v>5800000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5800000</v>
+        <v>6000000</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>6000000</v>
+        <v>6100000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>7300000</v>
+        <v>7650000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
+          <t>+3,980,000 ت از رتبه 5 ترب (+65.2%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>117300000</v>
+        <v>171360000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>8763180</v>
+        <v>8500000</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -994,39 +994,39 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>4780000</v>
+      <c r="F7" s="5" t="n">
+        <v>4740000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H7" s="6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>4599936</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>4695000</v>
-      </c>
       <c r="K7" s="6" t="n">
-        <v>4780000</v>
+        <v>4670000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+70,000 ت از رتبه 5 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>71700000</v>
+        <v>71100000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         <v>116379</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>129600</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>131500</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>134750</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>136100</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9895000</v>
+        <v>9960000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,10 +1226,10 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9895000</v>
+        <v>9960000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9900000</v>
+        <v>9995000</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>9999000</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>98950000</v>
+        <v>99600000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>13513760</v>
+        <v>8610000</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -1368,19 +1368,19 @@
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>5090000</v>
+        <v>4990000</v>
       </c>
       <c r="H12" s="6" t="n">
+        <v>5120000</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>5145000</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>5150000</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>5199000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5300000</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-140,000 ت از کف ترب (-2.8%)</t>
+          <t>-40,000 ت از کف ترب (-0.8%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1502,22 +1502,22 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>13300000</v>
+        <v>11000000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>13300000</v>
+        <v>11980000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>13300000</v>
+        <v>11980000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>13300000</v>
+        <v>11980000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13300000</v>
+        <v>13150000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21350000</v>
+        <v>23978040</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,550,000 ت از رتبه 5 ترب (+49.2%)</t>
+          <t>+6,700,000 ت از رتبه 5 ترب (+51.0%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1574,7 +1574,7 @@
         <v>7499000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7340000</v>
+        <v>7390000</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>7398000</v>
@@ -1646,10 +1646,10 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
+        <v>5199000</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>5200000</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>5339000</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>5340000</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-580,000 ت از کف ترب (-11.2%)</t>
+          <t>-579,000 ت از کف ترب (-11.1%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1803,16 +1803,16 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>10000000</v>
+        <v>14500000</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>14500000</v>
+        <v>18000000</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>18000000</v>
+        <v>18900000</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>18900000</v>
+        <v>29500000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9895000</v>
+        <v>9960000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,10 +1880,10 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9895000</v>
+        <v>9960000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9900000</v>
+        <v>9995000</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>9999000</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>98950000</v>
+        <v>99600000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>13513760</v>
+        <v>8610000</v>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17255580</v>
+        <v>16890000</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>13300000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>7800000</v>
+        <v>6902400</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
@@ -2248,8 +2248,8 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>7050000</v>
+      <c r="F24" s="5" t="n">
+        <v>7300000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
@@ -2258,29 +2258,29 @@
         <v>6300000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6845000</v>
+        <v>6900000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>6900000</v>
+        <v>7100000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>7100000</v>
+        <v>7199000</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>9186000</v>
       </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+101,000 ت از رتبه 5 ترب (+1.4%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>35250000</v>
+        <v>36500000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2332,13 +2332,13 @@
         <v>6980000</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7500000</v>
+        <v>8200000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8200000</v>
+        <v>8800000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8600000</v>
+        <v>8900000</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>15900000</v>
@@ -2470,19 +2470,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>10800000</v>
+        <v>11000000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>11000000</v>
+        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>15500000</v>
+        <v>17900000</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>17900000</v>
+        <v>20600000</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2619,13 +2619,13 @@
         <v>4</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>5650000</v>
+        <v>5670000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5200000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>5340000</v>
+        <v>5390000</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>5400000</v>
@@ -2646,11 +2646,11 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+150,000 ت از رتبه 5 ترب (+2.7%)</t>
+          <t>+170,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>22600000</v>
+        <v>22680000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>19090000</v>
+        <v>18518040</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>6000000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>6500000</v>
+        <v>6999000</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>6999000</v>
@@ -2999,13 +2999,17 @@
         <v>9889000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>10650000</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>10650000</v>
-      </c>
-      <c r="J34" s="6" t="n">
         <v>14160000</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3129,13 +3133,13 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="G36" s="6" t="n">
+        <v>6980000</v>
+      </c>
+      <c r="H36" s="6" t="n">
         <v>7000000</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>7500000</v>
@@ -3144,7 +3148,7 @@
         <v>7500000</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>7580000</v>
+        <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>8500000</v>
@@ -3156,11 +3160,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,920,000 ت از رتبه 5 ترب (+25.3%)</t>
+          <t>+1,000,000 ت از رتبه 5 ترب (+13.3%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3201,13 +3205,13 @@
         <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="G37" s="6" t="n">
+        <v>6980000</v>
+      </c>
+      <c r="H37" s="6" t="n">
         <v>7000000</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>7500000</v>
@@ -3216,7 +3220,7 @@
         <v>7500000</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>7580000</v>
+        <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>8500000</v>
@@ -3228,11 +3232,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,920,000 ت از رتبه 5 ترب (+25.3%)</t>
+          <t>+1,000,000 ت از رتبه 5 ترب (+13.3%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3273,38 +3277,38 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>19120000</v>
+        <v>19250000</v>
       </c>
       <c r="G38" s="6" t="n">
+        <v>12821000</v>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>12989000</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>18498000</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="J38" s="6" t="n">
         <v>19000000</v>
       </c>
-      <c r="J38" s="6" t="n">
-        <v>19120000</v>
-      </c>
       <c r="K38" s="6" t="n">
-        <v>19500000</v>
+        <v>19250000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>18690000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>38240000</v>
+        <v>38500000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3344,39 +3348,39 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>4780000</v>
+      <c r="F39" s="5" t="n">
+        <v>4740000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H39" s="6" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="I39" s="6" t="n">
         <v>4200000</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="J39" s="6" t="n">
         <v>4599936</v>
       </c>
-      <c r="J39" s="6" t="n">
-        <v>4695000</v>
-      </c>
       <c r="K39" s="6" t="n">
-        <v>4780000</v>
+        <v>4670000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+70,000 ت از رتبه 5 ترب (+1.5%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>71700000</v>
+        <v>71100000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3422,19 +3426,19 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>10800000</v>
+        <v>11000000</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>11000000</v>
+        <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>15500000</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>15500000</v>
+        <v>17900000</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>17900000</v>
+        <v>20600000</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3656,19 +3660,19 @@
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>6980000</v>
+        <v>8000000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>8000000</v>
+        <v>8489000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8489000</v>
+        <v>8500000</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>8500000</v>
+        <v>8900000</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8900000</v>
+        <v>9083230</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3892,19 +3896,19 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>2839550</v>
+        <v>2989000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>3260000</v>
+        <v>3200000</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>4150000</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>4400000</v>
+        <v>4300000</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>4469000</v>
+        <v>4350000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
@@ -3916,7 +3920,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>+331,000 ت از رتبه 5 ترب (+7.4%)</t>
+          <t>+450,000 ت از رتبه 5 ترب (+10.3%)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3957,26 +3961,22 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7050000</v>
+        <v>7300000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>5616000</v>
+        <v>4500000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>5650000</v>
+        <v>6300000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>5698000</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6900000</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>7199000</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>9186000</v>
@@ -3988,11 +3988,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,352,000 ت از رتبه 3 ترب (+23.7%)</t>
+          <t>+101,000 ت از رتبه 5 ترب (+1.4%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14100000</v>
+        <v>14600000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4032,39 +4032,35 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="8" t="n">
         <v>12799000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>8700000</v>
+        <v>12100000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>8900000</v>
+        <v>12500000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>12699000</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>12750000</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>12799000</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>15700000</v>
       </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,699,000 ت از رتبه 3 ترب (+40.6%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -4185,7 +4181,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>8690000</v>
+        <v>8350000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4218,11 +4214,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+1,840,000 ت از رتبه 3 ترب (+26.9%)</t>
+          <t>+1,500,000 ت از رتبه 3 ترب (+21.9%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>17380000</v>
+        <v>16700000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4263,7 +4259,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>19120000</v>
+        <v>19250000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4294,11 +4290,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+6,220,000 ت از رتبه 3 ترب (+48.2%)</t>
+          <t>+6,350,000 ت از رتبه 3 ترب (+49.2%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>38240000</v>
+        <v>38500000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4339,7 +4335,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17830000</v>
+        <v>17950000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4372,11 +4368,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,330,000 ت از رتبه 3 ترب (+55.0%)</t>
+          <t>+6,450,000 ت از رتبه 3 ترب (+56.1%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35660000</v>
+        <v>35900000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4417,7 +4413,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>7950000</v>
+        <v>7830000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4448,11 +4444,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+461,000 ت از رتبه 3 ترب (+6.2%)</t>
+          <t>+341,000 ت از رتبه 3 ترب (+4.6%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>15900000</v>
+        <v>15660000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4829,7 +4825,7 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>9900000</v>
+        <v>8990000</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
@@ -5117,7 +5113,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5140000</v>
+        <v>5099500</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5139,7 +5135,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5860000</v>
+        <v>5990000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5148,11 +5144,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,190,000 ت از رتبه 3 ترب (+30.1%)</t>
+          <t>+1,149,500 ت از رتبه 3 ترب (+29.1%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10280000</v>
+        <v>10199000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5273,7 +5269,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5650000</v>
+        <v>5670000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5304,11 +5300,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+700,000 ت از رتبه 3 ترب (+14.1%)</t>
+          <t>+720,000 ت از رتبه 3 ترب (+14.5%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>22600000</v>
+        <v>22680000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -6005,7 +6001,7 @@
         </is>
       </c>
       <c r="L73" s="6" t="n">
-        <v>4700000</v>
+        <v>4703670</v>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
@@ -6207,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27970000</v>
+        <v>27955000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6238,11 +6234,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+12,370,000 ت از رتبه 3 ترب (+79.3%)</t>
+          <t>+12,355,000 ت از رتبه 3 ترب (+79.2%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27970000</v>
+        <v>27955000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6355,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12009000</v>
+        <v>12750000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -6386,11 +6382,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+2,809,000 ت از رتبه 3 ترب (+30.5%)</t>
+          <t>+3,550,000 ت از رتبه 3 ترب (+38.6%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12009000</v>
+        <v>12750000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6507,7 +6503,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15770000</v>
+        <v>15860000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6538,11 +6534,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+780,000 ت از رتبه 3 ترب (+5.2%)</t>
+          <t>+870,000 ت از رتبه 3 ترب (+5.8%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15770000</v>
+        <v>15860000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6659,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6340000</v>
+        <v>6400000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6692,11 +6688,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+390,000 ت از رتبه 2 ترب (+6.6%)</t>
+          <t>+450,000 ت از رتبه 2 ترب (+7.6%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6340000</v>
+        <v>6400000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6737,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22980000</v>
+        <v>22995000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6768,11 +6764,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,180,000 ت از رتبه 3 ترب (+94.7%)</t>
+          <t>+11,195,000 ت از رتبه 3 ترب (+94.9%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22980000</v>
+        <v>22995000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6809,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2740000</v>
+        <v>2710000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6844,11 +6840,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+295,000 ت از رتبه 3 ترب (+12.1%)</t>
+          <t>+265,000 ت از رتبه 3 ترب (+10.8%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2740000</v>
+        <v>2710000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6885,7 +6881,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>5710000</v>
+        <v>5695000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6916,11 +6912,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-3,289,000 ت از کف ترب (-36.5%)</t>
+          <t>-3,304,000 ت از کف ترب (-36.7%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>5710000</v>
+        <v>5695000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7207,7 +7203,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7238,11 +7234,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
+          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7283,7 +7279,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>9500000</v>
+        <v>8500000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7314,11 +7310,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
+          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>19000000</v>
+        <v>17000000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7359,7 +7355,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5140000</v>
+        <v>5099500</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7381,7 +7377,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5860000</v>
+        <v>5990000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7390,11 +7386,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,190,000 ت از رتبه 3 ترب (+30.1%)</t>
+          <t>+1,149,500 ت از رتبه 3 ترب (+29.1%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5140000</v>
+        <v>5099500</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7435,7 +7431,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3885000</v>
+        <v>3840000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7457,7 +7453,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4120000</v>
+        <v>4280000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7466,11 +7462,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+897,000 ت از رتبه 3 ترب (+30.0%)</t>
+          <t>+852,000 ت از رتبه 3 ترب (+28.5%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3885000</v>
+        <v>3840000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7689,7 +7685,7 @@
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>27900000</v>
+        <v>29700000</v>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
@@ -7743,7 +7739,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5430000</v>
+        <v>5490000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7780,11 +7776,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+930,000 ت از رتبه 1 ترب (+20.7%)</t>
+          <t>+990,000 ت از رتبه 1 ترب (+22.0%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5430000</v>
+        <v>5490000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8005,7 +8001,7 @@
         </is>
       </c>
       <c r="L99" s="6" t="n">
-        <v>4700000</v>
+        <v>4703670</v>
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
@@ -8215,7 +8211,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27970000</v>
+        <v>27955000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8252,7 +8248,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27970000</v>
+        <v>27955000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -9205,7 +9201,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11294100</v>
+        <v>11194590</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9339,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3885000</v>
+        <v>3840000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9361,7 +9357,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4120000</v>
+        <v>4280000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9370,11 +9366,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+897,000 ت از رتبه 3 ترب (+30.0%)</t>
+          <t>+852,000 ت از رتبه 3 ترب (+28.5%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3885000</v>
+        <v>3840000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9577,7 +9573,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>7950000</v>
+        <v>7830000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9608,11 +9604,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+461,000 ت از رتبه 3 ترب (+6.2%)</t>
+          <t>+341,000 ت از رتبه 3 ترب (+4.6%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>15900000</v>
+        <v>15660000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9833,7 +9829,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>19000000</v>
+        <v>18518040</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10143,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>19000000</v>
+        <v>18518040</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
@@ -10711,7 +10707,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="n">
-        <v>7800000</v>
+        <v>7600000</v>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -645,10 +645,10 @@
         <v>10769000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10769000</v>
+        <v>10800000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12900000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+410,000 ت از رتبه 5 ترب (+3.8%)</t>
+          <t>+260,000 ت از رتبه 5 ترب (+2.4%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>15365000</v>
+        <v>15670000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14990000</v>
@@ -789,26 +789,26 @@
         <v>15360000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>15365000</v>
+        <v>15390000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>15390000</v>
+        <v>15670000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>460950000</v>
+        <v>470100000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -855,13 +855,13 @@
         <v>5690000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5800000</v>
+        <v>5950000</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>6000000</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>6000000</v>
+        <v>6099900</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>6100000</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="L6" s="6" t="n">
-        <v>8500000</v>
+        <v>9200000</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -994,39 +994,39 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>4740000</v>
+      <c r="F7" s="8" t="n">
+        <v>4710000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3800000</v>
+        <v>4200000</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>4200000</v>
+        <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4599936</v>
+        <v>4695000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4670000</v>
+        <v>4710000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه 5 ترب (+1.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>71100000</v>
+        <v>70650000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1155,16 +1155,16 @@
         <v>100000</v>
       </c>
       <c r="H9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>116379</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>129600</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>131500</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>134750</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9960000</v>
+        <v>9970000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,7 +1226,7 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9960000</v>
+        <v>9970000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9995000</v>
@@ -1235,7 +1235,7 @@
         <v>9999000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>10000000</v>
+        <v>9800000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>99600000</v>
+        <v>99700000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7890000</v>
+        <v>8690000</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>6799000</v>
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>8610000</v>
+        <v>11754940</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+290,000 ت از رتبه 3 ترب (+3.8%)</t>
+          <t>+1,090,000 ت از رتبه 3 ترب (+14.3%)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
-        <v>15780000</v>
+        <v>17380000</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1364,11 +1364,11 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="8" t="n">
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4990000</v>
+        <v>4900000</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>5120000</v>
@@ -1385,14 +1385,14 @@
       <c r="L12" s="6" t="n">
         <v>5300000</v>
       </c>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-40,000 ت از کف ترب (-0.8%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1444,7 +1444,7 @@
         <v>13800000</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>13900000</v>
+        <v>14500000</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>15000000</v>
@@ -1505,19 +1505,19 @@
         <v>11000000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11980000</v>
+        <v>11590000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11980000</v>
+        <v>11590000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11980000</v>
+        <v>11590000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13150000</v>
+        <v>11600000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>23978040</v>
+        <v>23506170</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,700,000 ت از رتبه 5 ترب (+51.0%)</t>
+          <t>+8,250,000 ت از رتبه 5 ترب (+71.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1570,7 +1570,7 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="8" t="n">
         <v>7499000</v>
       </c>
       <c r="G15" s="6" t="n">
@@ -1583,22 +1583,22 @@
         <v>7399000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7400000</v>
+        <v>7499000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7400000</v>
+        <v>7499000</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>9120000</v>
       </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+99,000 ت از رتبه 5 ترب (+1.3%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1803,7 +1803,7 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>14500000</v>
+        <v>17500000</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>18000000</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9960000</v>
+        <v>9970000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,7 +1880,7 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9960000</v>
+        <v>9970000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9995000</v>
@@ -1889,7 +1889,7 @@
         <v>9999000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>10000000</v>
+        <v>9800000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>99600000</v>
+        <v>99700000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>8610000</v>
+        <v>11754940</v>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16890000</v>
+        <v>17351400</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2189,13 +2189,13 @@
         <v>8800000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>9790000</v>
+        <v>9660000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>13300000</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>6902400</v>
+        <v>7600000</v>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
@@ -2248,35 +2248,35 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="8" t="n">
         <v>7300000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>6300000</v>
+        <v>6900000</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>6900000</v>
+        <v>7100000</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>7100000</v>
+        <v>7370000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>7199000</v>
+        <v>7390000</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>9186000</v>
       </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+101,000 ت از رتبه 5 ترب (+1.4%)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2341,7 +2341,7 @@
         <v>8900000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15900000</v>
+        <v>16950000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="H27" s="6" t="n">
         <v>11000000</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>15500000</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>15500000</v>
       </c>
       <c r="J27" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="K27" s="6" t="n">
         <v>17900000</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>20600000</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>19500000</v>
@@ -2625,19 +2625,19 @@
         <v>5200000</v>
       </c>
       <c r="H29" s="6" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="I29" s="6" t="n">
         <v>5390000</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>5400000</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>5450000</v>
       </c>
-      <c r="K29" s="6" t="n">
-        <v>5500000</v>
-      </c>
       <c r="L29" s="6" t="n">
-        <v>6800000</v>
+        <v>7150000</v>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+170,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>+220,000 ت از رتبه 5 ترب (+4.0%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2780,10 +2780,10 @@
         <v>13000000</v>
       </c>
       <c r="I31" s="6" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="J31" s="6" t="n">
         <v>13599000</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>13600000</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>13700000</v>
@@ -2851,10 +2851,10 @@
         <v>11300000</v>
       </c>
       <c r="H32" s="6" t="n">
+        <v>12490000</v>
+      </c>
+      <c r="I32" s="6" t="n">
         <v>12497000</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>12500000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>12500000</v>
@@ -2863,7 +2863,7 @@
         <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>18518040</v>
+        <v>17990000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
+        <v>9592330</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>9889000</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>14160000</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>7500000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>8500000</v>
+        <v>8600000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>7500000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>8500000</v>
+        <v>8600000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
         <v>12989000</v>
       </c>
       <c r="I38" s="6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="J38" s="6" t="n">
         <v>18498000</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>19000000</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>19250000</v>
@@ -3348,39 +3348,39 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>4740000</v>
+      <c r="F39" s="8" t="n">
+        <v>4710000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>3800000</v>
+        <v>4200000</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4200000</v>
+        <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4599936</v>
+        <v>4695000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4670000</v>
+        <v>4710000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+70,000 ت از رتبه 5 ترب (+1.5%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>71100000</v>
+        <v>70650000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="H40" s="6" t="n">
         <v>11000000</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>15500000</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>15500000</v>
       </c>
       <c r="J40" s="6" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="K40" s="6" t="n">
         <v>17900000</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>20600000</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>8000000</v>
       </c>
       <c r="H43" s="6" t="n">
+        <v>8064550</v>
+      </c>
+      <c r="I43" s="6" t="n">
         <v>8489000</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="J43" s="6" t="n">
         <v>8500000</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="6" t="n">
         <v>8900000</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>9083230</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3816,17 +3816,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7600000</v>
+        <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7615000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3843,14 +3843,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3892,35 +3892,39 @@
       <c r="E46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="8" t="n">
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>2989000</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>3200000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4150000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>4300000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>4350000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>+450,000 ت از رتبه 5 ترب (+10.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3964,19 +3968,23 @@
         <v>7300000</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>4500000</v>
+        <v>5616000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>6300000</v>
+        <v>5650000</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>6900000</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>7199000</v>
+        <v>5698000</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L47" s="6" t="n">
         <v>9186000</v>
@@ -3988,7 +3996,7 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+101,000 ت از رتبه 5 ترب (+1.4%)</t>
+          <t>+1,602,000 ت از رتبه 3 ترب (+28.1%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -4032,35 +4040,39 @@
       <c r="E48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="5" t="n">
         <v>12799000</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>12100000</v>
+        <v>8700000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>12500000</v>
+        <v>8900000</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>12699000</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>12750000</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>12799000</v>
+        <v>9100000</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L48" s="6" t="n">
         <v>15700000</v>
       </c>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+3,699,000 ت از رتبه 3 ترب (+40.6%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -4335,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17950000</v>
+        <v>17970000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4368,11 +4380,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,450,000 ت از رتبه 3 ترب (+56.1%)</t>
+          <t>+6,470,000 ت از رتبه 3 ترب (+56.3%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35900000</v>
+        <v>35940000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4413,7 +4425,7 @@
         <v>2</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>7830000</v>
+        <v>7810000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>6750000</v>
@@ -4444,11 +4456,11 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>+341,000 ت از رتبه 3 ترب (+4.6%)</t>
+          <t>+321,000 ت از رتبه 3 ترب (+4.3%)</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
-        <v>15660000</v>
+        <v>15620000</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
@@ -4825,7 +4837,7 @@
         </is>
       </c>
       <c r="L58" s="6" t="n">
-        <v>8990000</v>
+        <v>7900000</v>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
@@ -4979,7 +4991,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7300000</v>
+        <v>7305320</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5135,7 +5147,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5990000</v>
+        <v>5980000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5215,7 +5227,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>19000000</v>
+        <v>8075000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5291,7 +5303,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6800000</v>
+        <v>5500000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -6427,7 +6439,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4540000</v>
+        <v>4530000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6458,11 +6470,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+675,000 ت از رتبه 3 ترب (+17.5%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4540000</v>
+        <v>4530000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6503,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15860000</v>
+        <v>15940000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6525,7 +6537,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>22250000</v>
+        <v>21800000</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6534,11 +6546,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+870,000 ت از رتبه 3 ترب (+5.8%)</t>
+          <t>+950,000 ت از رتبه 3 ترب (+6.3%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15860000</v>
+        <v>15940000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6655,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6400000</v>
+        <v>6430000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6688,11 +6700,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+450,000 ت از رتبه 2 ترب (+7.6%)</t>
+          <t>+480,000 ت از رتبه 2 ترب (+8.1%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6400000</v>
+        <v>6430000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6733,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22995000</v>
+        <v>22997000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6764,11 +6776,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,195,000 ت از رتبه 3 ترب (+94.9%)</t>
+          <t>+11,197,000 ت از رتبه 3 ترب (+94.9%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22995000</v>
+        <v>22997000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6809,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2710000</v>
+        <v>2747000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6840,11 +6852,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+265,000 ت از رتبه 3 ترب (+10.8%)</t>
+          <t>+302,000 ت از رتبه 3 ترب (+12.4%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2710000</v>
+        <v>2747000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6881,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>5695000</v>
+        <v>5990000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6912,11 +6924,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-3,304,000 ت از کف ترب (-36.7%)</t>
+          <t>-3,009,000 ت از کف ترب (-33.4%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>5695000</v>
+        <v>5990000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7237,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>8500000</v>
+        <v>8600000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7301,7 +7313,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>8500000</v>
+        <v>8600000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7377,7 +7389,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5990000</v>
+        <v>5980000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7431,7 +7443,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3840000</v>
+        <v>3940000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7453,7 +7465,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4280000</v>
+        <v>4250000</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7462,11 +7474,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+852,000 ت از رتبه 3 ترب (+28.5%)</t>
+          <t>+952,000 ت از رتبه 3 ترب (+31.9%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3840000</v>
+        <v>3940000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7663,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>26670000</v>
+        <v>27320000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7685,7 +7697,7 @@
         </is>
       </c>
       <c r="L95" s="6" t="n">
-        <v>29700000</v>
+        <v>31000000</v>
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
@@ -7694,11 +7706,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
+          <t>+5,970,000 ت از رتبه 3 ترب (+28.0%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>26670000</v>
+        <v>27320000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7739,7 +7751,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5490000</v>
+        <v>5520000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7776,11 +7788,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+990,000 ت از رتبه 1 ترب (+22.0%)</t>
+          <t>+1,020,000 ت از رتبه 1 ترب (+22.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5490000</v>
+        <v>5520000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8369,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4540000</v>
+        <v>4530000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8400,11 +8412,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+685,000 ت از رتبه 3 ترب (+17.8%)</t>
+          <t>+675,000 ت از رتبه 3 ترب (+17.5%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4540000</v>
+        <v>4530000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9123,7 +9135,7 @@
         </is>
       </c>
       <c r="L113" s="6" t="n">
-        <v>7900000</v>
+        <v>8990000</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -9201,7 +9213,7 @@
         </is>
       </c>
       <c r="L114" s="6" t="n">
-        <v>11194590</v>
+        <v>11200210</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
@@ -9335,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3840000</v>
+        <v>3940000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9357,7 +9369,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4280000</v>
+        <v>4250000</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9366,11 +9378,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+852,000 ت از رتبه 3 ترب (+28.5%)</t>
+          <t>+952,000 ت از رتبه 3 ترب (+31.9%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3840000</v>
+        <v>3940000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9516,10 +9528,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L118" s="6" t="n">
+        <v>9200000</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
@@ -9573,7 +9583,7 @@
         <v>2</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>7830000</v>
+        <v>7810000</v>
       </c>
       <c r="G119" s="6" t="n">
         <v>6750000</v>
@@ -9604,11 +9614,11 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>+341,000 ت از رتبه 3 ترب (+4.6%)</t>
+          <t>+321,000 ت از رتبه 3 ترب (+4.3%)</t>
         </is>
       </c>
       <c r="O119" s="6" t="n">
-        <v>15660000</v>
+        <v>15620000</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
@@ -9829,7 +9839,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>18518040</v>
+        <v>17990000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10143,7 +10153,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>18518040</v>
+        <v>17990000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -642,13 +642,13 @@
         <v>10500000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10769000</v>
+        <v>10879000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10950000</v>
+        <v>10999000</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>12900000</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+260,000 ت از رتبه 5 ترب (+2.4%)</t>
+          <t>+211,000 ت از رتبه 5 ترب (+1.9%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20510000</v>
+        <v>20210000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -717,10 +717,10 @@
         <v>20131000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20510000</v>
+        <v>20210000</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20790000</v>
+        <v>20290000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18990000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1292130000</v>
+        <v>1273230000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10080000</v>
+        <v>6900000</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>5690000</v>
@@ -858,16 +858,16 @@
         <v>5950000</v>
       </c>
       <c r="I5" s="6" t="n">
+        <v>5950000</v>
+      </c>
+      <c r="J5" s="6" t="n">
         <v>6000000</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>6099900</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>6100000</v>
-      </c>
       <c r="L5" s="6" t="n">
-        <v>7650000</v>
+        <v>7620000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+3,980,000 ت از رتبه 5 ترب (+65.2%)</t>
+          <t>+800,100 ت از رتبه 5 ترب (+13.1%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>171360000</v>
+        <v>117300000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -994,8 +994,8 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="n">
-        <v>4710000</v>
+      <c r="F7" s="5" t="n">
+        <v>4830000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1007,26 +1007,26 @@
         <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
+        <v>4670000</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>4695000</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>4710000</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+135,000 ت از رتبه 5 ترب (+2.9%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>70650000</v>
+        <v>72450000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>100000</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>108300</v>
+        <v>101200</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>116379</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9970000</v>
+        <v>9980000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,7 +1226,7 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9970000</v>
+        <v>9980000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9995000</v>
@@ -1235,7 +1235,7 @@
         <v>9999000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>9800000</v>
+        <v>10200000</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>99700000</v>
+        <v>99800000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1288,17 +1288,17 @@
       <c r="E11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="8" t="n">
         <v>8690000</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>6799000</v>
+        <v>7600000</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>7600000</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7600000</v>
+        <v>8999000</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1311,16 +1311,16 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>11754940</v>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>11430000</v>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+1,090,000 ت از رتبه 3 ترب (+14.3%)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1364,35 +1364,35 @@
       <c r="E12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="11" t="n">
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4900000</v>
+        <v>4980000</v>
       </c>
       <c r="H12" s="6" t="n">
+        <v>5020000</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>5120000</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="J12" s="6" t="n">
         <v>5130000</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>5145000</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>5150000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5300000</v>
       </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-30,000 ت از کف ترب (-0.6%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1447,7 +1447,7 @@
         <v>14500000</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>15000000</v>
+        <v>16000000</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>17250000</v>
@@ -1502,22 +1502,22 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>11000000</v>
+        <v>12800000</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>11590000</v>
+        <v>12800000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>11590000</v>
+        <v>12800000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>11590000</v>
+        <v>12900000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>11600000</v>
+        <v>13000000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>23506170</v>
+        <v>21047760</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+8,250,000 ت از رتبه 5 ترب (+71.1%)</t>
+          <t>+6,850,000 ت از رتبه 5 ترب (+52.7%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1577,28 +1577,28 @@
         <v>7390000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7398000</v>
+        <v>7499000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7399000</v>
+        <v>7499000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7499000</v>
+        <v>7500000</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>7499000</v>
+        <v>7500000</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>9120000</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1803,7 +1803,7 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>17500000</v>
+        <v>17000000</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>18000000</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9970000</v>
+        <v>9980000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,7 +1880,7 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9970000</v>
+        <v>9980000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9995000</v>
@@ -1889,7 +1889,7 @@
         <v>9999000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9800000</v>
+        <v>10200000</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>99700000</v>
+        <v>99800000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2020,17 +2020,17 @@
       <c r="E21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="11" t="n">
         <v>7450000</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>6799000</v>
+        <v>7600000</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>7600000</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>7600000</v>
+        <v>8999000</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2043,16 +2043,16 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>11754940</v>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+        <v>11430000</v>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>-150,000 ت از کف ترب (-2.0%)</t>
         </is>
       </c>
       <c r="O21" s="6" t="n">
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>17351400</v>
+        <v>16882550</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>8800000</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>9660000</v>
+        <v>9700000</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>13300000</v>
@@ -2249,38 +2249,38 @@
         <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>7300000</v>
+        <v>7130000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
       </c>
       <c r="H24" s="6" t="n">
+        <v>6290000</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="J24" s="6" t="n">
         <v>6900000</v>
       </c>
-      <c r="I24" s="6" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="6" t="n">
         <v>7370000</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>7390000</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>9186000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>36500000</v>
+        <v>35650000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>8900000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>16950000</v>
+        <v>16000000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>10800000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>11000000</v>
+        <v>11300000</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>15500000</v>
@@ -2631,10 +2631,10 @@
         <v>5390000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5400000</v>
+        <v>5450000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5450000</v>
+        <v>5500000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>7150000</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+220,000 ت از رتبه 5 ترب (+4.0%)</t>
+          <t>+170,000 ت از رتبه 5 ترب (+3.1%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2863,7 +2863,7 @@
         <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>17990000</v>
+        <v>17590000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -3001,10 +3001,8 @@
       <c r="H34" s="6" t="n">
         <v>9889000</v>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="I34" s="6" t="n">
+        <v>14160000</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3133,22 +3131,22 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>6980000</v>
+        <v>7500000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>7500000</v>
+        <v>7700000</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>7500000</v>
+        <v>7700000</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>8600000</v>
@@ -3160,11 +3158,11 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>+1,000,000 ت از رتبه 5 ترب (+13.3%)</t>
+          <t>+1,800,000 ت از رتبه 5 ترب (+23.4%)</t>
         </is>
       </c>
       <c r="O36" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -3205,22 +3203,22 @@
         <v>2</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6980000</v>
+        <v>7500000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>7000000</v>
+        <v>7500000</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>7500000</v>
+        <v>7700000</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>7500000</v>
+        <v>7700000</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>8600000</v>
@@ -3232,11 +3230,11 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>+1,000,000 ت از رتبه 5 ترب (+13.3%)</t>
+          <t>+1,800,000 ت از رتبه 5 ترب (+23.4%)</t>
         </is>
       </c>
       <c r="O37" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -3348,8 +3346,8 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>4710000</v>
+      <c r="F39" s="5" t="n">
+        <v>4830000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3361,26 +3359,26 @@
         <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
+        <v>4670000</v>
+      </c>
+      <c r="K39" s="6" t="n">
         <v>4695000</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4710000</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+135,000 ت از رتبه 5 ترب (+2.9%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>70650000</v>
+        <v>72450000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3429,7 +3427,7 @@
         <v>10800000</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>11000000</v>
+        <v>11300000</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>15500000</v>
@@ -3816,17 +3814,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3843,14 +3841,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3896,35 +3894,31 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>6200000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>6800000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>11000000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3965,7 +3959,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7300000</v>
+        <v>7130000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3996,11 +3990,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,602,000 ت از رتبه 3 ترب (+28.1%)</t>
+          <t>+1,432,000 ت از رتبه 3 ترب (+25.1%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14600000</v>
+        <v>14260000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4063,7 +4057,7 @@
         </is>
       </c>
       <c r="L48" s="6" t="n">
-        <v>15700000</v>
+        <v>11000000</v>
       </c>
       <c r="M48" s="7" t="inlineStr">
         <is>
@@ -4139,7 +4133,7 @@
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>4570000</v>
+        <v>4550000</v>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>8350000</v>
+        <v>8550000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4226,11 +4220,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+1,500,000 ت از رتبه 3 ترب (+21.9%)</t>
+          <t>+1,700,000 ت از رتبه 3 ترب (+24.8%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>16700000</v>
+        <v>17100000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4347,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17970000</v>
+        <v>17980000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4380,11 +4374,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,470,000 ت از رتبه 3 ترب (+56.3%)</t>
+          <t>+6,480,000 ت از رتبه 3 ترب (+56.3%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35940000</v>
+        <v>35960000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4991,7 +4985,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7305320</v>
+        <v>7200000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5125,7 +5119,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5099500</v>
+        <v>5080000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5156,11 +5150,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,149,500 ت از رتبه 3 ترب (+29.1%)</t>
+          <t>+1,130,000 ت از رتبه 3 ترب (+28.6%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10199000</v>
+        <v>10160000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5227,7 +5221,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>8075000</v>
+        <v>20000000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5303,7 +5297,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>5500000</v>
+        <v>7150000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5615,7 +5609,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4150000</v>
+        <v>4621120</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -6439,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4530000</v>
+        <v>4850000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6470,11 +6464,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+675,000 ت از رتبه 3 ترب (+17.5%)</t>
+          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4530000</v>
+        <v>4850000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6537,7 +6531,7 @@
         </is>
       </c>
       <c r="L80" s="6" t="n">
-        <v>21800000</v>
+        <v>21900000</v>
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
@@ -6667,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6430000</v>
+        <v>6460000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6700,11 +6694,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+480,000 ت از رتبه 2 ترب (+8.1%)</t>
+          <t>+510,000 ت از رتبه 2 ترب (+8.6%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6430000</v>
+        <v>6460000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6745,7 +6739,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22997000</v>
+        <v>22998000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6776,11 +6770,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,197,000 ت از رتبه 3 ترب (+94.9%)</t>
+          <t>+11,198,000 ت از رتبه 3 ترب (+94.9%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22997000</v>
+        <v>22998000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6821,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2747000</v>
+        <v>2750000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6852,11 +6846,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+302,000 ت از رتبه 3 ترب (+12.4%)</t>
+          <t>+305,000 ت از رتبه 3 ترب (+12.5%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2747000</v>
+        <v>2750000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6893,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>5990000</v>
+        <v>6070000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6924,11 +6918,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-3,009,000 ت از کف ترب (-33.4%)</t>
+          <t>-2,929,000 ت از کف ترب (-32.5%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>5990000</v>
+        <v>6070000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7215,7 +7209,7 @@
         <v>2</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G89" s="6" t="n">
         <v>6400000</v>
@@ -7246,11 +7240,11 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
         </is>
       </c>
       <c r="O89" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
@@ -7291,7 +7285,7 @@
         <v>2</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>8500000</v>
+        <v>9500000</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>6400000</v>
@@ -7322,11 +7316,11 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>+1,550,000 ت از رتبه 3 ترب (+22.3%)</t>
+          <t>+2,550,000 ت از رتبه 3 ترب (+36.7%)</t>
         </is>
       </c>
       <c r="O90" s="6" t="n">
-        <v>17000000</v>
+        <v>19000000</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
@@ -7367,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5099500</v>
+        <v>5080000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7398,11 +7392,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,149,500 ت از رتبه 3 ترب (+29.1%)</t>
+          <t>+1,130,000 ت از رتبه 3 ترب (+28.6%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5099500</v>
+        <v>5080000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7443,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3940000</v>
+        <v>3950000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7465,7 +7459,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4250000</v>
+        <v>4257520</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7474,11 +7468,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+952,000 ت از رتبه 3 ترب (+31.9%)</t>
+          <t>+962,000 ت از رتبه 3 ترب (+32.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3940000</v>
+        <v>3950000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7675,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>27320000</v>
+        <v>26670000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7706,11 +7700,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,970,000 ت از رتبه 3 ترب (+28.0%)</t>
+          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>27320000</v>
+        <v>26670000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7751,7 +7745,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5520000</v>
+        <v>5550000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7788,11 +7782,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+1,020,000 ت از رتبه 1 ترب (+22.7%)</t>
+          <t>+1,050,000 ت از رتبه 1 ترب (+23.3%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5520000</v>
+        <v>5550000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8381,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4530000</v>
+        <v>4850000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8412,11 +8406,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+675,000 ت از رتبه 3 ترب (+17.5%)</t>
+          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4530000</v>
+        <v>4850000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9135,7 +9129,7 @@
         </is>
       </c>
       <c r="L113" s="6" t="n">
-        <v>8990000</v>
+        <v>7900000</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
@@ -9347,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3940000</v>
+        <v>3950000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9369,7 +9363,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4250000</v>
+        <v>4257520</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9378,11 +9372,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+952,000 ت از رتبه 3 ترب (+31.9%)</t>
+          <t>+962,000 ت از رتبه 3 ترب (+32.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3940000</v>
+        <v>3950000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9839,7 +9833,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>17990000</v>
+        <v>17590000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10153,7 +10147,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>17990000</v>
+        <v>17590000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -642,7 +642,7 @@
         <v>10500000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10879000</v>
+        <v>10800000</v>
       </c>
       <c r="J2" s="6" t="n">
         <v>10950000</v>
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20210000</v>
+        <v>20030000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -714,13 +714,13 @@
         <v>19990000</v>
       </c>
       <c r="I3" s="6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>20030000</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>20131000</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>20210000</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>20290000</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>18990000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1273230000</v>
+        <v>1261890000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -776,39 +776,39 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>15670000</v>
+      <c r="F4" s="5" t="n">
+        <v>15590000</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>14990000</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>15191000</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>15360000</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>15390000</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>15670000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+200,000 ت از رتبه 5 ترب (+1.3%)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>470100000</v>
+        <v>467700000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>6900000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5690000</v>
+        <v>5700000</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>5950000</v>
@@ -861,13 +861,13 @@
         <v>5950000</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>5950000</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>6000000</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>6099900</v>
-      </c>
       <c r="L5" s="6" t="n">
-        <v>7620000</v>
+        <v>7650000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+800,100 ت از رتبه 5 ترب (+13.1%)</t>
+          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -995,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4830000</v>
+        <v>4910000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1022,11 +1022,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+135,000 ت از رتبه 5 ترب (+2.9%)</t>
+          <t>+215,000 ت از رتبه 5 ترب (+4.6%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>72450000</v>
+        <v>73650000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         <v>101200</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>116379</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>129600</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>131500</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9980000</v>
+        <v>9990000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,7 +1226,7 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9980000</v>
+        <v>9990000</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>9995000</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>99800000</v>
+        <v>99900000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1368,19 +1368,19 @@
         <v>4950000</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4980000</v>
+        <v>5000000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5020000</v>
+        <v>5010000</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5120000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5130000</v>
+        <v>5145000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5145000</v>
+        <v>5150000</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>5300000</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-30,000 ت از کف ترب (-0.6%)</t>
+          <t>-50,000 ت از کف ترب (-1.0%)</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1508,16 +1508,16 @@
         <v>12800000</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>12800000</v>
+        <v>12900000</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>12900000</v>
+        <v>13000000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13000000</v>
+        <v>13310000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21047760</v>
+        <v>22000000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,850,000 ت از رتبه 5 ترب (+52.7%)</t>
+          <t>+6,540,000 ت از رتبه 5 ترب (+49.1%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1574,7 +1574,7 @@
         <v>7499000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7390000</v>
+        <v>7490000</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>7499000</v>
@@ -1589,7 +1589,7 @@
         <v>7500000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>9120000</v>
+        <v>8450000</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -1646,19 +1646,19 @@
         <v>4620000</v>
       </c>
       <c r="G16" s="6" t="n">
+        <v>5195000</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>5199000</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="6" t="n">
         <v>5200000</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>5340000</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>5350000</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>5400000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>5800000</v>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-579,000 ت از کف ترب (-11.1%)</t>
+          <t>-575,000 ت از کف ترب (-11.1%)</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9980000</v>
+        <v>9990000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,7 +1880,7 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9980000</v>
+        <v>9990000</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>9995000</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>99800000</v>
+        <v>99900000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16882550</v>
+        <v>16988870</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2186,13 +2186,13 @@
         <v>7490000</v>
       </c>
       <c r="I23" s="6" t="n">
+        <v>8355000</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>8800000</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>9700000</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>13300000</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>7600000</v>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>7130000</v>
+        <v>6600000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
@@ -2267,20 +2267,20 @@
         <v>7370000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>9186000</v>
+        <v>8964000</v>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>35650000</v>
+        <v>33000000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>8900000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2400,19 +2400,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>8390000</v>
+        <v>8400000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>8400000</v>
+        <v>8500000</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>8500000</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>8500000</v>
+        <v>8800000</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>8800000</v>
+        <v>9000000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2926,7 +2926,7 @@
         <v>6999000</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>6999000</v>
+        <v>7299000</v>
       </c>
       <c r="J33" s="6" t="n">
         <v>7550000</v>
@@ -2996,13 +2996,17 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>9592330</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>9889000</v>
-      </c>
-      <c r="I34" s="6" t="n">
         <v>14160000</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3275,38 +3279,38 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>19250000</v>
+        <v>17370000</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>12821000</v>
+        <v>14500000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>12989000</v>
+        <v>17000000</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>17000000</v>
+        <v>17370000</v>
       </c>
       <c r="J38" s="6" t="n">
         <v>18498000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19250000</v>
+        <v>19500000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>18690000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>38500000</v>
+        <v>34740000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3347,7 +3351,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4830000</v>
+        <v>4910000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3374,11 +3378,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+135,000 ت از رتبه 5 ترب (+2.9%)</t>
+          <t>+215,000 ت از رتبه 5 ترب (+4.6%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>72450000</v>
+        <v>73650000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3658,19 +3662,23 @@
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>8000000</v>
+        <v>6980000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>8064550</v>
+        <v>7000000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8489000</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>8900000</v>
+        <v>7289000</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3814,17 +3822,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="F45" s="5" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7600000</v>
+        <v>7000000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7615000</v>
+        <v>7517200</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7893100</v>
+        <v>7607000</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3841,14 +3849,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3894,31 +3902,35 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>45500</v>
+        <v>4400000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>6200000</v>
+        <v>4600000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>11000000</v>
+        <v>4800000</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3959,7 +3971,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>7130000</v>
+        <v>6600000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3981,7 +3993,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>9186000</v>
+        <v>8963800</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -3990,11 +4002,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+1,432,000 ت از رتبه 3 ترب (+25.1%)</t>
+          <t>+902,000 ت از رتبه 3 ترب (+15.8%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>14260000</v>
+        <v>13200000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4265,7 +4277,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>19250000</v>
+        <v>17370000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4296,11 +4308,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+6,350,000 ت از رتبه 3 ترب (+49.2%)</t>
+          <t>+4,470,000 ت از رتبه 3 ترب (+34.7%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>38500000</v>
+        <v>34740000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4341,7 +4353,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17980000</v>
+        <v>17995000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4374,11 +4386,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,480,000 ت از رتبه 3 ترب (+56.3%)</t>
+          <t>+6,495,000 ت از رتبه 3 ترب (+56.5%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35960000</v>
+        <v>35990000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -5609,7 +5621,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4621120</v>
+        <v>4817040</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -6137,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>23000000</v>
+        <v>23420000</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>2350000</v>
@@ -6168,11 +6180,11 @@
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>+20,555,000 ت از رتبه 3 ترب (+840.7%)</t>
+          <t>+20,975,000 ت از رتبه 3 ترب (+857.9%)</t>
         </is>
       </c>
       <c r="O75" s="6" t="n">
-        <v>23000000</v>
+        <v>23420000</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27955000</v>
+        <v>27951000</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6240,11 +6252,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+12,355,000 ت از رتبه 3 ترب (+79.2%)</t>
+          <t>+12,351,000 ت از رتبه 3 ترب (+79.2%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27955000</v>
+        <v>27951000</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6357,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>12750000</v>
+        <v>12850000</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>8999000</v>
@@ -6388,11 +6400,11 @@
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>+3,550,000 ت از رتبه 3 ترب (+38.6%)</t>
+          <t>+3,650,000 ت از رتبه 3 ترب (+39.7%)</t>
         </is>
       </c>
       <c r="O78" s="6" t="n">
-        <v>12750000</v>
+        <v>12850000</v>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
@@ -6509,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>15940000</v>
+        <v>16100000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6540,11 +6552,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+950,000 ت از رتبه 3 ترب (+6.3%)</t>
+          <t>+1,110,000 ت از رتبه 3 ترب (+7.4%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>15940000</v>
+        <v>16100000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6607,7 +6619,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>9120000</v>
+        <v>8450000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6661,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6460000</v>
+        <v>6520000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6694,11 +6706,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+510,000 ت از رتبه 2 ترب (+8.6%)</t>
+          <t>+570,000 ت از رتبه 2 ترب (+9.6%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6460000</v>
+        <v>6520000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22998000</v>
+        <v>22999500</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6770,11 +6782,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,198,000 ت از رتبه 3 ترب (+94.9%)</t>
+          <t>+11,199,500 ت از رتبه 3 ترب (+94.9%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22998000</v>
+        <v>22999500</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6815,7 +6827,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2750000</v>
+        <v>2870000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6846,11 +6858,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+305,000 ت از رتبه 3 ترب (+12.5%)</t>
+          <t>+425,000 ت از رتبه 3 ترب (+17.4%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2750000</v>
+        <v>2870000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6887,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6070000</v>
+        <v>6220000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6918,11 +6930,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-2,929,000 ت از کف ترب (-32.5%)</t>
+          <t>-2,779,000 ت از کف ترب (-30.9%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>6070000</v>
+        <v>6220000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7383,7 +7395,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5980000</v>
+        <v>6000000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7437,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3950000</v>
+        <v>3820000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7468,11 +7480,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+962,000 ت از رتبه 3 ترب (+32.2%)</t>
+          <t>+832,000 ت از رتبه 3 ترب (+27.8%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3950000</v>
+        <v>3820000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7745,7 +7757,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5550000</v>
+        <v>5610000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7782,11 +7794,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+1,050,000 ت از رتبه 1 ترب (+23.3%)</t>
+          <t>+1,110,000 ت از رتبه 1 ترب (+24.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5550000</v>
+        <v>5610000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8229,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27955000</v>
+        <v>27951000</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8254,7 +8266,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27955000</v>
+        <v>27951000</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -9341,7 +9353,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3950000</v>
+        <v>3820000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9372,11 +9384,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+962,000 ت از رتبه 3 ترب (+32.2%)</t>
+          <t>+832,000 ت از رتبه 3 ترب (+27.8%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3950000</v>
+        <v>3820000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9833,7 +9845,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>17590000</v>
+        <v>17548880</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10147,7 +10159,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>17590000</v>
+        <v>17548880</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20030000</v>
+        <v>20010000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -717,7 +717,7 @@
         <v>20000000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20030000</v>
+        <v>20010000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>20131000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1261890000</v>
+        <v>1260630000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -849,25 +849,25 @@
         <v>17</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6900000</v>
+        <v>6499000</v>
       </c>
       <c r="G5" s="6" t="n">
+        <v>5690000</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>5700000</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>5949999</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>5950000</v>
       </c>
-      <c r="I5" s="6" t="n">
-        <v>5950000</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>5950000</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>6000000</v>
-      </c>
       <c r="L5" s="6" t="n">
-        <v>7650000</v>
+        <v>7750000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,11 +876,11 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+900,000 ت از رتبه 5 ترب (+15.0%)</t>
+          <t>+549,000 ت از رتبه 5 ترب (+9.2%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
-        <v>117300000</v>
+        <v>110483000</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7999000</v>
+        <v>7990000</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>7350000</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>135983000</v>
+        <v>135830000</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>15</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4910000</v>
+        <v>4950000</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1022,11 +1022,11 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+215,000 ت از رتبه 5 ترب (+4.6%)</t>
+          <t>+255,000 ت از رتبه 5 ترب (+5.4%)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>73650000</v>
+        <v>74250000</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         <v>101200</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>116379</v>
+        <v>129600</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>129600</v>
+        <v>131500</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
@@ -1217,7 +1217,7 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9990000</v>
+        <v>9995000</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>9200000</v>
@@ -1226,13 +1226,13 @@
         <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9990000</v>
+        <v>9995000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9995000</v>
+        <v>10000000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>9999000</v>
+        <v>10000000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>10200000</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>99900000</v>
+        <v>99950000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>5000000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>5010000</v>
+        <v>5020000</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>5120000</v>
@@ -1517,7 +1517,7 @@
         <v>13310000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>22000000</v>
+        <v>21710000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1570,20 +1570,20 @@
       <c r="E15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="5" t="n">
+        <v>7799000</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>7400000</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>7480000</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>7490000</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>7499000</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>7490000</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>7499000</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7499000</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>7500000</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>7500000</v>
@@ -1591,18 +1591,18 @@
       <c r="L15" s="6" t="n">
         <v>8450000</v>
       </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۲ ترب (ایده‌آل)</t>
+          <t>+299,000 ت از رتبه 5 ترب (+4.0%)</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
-        <v>37495000</v>
+        <v>38995000</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>17000000</v>
+        <v>14980000</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>18000000</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9990000</v>
+        <v>9995000</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>9200000</v>
@@ -1880,13 +1880,13 @@
         <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9990000</v>
+        <v>9995000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9995000</v>
+        <v>10000000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>9999000</v>
+        <v>10000000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>10200000</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>99900000</v>
+        <v>99950000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="n">
-        <v>16988870</v>
+        <v>16878870</v>
       </c>
       <c r="M22" s="12" t="inlineStr">
         <is>
@@ -2248,8 +2248,8 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>6600000</v>
+      <c r="F24" s="5" t="n">
+        <v>7130000</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>4500000</v>
@@ -2264,23 +2264,23 @@
         <v>6900000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>7370000</v>
+        <v>7100000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>8964000</v>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+        <v>8959900</v>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>+30,000 ت از رتبه 5 ترب (+0.4%)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
-        <v>33000000</v>
+        <v>35650000</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
         <v>8800000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>8900000</v>
+        <v>9000000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15000000</v>
+        <v>15990000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>11300000</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>15500000</v>
+        <v>13500000</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>15500000</v>
@@ -2618,7 +2618,7 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="8" t="n">
         <v>5670000</v>
       </c>
       <c r="G29" s="6" t="n">
@@ -2628,25 +2628,25 @@
         <v>5350000</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5390000</v>
+        <v>5500000</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>5450000</v>
+        <v>5650000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5500000</v>
+        <v>5670000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>7150000</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>6976080</v>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>+170,000 ت از رتبه 5 ترب (+3.1%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2783,10 +2783,10 @@
         <v>13500000</v>
       </c>
       <c r="J31" s="6" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="K31" s="6" t="n">
         <v>13599000</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>13700000</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27300000</v>
@@ -2854,7 +2854,7 @@
         <v>12490000</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12497000</v>
+        <v>12500000</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>12500000</v>
@@ -2863,7 +2863,7 @@
         <v>12500000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>17590000</v>
+        <v>17548880</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2996,12 +2996,10 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
+        <v>9889000</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>14160000</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -3153,7 +3151,7 @@
         <v>7700000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>8600000</v>
+        <v>8889990</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3225,7 +3223,7 @@
         <v>7700000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>8600000</v>
+        <v>8889990</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3279,38 +3277,38 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17370000</v>
+        <v>17180000</v>
       </c>
       <c r="G38" s="6" t="n">
+        <v>12989000</v>
+      </c>
+      <c r="H38" s="6" t="n">
         <v>14500000</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="6" t="n">
         <v>17000000</v>
       </c>
-      <c r="I38" s="6" t="n">
-        <v>17370000</v>
-      </c>
       <c r="J38" s="6" t="n">
-        <v>18498000</v>
+        <v>17180000</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>19500000</v>
+        <v>17500000</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>18690000</v>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>34740000</v>
+        <v>34360000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3351,7 +3349,7 @@
         <v>15</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>4910000</v>
+        <v>4950000</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3378,11 +3376,11 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+215,000 ت از رتبه 5 ترب (+4.6%)</t>
+          <t>+255,000 ت از رتبه 5 ترب (+5.4%)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>73650000</v>
+        <v>74250000</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3434,7 +3432,7 @@
         <v>11300000</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15500000</v>
+        <v>13500000</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>15500000</v>
@@ -3582,7 +3580,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>4150000</v>
+        <v>3150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3971,7 +3969,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>6600000</v>
+        <v>7130000</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>5616000</v>
@@ -3993,7 +3991,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>8963800</v>
+        <v>8959900</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -4002,11 +4000,11 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>+902,000 ت از رتبه 3 ترب (+15.8%)</t>
+          <t>+1,432,000 ت از رتبه 3 ترب (+25.1%)</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
-        <v>13200000</v>
+        <v>14260000</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -4047,7 +4045,7 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>12799000</v>
+        <v>12899000</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>8700000</v>
@@ -4078,11 +4076,11 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>+3,699,000 ت از رتبه 3 ترب (+40.6%)</t>
+          <t>+3,799,000 ت از رتبه 3 ترب (+41.7%)</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
-        <v>25598000</v>
+        <v>25798000</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -4277,7 +4275,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17370000</v>
+        <v>17180000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4308,11 +4306,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+4,470,000 ت از رتبه 3 ترب (+34.7%)</t>
+          <t>+4,280,000 ت از رتبه 3 ترب (+33.2%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>34740000</v>
+        <v>34360000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4353,7 +4351,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17995000</v>
+        <v>17997000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4386,11 +4384,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,495,000 ت از رتبه 3 ترب (+56.5%)</t>
+          <t>+6,497,000 ت از رتبه 3 ترب (+56.5%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35990000</v>
+        <v>35994000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -5131,7 +5129,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5080000</v>
+        <v>5370000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5153,7 +5151,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5980000</v>
+        <v>5782500</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5162,11 +5160,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,130,000 ت از رتبه 3 ترب (+28.6%)</t>
+          <t>+1,420,000 ت از رتبه 3 ترب (+35.9%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10160000</v>
+        <v>10740000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5233,7 +5231,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="n">
-        <v>20000000</v>
+        <v>18500000</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
@@ -5309,7 +5307,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>7150000</v>
+        <v>6976080</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5997,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4489000</v>
+        <v>4650000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6028,11 +6026,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
+          <t>+760,000 ت از رتبه 3 ترب (+19.5%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4489000</v>
+        <v>4650000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6095,7 +6093,7 @@
         </is>
       </c>
       <c r="L74" s="6" t="n">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
@@ -6293,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>10990000</v>
+        <v>10540000</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>8999000</v>
@@ -6315,7 +6313,7 @@
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
@@ -6324,11 +6322,11 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>+1,790,000 ت از رتبه 3 ترب (+19.5%)</t>
+          <t>+1,340,000 ت از رتبه 3 ترب (+14.6%)</t>
         </is>
       </c>
       <c r="O77" s="6" t="n">
-        <v>10990000</v>
+        <v>10540000</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6389,7 @@
         </is>
       </c>
       <c r="L78" s="6" t="n">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
@@ -6673,7 +6671,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6520000</v>
+        <v>6550000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6697,7 +6695,7 @@
         </is>
       </c>
       <c r="L82" s="6" t="n">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
@@ -6706,11 +6704,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+570,000 ت از رتبه 2 ترب (+9.6%)</t>
+          <t>+600,000 ت از رتبه 2 ترب (+10.1%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6520000</v>
+        <v>6550000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6751,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>22999500</v>
+        <v>23490000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6782,11 +6780,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,199,500 ت از رتبه 3 ترب (+94.9%)</t>
+          <t>+11,690,000 ت از رتبه 3 ترب (+99.1%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>22999500</v>
+        <v>23490000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6827,7 +6825,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>2870000</v>
+        <v>3000000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6858,11 +6856,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+425,000 ت از رتبه 3 ترب (+17.4%)</t>
+          <t>+555,000 ت از رتبه 3 ترب (+22.7%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>2870000</v>
+        <v>3000000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6899,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6220000</v>
+        <v>6420000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6921,7 +6919,7 @@
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
@@ -6930,11 +6928,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-2,779,000 ت از کف ترب (-30.9%)</t>
+          <t>-2,579,000 ت از کف ترب (-28.7%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>6220000</v>
+        <v>6420000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7243,7 +7241,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>8600000</v>
+        <v>8889990</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7319,7 +7317,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>8600000</v>
+        <v>8889990</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7373,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5080000</v>
+        <v>5370000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7395,7 +7393,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>6000000</v>
+        <v>5782500</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7404,11 +7402,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,130,000 ت از رتبه 3 ترب (+28.6%)</t>
+          <t>+1,420,000 ت از رتبه 3 ترب (+35.9%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5080000</v>
+        <v>5370000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7449,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>3820000</v>
+        <v>4190000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7480,11 +7478,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+832,000 ت از رتبه 3 ترب (+27.8%)</t>
+          <t>+1,202,000 ت از رتبه 3 ترب (+40.2%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>3820000</v>
+        <v>4190000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7681,7 +7679,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>26670000</v>
+        <v>25840000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7712,11 +7710,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+5,320,000 ت از رتبه 3 ترب (+24.9%)</t>
+          <t>+4,490,000 ت از رتبه 3 ترب (+21.0%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>26670000</v>
+        <v>25840000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7755,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5610000</v>
+        <v>5640000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7794,11 +7792,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+1,110,000 ت از رتبه 1 ترب (+24.7%)</t>
+          <t>+1,140,000 ت از رتبه 1 ترب (+25.3%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5610000</v>
+        <v>5640000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7997,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4489000</v>
+        <v>4650000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8028,11 +8026,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+599,000 ت از رتبه 3 ترب (+15.4%)</t>
+          <t>+760,000 ت از رتبه 3 ترب (+19.5%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4489000</v>
+        <v>4650000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8731,7 +8729,7 @@
         </is>
       </c>
       <c r="L108" s="6" t="n">
-        <v>14550000</v>
+        <v>17990000</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
@@ -9296,10 +9294,8 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+      <c r="L115" s="6" t="n">
+        <v>12950000</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
@@ -9353,7 +9349,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3820000</v>
+        <v>4190000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9384,11 +9380,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+832,000 ت از رتبه 3 ترب (+27.8%)</t>
+          <t>+1,202,000 ت از رتبه 3 ترب (+40.2%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>3820000</v>
+        <v>4190000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -636,22 +636,22 @@
         <v>11210000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10200000</v>
+        <v>10500000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10500000</v>
+        <v>10800000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10950000</v>
+        <v>10999000</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>10999000</v>
+        <v>11000000</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>12900000</v>
+        <v>12800000</v>
       </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>+211,000 ت از رتبه 5 ترب (+1.9%)</t>
+          <t>+210,000 ت از رتبه 5 ترب (+1.9%)</t>
         </is>
       </c>
       <c r="O2" s="6" t="n">
@@ -776,35 +776,35 @@
       <c r="E4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="8" t="n">
         <v>15590000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14800000</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>14990000</v>
+        <v>15191000</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>15191000</v>
+        <v>15360000</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>15360000</v>
+        <v>15390000</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>15390000</v>
+        <v>15590000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
-      <c r="M4" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>+200,000 ت از رتبه 5 ترب (+1.3%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -855,19 +855,19 @@
         <v>5690000</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>5700000</v>
+        <v>5900000</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5900000</v>
+        <v>5949999</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5949999</v>
+        <v>5950000</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5950000</v>
+        <v>6000000</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>7750000</v>
+        <v>7850000</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+549,000 ت از رتبه 5 ترب (+9.2%)</t>
+          <t>+499,000 ت از رتبه 5 ترب (+8.3%)</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -1158,10 +1158,10 @@
         <v>101200</v>
       </c>
       <c r="I9" s="6" t="n">
+        <v>108300</v>
+      </c>
+      <c r="J9" s="6" t="n">
         <v>116379</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>129600</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>131500</v>
@@ -1223,28 +1223,28 @@
         <v>9200000</v>
       </c>
       <c r="H10" s="6" t="n">
+        <v>9850000</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>9880000</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>9995000</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>10000000</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>10200000</v>
+        <v>10927940</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1502,13 +1502,13 @@
         <v>19850000</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>12700000</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>12800000</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>12800000</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>12900000</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>13000000</v>
@@ -1517,7 +1517,7 @@
         <v>13310000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21710000</v>
+        <v>21100000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>7799000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7400000</v>
+        <v>7388000</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>7480000</v>
@@ -1877,28 +1877,28 @@
         <v>9200000</v>
       </c>
       <c r="H19" s="6" t="n">
+        <v>9850000</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>9880000</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>9995000</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>10000000</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>10000000</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>10200000</v>
+        <v>10927940</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
@@ -2248,7 +2248,7 @@
       <c r="E24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="8" t="n">
         <v>7130000</v>
       </c>
       <c r="G24" s="6" t="n">
@@ -2264,19 +2264,19 @@
         <v>6900000</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>7100000</v>
+        <v>7370000</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>8959900</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+        <v>8964000</v>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>+30,000 ت از رتبه 5 ترب (+0.4%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O24" s="6" t="n">
@@ -2341,7 +2341,7 @@
         <v>9000000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15990000</v>
+        <v>15500000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>5670000</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>6976080</v>
+        <v>6800000</v>
       </c>
       <c r="M29" s="9" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>12500000</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>12500000</v>
+        <v>12650000</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>17548880</v>
@@ -2999,12 +2999,10 @@
         <v>9889000</v>
       </c>
       <c r="H34" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I34" s="6" t="n">
         <v>14160000</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3151,7 +3149,7 @@
         <v>7700000</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>8889990</v>
+        <v>8900000</v>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
@@ -3223,7 +3221,7 @@
         <v>7700000</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>8889990</v>
+        <v>8900000</v>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
@@ -3498,7 +3496,7 @@
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>12000000</v>
+        <v>10000000</v>
       </c>
       <c r="H41" s="6" t="n">
         <v>13500000</v>
@@ -3580,7 +3578,7 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>3150000</v>
+        <v>4150000</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3660,23 +3658,19 @@
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>6980000</v>
+        <v>8000000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7000000</v>
+        <v>8489000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>7289000</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>8500000</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>11758230</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -3820,17 +3814,17 @@
       <c r="E45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="8" t="n">
         <v>7615000</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7000000</v>
+        <v>7600000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7517200</v>
+        <v>7615000</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>7607000</v>
+        <v>7893100</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3847,14 +3841,14 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>+8,000 ت از رتبه 3 ترب (+0.1%)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3900,35 +3894,31 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>4400000</v>
+        <v>45500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>4600000</v>
+        <v>4140000</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>ناموجود</t>
-        </is>
+        <v>4450000</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>7900000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3991,7 +3981,7 @@
         </is>
       </c>
       <c r="L47" s="6" t="n">
-        <v>8959900</v>
+        <v>8964000</v>
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
@@ -4143,7 +4133,7 @@
         </is>
       </c>
       <c r="L49" s="6" t="n">
-        <v>4550000</v>
+        <v>4510000</v>
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
@@ -4995,7 +4985,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7200000</v>
+        <v>7400000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5151,7 +5141,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>5782500</v>
+        <v>6300000</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5307,7 +5297,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="n">
-        <v>6976080</v>
+        <v>6800000</v>
       </c>
       <c r="M64" s="7" t="inlineStr">
         <is>
@@ -5619,7 +5609,7 @@
         </is>
       </c>
       <c r="L68" s="6" t="n">
-        <v>4817040</v>
+        <v>4818090</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -7241,7 +7231,7 @@
         </is>
       </c>
       <c r="L89" s="6" t="n">
-        <v>8889990</v>
+        <v>8900000</v>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
@@ -7317,7 +7307,7 @@
         </is>
       </c>
       <c r="L90" s="6" t="n">
-        <v>8889990</v>
+        <v>8900000</v>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
@@ -7393,7 +7383,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>5782500</v>
+        <v>6300000</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>

--- a/data/گزارش_انبار_قیمت_به_روز.xlsx
+++ b/data/گزارش_انبار_قیمت_به_روز.xlsx
@@ -636,16 +636,16 @@
         <v>11210000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10500000</v>
+        <v>10800000</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10800000</v>
+        <v>10950000</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>10950000</v>
+        <v>10999000</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>10999000</v>
+        <v>11000000</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>11000000</v>
@@ -705,7 +705,7 @@
         <v>63</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>20010000</v>
+        <v>20002000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>18990000</v>
@@ -717,7 +717,7 @@
         <v>20000000</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>20010000</v>
+        <v>20002000</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>20131000</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1260630000</v>
+        <v>1260126000</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>15590000</v>
+        <v>15370000</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>14800000</v>
@@ -789,26 +789,26 @@
         <v>15360000</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>15370000</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>15390000</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>15590000</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>17190000</v>
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+          <t>✓ رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>رتبه ۴ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
-        <v>467700000</v>
+        <v>461100000</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -855,13 +855,13 @@
         <v>5690000</v>
       </c>
       <c r="H5" s="6" t="n">
+        <v>5860000</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>5900000</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>5949999</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>5950000</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>6000000</v>
@@ -994,8 +994,8 @@
       <c r="E7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>4950000</v>
+      <c r="F7" s="8" t="n">
+        <v>4999500</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1890000</v>
@@ -1007,26 +1007,26 @@
         <v>4599936</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>4670000</v>
+        <v>4999000</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4695000</v>
+        <v>4999500</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>+255,000 ت از رتبه 5 ترب (+5.4%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
-        <v>74250000</v>
+        <v>74992500</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1148,35 +1148,35 @@
       <c r="E9" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="11" t="n">
         <v>100000</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>100000</v>
+        <v>101200</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>101200</v>
+        <v>108300</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>108300</v>
+        <v>116379</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>116379</v>
+        <v>131500</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>131500</v>
+        <v>134750</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>195000</v>
       </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۱ ترب (کف قیمت)</t>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>⚠️ اخطار: ارزان‌تر از رتبه ۱ (سود سوخته)</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۱ ترب (کف قیمت)</t>
+          <t>-1,200 ت از کف ترب (-1.2%)</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1217,38 +1217,38 @@
         <v>10</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>9995000</v>
+        <v>9900000</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9200000</v>
+        <v>9850000</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>9850000</v>
+        <v>9880000</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>9995000</v>
+        <v>10000000</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>10000000</v>
+        <v>10090000</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>10927940</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
-        <v>99950000</v>
+        <v>99000000</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1295,11 +1295,13 @@
         <v>7600000</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7600000</v>
-      </c>
-      <c r="I11" s="6" t="n">
         <v>8999000</v>
       </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -1311,16 +1313,16 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>11430000</v>
+        <v>12440000</v>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۳ ترب (رقابتی)</t>
+          <t>✓ رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۳ ترب (رقابتی)</t>
+          <t>رتبه ۲ ترب (ایده‌آل)</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1377,13 +1379,13 @@
         <v>5120000</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5145000</v>
+        <v>5150000</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5150000</v>
+        <v>5200000</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5300000</v>
+        <v>5700000</v>
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
@@ -1438,10 +1440,10 @@
         <v>10200000</v>
       </c>
       <c r="G13" s="6" t="n">
+        <v>13300000</v>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>13500000</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>13800000</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>14500000</v>
@@ -1462,7 +1464,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-3,300,000 ت از کف ترب (-24.4%)</t>
+          <t>-3,100,000 ت از کف ترب (-23.3%)</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1514,10 +1516,10 @@
         <v>13000000</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>13310000</v>
+        <v>14700000</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>21100000</v>
+        <v>21800000</v>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1526,7 +1528,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>+6,540,000 ت از رتبه 5 ترب (+49.1%)</t>
+          <t>+5,150,000 ت از رتبه 5 ترب (+35.0%)</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1574,22 +1576,22 @@
         <v>7799000</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>7388000</v>
+        <v>7480000</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7480000</v>
+        <v>7490000</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>7490000</v>
+        <v>7499000</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7499000</v>
+        <v>7500000</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>7500000</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>8450000</v>
+        <v>8850000</v>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1655,10 +1657,10 @@
         <v>5200000</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>5340000</v>
+        <v>5350000</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5350000</v>
+        <v>5400000</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>5800000</v>
@@ -1803,16 +1805,16 @@
         <v>9450000</v>
       </c>
       <c r="H18" s="6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>14980000</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="J18" s="6" t="n">
         <v>18000000</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>18900000</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>29500000</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1871,38 +1873,38 @@
         <v>10</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>9995000</v>
+        <v>9900000</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>9200000</v>
+        <v>9850000</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>9850000</v>
+        <v>9880000</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>9880000</v>
+        <v>9900000</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>9995000</v>
+        <v>10000000</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>10000000</v>
+        <v>10090000</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>10927940</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>✓ رتبه ۴ ترب (رقابتی)</t>
+          <t>✓ رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۴ ترب (رقابتی)</t>
+          <t>رتبه ۳ ترب (رقابتی)</t>
         </is>
       </c>
       <c r="O19" s="6" t="n">
-        <v>99950000</v>
+        <v>99000000</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
@@ -2027,11 +2029,13 @@
         <v>7600000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>7600000</v>
-      </c>
-      <c r="I21" s="6" t="n">
         <v>8999000</v>
       </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>ناموجود</t>
@@ -2043,7 +2047,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="n">
-        <v>11430000</v>
+        <v>12440000</v>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
@@ -2335,13 +2339,13 @@
         <v>8200000</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>8800000</v>
+        <v>8600000</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>9000000</v>
+        <v>8750000</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>15500000</v>
+        <v>15990000</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2400,19 +2404,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
+        <v>8390000</v>
+      </c>
+      <c r="H26" s="6" t="n">
         <v>8400000</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>8500000</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>8500000</v>
       </c>
       <c r="J26" s="6" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="K26" s="6" t="n">
         <v>8800000</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>9000000</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>5400000</v>
@@ -2618,8 +2622,8 @@
       <c r="E29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>5670000</v>
+      <c r="F29" s="5" t="n">
+        <v>5720000</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>5200000</v>
@@ -2634,23 +2638,23 @@
         <v>5650000</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>5670000</v>
+        <v>5690000</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>6800000</v>
       </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>✓ رتبه ۵ ترب (مجاز)</t>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>رتبه ۵ ترب (مجاز)</t>
+          <t>+30,000 ت از رتبه 5 ترب (+0.5%)</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
-        <v>22680000</v>
+        <v>22880000</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
@@ -2863,7 +2867,7 @@
         <v>12650000</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>17548880</v>
+        <v>17090000</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3279,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>17180000</v>
+        <v>17040000</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>12989000</v>
@@ -3287,7 +3291,7 @@
         <v>17000000</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>17180000</v>
+        <v>17040000</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>17500000</v>
@@ -3306,7 +3310,7 @@
         </is>
       </c>
       <c r="O38" s="6" t="n">
-        <v>34360000</v>
+        <v>34080000</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -3346,8 +3350,8 @@
       <c r="E39" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>4950000</v>
+      <c r="F39" s="8" t="n">
+        <v>4999500</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>1890000</v>
@@ -3359,26 +3363,26 @@
         <v>4599936</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4670000</v>
+        <v>4999000</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>4695000</v>
+        <v>4999500</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>4250000</v>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>❌ اخطار: گران‌تر از ۵ رتبه اول</t>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>✓ رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>+255,000 ت از رتبه 5 ترب (+5.4%)</t>
+          <t>رتبه ۵ ترب (مجاز)</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>74250000</v>
+        <v>74992500</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -3661,13 +3665,13 @@
         <v>8000000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>8489000</v>
+        <v>8500000</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>8500000</v>
+        <v>8900000</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>8900000</v>
+        <v>10989000</v>
       </c>
       <c r="K43" s="6" t="n">
         <v>11758230</v>
@@ -3894,19 +3898,19 @@
         <v>4800000</v>
       </c>
       <c r="G46" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H46" s="6" t="n">
         <v>45500</v>
       </c>
-      <c r="H46" s="6" t="n">
-        <v>4140000</v>
-      </c>
       <c r="I46" s="6" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="J46" s="6" t="n">
         <v>4450000</v>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>4500000</v>
-      </c>
       <c r="K46" s="6" t="n">
-        <v>7900000</v>
+        <v>6800000</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>4630000</v>
@@ -4187,7 +4191,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>8550000</v>
+        <v>8890000</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>6690000</v>
@@ -4220,11 +4224,11 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>+1,700,000 ت از رتبه 3 ترب (+24.8%)</t>
+          <t>+2,040,000 ت از رتبه 3 ترب (+29.8%)</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
-        <v>17100000</v>
+        <v>17780000</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -4265,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17180000</v>
+        <v>17040000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>11890000</v>
@@ -4296,11 +4300,11 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>+4,280,000 ت از رتبه 3 ترب (+33.2%)</t>
+          <t>+4,140,000 ت از رتبه 3 ترب (+32.1%)</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
-        <v>34360000</v>
+        <v>34080000</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -4341,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>17997000</v>
+        <v>17999000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>11000000</v>
@@ -4374,11 +4378,11 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>+6,497,000 ت از رتبه 3 ترب (+56.5%)</t>
+          <t>+6,499,000 ت از رتبه 3 ترب (+56.5%)</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
-        <v>35994000</v>
+        <v>35998000</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
@@ -4441,7 +4445,7 @@
         </is>
       </c>
       <c r="L53" s="6" t="n">
-        <v>23000000</v>
+        <v>22000000</v>
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
@@ -4985,7 +4989,7 @@
         </is>
       </c>
       <c r="L60" s="6" t="n">
-        <v>7400000</v>
+        <v>7300000</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
@@ -5119,7 +5123,7 @@
         <v>2</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>5370000</v>
+        <v>5150000</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>3900000</v>
@@ -5141,7 +5145,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="n">
-        <v>6300000</v>
+        <v>6031680</v>
       </c>
       <c r="M62" s="7" t="inlineStr">
         <is>
@@ -5150,11 +5154,11 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>+1,420,000 ت از رتبه 3 ترب (+35.9%)</t>
+          <t>+1,200,000 ت از رتبه 3 ترب (+30.4%)</t>
         </is>
       </c>
       <c r="O62" s="6" t="n">
-        <v>10740000</v>
+        <v>10300000</v>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
@@ -5275,7 +5279,7 @@
         <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>5670000</v>
+        <v>5720000</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>4600000</v>
@@ -5306,11 +5310,11 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>+720,000 ت از رتبه 3 ترب (+14.5%)</t>
+          <t>+770,000 ت از رتبه 3 ترب (+15.6%)</t>
         </is>
       </c>
       <c r="O64" s="6" t="n">
-        <v>22680000</v>
+        <v>22880000</v>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
@@ -5849,7 +5853,7 @@
         </is>
       </c>
       <c r="L71" s="6" t="n">
-        <v>9700000</v>
+        <v>6377900</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
@@ -5985,7 +5989,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>4650000</v>
+        <v>4570000</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>3290000</v>
@@ -6016,11 +6020,11 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>+760,000 ت از رتبه 3 ترب (+19.5%)</t>
+          <t>+680,000 ت از رتبه 3 ترب (+17.5%)</t>
         </is>
       </c>
       <c r="O73" s="6" t="n">
-        <v>4650000</v>
+        <v>4570000</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
@@ -6083,7 +6087,7 @@
         </is>
       </c>
       <c r="L74" s="6" t="n">
-        <v>13300000</v>
+        <v>21700000</v>
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
@@ -6209,7 +6213,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>27951000</v>
+        <v>27950250</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>10000000</v>
@@ -6240,11 +6244,11 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>+12,351,000 ت از رتبه 3 ترب (+79.2%)</t>
+          <t>+12,350,250 ت از رتبه 3 ترب (+79.2%)</t>
         </is>
       </c>
       <c r="O76" s="6" t="n">
-        <v>27951000</v>
+        <v>27950250</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
@@ -6303,7 +6307,7 @@
         </is>
       </c>
       <c r="L77" s="6" t="n">
-        <v>13300000</v>
+        <v>21700000</v>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
@@ -6379,7 +6383,7 @@
         </is>
       </c>
       <c r="L78" s="6" t="n">
-        <v>13300000</v>
+        <v>21700000</v>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>4850000</v>
+        <v>4500000</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>3750000</v>
@@ -6464,11 +6468,11 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
+          <t>+645,000 ت از رتبه 3 ترب (+16.7%)</t>
         </is>
       </c>
       <c r="O79" s="6" t="n">
-        <v>4850000</v>
+        <v>4500000</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
@@ -6509,7 +6513,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>16100000</v>
+        <v>15990000</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>14700000</v>
@@ -6540,11 +6544,11 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>+1,110,000 ت از رتبه 3 ترب (+7.4%)</t>
+          <t>+1,000,000 ت از رتبه 3 ترب (+6.7%)</t>
         </is>
       </c>
       <c r="O80" s="6" t="n">
-        <v>16100000</v>
+        <v>15990000</v>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
@@ -6607,7 +6611,7 @@
         </is>
       </c>
       <c r="L81" s="6" t="n">
-        <v>8450000</v>
+        <v>8850000</v>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
@@ -6661,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6550000</v>
+        <v>6610000</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>4800000</v>
@@ -6685,7 +6689,7 @@
         </is>
       </c>
       <c r="L82" s="6" t="n">
-        <v>13300000</v>
+        <v>21700000</v>
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
@@ -6694,11 +6698,11 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>+600,000 ت از رتبه 2 ترب (+10.1%)</t>
+          <t>+660,000 ت از رتبه 2 ترب (+11.1%)</t>
         </is>
       </c>
       <c r="O82" s="6" t="n">
-        <v>6550000</v>
+        <v>6610000</v>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>23490000</v>
+        <v>23870000</v>
       </c>
       <c r="G83" s="6" t="n">
         <v>10000000</v>
@@ -6761,7 +6765,7 @@
         </is>
       </c>
       <c r="L83" s="6" t="n">
-        <v>38000000</v>
+        <v>44000000</v>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
@@ -6770,11 +6774,11 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>+11,690,000 ت از رتبه 3 ترب (+99.1%)</t>
+          <t>+12,070,000 ت از رتبه 3 ترب (+102.3%)</t>
         </is>
       </c>
       <c r="O83" s="6" t="n">
-        <v>23490000</v>
+        <v>23870000</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
@@ -6815,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>3000000</v>
+        <v>2870000</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>2350000</v>
@@ -6846,11 +6850,11 @@
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>+555,000 ت از رتبه 3 ترب (+22.7%)</t>
+          <t>+425,000 ت از رتبه 3 ترب (+17.4%)</t>
         </is>
       </c>
       <c r="O84" s="6" t="n">
-        <v>3000000</v>
+        <v>2870000</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
@@ -6887,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>6420000</v>
+        <v>6320000</v>
       </c>
       <c r="G85" s="6" t="n">
         <v>8999000</v>
@@ -6909,7 +6913,7 @@
         </is>
       </c>
       <c r="L85" s="6" t="n">
-        <v>13300000</v>
+        <v>21700000</v>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
@@ -6918,11 +6922,11 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-2,579,000 ت از کف ترب (-28.7%)</t>
+          <t>-2,679,000 ت از کف ترب (-29.8%)</t>
         </is>
       </c>
       <c r="O85" s="6" t="n">
-        <v>6420000</v>
+        <v>6320000</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
@@ -7361,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>5370000</v>
+        <v>5150000</v>
       </c>
       <c r="G91" s="6" t="n">
         <v>3900000</v>
@@ -7383,7 +7387,7 @@
         </is>
       </c>
       <c r="L91" s="6" t="n">
-        <v>6300000</v>
+        <v>6031680</v>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
@@ -7392,11 +7396,11 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>+1,420,000 ت از رتبه 3 ترب (+35.9%)</t>
+          <t>+1,200,000 ت از رتبه 3 ترب (+30.4%)</t>
         </is>
       </c>
       <c r="O91" s="6" t="n">
-        <v>5370000</v>
+        <v>5150000</v>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
@@ -7437,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>4190000</v>
+        <v>3792000</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>2900000</v>
@@ -7459,7 +7463,7 @@
         </is>
       </c>
       <c r="L92" s="6" t="n">
-        <v>4257520</v>
+        <v>4557520</v>
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
@@ -7468,11 +7472,11 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>+1,202,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+804,000 ت از رتبه 3 ترب (+26.9%)</t>
         </is>
       </c>
       <c r="O92" s="6" t="n">
-        <v>4190000</v>
+        <v>3792000</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
@@ -7535,7 +7539,7 @@
         </is>
       </c>
       <c r="L93" s="6" t="n">
-        <v>8330600</v>
+        <v>8149180</v>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
@@ -7669,7 +7673,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>25840000</v>
+        <v>26190000</v>
       </c>
       <c r="G95" s="6" t="n">
         <v>19800000</v>
@@ -7700,11 +7704,11 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>+4,490,000 ت از رتبه 3 ترب (+21.0%)</t>
+          <t>+4,840,000 ت از رتبه 3 ترب (+22.7%)</t>
         </is>
       </c>
       <c r="O95" s="6" t="n">
-        <v>25840000</v>
+        <v>26190000</v>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
@@ -7745,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>5640000</v>
+        <v>5700000</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>4500000</v>
@@ -7782,11 +7786,11 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>+1,140,000 ت از رتبه 1 ترب (+25.3%)</t>
+          <t>+1,200,000 ت از رتبه 1 ترب (+26.7%)</t>
         </is>
       </c>
       <c r="O96" s="6" t="n">
-        <v>5640000</v>
+        <v>5700000</v>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
@@ -7985,7 +7989,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>4650000</v>
+        <v>4570000</v>
       </c>
       <c r="G99" s="6" t="n">
         <v>3290000</v>
@@ -8016,11 +8020,11 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>+760,000 ت از رتبه 3 ترب (+19.5%)</t>
+          <t>+680,000 ت از رتبه 3 ترب (+17.5%)</t>
         </is>
       </c>
       <c r="O99" s="6" t="n">
-        <v>4650000</v>
+        <v>4570000</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
@@ -8217,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="8" t="n">
-        <v>27951000</v>
+        <v>27950250</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>25757000</v>
@@ -8254,7 +8258,7 @@
         </is>
       </c>
       <c r="O102" s="6" t="n">
-        <v>27951000</v>
+        <v>27950250</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
@@ -8375,7 +8379,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>4850000</v>
+        <v>4500000</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>3750000</v>
@@ -8406,11 +8410,11 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>+995,000 ت از رتبه 3 ترب (+25.8%)</t>
+          <t>+645,000 ت از رتبه 3 ترب (+16.7%)</t>
         </is>
       </c>
       <c r="O104" s="6" t="n">
-        <v>4850000</v>
+        <v>4500000</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
@@ -9284,8 +9288,10 @@
           <t>ناموجود</t>
         </is>
       </c>
-      <c r="L115" s="6" t="n">
-        <v>12950000</v>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>ناموجود</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
@@ -9339,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>4190000</v>
+        <v>3792000</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>2900000</v>
@@ -9361,7 +9367,7 @@
         </is>
       </c>
       <c r="L116" s="6" t="n">
-        <v>4257520</v>
+        <v>4557520</v>
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
@@ -9370,11 +9376,11 @@
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>+1,202,000 ت از رتبه 3 ترب (+40.2%)</t>
+          <t>+804,000 ت از رتبه 3 ترب (+26.9%)</t>
         </is>
       </c>
       <c r="O116" s="6" t="n">
-        <v>4190000</v>
+        <v>3792000</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
@@ -9597,7 +9603,7 @@
         </is>
       </c>
       <c r="L119" s="6" t="n">
-        <v>23000000</v>
+        <v>22000000</v>
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
@@ -9831,7 +9837,7 @@
         </is>
       </c>
       <c r="L122" s="6" t="n">
-        <v>17548880</v>
+        <v>17090000</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
@@ -10067,7 +10073,7 @@
         </is>
       </c>
       <c r="L125" s="6" t="n">
-        <v>16000000</v>
+        <v>15000000</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
@@ -10145,7 +10151,7 @@
         </is>
       </c>
       <c r="L126" s="6" t="n">
-        <v>17548880</v>
+        <v>17090000</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
